--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21924AD-AF8D-4AEF-AE95-E5991314F7AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C99303C-79C1-411E-953D-54EDC2AF71AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -146,7 +146,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
-    <numFmt numFmtId="181" formatCode="mm/dd"/>
+    <numFmt numFmtId="176" formatCode="mm/dd"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -249,7 +249,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C99303C-79C1-411E-953D-54EDC2AF71AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEF88A9F-FF55-495E-A630-759E2B66F66F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -139,6 +139,85 @@
   </si>
   <si>
     <t>Lv.03</t>
+  </si>
+  <si>
+    <t>分野</t>
+    <rPh sb="0" eb="2">
+      <t>ブンヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>システム</t>
+  </si>
+  <si>
+    <t>システム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>受注</t>
+    <rPh sb="0" eb="2">
+      <t>ジュチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>教育</t>
+    <rPh sb="0" eb="2">
+      <t>キョウイク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>生産</t>
+    <rPh sb="0" eb="2">
+      <t>セイサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>教育メニュー構築</t>
+    <rPh sb="0" eb="2">
+      <t>キョウイク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コウチク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カテゴリー一覧のみのメニューを作成する。</t>
+    <rPh sb="5" eb="7">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メニュー情報構築</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コウチク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メニュー情報テーブルを構築する。　sys_menu</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コウチク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -171,7 +250,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -224,13 +303,52 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -251,6 +369,18 @@
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -588,7 +718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="B1:I13"/>
+  <dimension ref="B1:J16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -598,12 +728,13 @@
     <col min="5" max="5" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5.453125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.453125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="23.1796875" customWidth="1"/>
-    <col min="9" max="9" width="50.1796875" customWidth="1"/>
+    <col min="8" max="8" width="8.7265625" style="1"/>
+    <col min="9" max="9" width="23.1796875" customWidth="1"/>
+    <col min="10" max="10" width="50.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:10" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:10" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -623,115 +754,175 @@
         <v>8</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="6">
-        <v>45629</v>
+        <v>45630</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="6">
-        <v>45629</v>
-      </c>
+      <c r="E3" s="6"/>
       <c r="G3" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
         <f>B3+1</f>
         <v>2</v>
       </c>
-      <c r="C4" s="6"/>
+      <c r="C4" s="6">
+        <v>45630</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="E4" s="6"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="F4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <f t="shared" ref="B5:B13" si="0">B4+1</f>
         <v>3</v>
       </c>
       <c r="C5" s="6"/>
       <c r="E5" s="6"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C6" s="6"/>
       <c r="E6" s="6"/>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C7" s="6"/>
       <c r="E7" s="6"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C8" s="6"/>
       <c r="E8" s="6"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C9" s="6"/>
       <c r="E9" s="6"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C10" s="6"/>
       <c r="E10" s="6"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="C11" s="6"/>
       <c r="E11" s="6"/>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="C12" s="6"/>
       <c r="E12" s="6"/>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="C13" s="6"/>
       <c r="E13" s="6"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C61EF0EC-B820-4CEA-8AA2-04B5D172AE2C}">
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
@@ -744,6 +935,12 @@
           </x14:formula1>
           <xm:sqref>G3:G13</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B4A065F5-E745-4CD6-9C94-45B6B3E69BD7}">
+          <x14:formula1>
+            <xm:f>選択情報!$D$3:$D$6</xm:f>
+          </x14:formula1>
+          <xm:sqref>H3:H13</xm:sqref>
+        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
@@ -752,39 +949,56 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D5D5AD1-8B35-4B1A-BA80-9423D5B69C8E}">
-  <dimension ref="B2:C5"/>
+  <dimension ref="B2:D6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="7" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="D3" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="8" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="9" t="s">
         <v>17</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D6" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEF88A9F-FF55-495E-A630-759E2B66F66F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{036E76B8-63CB-4C30-AF4F-A2B840595066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -216,6 +216,61 @@
     </rPh>
     <rPh sb="11" eb="13">
       <t>コウチク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示情報修正</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示情報にタイトルを追加する。 disp_title varchar(100)</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示情報登録</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>教育メニューの表示情報を登録する。</t>
+    <rPh sb="0" eb="2">
+      <t>キョウイク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>トウロク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -348,7 +403,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -377,9 +432,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -718,7 +770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="B1:J16"/>
+  <dimension ref="B1:J13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -780,10 +832,10 @@
       <c r="H3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" t="s">
         <v>25</v>
       </c>
     </row>
@@ -808,10 +860,10 @@
       <c r="H4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" t="s">
         <v>28</v>
       </c>
     </row>
@@ -820,20 +872,58 @@
         <f t="shared" ref="B5:B13" si="0">B4+1</f>
         <v>3</v>
       </c>
-      <c r="C5" s="6"/>
+      <c r="C5" s="6">
+        <v>45630</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="E5" s="6"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
+      <c r="F5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
+      <c r="C6" s="6">
+        <v>45630</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="6">
+        <v>45630</v>
+      </c>
+      <c r="F6" s="2">
+        <v>3</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
@@ -842,8 +932,6 @@
       </c>
       <c r="C7" s="6"/>
       <c r="E7" s="6"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
@@ -852,8 +940,6 @@
       </c>
       <c r="C8" s="6"/>
       <c r="E8" s="6"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
@@ -862,8 +948,6 @@
       </c>
       <c r="C9" s="6"/>
       <c r="E9" s="6"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
@@ -872,8 +956,6 @@
       </c>
       <c r="C10" s="6"/>
       <c r="E10" s="6"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
@@ -882,8 +964,6 @@
       </c>
       <c r="C11" s="6"/>
       <c r="E11" s="6"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
@@ -892,8 +972,6 @@
       </c>
       <c r="C12" s="6"/>
       <c r="E12" s="6"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
@@ -902,20 +980,6 @@
       </c>
       <c r="C13" s="6"/>
       <c r="E13" s="6"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{036E76B8-63CB-4C30-AF4F-A2B840595066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C074EA5-0705-4A6E-B4B9-EA6D9EA51995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="34">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -210,16 +210,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>メニュー情報テーブルを構築する。　sys_menu</t>
-    <rPh sb="4" eb="6">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>コウチク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>表示情報修正</t>
     <rPh sb="0" eb="2">
       <t>ヒョウジ</t>
@@ -271,6 +261,58 @@
     </rPh>
     <rPh sb="12" eb="14">
       <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示メニュー情報テーブルを構築する。　sys_dispmenu
+項目 : 表示メニュー情報ID、表示メニュー識別コード、メニュータイトル
+※位置に関する情報は未実装</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>コウチク</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>シキベツ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="73" eb="74">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="79" eb="82">
+      <t>ミジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>教育メニューにメニューボタンを表示する。</t>
+    <rPh sb="0" eb="2">
+      <t>キョウイク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -403,7 +445,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -433,6 +475,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -823,7 +868,7 @@
         <v>45630</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="6"/>
       <c r="G3" s="1" t="s">
@@ -839,7 +884,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
         <f>B3+1</f>
         <v>2</v>
@@ -848,7 +893,7 @@
         <v>45630</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="2" t="s">
@@ -863,8 +908,8 @@
       <c r="I4" t="s">
         <v>27</v>
       </c>
-      <c r="J4" t="s">
-        <v>28</v>
+      <c r="J4" s="10" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
@@ -876,9 +921,11 @@
         <v>45630</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="6"/>
+        <v>12</v>
+      </c>
+      <c r="E5" s="6">
+        <v>45631</v>
+      </c>
       <c r="F5" s="2" t="s">
         <v>1</v>
       </c>
@@ -889,10 +936,10 @@
         <v>19</v>
       </c>
       <c r="I5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" t="s">
         <v>29</v>
-      </c>
-      <c r="J5" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
@@ -919,10 +966,10 @@
         <v>22</v>
       </c>
       <c r="I6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" t="s">
         <v>31</v>
-      </c>
-      <c r="J6" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
@@ -930,8 +977,28 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C7" s="6"/>
+      <c r="C7" s="6">
+        <v>45633</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="E7" s="6"/>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
@@ -984,6 +1051,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C074EA5-0705-4A6E-B4B9-EA6D9EA51995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB7114B-1047-48E4-A27D-94B36DD004BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="42">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -313,6 +313,113 @@
     </rPh>
     <rPh sb="15" eb="17">
       <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示情報クラス</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>取得時に表示メニュー情報の一覧を取得する。</t>
+    <rPh sb="0" eb="3">
+      <t>シュトクジ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シュトク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示メニュー情報登録</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>教員メニューのメニュー情報を登録する。「カテゴリー一覧」</t>
+    <rPh sb="0" eb="2">
+      <t>キョウイン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示メニュー情報の採番情報を登録する。</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>サイバン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メニュー情報の採番情報登録</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>サイバン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メニューアクションの項目追加</t>
+    <rPh sb="10" eb="12">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ツイカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -445,7 +552,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -478,6 +585,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -815,7 +925,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="B1:J13"/>
+  <dimension ref="B1:K16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -830,8 +940,8 @@
     <col min="10" max="10" width="50.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:10" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:11" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -860,7 +970,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
@@ -884,7 +994,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
         <f>B3+1</f>
         <v>2</v>
@@ -893,9 +1003,11 @@
         <v>45630</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="6"/>
+        <v>12</v>
+      </c>
+      <c r="E4" s="6">
+        <v>45630</v>
+      </c>
       <c r="F4" s="2" t="s">
         <v>26</v>
       </c>
@@ -912,22 +1024,22 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
-        <f t="shared" ref="B5:B13" si="0">B4+1</f>
+        <f>B4+1</f>
         <v>3</v>
       </c>
       <c r="C5" s="6">
-        <v>45630</v>
+        <v>45633</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E5" s="6">
-        <v>45631</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>1</v>
+        <v>45633</v>
+      </c>
+      <c r="F5" s="2">
+        <v>2</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>14</v>
@@ -936,103 +1048,190 @@
         <v>19</v>
       </c>
       <c r="I5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
-        <f t="shared" si="0"/>
+        <f>B5+1</f>
         <v>4</v>
       </c>
       <c r="C6" s="6">
-        <v>45630</v>
+        <v>45633</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E6" s="6">
-        <v>45630</v>
+        <v>45633</v>
       </c>
       <c r="F6" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
-        <f t="shared" si="0"/>
+        <f>B6+1</f>
         <v>5</v>
       </c>
       <c r="C7" s="6">
-        <v>45633</v>
+        <v>45630</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="1">
+        <v>12</v>
+      </c>
+      <c r="E7" s="6">
+        <v>45631</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>1</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B8" s="2">
+        <f t="shared" ref="B8:B16" si="0">B7+1</f>
+        <v>6</v>
+      </c>
+      <c r="C8" s="6">
+        <v>45630</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="6">
+        <v>45630</v>
+      </c>
+      <c r="F8" s="2">
+        <v>3</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B8" s="2">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="C8" s="6"/>
-      <c r="E8" s="6"/>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="I8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C9" s="6"/>
+      <c r="C9" s="6">
+        <v>45633</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="E9" s="6"/>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="6">
+        <v>45633</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="E10" s="6"/>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F10" s="1">
+        <v>3</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C11" s="6"/>
+      <c r="C11" s="6">
+        <v>45633</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="E11" s="6"/>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F11" s="1">
+        <v>2</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11" t="s">
+        <v>34</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1040,13 +1239,37 @@
       <c r="C12" s="6"/>
       <c r="E12" s="6"/>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="C13" s="6"/>
       <c r="E13" s="6"/>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B14" s="2">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C14" s="6"/>
+      <c r="E14" s="6"/>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B15" s="2">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="C15" s="6"/>
+      <c r="E15" s="6"/>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B16" s="2">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C16" s="6"/>
+      <c r="E16" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -1059,19 +1282,19 @@
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D13</xm:sqref>
+          <xm:sqref>D3:D16</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G13</xm:sqref>
+          <xm:sqref>G3:G16</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B4A065F5-E745-4CD6-9C94-45B6B3E69BD7}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H3:H13</xm:sqref>
+          <xm:sqref>H3:H16</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB7114B-1047-48E4-A27D-94B36DD004BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A6574A-5708-412C-825D-5E866DD97EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="選択情報" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$21</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="46">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -420,6 +423,78 @@
     </rPh>
     <rPh sb="12" eb="14">
       <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>教育カテゴリー情報テーブル</t>
+    <rPh sb="0" eb="2">
+      <t>キョウイク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テーブル構築。テーブル名 : edu_category、項目 category_id、category_cd、category_name
+作成するクラス M_EduCategory、X_EduCategory、I_EduCategory</t>
+    <rPh sb="4" eb="6">
+      <t>コウチク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示情報</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>教育カテゴリー一覧Lv.01を表示情報に登録する。
+※できればここで一覧用表示の汎用化を検討する。</t>
+    <rPh sb="0" eb="2">
+      <t>キョウイク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="34" eb="37">
+      <t>イチランヨウ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ハンヨウ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ケントウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -454,7 +529,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -546,22 +621,154 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top style="medium">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top style="medium">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right style="medium">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top style="medium">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right style="medium">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right style="medium">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -571,9 +778,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -583,17 +787,71 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{2FEB87D1-ABD7-4345-973B-AA71709FD3EB}"/>
   </tableStyles>
@@ -925,7 +1183,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="B1:K16"/>
+  <dimension ref="B1:K21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -937,180 +1195,183 @@
     <col min="7" max="7" width="6.453125" style="1" customWidth="1"/>
     <col min="8" max="8" width="8.7265625" style="1"/>
     <col min="9" max="9" width="23.1796875" customWidth="1"/>
-    <col min="10" max="10" width="50.1796875" customWidth="1"/>
+    <col min="10" max="10" width="68.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1" spans="2:11" ht="8.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="10" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="12">
         <v>45630</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="6"/>
-      <c r="G3" s="1" t="s">
+      <c r="D3" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="12">
+        <v>45638</v>
+      </c>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="15" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B4" s="2">
+      <c r="B4" s="11">
         <f>B3+1</f>
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="12">
         <v>45630</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="12">
         <v>45630</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="17" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B5" s="2">
+      <c r="B5" s="11">
         <f>B4+1</f>
         <v>3</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="12">
         <v>45633</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="12">
         <v>45633</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="16">
         <v>2</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="17" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B6" s="2">
+      <c r="B6" s="11">
         <f>B5+1</f>
         <v>4</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="12">
         <v>45633</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="12">
         <v>45633</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="16">
         <v>2</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="17" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B7" s="2">
+      <c r="B7" s="11">
         <f>B6+1</f>
         <v>5</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="12">
         <v>45630</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="12">
         <v>45631</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="15" t="s">
         <v>29</v>
       </c>
       <c r="K7" t="s">
@@ -1118,161 +1379,300 @@
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B8" s="2">
-        <f t="shared" ref="B8:B16" si="0">B7+1</f>
+      <c r="B8" s="11">
+        <f t="shared" ref="B8:B21" si="0">B7+1</f>
         <v>6</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="12">
         <v>45630</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="12">
         <v>45630</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="16">
         <v>3</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="15" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B9" s="2">
+      <c r="B9" s="11">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="12">
         <v>45633</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="1">
+      <c r="D9" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="12">
+        <v>45638</v>
+      </c>
+      <c r="F9" s="13">
         <v>1</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="15" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B10" s="2">
+      <c r="B10" s="11">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="12">
         <v>45633</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="1">
+      <c r="D10" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="12">
+        <v>45638</v>
+      </c>
+      <c r="F10" s="13">
         <v>3</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="J10" s="11" t="s">
+      <c r="J10" s="15" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B11" s="2">
+      <c r="B11" s="11">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="12">
         <v>45633</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="6"/>
-      <c r="F11" s="1">
+      <c r="D11" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="12">
+        <v>45638</v>
+      </c>
+      <c r="F11" s="13">
         <v>2</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="J11" s="11" t="s">
+      <c r="J11" s="15" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B12" s="2">
+    <row r="12" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B12" s="11">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="E12" s="6"/>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B13" s="2">
+      <c r="C12" s="12">
+        <v>45638</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="12"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="J12" s="17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B13" s="11">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C13" s="6"/>
-      <c r="E13" s="6"/>
+      <c r="C13" s="12">
+        <v>45638</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="12"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="J13" s="17" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B14" s="2">
+      <c r="B14" s="11">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C14" s="6"/>
-      <c r="E14" s="6"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="15"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B15" s="2">
+      <c r="B15" s="11">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C15" s="6"/>
-      <c r="E15" s="6"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="15"/>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B16" s="2">
+      <c r="B16" s="11">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C16" s="6"/>
-      <c r="E16" s="6"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="15"/>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B17" s="11">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="C17" s="12"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="15"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B18" s="11">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C18" s="12"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="15"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B19" s="11">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C19" s="12"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="15"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B20" s="11">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="C20" s="12"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="15"/>
+    </row>
+    <row r="21" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="18">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="C21" s="19"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="22"/>
     </row>
   </sheetData>
+  <autoFilter ref="B2:J21" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
+  <conditionalFormatting sqref="B3:J21">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>$D3="完了"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>$D3="着手中"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
   <extLst>
@@ -1282,19 +1682,19 @@
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D16</xm:sqref>
+          <xm:sqref>D3:D21</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G16</xm:sqref>
+          <xm:sqref>G3:G21</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B4A065F5-E745-4CD6-9C94-45B6B3E69BD7}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H3:H16</xm:sqref>
+          <xm:sqref>H3:H21</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1319,40 +1719,40 @@
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>23</v>
       </c>
     </row>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A6574A-5708-412C-825D-5E866DD97EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCCBD000-19D5-433E-84F5-AD3C7C175B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCCBD000-19D5-433E-84F5-AD3C7C175B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A562B1-B54C-4B1F-B63E-4431E840F115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="51">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -464,8 +464,25 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>カテゴリー情報</t>
+    <rPh sb="5" eb="7">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カテゴリーの初期情報として「Java」「SQL」を登録する。</t>
+    <rPh sb="6" eb="10">
+      <t>ショキジョウホウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>教育カテゴリー一覧Lv.01を表示情報に登録する。
-※できればここで一覧用表示の汎用化を検討する。</t>
+※できればここで一覧用表示の汎用化を検討する。一覧で表示するのは、カテゴリー名のみ、動作確認はタイトル表示のみとする。</t>
     <rPh sb="0" eb="2">
       <t>キョウイク</t>
     </rPh>
@@ -495,6 +512,69 @@
     </rPh>
     <rPh sb="44" eb="46">
       <t>ケントウ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="64" eb="65">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="68" eb="72">
+      <t>ドウサカクニン</t>
+    </rPh>
+    <rPh sb="77" eb="79">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カテゴリー一覧情報を明細として表示する。</t>
+    <rPh sb="5" eb="7">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>メイサイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>教育カテゴリー画面</t>
+    <rPh sb="0" eb="2">
+      <t>キョウイク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カテゴリー一覧画面の各行に問題一覧ボタンを追加する。</t>
+    <rPh sb="5" eb="7">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カクギョウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ツイカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1507,9 +1587,11 @@
         <v>45638</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E12" s="12">
+        <v>45641</v>
+      </c>
       <c r="F12" s="13"/>
       <c r="G12" s="13" t="s">
         <v>14</v>
@@ -1524,7 +1606,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B13" s="11">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1533,10 +1615,12 @@
         <v>45638</v>
       </c>
       <c r="D13" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="12"/>
+      <c r="F13" s="13">
         <v>10</v>
       </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="13"/>
       <c r="G13" s="13" t="s">
         <v>14</v>
       </c>
@@ -1547,7 +1631,7 @@
         <v>44</v>
       </c>
       <c r="J13" s="17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.3">
@@ -1555,42 +1639,84 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="13"/>
+      <c r="C14" s="12">
+        <v>45641</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E14" s="12"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="15"/>
+      <c r="F14" s="13">
+        <v>10</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" s="11">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="13"/>
+      <c r="C15" s="12">
+        <v>45642</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E15" s="12"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="15"/>
+      <c r="F15" s="13">
+        <v>12</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" s="11">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C16" s="12"/>
-      <c r="D16" s="13"/>
+      <c r="C16" s="12">
+        <v>45642</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E16" s="12"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="15"/>
+      <c r="F16" s="13">
+        <v>13</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" s="11">

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A562B1-B54C-4B1F-B63E-4431E840F115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{952921FF-B6A4-43F0-9CFD-358F950E3AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -1643,9 +1643,11 @@
         <v>45641</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E14" s="12">
+        <v>45642</v>
+      </c>
       <c r="F14" s="13">
         <v>10</v>
       </c>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{952921FF-B6A4-43F0-9CFD-358F950E3AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39279E93-9773-4652-9AE2-994CE2B9D8B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="選択情報" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="58">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -557,7 +557,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>カテゴリー一覧画面の各行に問題一覧ボタンを追加する。</t>
+    <t>カテゴリー一覧画面の各行に問題一覧ボタンを追加し、EducateServletまで遷移する。</t>
     <rPh sb="5" eb="7">
       <t>イチラン</t>
     </rPh>
@@ -575,6 +575,105 @@
     </rPh>
     <rPh sb="21" eb="23">
       <t>ツイカ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>問題一覧画面</t>
+    <rPh sb="0" eb="2">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カテゴリー一覧から遷移して問題一覧画面を表示する。</t>
+    <rPh sb="5" eb="7">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>モンダイイチラン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示情報</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>問題一覧の表示情報を初期登録する。</t>
+    <rPh sb="0" eb="2">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>ショキトウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>問題情報テーブル</t>
+    <rPh sb="0" eb="4">
+      <t>モンダイジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>問題情報テーブルを生成する。
+テーブル名 edu_question 項目 : edu_question_id、category_id、question_title
+作成クラス M_EduQuestion、XおよびI</t>
+    <rPh sb="0" eb="4">
+      <t>モンダイジョウホウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="82" eb="84">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面生成クラス : HTMLEduQuestionList</t>
+    <rPh sb="0" eb="4">
+      <t>ガメンセイセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1263,7 +1362,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="B1:K21"/>
+  <dimension ref="B1:K29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -1460,7 +1559,7 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
-        <f t="shared" ref="B8:B21" si="0">B7+1</f>
+        <f t="shared" ref="B8:B29" si="0">B7+1</f>
         <v>6</v>
       </c>
       <c r="C8" s="12">
@@ -1673,9 +1772,11 @@
         <v>45642</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E15" s="12">
+        <v>45644</v>
+      </c>
       <c r="F15" s="13">
         <v>12</v>
       </c>
@@ -1701,9 +1802,11 @@
         <v>45642</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E16" s="12">
+        <v>45645</v>
+      </c>
       <c r="F16" s="13">
         <v>13</v>
       </c>
@@ -1725,75 +1828,237 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C17" s="12"/>
-      <c r="D17" s="13"/>
+      <c r="C17" s="12">
+        <v>45645</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E17" s="12"/>
       <c r="F17" s="13"/>
       <c r="G17" s="13"/>
       <c r="H17" s="13"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="15"/>
+      <c r="I17" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="J17" s="15" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="11">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="13"/>
+      <c r="C18" s="12">
+        <v>45645</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E18" s="12"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="15"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F18" s="13">
+        <v>15</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="J18" s="15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B19" s="11">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C19" s="12"/>
-      <c r="D19" s="13"/>
+      <c r="C19" s="12">
+        <v>45645</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E19" s="12"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="15"/>
+      <c r="F19" s="13">
+        <v>15</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="J19" s="17" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="11">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C20" s="12"/>
-      <c r="D20" s="13"/>
+      <c r="C20" s="12">
+        <v>45645</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E20" s="12"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="15"/>
-    </row>
-    <row r="21" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="18">
+      <c r="F20" s="13">
+        <v>15</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I20" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="J20" s="15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B21" s="11">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C21" s="19"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="22"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="15"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B22" s="11">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C22" s="12"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="15"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B23" s="11">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="C23" s="12"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="15"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B24" s="11">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="C24" s="12"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="15"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B25" s="11">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="C25" s="12"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="15"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B26" s="11">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="C26" s="12"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="15"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B27" s="11">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="C27" s="12"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="15"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B28" s="11">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="C28" s="12"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="15"/>
+    </row>
+    <row r="29" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B29" s="18">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="C29" s="19"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:J21" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
+  <autoFilter ref="B2:J29" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B3:J21">
+  <conditionalFormatting sqref="B3:J29">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>
@@ -1810,19 +2075,19 @@
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D21</xm:sqref>
+          <xm:sqref>D3:D29</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G21</xm:sqref>
+          <xm:sqref>G3:G29</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B4A065F5-E745-4CD6-9C94-45B6B3E69BD7}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H3:H21</xm:sqref>
+          <xm:sqref>H3:H29</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39279E93-9773-4652-9AE2-994CE2B9D8B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22917C10-95D4-4673-A677-72DD2ADE7434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="65">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -674,6 +674,147 @@
     <t>画面生成クラス : HTMLEduQuestionList</t>
     <rPh sb="0" eb="4">
       <t>ガメンセイセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>生産メニュー</t>
+    <rPh sb="0" eb="2">
+      <t>セイサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>総合メニューからの遷移で生産メニューを表示する。
+表示メニュー項目 : 製品一覧、部品マスター（内容は変わる可能性有り）</t>
+    <rPh sb="0" eb="2">
+      <t>ソウゴウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>セイサン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ブヒン</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="54" eb="57">
+      <t>カノウセイ</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>生産メニュー画面</t>
+    <rPh sb="0" eb="2">
+      <t>セイサン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示情報登録</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示情報に生産メニュー情報を初期登録する。</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セイサン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="14" eb="18">
+      <t>ショキトウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>システム管理メニュー構築</t>
+    <rPh sb="4" eb="6">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>コウチク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>システム管理用のメニューを生成する。（当面は単独で表示する。総合メニューとは連携しない）
+表示項目はユーザー一覧、テーブル一覧とする。</t>
+    <rPh sb="4" eb="7">
+      <t>カンリヨウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>トウメン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>タンドク</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ソウゴウ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>レンケイ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>イチラン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -941,7 +1082,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1009,6 +1150,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1375,6 +1519,7 @@
     <col min="8" max="8" width="8.7265625" style="1"/>
     <col min="9" max="9" width="23.1796875" customWidth="1"/>
     <col min="10" max="10" width="68.6328125" customWidth="1"/>
+    <col min="11" max="11" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="8.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
@@ -1823,7 +1968,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="11">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1845,7 +1990,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="11">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1873,7 +2018,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B19" s="11">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1901,7 +2046,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="11">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -1929,63 +2074,114 @@
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B21" s="11">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C21" s="12"/>
-      <c r="D21" s="13"/>
+      <c r="C21" s="12">
+        <v>45645</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>11</v>
+      </c>
       <c r="E21" s="12"/>
       <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="15"/>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="G21" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I21" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="J21" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="K21" s="23"/>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="11">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C22" s="12"/>
-      <c r="D22" s="13"/>
+      <c r="C22" s="12">
+        <v>45645</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E22" s="12"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="14"/>
+      <c r="F22" s="13">
+        <v>19</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I22" s="14" t="s">
+        <v>60</v>
+      </c>
       <c r="J22" s="15"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="11">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C23" s="12"/>
-      <c r="D23" s="13"/>
+      <c r="C23" s="12">
+        <v>45645</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E23" s="12"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="15"/>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F23" s="13">
+        <v>20</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I23" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="J23" s="15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B24" s="11">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C24" s="12"/>
-      <c r="D24" s="13"/>
+      <c r="C24" s="12">
+        <v>45645</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E24" s="12"/>
       <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="15"/>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="G24" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="J24" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B25" s="11">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -1999,7 +2195,7 @@
       <c r="I25" s="14"/>
       <c r="J25" s="15"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B26" s="11">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2013,7 +2209,7 @@
       <c r="I26" s="14"/>
       <c r="J26" s="15"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B27" s="11">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -2027,7 +2223,7 @@
       <c r="I27" s="14"/>
       <c r="J27" s="15"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B28" s="11">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -2041,7 +2237,7 @@
       <c r="I28" s="14"/>
       <c r="J28" s="15"/>
     </row>
-    <row r="29" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B29" s="18">
         <f t="shared" si="0"/>
         <v>27</v>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22917C10-95D4-4673-A677-72DD2ADE7434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D693D6-5004-4E20-9D19-00EE1A91BB40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="選択情報" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$37</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="68">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -815,6 +815,51 @@
     </rPh>
     <rPh sb="61" eb="63">
       <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「メニューへ戻る」ボタン構築</t>
+    <rPh sb="6" eb="7">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>コウチク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「商品一覧ボタン」構築、遷移機能追加</t>
+    <rPh sb="1" eb="3">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コウチク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品一覧画面</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1159,7 +1204,21 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1506,7 +1565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="B1:K29"/>
+  <dimension ref="B1:K37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -1704,7 +1763,7 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
-        <f t="shared" ref="B8:B29" si="0">B7+1</f>
+        <f t="shared" ref="B8:B37" si="0">B7+1</f>
         <v>6</v>
       </c>
       <c r="C8" s="12">
@@ -2110,7 +2169,7 @@
         <v>45645</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E22" s="12"/>
       <c r="F22" s="13">
@@ -2136,7 +2195,7 @@
         <v>45645</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E23" s="12"/>
       <c r="F23" s="13">
@@ -2155,30 +2214,34 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="11">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="C24" s="12">
-        <v>45645</v>
+        <v>45652</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" s="12"/>
-      <c r="F24" s="13"/>
+        <v>12</v>
+      </c>
+      <c r="E24" s="12">
+        <v>45651</v>
+      </c>
+      <c r="F24" s="13">
+        <v>21</v>
+      </c>
       <c r="G24" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="J24" s="17" t="s">
-        <v>64</v>
+        <v>60</v>
+      </c>
+      <c r="J24" s="15" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.3">
@@ -2186,27 +2249,53 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C25" s="12"/>
-      <c r="D25" s="13"/>
+      <c r="C25" s="12">
+        <v>45652</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E25" s="12"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="15"/>
+      <c r="F25" s="13">
+        <v>21</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I25" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="J25" s="15" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B26" s="11">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C26" s="12"/>
-      <c r="D26" s="13"/>
+      <c r="C26" s="12">
+        <v>45652</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E26" s="12"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="14"/>
+      <c r="F26" s="13">
+        <v>21</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I26" s="14" t="s">
+        <v>67</v>
+      </c>
       <c r="J26" s="15"/>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.3">
@@ -2237,29 +2326,160 @@
       <c r="I28" s="14"/>
       <c r="J28" s="15"/>
     </row>
-    <row r="29" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="18">
+    <row r="29" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B29" s="11">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="21"/>
-      <c r="J29" s="22"/>
+      <c r="C29" s="12">
+        <v>45645</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="12"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I29" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="J29" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B30" s="11">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C30" s="12"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="15"/>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B31" s="11">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="C31" s="12"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="15"/>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B32" s="11">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="C32" s="12"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="15"/>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B33" s="11">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="C33" s="12"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="15"/>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B34" s="11">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="C34" s="12"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="15"/>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B35" s="11">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="C35" s="12"/>
+      <c r="D35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="15"/>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B36" s="11">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="C36" s="12"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="15"/>
+    </row>
+    <row r="37" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B37" s="18">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="C37" s="19"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
+      <c r="H37" s="20"/>
+      <c r="I37" s="21"/>
+      <c r="J37" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:J29" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
+  <autoFilter ref="B2:J37" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B3:J29">
-    <cfRule type="expression" dxfId="1" priority="1">
+  <conditionalFormatting sqref="B36:J37 B34:D35 F34:J35 B3:J33">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>$D3="着手中"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E34">
+    <cfRule type="expression" dxfId="1" priority="5">
+      <formula>$D35="完了"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="6">
+      <formula>$D35="着手中"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2271,19 +2491,19 @@
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D29</xm:sqref>
+          <xm:sqref>D3:D37</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G29</xm:sqref>
+          <xm:sqref>G3:G37</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B4A065F5-E745-4CD6-9C94-45B6B3E69BD7}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H3:H29</xm:sqref>
+          <xm:sqref>H3:H37</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D693D6-5004-4E20-9D19-00EE1A91BB40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A6B8154-6FF3-4F24-B943-D48184351B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="選択情報" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$40</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="75">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -829,6 +829,26 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>商品一覧画面</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/productServlet01→HTMLProProductListの構築</t>
+    <rPh sb="37" eb="39">
+      <t>コウチク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>「商品一覧ボタン」構築、遷移機能追加</t>
     <rPh sb="1" eb="3">
       <t>ショウヒン</t>
@@ -851,15 +871,86 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>商品一覧画面</t>
+    <t>商品情報テーブル生成</t>
     <rPh sb="0" eb="2">
       <t>ショウヒン</t>
     </rPh>
     <rPh sb="2" eb="4">
-      <t>イチラン</t>
-    </rPh>
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>セイセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品情報初期登録</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>ショキトウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テーブル情報テーブル構築</t>
     <rPh sb="4" eb="6">
-      <t>ガメン</t>
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>コウチク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テーブル名 : sys_table、項目 : テーブル情報ID、テーブル識別コード、名前、説明</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>シキベツ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テーブル名 : prd_product 項目 : product_id, product_cd, name, description</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>コウモク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品A(proA)、商品B(proB)をテスト用として登録する。</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>トウロク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1565,7 +1656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="B1:K37"/>
+  <dimension ref="B1:K40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -1763,7 +1854,7 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
-        <f t="shared" ref="B8:B37" si="0">B7+1</f>
+        <f t="shared" ref="B8:B40" si="0">B7+1</f>
         <v>6</v>
       </c>
       <c r="C8" s="12">
@@ -2253,9 +2344,11 @@
         <v>45652</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E25" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E25" s="12">
+        <v>45653</v>
+      </c>
       <c r="F25" s="13">
         <v>21</v>
       </c>
@@ -2268,8 +2361,8 @@
       <c r="I25" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="J25" s="15" t="s">
-        <v>66</v>
+      <c r="J25" s="17" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.3">
@@ -2294,63 +2387,83 @@
         <v>23</v>
       </c>
       <c r="I26" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="J26" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="J26" s="15"/>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B27" s="11">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C27" s="12"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="15"/>
+      <c r="C27" s="12">
+        <v>45654</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" s="12">
+        <v>45665</v>
+      </c>
+      <c r="F27" s="13">
+        <v>24</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I27" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="J27" s="15" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B28" s="11">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C28" s="12"/>
-      <c r="D28" s="13"/>
+      <c r="C28" s="12">
+        <v>45654</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E28" s="12"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="15"/>
-    </row>
-    <row r="29" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F28" s="13">
+        <v>25</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I28" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="J28" s="15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B29" s="11">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C29" s="12">
-        <v>45645</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C29" s="12"/>
+      <c r="D29" s="13"/>
       <c r="E29" s="12"/>
       <c r="F29" s="13"/>
-      <c r="G29" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I29" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="J29" s="17" t="s">
-        <v>64</v>
-      </c>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="15"/>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B30" s="11">
@@ -2380,33 +2493,57 @@
       <c r="I31" s="14"/>
       <c r="J31" s="15"/>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B32" s="11">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C32" s="12"/>
-      <c r="D32" s="13"/>
+      <c r="C32" s="12">
+        <v>45645</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E32" s="12"/>
       <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="15"/>
+      <c r="G32" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I32" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="J32" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B33" s="11">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C33" s="12"/>
-      <c r="D33" s="13"/>
+      <c r="C33" s="12">
+        <v>45654</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E33" s="12"/>
       <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="15"/>
+      <c r="G33" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I33" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="J33" s="15" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="11">
@@ -2429,6 +2566,7 @@
       </c>
       <c r="C35" s="12"/>
       <c r="D35" s="13"/>
+      <c r="E35" s="12"/>
       <c r="F35" s="13"/>
       <c r="G35" s="13"/>
       <c r="H35" s="13"/>
@@ -2449,24 +2587,65 @@
       <c r="I36" s="14"/>
       <c r="J36" s="15"/>
     </row>
-    <row r="37" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="18">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B37" s="11">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C37" s="19"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="21"/>
-      <c r="J37" s="22"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="15"/>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B38" s="11">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="C38" s="12"/>
+      <c r="D38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="15"/>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B39" s="11">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="C39" s="12"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="14"/>
+      <c r="J39" s="15"/>
+    </row>
+    <row r="40" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="18">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="C40" s="19"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="21"/>
+      <c r="J40" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:J37" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
+  <autoFilter ref="B2:J40" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B36:J37 B34:D35 F34:J35 B3:J33">
+  <conditionalFormatting sqref="B3:J36 B37:D38 F37:J38 B39:J40">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>
@@ -2474,12 +2653,12 @@
       <formula>$D3="着手中"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E34">
+  <conditionalFormatting sqref="E37">
     <cfRule type="expression" dxfId="1" priority="5">
-      <formula>$D35="完了"</formula>
+      <formula>$D38="完了"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="6">
-      <formula>$D35="着手中"</formula>
+      <formula>$D38="着手中"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2491,19 +2670,19 @@
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D37</xm:sqref>
+          <xm:sqref>D3:D40</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G37</xm:sqref>
+          <xm:sqref>G3:G40</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B4A065F5-E745-4CD6-9C94-45B6B3E69BD7}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H3:H37</xm:sqref>
+          <xm:sqref>H3:H40</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A6B8154-6FF3-4F24-B943-D48184351B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57020D32-CC42-447F-BE51-2DBC120DCE61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="選択情報" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$41</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="78">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -842,13 +842,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>/productServlet01→HTMLProProductListの構築</t>
-    <rPh sb="37" eb="39">
-      <t>コウチク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>「商品一覧ボタン」構築、遷移機能追加</t>
     <rPh sb="1" eb="3">
       <t>ショウヒン</t>
@@ -951,6 +944,62 @@
     </rPh>
     <rPh sb="27" eb="29">
       <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示情報登録</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品情報一覧画面用の表示情報を初期登録する。</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>ショキトウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/productServlet01→HTMLProProductListの構築
+一覧で出力する項目は「商品コード」「名前」とする。</t>
+    <rPh sb="37" eb="39">
+      <t>コウチク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HTMLProProductList構築</t>
+    <rPh sb="18" eb="20">
+      <t>コウチク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1656,7 +1705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="B1:K40"/>
+  <dimension ref="B1:K41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -1854,7 +1903,7 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
-        <f t="shared" ref="B8:B40" si="0">B7+1</f>
+        <f t="shared" ref="B8:B41" si="0">B7+1</f>
         <v>6</v>
       </c>
       <c r="C8" s="12">
@@ -2362,10 +2411,10 @@
         <v>60</v>
       </c>
       <c r="J25" s="17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B26" s="11">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2389,8 +2438,8 @@
       <c r="I26" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="J26" s="15" t="s">
-        <v>67</v>
+      <c r="J26" s="17" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.3">
@@ -2417,10 +2466,10 @@
         <v>23</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J27" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.3">
@@ -2429,12 +2478,14 @@
         <v>26</v>
       </c>
       <c r="C28" s="12">
-        <v>45654</v>
+        <v>45666</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E28" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E28" s="12">
+        <v>45672</v>
+      </c>
       <c r="F28" s="13">
         <v>25</v>
       </c>
@@ -2445,10 +2496,10 @@
         <v>23</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="J28" s="15" t="s">
         <v>74</v>
+      </c>
+      <c r="J28" s="17" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.3">
@@ -2456,28 +2507,56 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C29" s="12"/>
-      <c r="D29" s="13"/>
+      <c r="C29" s="12">
+        <v>45654</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E29" s="12"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="15"/>
+      <c r="F29" s="13">
+        <v>26</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I29" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="J29" s="15" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B30" s="11">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C30" s="12"/>
-      <c r="D30" s="13"/>
+      <c r="C30" s="12">
+        <v>45672</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E30" s="12"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="15"/>
+      <c r="F30" s="13">
+        <v>21</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I30" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="J30" s="15" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B31" s="11">
@@ -2493,39 +2572,27 @@
       <c r="I31" s="14"/>
       <c r="J31" s="15"/>
     </row>
-    <row r="32" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B32" s="11">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C32" s="12">
-        <v>45645</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C32" s="12"/>
+      <c r="D32" s="13"/>
       <c r="E32" s="12"/>
       <c r="F32" s="13"/>
-      <c r="G32" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H32" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I32" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="J32" s="17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="15"/>
+    </row>
+    <row r="33" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B33" s="11">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="C33" s="12">
-        <v>45654</v>
+        <v>45645</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>10</v>
@@ -2539,10 +2606,10 @@
         <v>19</v>
       </c>
       <c r="I33" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="J33" s="15" t="s">
-        <v>72</v>
+        <v>63</v>
+      </c>
+      <c r="J33" s="17" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
@@ -2550,14 +2617,26 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C34" s="12"/>
-      <c r="D34" s="13"/>
+      <c r="C34" s="12">
+        <v>45654</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E34" s="12"/>
       <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="14"/>
-      <c r="J34" s="15"/>
+      <c r="G34" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I34" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="J34" s="15" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B35" s="11">
@@ -2608,6 +2687,7 @@
       </c>
       <c r="C38" s="12"/>
       <c r="D38" s="13"/>
+      <c r="E38" s="12"/>
       <c r="F38" s="13"/>
       <c r="G38" s="13"/>
       <c r="H38" s="13"/>
@@ -2621,31 +2701,44 @@
       </c>
       <c r="C39" s="12"/>
       <c r="D39" s="13"/>
-      <c r="E39" s="12"/>
       <c r="F39" s="13"/>
       <c r="G39" s="13"/>
       <c r="H39" s="13"/>
       <c r="I39" s="14"/>
       <c r="J39" s="15"/>
     </row>
-    <row r="40" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="18">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B40" s="11">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C40" s="19"/>
-      <c r="D40" s="20"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="20"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="21"/>
-      <c r="J40" s="22"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="14"/>
+      <c r="J40" s="15"/>
+    </row>
+    <row r="41" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="18">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="C41" s="19"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+      <c r="I41" s="21"/>
+      <c r="J41" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:J40" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
+  <autoFilter ref="B2:J41" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B3:J36 B37:D38 F37:J38 B39:J40">
+  <conditionalFormatting sqref="B38:D39 F38:J39 B40:J41 B3:J37">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>
@@ -2653,12 +2746,12 @@
       <formula>$D3="着手中"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E37">
+  <conditionalFormatting sqref="E38">
     <cfRule type="expression" dxfId="1" priority="5">
-      <formula>$D38="完了"</formula>
+      <formula>$D39="完了"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="6">
-      <formula>$D38="着手中"</formula>
+      <formula>$D39="着手中"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2670,19 +2763,19 @@
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D40</xm:sqref>
+          <xm:sqref>D3:D41</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G40</xm:sqref>
+          <xm:sqref>G3:G41</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B4A065F5-E745-4CD6-9C94-45B6B3E69BD7}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H3:H40</xm:sqref>
+          <xm:sqref>H3:H41</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57020D32-CC42-447F-BE51-2DBC120DCE61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{079524F6-0EA4-4E5C-971F-1978497CDB5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="選択情報" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$47</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="84">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -999,6 +999,111 @@
   <si>
     <t>HTMLProProductList構築</t>
     <rPh sb="18" eb="20">
+      <t>コウチク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遷移機能</t>
+    <rPh sb="0" eb="2">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>任意の画面へ遷移する為のメソッドをBaseHTMLにセットする。</t>
+    <rPh sb="0" eb="2">
+      <t>ニンイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>タメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示情報の子情報として画面に対する処理を定義する情報を追加する。</t>
+    <rPh sb="24" eb="26">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テーブル構築。テーブル名 : sys_dispprocess 項目 : dispprocess_ID,buttonTitle,actionURI,actionName</t>
+    <rPh sb="4" eb="6">
+      <t>コウチク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>コウモク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示情報取込修正 : 表示情報を取り込む際に画面処理情報も取込を行う。</t>
+    <rPh sb="4" eb="6">
+      <t>トリコミ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>トリコミ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面処理情報構築</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
       <t>コウチク</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -1705,7 +1810,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="B1:K41"/>
+  <dimension ref="B1:K47"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -1903,7 +2008,7 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
-        <f t="shared" ref="B8:B41" si="0">B7+1</f>
+        <f t="shared" ref="B8:B47" si="0">B7+1</f>
         <v>6</v>
       </c>
       <c r="C8" s="12">
@@ -2423,7 +2528,7 @@
         <v>45652</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E26" s="12"/>
       <c r="F26" s="13">
@@ -2539,7 +2644,7 @@
         <v>45672</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E30" s="12"/>
       <c r="F30" s="13">
@@ -2563,42 +2668,72 @@
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C31" s="12"/>
-      <c r="D31" s="13"/>
+      <c r="C31" s="12">
+        <v>45673</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E31" s="12"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="15"/>
+      <c r="F31" s="13">
+        <v>24</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I31" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J31" s="15" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B32" s="11">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C32" s="12"/>
-      <c r="D32" s="13"/>
+      <c r="C32" s="12">
+        <v>45673</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E32" s="12"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="15"/>
-    </row>
-    <row r="33" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F32" s="13">
+        <v>29</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I32" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="J32" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B33" s="11">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="C33" s="12">
-        <v>45645</v>
+        <v>45673</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E33" s="12"/>
-      <c r="F33" s="13"/>
+      <c r="F33" s="13">
+        <v>30</v>
+      </c>
       <c r="G33" s="13" t="s">
         <v>14</v>
       </c>
@@ -2606,10 +2741,10 @@
         <v>19</v>
       </c>
       <c r="I33" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="J33" s="17" t="s">
-        <v>64</v>
+        <v>83</v>
+      </c>
+      <c r="J33" s="15" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
@@ -2618,13 +2753,15 @@
         <v>32</v>
       </c>
       <c r="C34" s="12">
-        <v>45654</v>
+        <v>45673</v>
       </c>
       <c r="D34" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E34" s="12"/>
-      <c r="F34" s="13"/>
+      <c r="F34" s="13">
+        <v>30</v>
+      </c>
       <c r="G34" s="13" t="s">
         <v>14</v>
       </c>
@@ -2632,10 +2769,10 @@
         <v>19</v>
       </c>
       <c r="I34" s="14" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="J34" s="15" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.3">
@@ -2694,51 +2831,159 @@
       <c r="I38" s="14"/>
       <c r="J38" s="15"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B39" s="11">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C39" s="12"/>
-      <c r="D39" s="13"/>
+      <c r="C39" s="12">
+        <v>45645</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" s="12"/>
       <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="14"/>
-      <c r="J39" s="15"/>
+      <c r="G39" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H39" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I39" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="J39" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B40" s="11">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C40" s="12"/>
-      <c r="D40" s="13"/>
+      <c r="C40" s="12">
+        <v>45654</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E40" s="12"/>
       <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
-      <c r="H40" s="13"/>
-      <c r="I40" s="14"/>
-      <c r="J40" s="15"/>
-    </row>
-    <row r="41" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="18">
+      <c r="G40" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H40" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I40" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="J40" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B41" s="11">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C41" s="19"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="20"/>
-      <c r="G41" s="20"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="21"/>
-      <c r="J41" s="22"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="14"/>
+      <c r="J41" s="15"/>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B42" s="11">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="C42" s="12"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="14"/>
+      <c r="J42" s="15"/>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B43" s="11">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="C43" s="12"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="14"/>
+      <c r="J43" s="15"/>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B44" s="11">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="C44" s="12"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="13"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="14"/>
+      <c r="J44" s="15"/>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B45" s="11">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="C45" s="12"/>
+      <c r="D45" s="13"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="14"/>
+      <c r="J45" s="15"/>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B46" s="11">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="C46" s="12"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="14"/>
+      <c r="J46" s="15"/>
+    </row>
+    <row r="47" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B47" s="18">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="C47" s="19"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="20"/>
+      <c r="H47" s="20"/>
+      <c r="I47" s="21"/>
+      <c r="J47" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:J41" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
+  <autoFilter ref="B2:J47" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B38:D39 F38:J39 B40:J41 B3:J37">
+  <conditionalFormatting sqref="B44:D45 F44:J45 B46:J47 B3:J43">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>
@@ -2746,12 +2991,12 @@
       <formula>$D3="着手中"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E38">
+  <conditionalFormatting sqref="E44">
     <cfRule type="expression" dxfId="1" priority="5">
-      <formula>$D39="完了"</formula>
+      <formula>$D45="完了"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="6">
-      <formula>$D39="着手中"</formula>
+      <formula>$D45="着手中"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2763,19 +3008,19 @@
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D41</xm:sqref>
+          <xm:sqref>D3:D47</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G41</xm:sqref>
+          <xm:sqref>G3:G47</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B4A065F5-E745-4CD6-9C94-45B6B3E69BD7}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H3:H41</xm:sqref>
+          <xm:sqref>H3:H47</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{079524F6-0EA4-4E5C-971F-1978497CDB5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D4C3DB-5C95-4917-AD1E-A04581BDD355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="86">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -1040,19 +1040,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>テーブル構築。テーブル名 : sys_dispprocess 項目 : dispprocess_ID,buttonTitle,actionURI,actionName</t>
-    <rPh sb="4" eb="6">
-      <t>コウチク</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>コウモク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>表示情報取込修正 : 表示情報を取り込む際に画面処理情報も取込を行う。</t>
     <rPh sb="4" eb="6">
       <t>トリコミ</t>
@@ -1105,6 +1092,63 @@
     </rPh>
     <rPh sb="6" eb="8">
       <t>コウチク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テーブル構築。テーブル名 : sys_dispprocess 項目 : dispprocess_ID,disp_id,buttonTitle,actionURL,actionName</t>
+    <rPh sb="4" eb="6">
+      <t>コウチク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>コウモク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面処理情報初期登録</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ショキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品一覧で、「新規登録」と「メニューに戻る」表示処理を登録する。</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>シンキトウロク</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>トウロク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2672,7 +2716,7 @@
         <v>45673</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E31" s="12"/>
       <c r="F31" s="13">
@@ -2700,7 +2744,7 @@
         <v>45673</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E32" s="12"/>
       <c r="F32" s="13">
@@ -2713,13 +2757,13 @@
         <v>19</v>
       </c>
       <c r="I32" s="14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J32" s="17" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B33" s="11">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -2728,9 +2772,11 @@
         <v>45673</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E33" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E33" s="12">
+        <v>45678</v>
+      </c>
       <c r="F33" s="13">
         <v>30</v>
       </c>
@@ -2741,10 +2787,10 @@
         <v>19</v>
       </c>
       <c r="I33" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="J33" s="17" t="s">
         <v>83</v>
-      </c>
-      <c r="J33" s="15" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
@@ -2769,10 +2815,10 @@
         <v>19</v>
       </c>
       <c r="I34" s="14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J34" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.3">
@@ -2780,14 +2826,28 @@
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C35" s="12"/>
-      <c r="D35" s="13"/>
+      <c r="C35" s="12">
+        <v>45678</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E35" s="12"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="14"/>
-      <c r="J35" s="15"/>
+      <c r="F35" s="13">
+        <v>30</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H35" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I35" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="J35" s="15" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B36" s="11">

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D4C3DB-5C95-4917-AD1E-A04581BDD355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBFFA414-583D-4C26-8E7F-FC065724EF99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="選択情報" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$49</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="89">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -1149,6 +1149,69 @@
     </rPh>
     <rPh sb="27" eb="29">
       <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示処理情報登録メソッドの追加 : addDispProcessData</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>採番情報初期登録</t>
+    <rPh sb="0" eb="2">
+      <t>サイバン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ショキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示処理情報用の採番情報の初期登録を設定する。</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>サイバン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>ショキトウロク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>セッテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1854,7 +1917,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="B1:K47"/>
+  <dimension ref="B1:K49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -2052,7 +2115,7 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
-        <f t="shared" ref="B8:B47" si="0">B7+1</f>
+        <f t="shared" ref="B8:B49" si="0">B7+1</f>
         <v>6</v>
       </c>
       <c r="C8" s="12">
@@ -2799,10 +2862,10 @@
         <v>32</v>
       </c>
       <c r="C34" s="12">
-        <v>45673</v>
+        <v>45678</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E34" s="12"/>
       <c r="F34" s="13">
@@ -2817,8 +2880,8 @@
       <c r="I34" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="J34" s="15" t="s">
-        <v>81</v>
+      <c r="J34" s="17" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.3">
@@ -2827,7 +2890,7 @@
         <v>33</v>
       </c>
       <c r="C35" s="12">
-        <v>45678</v>
+        <v>45673</v>
       </c>
       <c r="D35" s="13" t="s">
         <v>10</v>
@@ -2840,13 +2903,13 @@
         <v>14</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I35" s="14" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J35" s="15" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.3">
@@ -2854,28 +2917,56 @@
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C36" s="12"/>
-      <c r="D36" s="13"/>
+      <c r="C36" s="12">
+        <v>45678</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>11</v>
+      </c>
       <c r="E36" s="12"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="14"/>
-      <c r="J36" s="15"/>
+      <c r="F36" s="13">
+        <v>30</v>
+      </c>
+      <c r="G36" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H36" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I36" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="J36" s="15" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B37" s="11">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C37" s="12"/>
-      <c r="D37" s="13"/>
+      <c r="C37" s="12">
+        <v>45678</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>11</v>
+      </c>
       <c r="E37" s="12"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="15"/>
+      <c r="F37" s="13">
+        <v>30</v>
+      </c>
+      <c r="G37" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H37" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I37" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="J37" s="15" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B38" s="11">
@@ -2891,85 +2982,85 @@
       <c r="I38" s="14"/>
       <c r="J38" s="15"/>
     </row>
-    <row r="39" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B39" s="11">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C39" s="12">
-        <v>45645</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C39" s="12"/>
+      <c r="D39" s="13"/>
       <c r="E39" s="12"/>
       <c r="F39" s="13"/>
-      <c r="G39" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H39" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I39" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="J39" s="17" t="s">
-        <v>64</v>
-      </c>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="14"/>
+      <c r="J39" s="15"/>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B40" s="11">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C40" s="12">
-        <v>45654</v>
-      </c>
-      <c r="D40" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C40" s="12"/>
+      <c r="D40" s="13"/>
       <c r="E40" s="12"/>
       <c r="F40" s="13"/>
-      <c r="G40" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H40" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I40" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="J40" s="15" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="14"/>
+      <c r="J40" s="15"/>
+    </row>
+    <row r="41" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B41" s="11">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C41" s="12"/>
-      <c r="D41" s="13"/>
+      <c r="C41" s="12">
+        <v>45645</v>
+      </c>
+      <c r="D41" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E41" s="12"/>
       <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="14"/>
-      <c r="J41" s="15"/>
+      <c r="G41" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I41" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="J41" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B42" s="11">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C42" s="12"/>
-      <c r="D42" s="13"/>
+      <c r="C42" s="12">
+        <v>45654</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E42" s="12"/>
       <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
-      <c r="H42" s="13"/>
-      <c r="I42" s="14"/>
-      <c r="J42" s="15"/>
+      <c r="G42" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H42" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I42" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="J42" s="15" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B43" s="11">
@@ -3006,6 +3097,7 @@
       </c>
       <c r="C45" s="12"/>
       <c r="D45" s="13"/>
+      <c r="E45" s="12"/>
       <c r="F45" s="13"/>
       <c r="G45" s="13"/>
       <c r="H45" s="13"/>
@@ -3026,24 +3118,51 @@
       <c r="I46" s="14"/>
       <c r="J46" s="15"/>
     </row>
-    <row r="47" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="18">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B47" s="11">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="C47" s="19"/>
-      <c r="D47" s="20"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="20"/>
-      <c r="H47" s="20"/>
-      <c r="I47" s="21"/>
-      <c r="J47" s="22"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="13"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="13"/>
+      <c r="H47" s="13"/>
+      <c r="I47" s="14"/>
+      <c r="J47" s="15"/>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B48" s="11">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="C48" s="12"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="13"/>
+      <c r="H48" s="13"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="15"/>
+    </row>
+    <row r="49" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B49" s="18">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="C49" s="19"/>
+      <c r="D49" s="20"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="20"/>
+      <c r="G49" s="20"/>
+      <c r="H49" s="20"/>
+      <c r="I49" s="21"/>
+      <c r="J49" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:J47" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
+  <autoFilter ref="B2:J49" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B44:D45 F44:J45 B46:J47 B3:J43">
+  <conditionalFormatting sqref="B46:D47 F46:J47 B48:J49 B3:J45">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>
@@ -3051,12 +3170,12 @@
       <formula>$D3="着手中"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E44">
+  <conditionalFormatting sqref="E46">
     <cfRule type="expression" dxfId="1" priority="5">
-      <formula>$D45="完了"</formula>
+      <formula>$D47="完了"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="6">
-      <formula>$D45="着手中"</formula>
+      <formula>$D47="着手中"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3068,19 +3187,19 @@
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D47</xm:sqref>
+          <xm:sqref>D3:D49</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G47</xm:sqref>
+          <xm:sqref>G3:G49</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B4A065F5-E745-4CD6-9C94-45B6B3E69BD7}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H3:H47</xm:sqref>
+          <xm:sqref>H3:H49</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBFFA414-583D-4C26-8E7F-FC065724EF99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18DD31D6-D9E5-44DF-8EEF-EEB9177BE1D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -2921,9 +2921,11 @@
         <v>45678</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E36" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E36" s="12">
+        <v>45678</v>
+      </c>
       <c r="F36" s="13">
         <v>30</v>
       </c>
@@ -2949,9 +2951,11 @@
         <v>45678</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E37" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E37" s="12">
+        <v>45678</v>
+      </c>
       <c r="F37" s="13">
         <v>30</v>
       </c>
@@ -3162,7 +3166,7 @@
   </sheetData>
   <autoFilter ref="B2:J49" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B46:D47 F46:J47 B48:J49 B3:J45">
+  <conditionalFormatting sqref="B3:J45 B46:D47 F46:J47 B48:J49">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18DD31D6-D9E5-44DF-8EEF-EEB9177BE1D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26F4D156-61A6-434D-A890-360BCBB0FAC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="選択情報" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$50</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="91">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -1213,6 +1213,17 @@
     <rPh sb="18" eb="20">
       <t>セッテイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面処理情報クラス構築</t>
+    <rPh sb="9" eb="11">
+      <t>コウチク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>X_sysDispProcessクラス</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1917,7 +1928,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="B1:K49"/>
+  <dimension ref="B1:K50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -2115,7 +2126,7 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
-        <f t="shared" ref="B8:B49" si="0">B7+1</f>
+        <f t="shared" ref="B8:B50" si="0">B7+1</f>
         <v>6</v>
       </c>
       <c r="C8" s="12">
@@ -2865,9 +2876,11 @@
         <v>45678</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E34" s="12">
+        <v>45678</v>
+      </c>
       <c r="F34" s="13">
         <v>30</v>
       </c>
@@ -2893,9 +2906,11 @@
         <v>45673</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E35" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E35" s="12">
+        <v>45680</v>
+      </c>
       <c r="F35" s="13">
         <v>30</v>
       </c>
@@ -2918,16 +2933,16 @@
         <v>34</v>
       </c>
       <c r="C36" s="12">
-        <v>45678</v>
+        <v>45679</v>
       </c>
       <c r="D36" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E36" s="12">
-        <v>45678</v>
+        <v>45680</v>
       </c>
       <c r="F36" s="13">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G36" s="13" t="s">
         <v>14</v>
@@ -2936,10 +2951,10 @@
         <v>19</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J36" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.3">
@@ -2963,13 +2978,13 @@
         <v>14</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I37" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J37" s="15" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.3">
@@ -2977,21 +2992,39 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C38" s="12"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="14"/>
-      <c r="J38" s="15"/>
+      <c r="C38" s="12">
+        <v>45678</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" s="12">
+        <v>45678</v>
+      </c>
+      <c r="F38" s="13">
+        <v>30</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H38" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I38" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="J38" s="15" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B39" s="11">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C39" s="12"/>
+      <c r="C39" s="12">
+        <v>45680</v>
+      </c>
       <c r="D39" s="13"/>
       <c r="E39" s="12"/>
       <c r="F39" s="13"/>
@@ -3014,39 +3047,27 @@
       <c r="I40" s="14"/>
       <c r="J40" s="15"/>
     </row>
-    <row r="41" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="11">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C41" s="12">
-        <v>45645</v>
-      </c>
-      <c r="D41" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C41" s="12"/>
+      <c r="D41" s="13"/>
       <c r="E41" s="12"/>
       <c r="F41" s="13"/>
-      <c r="G41" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H41" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I41" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="J41" s="17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="14"/>
+      <c r="J41" s="15"/>
+    </row>
+    <row r="42" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B42" s="11">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="C42" s="12">
-        <v>45654</v>
+        <v>45645</v>
       </c>
       <c r="D42" s="13" t="s">
         <v>10</v>
@@ -3060,10 +3081,10 @@
         <v>19</v>
       </c>
       <c r="I42" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="J42" s="15" t="s">
-        <v>71</v>
+        <v>63</v>
+      </c>
+      <c r="J42" s="17" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.3">
@@ -3071,14 +3092,26 @@
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="C43" s="12"/>
-      <c r="D43" s="13"/>
+      <c r="C43" s="12">
+        <v>45654</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E43" s="12"/>
       <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
-      <c r="H43" s="13"/>
-      <c r="I43" s="14"/>
-      <c r="J43" s="15"/>
+      <c r="G43" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H43" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I43" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="J43" s="15" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" s="11">
@@ -3129,6 +3162,7 @@
       </c>
       <c r="C47" s="12"/>
       <c r="D47" s="13"/>
+      <c r="E47" s="12"/>
       <c r="F47" s="13"/>
       <c r="G47" s="13"/>
       <c r="H47" s="13"/>
@@ -3142,31 +3176,44 @@
       </c>
       <c r="C48" s="12"/>
       <c r="D48" s="13"/>
-      <c r="E48" s="12"/>
       <c r="F48" s="13"/>
       <c r="G48" s="13"/>
       <c r="H48" s="13"/>
       <c r="I48" s="14"/>
       <c r="J48" s="15"/>
     </row>
-    <row r="49" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="18">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B49" s="11">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="C49" s="19"/>
-      <c r="D49" s="20"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="20"/>
-      <c r="G49" s="20"/>
-      <c r="H49" s="20"/>
-      <c r="I49" s="21"/>
-      <c r="J49" s="22"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="13"/>
+      <c r="H49" s="13"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="15"/>
+    </row>
+    <row r="50" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B50" s="18">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="C50" s="19"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="19"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="20"/>
+      <c r="H50" s="20"/>
+      <c r="I50" s="21"/>
+      <c r="J50" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:J49" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
+  <autoFilter ref="B2:J50" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B3:J45 B46:D47 F46:J47 B48:J49">
+  <conditionalFormatting sqref="B3:J46 B47:D48 F47:J48 B49:J50">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>
@@ -3174,12 +3221,12 @@
       <formula>$D3="着手中"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E46">
+  <conditionalFormatting sqref="E47">
     <cfRule type="expression" dxfId="1" priority="5">
-      <formula>$D47="完了"</formula>
+      <formula>$D48="完了"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="6">
-      <formula>$D47="着手中"</formula>
+      <formula>$D48="着手中"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3191,19 +3238,19 @@
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D49</xm:sqref>
+          <xm:sqref>D3:D50</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G49</xm:sqref>
+          <xm:sqref>G3:G50</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B4A065F5-E745-4CD6-9C94-45B6B3E69BD7}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H3:H49</xm:sqref>
+          <xm:sqref>H3:H50</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26F4D156-61A6-434D-A890-360BCBB0FAC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A9D6BD-5241-4F6A-B532-45CBC74F2B68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -2790,9 +2790,11 @@
         <v>45673</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E31" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E31" s="12">
+        <v>45684</v>
+      </c>
       <c r="F31" s="13">
         <v>24</v>
       </c>
@@ -2818,9 +2820,11 @@
         <v>45673</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E32" s="12">
+        <v>45680</v>
+      </c>
       <c r="F32" s="13">
         <v>29</v>
       </c>
@@ -3023,7 +3027,7 @@
         <v>37</v>
       </c>
       <c r="C39" s="12">
-        <v>45680</v>
+        <v>45684</v>
       </c>
       <c r="D39" s="13"/>
       <c r="E39" s="12"/>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -5,19 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\officinaWork03\busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A9D6BD-5241-4F6A-B532-45CBC74F2B68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{683BA4F1-1AA9-4C06-803D-BA71F2D06874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24510" windowHeight="15990" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="選択情報" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$53</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="95">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -1224,6 +1224,55 @@
   </si>
   <si>
     <t>X_sysDispProcessクラス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品情報登録画面</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品情報登録</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>save()メソッド構築</t>
+    <rPh sb="10" eb="12">
+      <t>コウチク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>初期登録追加</t>
+    <rPh sb="0" eb="2">
+      <t>ショキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ツイカ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1928,24 +1977,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="B1:K50"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:K53"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.26953125" customWidth="1"/>
-    <col min="2" max="2" width="3.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7265625" style="1"/>
+    <col min="1" max="1" width="1.25" customWidth="1"/>
+    <col min="2" max="2" width="3.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.75" style="1"/>
     <col min="5" max="5" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.453125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.7265625" style="1"/>
-    <col min="9" max="9" width="23.1796875" customWidth="1"/>
-    <col min="10" max="10" width="68.6328125" customWidth="1"/>
-    <col min="11" max="11" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.75" style="1"/>
+    <col min="9" max="9" width="23.125" customWidth="1"/>
+    <col min="10" max="10" width="68.625" customWidth="1"/>
+    <col min="11" max="11" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="8.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:11" ht="8.4499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
@@ -1974,7 +2023,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
         <v>1</v>
       </c>
@@ -2001,7 +2050,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="B4" s="11">
         <f>B3+1</f>
         <v>2</v>
@@ -2031,7 +2080,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B5" s="11">
         <f>B4+1</f>
         <v>3</v>
@@ -2061,7 +2110,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="11">
         <f>B5+1</f>
         <v>4</v>
@@ -2091,7 +2140,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="11">
         <f>B6+1</f>
         <v>5</v>
@@ -2124,9 +2173,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" s="11">
-        <f t="shared" ref="B8:B50" si="0">B7+1</f>
+        <f t="shared" ref="B8:B53" si="0">B7+1</f>
         <v>6</v>
       </c>
       <c r="C8" s="12">
@@ -2154,7 +2203,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" s="11">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2184,7 +2233,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" s="11">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2214,7 +2263,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" s="11">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2244,7 +2293,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="B12" s="11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2272,7 +2321,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="B13" s="11">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2300,7 +2349,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" s="11">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2330,7 +2379,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="11">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2360,7 +2409,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" s="11">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2390,7 +2439,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" s="11">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2412,7 +2461,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" s="11">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2440,7 +2489,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="B19" s="11">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2468,7 +2517,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="11">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2496,7 +2545,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:11" ht="28.5" x14ac:dyDescent="0.25">
       <c r="B21" s="11">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2523,7 +2572,7 @@
       </c>
       <c r="K21" s="23"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" s="11">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2549,7 +2598,7 @@
       </c>
       <c r="J22" s="15"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" s="11">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2577,7 +2626,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" s="11">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -2607,7 +2656,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" s="11">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -2637,7 +2686,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:11" ht="28.5" x14ac:dyDescent="0.25">
       <c r="B26" s="11">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2665,7 +2714,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" s="11">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -2695,7 +2744,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" s="11">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -2725,7 +2774,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" s="11">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2734,7 +2783,7 @@
         <v>45654</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E29" s="12"/>
       <c r="F29" s="13">
@@ -2753,20 +2802,20 @@
         <v>73</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" s="11">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="C30" s="12">
-        <v>45672</v>
+        <v>45684</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>11</v>
       </c>
       <c r="E30" s="12"/>
       <c r="F30" s="13">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>14</v>
@@ -2775,118 +2824,98 @@
         <v>23</v>
       </c>
       <c r="I30" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="J30" s="15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B31" s="11">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="C31" s="12">
+        <v>45684</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" s="12"/>
+      <c r="F31" s="13">
+        <v>27</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I31" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="J31" s="15" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B32" s="11">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="C32" s="12"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="15"/>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B33" s="11">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="C33" s="12">
+        <v>45672</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="12"/>
+      <c r="F33" s="13">
+        <v>21</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I33" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="J30" s="15" t="s">
+      <c r="J33" s="15" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B31" s="11">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="C31" s="12">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B34" s="11">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="C34" s="12">
         <v>45673</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E31" s="12">
-        <v>45684</v>
-      </c>
-      <c r="F31" s="13">
-        <v>24</v>
-      </c>
-      <c r="G31" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I31" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="J31" s="15" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B32" s="11">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="C32" s="12">
-        <v>45673</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E32" s="12">
-        <v>45680</v>
-      </c>
-      <c r="F32" s="13">
-        <v>29</v>
-      </c>
-      <c r="G32" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H32" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I32" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="J32" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="33" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B33" s="11">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="C33" s="12">
-        <v>45673</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E33" s="12">
-        <v>45678</v>
-      </c>
-      <c r="F33" s="13">
-        <v>30</v>
-      </c>
-      <c r="G33" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I33" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="J33" s="17" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B34" s="11">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="C34" s="12">
-        <v>45678</v>
       </c>
       <c r="D34" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E34" s="12">
-        <v>45678</v>
+        <v>45684</v>
       </c>
       <c r="F34" s="13">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G34" s="13" t="s">
         <v>14</v>
@@ -2895,13 +2924,13 @@
         <v>19</v>
       </c>
       <c r="I34" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="J34" s="17" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+      <c r="J34" s="15" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="11">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -2916,7 +2945,7 @@
         <v>45680</v>
       </c>
       <c r="F35" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G35" s="13" t="s">
         <v>14</v>
@@ -2927,26 +2956,26 @@
       <c r="I35" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="J35" s="15" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J35" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" ht="28.5" x14ac:dyDescent="0.25">
       <c r="B36" s="11">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="C36" s="12">
-        <v>45679</v>
+        <v>45673</v>
       </c>
       <c r="D36" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E36" s="12">
-        <v>45680</v>
+        <v>45678</v>
       </c>
       <c r="F36" s="13">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G36" s="13" t="s">
         <v>14</v>
@@ -2955,13 +2984,13 @@
         <v>19</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="J36" s="15" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+      <c r="J36" s="17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="11">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -2985,25 +3014,25 @@
         <v>19</v>
       </c>
       <c r="I37" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="J37" s="15" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+      <c r="J37" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="11">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="C38" s="12">
-        <v>45678</v>
+        <v>45673</v>
       </c>
       <c r="D38" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E38" s="12">
-        <v>45678</v>
+        <v>45680</v>
       </c>
       <c r="F38" s="13">
         <v>30</v>
@@ -3012,66 +3041,112 @@
         <v>14</v>
       </c>
       <c r="H38" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I38" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="J38" s="15" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B39" s="11">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="C39" s="12">
+        <v>45679</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39" s="12">
+        <v>45680</v>
+      </c>
+      <c r="F39" s="13">
+        <v>33</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H39" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I39" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="J39" s="15" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B40" s="11">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="C40" s="12">
+        <v>45678</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E40" s="12">
+        <v>45678</v>
+      </c>
+      <c r="F40" s="13">
+        <v>30</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H40" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I40" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="J40" s="15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B41" s="11">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="C41" s="12">
+        <v>45678</v>
+      </c>
+      <c r="D41" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" s="12">
+        <v>45678</v>
+      </c>
+      <c r="F41" s="13">
+        <v>30</v>
+      </c>
+      <c r="G41" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="I38" s="14" t="s">
+      <c r="I41" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="J38" s="15" t="s">
+      <c r="J41" s="15" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B39" s="11">
-        <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-      <c r="C39" s="12">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B42" s="11">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="C42" s="12">
         <v>45684</v>
-      </c>
-      <c r="D39" s="13"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="14"/>
-      <c r="J39" s="15"/>
-    </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B40" s="11">
-        <f t="shared" si="0"/>
-        <v>38</v>
-      </c>
-      <c r="C40" s="12"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
-      <c r="H40" s="13"/>
-      <c r="I40" s="14"/>
-      <c r="J40" s="15"/>
-    </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B41" s="11">
-        <f t="shared" si="0"/>
-        <v>39</v>
-      </c>
-      <c r="C41" s="12"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="14"/>
-      <c r="J41" s="15"/>
-    </row>
-    <row r="42" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B42" s="11">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="C42" s="12">
-        <v>45645</v>
       </c>
       <c r="D42" s="13" t="s">
         <v>10</v>
@@ -3082,42 +3157,28 @@
         <v>14</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I42" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="J42" s="17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="J42" s="15"/>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="11">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="C43" s="12">
-        <v>45654</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C43" s="12"/>
+      <c r="D43" s="13"/>
       <c r="E43" s="12"/>
       <c r="F43" s="13"/>
-      <c r="G43" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H43" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I43" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="J43" s="15" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="G43" s="13"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="14"/>
+      <c r="J43" s="15"/>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="11">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -3131,35 +3192,59 @@
       <c r="I44" s="14"/>
       <c r="J44" s="15"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:10" ht="28.5" x14ac:dyDescent="0.25">
       <c r="B45" s="11">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="C45" s="12"/>
-      <c r="D45" s="13"/>
+      <c r="C45" s="12">
+        <v>45645</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E45" s="12"/>
       <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
-      <c r="I45" s="14"/>
-      <c r="J45" s="15"/>
-    </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="G45" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H45" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I45" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="J45" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="11">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="C46" s="12"/>
-      <c r="D46" s="13"/>
+      <c r="C46" s="12">
+        <v>45654</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E46" s="12"/>
       <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="13"/>
-      <c r="I46" s="14"/>
-      <c r="J46" s="15"/>
-    </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="G46" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H46" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I46" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="J46" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="11">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -3173,20 +3258,21 @@
       <c r="I47" s="14"/>
       <c r="J47" s="15"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="11">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="C48" s="12"/>
       <c r="D48" s="13"/>
+      <c r="E48" s="12"/>
       <c r="F48" s="13"/>
       <c r="G48" s="13"/>
       <c r="H48" s="13"/>
       <c r="I48" s="14"/>
       <c r="J48" s="15"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="11">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -3200,24 +3286,65 @@
       <c r="I49" s="14"/>
       <c r="J49" s="15"/>
     </row>
-    <row r="50" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="18">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B50" s="11">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="C50" s="19"/>
-      <c r="D50" s="20"/>
-      <c r="E50" s="19"/>
-      <c r="F50" s="20"/>
-      <c r="G50" s="20"/>
-      <c r="H50" s="20"/>
-      <c r="I50" s="21"/>
-      <c r="J50" s="22"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="13"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="13"/>
+      <c r="H50" s="13"/>
+      <c r="I50" s="14"/>
+      <c r="J50" s="15"/>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B51" s="11">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="C51" s="12"/>
+      <c r="D51" s="13"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="13"/>
+      <c r="H51" s="13"/>
+      <c r="I51" s="14"/>
+      <c r="J51" s="15"/>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B52" s="11">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="C52" s="12"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="13"/>
+      <c r="G52" s="13"/>
+      <c r="H52" s="13"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="15"/>
+    </row>
+    <row r="53" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="18">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="C53" s="19"/>
+      <c r="D53" s="20"/>
+      <c r="E53" s="19"/>
+      <c r="F53" s="20"/>
+      <c r="G53" s="20"/>
+      <c r="H53" s="20"/>
+      <c r="I53" s="21"/>
+      <c r="J53" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:J50" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
+  <autoFilter ref="B2:J53" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B3:J46 B47:D48 F47:J48 B49:J50">
+  <conditionalFormatting sqref="B3:J49 B50:D51 F50:J51 B52:J53">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>
@@ -3225,12 +3352,12 @@
       <formula>$D3="着手中"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E47">
+  <conditionalFormatting sqref="E50">
     <cfRule type="expression" dxfId="1" priority="5">
-      <formula>$D48="完了"</formula>
+      <formula>$D51="完了"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="6">
-      <formula>$D48="着手中"</formula>
+      <formula>$D51="着手中"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3242,19 +3369,19 @@
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D50</xm:sqref>
+          <xm:sqref>D3:D53</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G50</xm:sqref>
+          <xm:sqref>G3:G53</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B4A065F5-E745-4CD6-9C94-45B6B3E69BD7}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H3:H50</xm:sqref>
+          <xm:sqref>H3:H53</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3265,9 +3392,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D5D5AD1-8B35-4B1A-BA80-9423D5B69C8E}">
   <dimension ref="B2:D6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>9</v>
       </c>
@@ -3278,7 +3405,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
@@ -3289,7 +3416,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
@@ -3300,7 +3427,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
@@ -3311,7 +3438,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D6" s="4" t="s">
         <v>23</v>
       </c>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -5,19 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\officinaWork03\busiframe\document\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{683BA4F1-1AA9-4C06-803D-BA71F2D06874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69BB0E47-656A-4200-91B7-EAAB4427B1E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24510" windowHeight="15990" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="選択情報" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$55</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="97">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -1271,6 +1271,38 @@
       <t>トウロク</t>
     </rPh>
     <rPh sb="4" eb="6">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>週品一覧表示</t>
+    <rPh sb="0" eb="2">
+      <t>シュウヒン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品照会画面への遷移追加</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショウカイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
       <t>ツイカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -1977,24 +2009,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="B1:K53"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:K55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.25" customWidth="1"/>
-    <col min="2" max="2" width="3.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.75" style="1"/>
+    <col min="1" max="1" width="1.26953125" customWidth="1"/>
+    <col min="2" max="2" width="3.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7265625" style="1"/>
     <col min="5" max="5" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.75" style="1"/>
-    <col min="9" max="9" width="23.125" customWidth="1"/>
-    <col min="10" max="10" width="68.625" customWidth="1"/>
-    <col min="11" max="11" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.453125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.7265625" style="1"/>
+    <col min="9" max="9" width="23.08984375" customWidth="1"/>
+    <col min="10" max="10" width="68.6328125" customWidth="1"/>
+    <col min="11" max="11" width="10.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="8.4499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:11" ht="8.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
@@ -2023,7 +2055,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B3" s="11" t="s">
         <v>1</v>
       </c>
@@ -2050,7 +2082,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="2:11" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B4" s="11">
         <f>B3+1</f>
         <v>2</v>
@@ -2080,7 +2112,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="11">
         <f>B4+1</f>
         <v>3</v>
@@ -2110,7 +2142,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="11">
         <f>B5+1</f>
         <v>4</v>
@@ -2140,7 +2172,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" s="11">
         <f>B6+1</f>
         <v>5</v>
@@ -2173,9 +2205,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
-        <f t="shared" ref="B8:B53" si="0">B7+1</f>
+        <f t="shared" ref="B8:B55" si="0">B7+1</f>
         <v>6</v>
       </c>
       <c r="C8" s="12">
@@ -2203,7 +2235,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" s="11">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2233,7 +2265,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" s="11">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2263,7 +2295,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11" s="11">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2293,7 +2325,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="2:11" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B12" s="11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2321,7 +2353,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="2:11" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B13" s="11">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2349,7 +2381,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" s="11">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2379,7 +2411,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" s="11">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2409,7 +2441,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" s="11">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2439,7 +2471,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="11">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2461,7 +2493,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="11">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2489,7 +2521,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="2:11" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B19" s="11">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2517,7 +2549,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="11">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2545,7 +2577,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="2:11" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B21" s="11">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2572,7 +2604,7 @@
       </c>
       <c r="K21" s="23"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="11">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2598,7 +2630,7 @@
       </c>
       <c r="J22" s="15"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="11">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2626,7 +2658,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="11">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -2656,7 +2688,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B25" s="11">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -2686,7 +2718,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B26" s="11">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2714,7 +2746,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B27" s="11">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -2744,7 +2776,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B28" s="11">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -2774,7 +2806,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B29" s="11">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2783,9 +2815,11 @@
         <v>45654</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E29" s="12">
+        <v>45686</v>
+      </c>
       <c r="F29" s="13">
         <v>26</v>
       </c>
@@ -2802,7 +2836,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B30" s="11">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -2811,9 +2845,11 @@
         <v>45684</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E30" s="12">
+        <v>45686</v>
+      </c>
       <c r="F30" s="13">
         <v>27</v>
       </c>
@@ -2830,7 +2866,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B31" s="11">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -2839,9 +2875,11 @@
         <v>45684</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E31" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E31" s="12">
+        <v>45686</v>
+      </c>
       <c r="F31" s="13">
         <v>27</v>
       </c>
@@ -2858,34 +2896,48 @@
         <v>94</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B32" s="11">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C32" s="12"/>
-      <c r="D32" s="13"/>
+      <c r="C32" s="12">
+        <v>45672</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>11</v>
+      </c>
       <c r="E32" s="12"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="15"/>
-    </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F32" s="13">
+        <v>21</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I32" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="J32" s="15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B33" s="11">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="C33" s="12">
-        <v>45672</v>
+        <v>45686</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E33" s="12"/>
       <c r="F33" s="13">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>14</v>
@@ -2897,70 +2949,52 @@
         <v>66</v>
       </c>
       <c r="J33" s="15" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="11">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="C34" s="12">
-        <v>45673</v>
+        <v>45686</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E34" s="12">
-        <v>45684</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E34" s="12"/>
       <c r="F34" s="13">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G34" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H34" s="13" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I34" s="14" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="J34" s="15" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B35" s="11">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C35" s="12">
-        <v>45673</v>
-      </c>
-      <c r="D35" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E35" s="12">
-        <v>45680</v>
-      </c>
-      <c r="F35" s="13">
-        <v>29</v>
-      </c>
-      <c r="G35" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H35" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I35" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="J35" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="36" spans="2:10" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="C35" s="12"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="15"/>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B36" s="11">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -2972,10 +3006,10 @@
         <v>12</v>
       </c>
       <c r="E36" s="12">
-        <v>45678</v>
+        <v>45684</v>
       </c>
       <c r="F36" s="13">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G36" s="13" t="s">
         <v>14</v>
@@ -2984,28 +3018,28 @@
         <v>19</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="J36" s="17" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="J36" s="15" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B37" s="11">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="C37" s="12">
-        <v>45678</v>
+        <v>45673</v>
       </c>
       <c r="D37" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E37" s="12">
-        <v>45678</v>
+        <v>45680</v>
       </c>
       <c r="F37" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G37" s="13" t="s">
         <v>14</v>
@@ -3017,10 +3051,10 @@
         <v>82</v>
       </c>
       <c r="J37" s="17" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B38" s="11">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -3032,7 +3066,7 @@
         <v>12</v>
       </c>
       <c r="E38" s="12">
-        <v>45680</v>
+        <v>45678</v>
       </c>
       <c r="F38" s="13">
         <v>30</v>
@@ -3046,26 +3080,26 @@
       <c r="I38" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="J38" s="15" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J38" s="17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B39" s="11">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="C39" s="12">
-        <v>45679</v>
+        <v>45678</v>
       </c>
       <c r="D39" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E39" s="12">
-        <v>45680</v>
+        <v>45678</v>
       </c>
       <c r="F39" s="13">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G39" s="13" t="s">
         <v>14</v>
@@ -3074,25 +3108,25 @@
         <v>19</v>
       </c>
       <c r="I39" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="J39" s="15" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+      <c r="J39" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B40" s="11">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
       <c r="C40" s="12">
-        <v>45678</v>
+        <v>45673</v>
       </c>
       <c r="D40" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E40" s="12">
-        <v>45678</v>
+        <v>45680</v>
       </c>
       <c r="F40" s="13">
         <v>30</v>
@@ -3104,175 +3138,207 @@
         <v>19</v>
       </c>
       <c r="I40" s="14" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J40" s="15" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="11">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="C41" s="12">
-        <v>45678</v>
+        <v>45679</v>
       </c>
       <c r="D41" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E41" s="12">
+        <v>45680</v>
+      </c>
+      <c r="F41" s="13">
+        <v>33</v>
+      </c>
+      <c r="G41" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I41" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="J41" s="15" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B42" s="11">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="C42" s="12">
         <v>45678</v>
       </c>
-      <c r="F41" s="13">
+      <c r="D42" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E42" s="12">
+        <v>45678</v>
+      </c>
+      <c r="F42" s="13">
         <v>30</v>
       </c>
-      <c r="G41" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H41" s="13" t="s">
+      <c r="G42" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H42" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I42" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="J42" s="15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B43" s="11">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="C43" s="12">
+        <v>45678</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" s="12">
+        <v>45678</v>
+      </c>
+      <c r="F43" s="13">
+        <v>30</v>
+      </c>
+      <c r="G43" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H43" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="I41" s="14" t="s">
+      <c r="I43" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="J41" s="15" t="s">
+      <c r="J43" s="15" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B42" s="11">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="C42" s="12">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B44" s="11">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="C44" s="12">
         <v>45684</v>
       </c>
-      <c r="D42" s="13" t="s">
+      <c r="D44" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E42" s="12"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H42" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="I42" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="J42" s="15"/>
-    </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B43" s="11">
-        <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
-      <c r="C43" s="12"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
-      <c r="H43" s="13"/>
-      <c r="I43" s="14"/>
-      <c r="J43" s="15"/>
-    </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B44" s="11">
-        <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
-      <c r="C44" s="12"/>
-      <c r="D44" s="13"/>
       <c r="E44" s="12"/>
       <c r="F44" s="13"/>
-      <c r="G44" s="13"/>
-      <c r="H44" s="13"/>
-      <c r="I44" s="14"/>
+      <c r="G44" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H44" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I44" s="14" t="s">
+        <v>91</v>
+      </c>
       <c r="J44" s="15"/>
     </row>
-    <row r="45" spans="2:10" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B45" s="11">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="C45" s="12">
-        <v>45645</v>
-      </c>
-      <c r="D45" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C45" s="12"/>
+      <c r="D45" s="13"/>
       <c r="E45" s="12"/>
       <c r="F45" s="13"/>
-      <c r="G45" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H45" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I45" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="J45" s="17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="G45" s="13"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="14"/>
+      <c r="J45" s="15"/>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B46" s="11">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="C46" s="12">
-        <v>45654</v>
-      </c>
-      <c r="D46" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C46" s="12"/>
+      <c r="D46" s="13"/>
       <c r="E46" s="12"/>
       <c r="F46" s="13"/>
-      <c r="G46" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H46" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I46" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="J46" s="15" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="G46" s="13"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="14"/>
+      <c r="J46" s="15"/>
+    </row>
+    <row r="47" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B47" s="11">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="C47" s="12"/>
-      <c r="D47" s="13"/>
+      <c r="C47" s="12">
+        <v>45645</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E47" s="12"/>
       <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="13"/>
-      <c r="I47" s="14"/>
-      <c r="J47" s="15"/>
-    </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="G47" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H47" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I47" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="J47" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B48" s="11">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="C48" s="12"/>
-      <c r="D48" s="13"/>
+      <c r="C48" s="12">
+        <v>45654</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E48" s="12"/>
       <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
-      <c r="I48" s="14"/>
-      <c r="J48" s="15"/>
-    </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="G48" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H48" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I48" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="J48" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B49" s="11">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -3286,7 +3352,7 @@
       <c r="I49" s="14"/>
       <c r="J49" s="15"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B50" s="11">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -3300,20 +3366,21 @@
       <c r="I50" s="14"/>
       <c r="J50" s="15"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B51" s="11">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="C51" s="12"/>
       <c r="D51" s="13"/>
+      <c r="E51" s="12"/>
       <c r="F51" s="13"/>
       <c r="G51" s="13"/>
       <c r="H51" s="13"/>
       <c r="I51" s="14"/>
       <c r="J51" s="15"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B52" s="11">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -3327,24 +3394,51 @@
       <c r="I52" s="14"/>
       <c r="J52" s="15"/>
     </row>
-    <row r="53" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="18">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B53" s="11">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="C53" s="19"/>
-      <c r="D53" s="20"/>
-      <c r="E53" s="19"/>
-      <c r="F53" s="20"/>
-      <c r="G53" s="20"/>
-      <c r="H53" s="20"/>
-      <c r="I53" s="21"/>
-      <c r="J53" s="22"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="13"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="13"/>
+      <c r="I53" s="14"/>
+      <c r="J53" s="15"/>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B54" s="11">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="C54" s="12"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="14"/>
+      <c r="J54" s="15"/>
+    </row>
+    <row r="55" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B55" s="18">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="C55" s="19"/>
+      <c r="D55" s="20"/>
+      <c r="E55" s="19"/>
+      <c r="F55" s="20"/>
+      <c r="G55" s="20"/>
+      <c r="H55" s="20"/>
+      <c r="I55" s="21"/>
+      <c r="J55" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:J53" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
+  <autoFilter ref="B2:J55" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B3:J49 B50:D51 F50:J51 B52:J53">
+  <conditionalFormatting sqref="B52:D53 F52:J53 B54:J55 B3:J51">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>
@@ -3352,12 +3446,12 @@
       <formula>$D3="着手中"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E50">
+  <conditionalFormatting sqref="E52">
     <cfRule type="expression" dxfId="1" priority="5">
-      <formula>$D51="完了"</formula>
+      <formula>$D53="完了"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="6">
-      <formula>$D51="着手中"</formula>
+      <formula>$D53="着手中"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3369,19 +3463,19 @@
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D53</xm:sqref>
+          <xm:sqref>D3:D55</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G53</xm:sqref>
+          <xm:sqref>G3:G55</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B4A065F5-E745-4CD6-9C94-45B6B3E69BD7}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H3:H53</xm:sqref>
+          <xm:sqref>H3:H55</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3392,9 +3486,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D5D5AD1-8B35-4B1A-BA80-9423D5B69C8E}">
   <dimension ref="B2:D6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>9</v>
       </c>
@@ -3405,7 +3499,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
@@ -3416,7 +3510,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
@@ -3427,7 +3521,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
@@ -3438,7 +3532,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D6" s="4" t="s">
         <v>23</v>
       </c>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69BB0E47-656A-4200-91B7-EAAB4427B1E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2D36F99-36FB-4BEA-A776-77B90C72FC6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -1276,9 +1276,28 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>週品一覧表示</t>
-    <rPh sb="0" eb="2">
-      <t>シュウヒン</t>
+    <t>商品照会画面への遷移追加</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショウカイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品一覧表示（登録済みの商品の一覧を明細行として表示する。）</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
     </rPh>
     <rPh sb="2" eb="4">
       <t>イチラン</t>
@@ -1286,24 +1305,23 @@
     <rPh sb="4" eb="6">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>商品照会画面への遷移追加</t>
-    <rPh sb="0" eb="2">
+    <rPh sb="7" eb="10">
+      <t>トウロクズ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
       <t>ショウヒン</t>
     </rPh>
-    <rPh sb="2" eb="4">
-      <t>ショウカイ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>センイ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ツイカ</t>
+    <rPh sb="15" eb="17">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>メイサイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ギョウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2933,7 +2951,7 @@
         <v>45686</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E33" s="12"/>
       <c r="F33" s="13">
@@ -2949,7 +2967,7 @@
         <v>66</v>
       </c>
       <c r="J33" s="15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
@@ -2977,7 +2995,7 @@
         <v>66</v>
       </c>
       <c r="J34" s="15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.3">
@@ -3438,7 +3456,7 @@
   </sheetData>
   <autoFilter ref="B2:J55" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B52:D53 F52:J53 B54:J55 B3:J51">
+  <conditionalFormatting sqref="B3:J51 B52:D53 F52:J53 B54:J55">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2D36F99-36FB-4BEA-A776-77B90C72FC6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E363F33-F043-4EF2-9B70-697D2B1567BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="選択情報" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$59</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="101">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -1322,6 +1322,91 @@
     </rPh>
     <rPh sb="24" eb="26">
       <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品照会画面</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショウカイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面CD : productdisp 、識別コード、名称、説明を表示し、画面には「編集」「一覧」「メニュー」の遷移ボタンを設置する。</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>シキベツ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>メイショウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>セッチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示情報、表示詳細情報の事前登録</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="12" eb="16">
+      <t>ジゼントウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ProductServlet01に照会画面への遷移ロジック追加</t>
+    <rPh sb="17" eb="19">
+      <t>ショウカイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ツイカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2027,7 +2112,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="B1:K55"/>
+  <dimension ref="B1:K59"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -2225,7 +2310,7 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
-        <f t="shared" ref="B8:B55" si="0">B7+1</f>
+        <f t="shared" ref="B8:B59" si="0">B7+1</f>
         <v>6</v>
       </c>
       <c r="C8" s="12">
@@ -2979,9 +3064,11 @@
         <v>45686</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E34" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E34" s="12">
+        <v>45691</v>
+      </c>
       <c r="F34" s="13">
         <v>30</v>
       </c>
@@ -2998,19 +3085,33 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B35" s="11">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C35" s="12"/>
-      <c r="D35" s="13"/>
+      <c r="C35" s="12">
+        <v>45691</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E35" s="12"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="14"/>
-      <c r="J35" s="15"/>
+      <c r="F35" s="13">
+        <v>31</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H35" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I35" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="J35" s="17" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B36" s="11">
@@ -3018,28 +3119,26 @@
         <v>34</v>
       </c>
       <c r="C36" s="12">
-        <v>45673</v>
+        <v>45691</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E36" s="12">
-        <v>45684</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E36" s="12"/>
       <c r="F36" s="13">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G36" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="J36" s="15" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.3">
@@ -3048,89 +3147,55 @@
         <v>35</v>
       </c>
       <c r="C37" s="12">
-        <v>45673</v>
+        <v>45691</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E37" s="12">
-        <v>45680</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E37" s="12"/>
       <c r="F37" s="13">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G37" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I37" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="J37" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="38" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+      <c r="J37" s="15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B38" s="11">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C38" s="12">
-        <v>45673</v>
-      </c>
-      <c r="D38" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E38" s="12">
-        <v>45678</v>
-      </c>
-      <c r="F38" s="13">
-        <v>30</v>
-      </c>
-      <c r="G38" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H38" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I38" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="J38" s="17" t="s">
-        <v>83</v>
-      </c>
+      <c r="C38" s="12"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="15"/>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B39" s="11">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C39" s="12">
-        <v>45678</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E39" s="12">
-        <v>45678</v>
-      </c>
-      <c r="F39" s="13">
-        <v>30</v>
-      </c>
-      <c r="G39" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H39" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I39" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="J39" s="17" t="s">
-        <v>86</v>
-      </c>
+      <c r="C39" s="12"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="14"/>
+      <c r="J39" s="15"/>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B40" s="11">
@@ -3144,10 +3209,10 @@
         <v>12</v>
       </c>
       <c r="E40" s="12">
-        <v>45680</v>
+        <v>45684</v>
       </c>
       <c r="F40" s="13">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G40" s="13" t="s">
         <v>14</v>
@@ -3156,10 +3221,10 @@
         <v>19</v>
       </c>
       <c r="I40" s="14" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="J40" s="15" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
@@ -3168,7 +3233,7 @@
         <v>39</v>
       </c>
       <c r="C41" s="12">
-        <v>45679</v>
+        <v>45673</v>
       </c>
       <c r="D41" s="13" t="s">
         <v>12</v>
@@ -3177,7 +3242,7 @@
         <v>45680</v>
       </c>
       <c r="F41" s="13">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G41" s="13" t="s">
         <v>14</v>
@@ -3186,19 +3251,19 @@
         <v>19</v>
       </c>
       <c r="I41" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="J41" s="15" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+      <c r="J41" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B42" s="11">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="C42" s="12">
-        <v>45678</v>
+        <v>45673</v>
       </c>
       <c r="D42" s="13" t="s">
         <v>12</v>
@@ -3216,10 +3281,10 @@
         <v>19</v>
       </c>
       <c r="I42" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="J42" s="15" t="s">
-        <v>88</v>
+        <v>82</v>
+      </c>
+      <c r="J42" s="17" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.3">
@@ -3243,13 +3308,13 @@
         <v>14</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I43" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="J43" s="15" t="s">
-        <v>85</v>
+        <v>82</v>
+      </c>
+      <c r="J43" s="17" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
@@ -3258,76 +3323,118 @@
         <v>42</v>
       </c>
       <c r="C44" s="12">
-        <v>45684</v>
+        <v>45673</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E44" s="12"/>
-      <c r="F44" s="13"/>
+        <v>12</v>
+      </c>
+      <c r="E44" s="12">
+        <v>45680</v>
+      </c>
+      <c r="F44" s="13">
+        <v>30</v>
+      </c>
       <c r="G44" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H44" s="13" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I44" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="J44" s="15"/>
+        <v>82</v>
+      </c>
+      <c r="J44" s="15" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B45" s="11">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="C45" s="12"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
-      <c r="I45" s="14"/>
-      <c r="J45" s="15"/>
+      <c r="C45" s="12">
+        <v>45679</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45" s="12">
+        <v>45680</v>
+      </c>
+      <c r="F45" s="13">
+        <v>33</v>
+      </c>
+      <c r="G45" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H45" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I45" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="J45" s="15" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B46" s="11">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="C46" s="12"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="13"/>
-      <c r="I46" s="14"/>
-      <c r="J46" s="15"/>
-    </row>
-    <row r="47" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C46" s="12">
+        <v>45678</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E46" s="12">
+        <v>45678</v>
+      </c>
+      <c r="F46" s="13">
+        <v>30</v>
+      </c>
+      <c r="G46" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H46" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I46" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="J46" s="15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47" s="11">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="C47" s="12">
-        <v>45645</v>
+        <v>45678</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E47" s="12"/>
-      <c r="F47" s="13"/>
+        <v>12</v>
+      </c>
+      <c r="E47" s="12">
+        <v>45678</v>
+      </c>
+      <c r="F47" s="13">
+        <v>30</v>
+      </c>
       <c r="G47" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I47" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="J47" s="17" t="s">
-        <v>64</v>
+        <v>84</v>
+      </c>
+      <c r="J47" s="15" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.3">
@@ -3336,7 +3443,7 @@
         <v>46</v>
       </c>
       <c r="C48" s="12">
-        <v>45654</v>
+        <v>45684</v>
       </c>
       <c r="D48" s="13" t="s">
         <v>10</v>
@@ -3347,14 +3454,12 @@
         <v>14</v>
       </c>
       <c r="H48" s="13" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I48" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="J48" s="15" t="s">
-        <v>71</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="J48" s="15"/>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B49" s="11">
@@ -3384,33 +3489,57 @@
       <c r="I50" s="14"/>
       <c r="J50" s="15"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B51" s="11">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="C51" s="12"/>
-      <c r="D51" s="13"/>
+      <c r="C51" s="12">
+        <v>45645</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E51" s="12"/>
       <c r="F51" s="13"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="13"/>
-      <c r="I51" s="14"/>
-      <c r="J51" s="15"/>
+      <c r="G51" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H51" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I51" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="J51" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B52" s="11">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="C52" s="12"/>
-      <c r="D52" s="13"/>
+      <c r="C52" s="12">
+        <v>45654</v>
+      </c>
+      <c r="D52" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E52" s="12"/>
       <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="13"/>
-      <c r="I52" s="14"/>
-      <c r="J52" s="15"/>
+      <c r="G52" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H52" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I52" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="J52" s="15" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B53" s="11">
@@ -3419,6 +3548,7 @@
       </c>
       <c r="C53" s="12"/>
       <c r="D53" s="13"/>
+      <c r="E53" s="12"/>
       <c r="F53" s="13"/>
       <c r="G53" s="13"/>
       <c r="H53" s="13"/>
@@ -3439,24 +3569,79 @@
       <c r="I54" s="14"/>
       <c r="J54" s="15"/>
     </row>
-    <row r="55" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="18">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B55" s="11">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="C55" s="19"/>
-      <c r="D55" s="20"/>
-      <c r="E55" s="19"/>
-      <c r="F55" s="20"/>
-      <c r="G55" s="20"/>
-      <c r="H55" s="20"/>
-      <c r="I55" s="21"/>
-      <c r="J55" s="22"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="14"/>
+      <c r="J55" s="15"/>
+    </row>
+    <row r="56" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B56" s="11">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="C56" s="12"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="15"/>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B57" s="11">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="C57" s="12"/>
+      <c r="D57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="14"/>
+      <c r="J57" s="15"/>
+    </row>
+    <row r="58" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B58" s="11">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="C58" s="12"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="12"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="14"/>
+      <c r="J58" s="15"/>
+    </row>
+    <row r="59" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B59" s="18">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="C59" s="19"/>
+      <c r="D59" s="20"/>
+      <c r="E59" s="19"/>
+      <c r="F59" s="20"/>
+      <c r="G59" s="20"/>
+      <c r="H59" s="20"/>
+      <c r="I59" s="21"/>
+      <c r="J59" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:J55" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
+  <autoFilter ref="B2:J59" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B3:J51 B52:D53 F52:J53 B54:J55">
+  <conditionalFormatting sqref="B56:D57 F56:J57 B58:J59 B3:J55">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>
@@ -3464,12 +3649,12 @@
       <formula>$D3="着手中"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E52">
+  <conditionalFormatting sqref="E56">
     <cfRule type="expression" dxfId="1" priority="5">
-      <formula>$D53="完了"</formula>
+      <formula>$D57="完了"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="6">
-      <formula>$D53="着手中"</formula>
+      <formula>$D57="着手中"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3481,19 +3666,19 @@
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D55</xm:sqref>
+          <xm:sqref>D3:D59</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G55</xm:sqref>
+          <xm:sqref>G3:G59</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B4A065F5-E745-4CD6-9C94-45B6B3E69BD7}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H3:H55</xm:sqref>
+          <xm:sqref>H3:H59</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E363F33-F043-4EF2-9B70-697D2B1567BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F5098DC-8360-4B85-8BFC-E10417CEC96F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="102">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -1407,6 +1407,13 @@
     </rPh>
     <rPh sb="29" eb="31">
       <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HtmlProductData構築</t>
+    <rPh sb="15" eb="17">
+      <t>コウチク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3094,7 +3101,7 @@
         <v>45691</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E35" s="12"/>
       <c r="F35" s="13">
@@ -3174,14 +3181,28 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C38" s="12"/>
-      <c r="D38" s="13"/>
+      <c r="C38" s="12">
+        <v>45691</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E38" s="12"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="14"/>
-      <c r="J38" s="15"/>
+      <c r="F38" s="13">
+        <v>31</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H38" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I38" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="J38" s="15" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B39" s="11">

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F5098DC-8360-4B85-8BFC-E10417CEC96F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DEFCA15-EBD1-4C58-9388-7C4BEE3C89E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -3129,9 +3129,11 @@
         <v>45691</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E36" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E36" s="12">
+        <v>45691</v>
+      </c>
       <c r="F36" s="13">
         <v>31</v>
       </c>
@@ -3157,7 +3159,7 @@
         <v>45691</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E37" s="12"/>
       <c r="F37" s="13">
@@ -3662,7 +3664,7 @@
   </sheetData>
   <autoFilter ref="B2:J59" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B56:D57 F56:J57 B58:J59 B3:J55">
+  <conditionalFormatting sqref="B3:J55 B56:D57 F56:J57 B58:J59">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DEFCA15-EBD1-4C58-9388-7C4BEE3C89E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D10ADE-CD01-4BDC-8BF0-74A241349D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="選択情報" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$72</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="111">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -1414,6 +1414,107 @@
     <t>HtmlProductData構築</t>
     <rPh sb="15" eb="17">
       <t>コウチク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロジェクト</t>
+  </si>
+  <si>
+    <t>プロジェクト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロジェクト管理</t>
+    <rPh sb="6" eb="8">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メニューの追加</t>
+    <rPh sb="5" eb="7">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メインメニュー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HtmlMenuの汎用化（現在は固定でメニューボタンを表示しているので、プロジェクト管理を2行目にする。</t>
+    <rPh sb="9" eb="12">
+      <t>ハンヨウカ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>コテイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ギョウメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示情報の初期登録化</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="5" eb="10">
+      <t>ショキトウロクカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示メニュー情報の初期登録化</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ショキ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HtmlMenuの修正（メニュー情報を読込、行毎にボタンを出力する。）</t>
+    <rPh sb="9" eb="11">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ヨミコミ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ギョウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ゴト</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>シュツリョク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1758,21 +1859,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
@@ -2119,7 +2206,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="B1:K59"/>
+  <dimension ref="B1:K72"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -2317,7 +2404,7 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
-        <f t="shared" ref="B8:B59" si="0">B7+1</f>
+        <f t="shared" ref="B8:B72" si="0">B7+1</f>
         <v>6</v>
       </c>
       <c r="C8" s="12">
@@ -3597,111 +3684,366 @@
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="C55" s="12"/>
-      <c r="D55" s="13"/>
+      <c r="C55" s="12">
+        <v>45698</v>
+      </c>
+      <c r="D55" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E55" s="12"/>
       <c r="F55" s="13"/>
-      <c r="G55" s="13"/>
-      <c r="H55" s="13"/>
-      <c r="I55" s="14"/>
-      <c r="J55" s="15"/>
+      <c r="G55" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H55" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I55" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="J55" s="15" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B56" s="11">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="C56" s="12"/>
-      <c r="D56" s="13"/>
+      <c r="C56" s="12">
+        <v>45698</v>
+      </c>
+      <c r="D56" s="13" t="s">
+        <v>11</v>
+      </c>
       <c r="E56" s="12"/>
-      <c r="F56" s="13"/>
-      <c r="G56" s="13"/>
-      <c r="H56" s="13"/>
-      <c r="I56" s="14"/>
-      <c r="J56" s="15"/>
+      <c r="F56" s="13">
+        <f>$B$55</f>
+        <v>53</v>
+      </c>
+      <c r="G56" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H56" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I56" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J56" s="15" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B57" s="11">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="C57" s="12"/>
-      <c r="D57" s="13"/>
-      <c r="F57" s="13"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="13"/>
-      <c r="I57" s="14"/>
-      <c r="J57" s="15"/>
+      <c r="C57" s="12">
+        <v>45698</v>
+      </c>
+      <c r="D57" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E57" s="12">
+        <v>45698</v>
+      </c>
+      <c r="F57" s="13">
+        <f>$B$56</f>
+        <v>54</v>
+      </c>
+      <c r="G57" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H57" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I57" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J57" s="15" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B58" s="11">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="C58" s="12"/>
-      <c r="D58" s="13"/>
+      <c r="C58" s="12">
+        <v>45698</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E58" s="12"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="13"/>
-      <c r="H58" s="13"/>
-      <c r="I58" s="14"/>
-      <c r="J58" s="15"/>
-    </row>
-    <row r="59" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B59" s="18">
+      <c r="F58" s="13">
+        <f>$B$56</f>
+        <v>54</v>
+      </c>
+      <c r="G58" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H58" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I58" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J58" s="15" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B59" s="11">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="C59" s="19"/>
-      <c r="D59" s="20"/>
-      <c r="E59" s="19"/>
-      <c r="F59" s="20"/>
-      <c r="G59" s="20"/>
-      <c r="H59" s="20"/>
-      <c r="I59" s="21"/>
-      <c r="J59" s="22"/>
+      <c r="C59" s="12">
+        <v>45698</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59" s="12"/>
+      <c r="F59" s="13">
+        <f>$B$56</f>
+        <v>54</v>
+      </c>
+      <c r="G59" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H59" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I59" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J59" s="15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B60" s="11">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="C60" s="12"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="13"/>
+      <c r="H60" s="13"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="15"/>
+    </row>
+    <row r="61" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B61" s="11">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="C61" s="12"/>
+      <c r="D61" s="13"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="13"/>
+      <c r="G61" s="13"/>
+      <c r="H61" s="13"/>
+      <c r="I61" s="14"/>
+      <c r="J61" s="15"/>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B62" s="11">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="C62" s="12"/>
+      <c r="D62" s="13"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="13"/>
+      <c r="G62" s="13"/>
+      <c r="H62" s="13"/>
+      <c r="I62" s="14"/>
+      <c r="J62" s="15"/>
+    </row>
+    <row r="63" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B63" s="11">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="C63" s="12"/>
+      <c r="D63" s="13"/>
+      <c r="E63" s="12"/>
+      <c r="F63" s="13"/>
+      <c r="G63" s="13"/>
+      <c r="H63" s="13"/>
+      <c r="I63" s="14"/>
+      <c r="J63" s="15"/>
+    </row>
+    <row r="64" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B64" s="11">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="C64" s="12"/>
+      <c r="D64" s="13"/>
+      <c r="E64" s="12"/>
+      <c r="F64" s="13"/>
+      <c r="G64" s="13"/>
+      <c r="H64" s="13"/>
+      <c r="I64" s="14"/>
+      <c r="J64" s="15"/>
+    </row>
+    <row r="65" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B65" s="11">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="C65" s="12"/>
+      <c r="D65" s="13"/>
+      <c r="E65" s="12"/>
+      <c r="F65" s="13"/>
+      <c r="G65" s="13"/>
+      <c r="H65" s="13"/>
+      <c r="I65" s="14"/>
+      <c r="J65" s="15"/>
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B66" s="11">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="C66" s="12"/>
+      <c r="D66" s="13"/>
+      <c r="E66" s="12"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="13"/>
+      <c r="H66" s="13"/>
+      <c r="I66" s="14"/>
+      <c r="J66" s="15"/>
+    </row>
+    <row r="67" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B67" s="11">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="C67" s="12"/>
+      <c r="D67" s="13"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="13"/>
+      <c r="G67" s="13"/>
+      <c r="H67" s="13"/>
+      <c r="I67" s="14"/>
+      <c r="J67" s="15"/>
+    </row>
+    <row r="68" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B68" s="11">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+      <c r="C68" s="12"/>
+      <c r="D68" s="13"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="13"/>
+      <c r="G68" s="13"/>
+      <c r="H68" s="13"/>
+      <c r="I68" s="14"/>
+      <c r="J68" s="15"/>
+    </row>
+    <row r="69" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B69" s="11">
+        <f t="shared" si="0"/>
+        <v>67</v>
+      </c>
+      <c r="C69" s="12"/>
+      <c r="D69" s="13"/>
+      <c r="E69" s="12"/>
+      <c r="F69" s="13"/>
+      <c r="G69" s="13"/>
+      <c r="H69" s="13"/>
+      <c r="I69" s="14"/>
+      <c r="J69" s="15"/>
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B70" s="11">
+        <f t="shared" si="0"/>
+        <v>68</v>
+      </c>
+      <c r="C70" s="12"/>
+      <c r="D70" s="13"/>
+      <c r="E70" s="12"/>
+      <c r="F70" s="13"/>
+      <c r="G70" s="13"/>
+      <c r="H70" s="13"/>
+      <c r="I70" s="14"/>
+      <c r="J70" s="15"/>
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B71" s="11">
+        <f t="shared" si="0"/>
+        <v>69</v>
+      </c>
+      <c r="C71" s="12"/>
+      <c r="D71" s="13"/>
+      <c r="E71" s="12"/>
+      <c r="F71" s="13"/>
+      <c r="G71" s="13"/>
+      <c r="H71" s="13"/>
+      <c r="I71" s="14"/>
+      <c r="J71" s="15"/>
+    </row>
+    <row r="72" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B72" s="18">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="C72" s="19"/>
+      <c r="D72" s="20"/>
+      <c r="E72" s="19"/>
+      <c r="F72" s="20"/>
+      <c r="G72" s="20"/>
+      <c r="H72" s="20"/>
+      <c r="I72" s="21"/>
+      <c r="J72" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:J59" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
+  <autoFilter ref="B2:J72" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B3:J55 B56:D57 F56:J57 B58:J59">
-    <cfRule type="expression" dxfId="3" priority="1">
+  <conditionalFormatting sqref="B3:J72">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>$D3="着手中"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E56">
-    <cfRule type="expression" dxfId="1" priority="5">
-      <formula>$D57="完了"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="6">
-      <formula>$D57="着手中"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C61EF0EC-B820-4CEA-8AA2-04B5D172AE2C}">
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D59</xm:sqref>
+          <xm:sqref>D3:D72</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G59</xm:sqref>
+          <xm:sqref>G3:G72</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B4A065F5-E745-4CD6-9C94-45B6B3E69BD7}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H3:H59</xm:sqref>
+          <xm:sqref>H3:H54 H56:H72</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D6F2F62E-6D63-4E2D-8772-1211A4C3A979}">
+          <x14:formula1>
+            <xm:f>選択情報!$D$3:$D$10</xm:f>
+          </x14:formula1>
+          <xm:sqref>H55</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3711,7 +4053,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D5D5AD1-8B35-4B1A-BA80-9423D5B69C8E}">
-  <dimension ref="B2:D6"/>
+  <dimension ref="B2:D7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3758,9 +4100,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D6" s="4" t="s">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D6" s="3" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D7" s="4" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D10ADE-CD01-4BDC-8BF0-74A241349D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{917905E2-42A4-4E9F-BC12-228D71640497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="選択情報" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$75</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="114">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -1515,6 +1515,63 @@
     </rPh>
     <rPh sb="29" eb="31">
       <t>シュツリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>週品情報読込 : M_Product.load(env, productId)</t>
+    <rPh sb="0" eb="2">
+      <t>シュウヒン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヨミコミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テーブル関連情報が出来るまで、固定的に商品情報の内容を画面のValueにセットする。</t>
+    <rPh sb="4" eb="6">
+      <t>カンレン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>デキ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>コテイテキ</t>
+    </rPh>
+    <rPh sb="19" eb="23">
+      <t>ショウヒンジョウホウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遷移ボタン : 「一覧へ戻る」「編集」を作成する。</t>
+    <rPh sb="0" eb="2">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>サクセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2206,7 +2263,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="B1:K72"/>
+  <dimension ref="B1:K75"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -2404,7 +2461,7 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
-        <f t="shared" ref="B8:B72" si="0">B7+1</f>
+        <f t="shared" ref="B8:B75" si="0">B7+1</f>
         <v>6</v>
       </c>
       <c r="C8" s="12">
@@ -3222,7 +3279,8 @@
         <v>45691</v>
       </c>
       <c r="F36" s="13">
-        <v>31</v>
+        <f>$B$35</f>
+        <v>33</v>
       </c>
       <c r="G36" s="13" t="s">
         <v>14</v>
@@ -3246,11 +3304,14 @@
         <v>45691</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E37" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E37" s="12">
+        <v>45692</v>
+      </c>
       <c r="F37" s="13">
-        <v>31</v>
+        <f>$B$35</f>
+        <v>33</v>
       </c>
       <c r="G37" s="13" t="s">
         <v>14</v>
@@ -3274,11 +3335,12 @@
         <v>45691</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E38" s="12"/>
       <c r="F38" s="13">
-        <v>31</v>
+        <f>$B$35</f>
+        <v>33</v>
       </c>
       <c r="G38" s="13" t="s">
         <v>14</v>
@@ -3298,14 +3360,31 @@
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C39" s="12"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="14"/>
-      <c r="J39" s="15"/>
+      <c r="C39" s="12">
+        <v>45700</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39" s="12">
+        <v>45700</v>
+      </c>
+      <c r="F39" s="13">
+        <f>$B$38</f>
+        <v>36</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H39" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I39" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="J39" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B40" s="11">
@@ -3313,28 +3392,29 @@
         <v>38</v>
       </c>
       <c r="C40" s="12">
-        <v>45673</v>
+        <v>45701</v>
       </c>
       <c r="D40" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E40" s="12">
-        <v>45684</v>
+        <v>45701</v>
       </c>
       <c r="F40" s="13">
-        <v>24</v>
+        <f>$B$38</f>
+        <v>36</v>
       </c>
       <c r="G40" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I40" s="14" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="J40" s="15" t="s">
-        <v>79</v>
+        <v>112</v>
       </c>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
@@ -3343,59 +3423,42 @@
         <v>39</v>
       </c>
       <c r="C41" s="12">
-        <v>45673</v>
+        <v>45701</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E41" s="12">
-        <v>45680</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E41" s="12"/>
       <c r="F41" s="13">
-        <v>29</v>
+        <f>$B$38</f>
+        <v>36</v>
       </c>
       <c r="G41" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I41" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="J41" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="42" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+      <c r="J41" s="15" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B42" s="11">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C42" s="12">
-        <v>45673</v>
-      </c>
-      <c r="D42" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E42" s="12">
-        <v>45678</v>
-      </c>
-      <c r="F42" s="13">
-        <v>30</v>
-      </c>
-      <c r="G42" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H42" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I42" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="J42" s="17" t="s">
-        <v>83</v>
-      </c>
+      <c r="C42" s="12"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="14"/>
+      <c r="J42" s="15"/>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B43" s="11">
@@ -3403,16 +3466,16 @@
         <v>41</v>
       </c>
       <c r="C43" s="12">
-        <v>45678</v>
+        <v>45673</v>
       </c>
       <c r="D43" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E43" s="12">
-        <v>45678</v>
+        <v>45684</v>
       </c>
       <c r="F43" s="13">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G43" s="13" t="s">
         <v>14</v>
@@ -3421,10 +3484,10 @@
         <v>19</v>
       </c>
       <c r="I43" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="J43" s="17" t="s">
-        <v>86</v>
+        <v>78</v>
+      </c>
+      <c r="J43" s="15" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
@@ -3442,7 +3505,7 @@
         <v>45680</v>
       </c>
       <c r="F44" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G44" s="13" t="s">
         <v>14</v>
@@ -3453,26 +3516,26 @@
       <c r="I44" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="J44" s="15" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J44" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B45" s="11">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="C45" s="12">
-        <v>45679</v>
+        <v>45673</v>
       </c>
       <c r="D45" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E45" s="12">
-        <v>45680</v>
+        <v>45678</v>
       </c>
       <c r="F45" s="13">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G45" s="13" t="s">
         <v>14</v>
@@ -3481,10 +3544,10 @@
         <v>19</v>
       </c>
       <c r="I45" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="J45" s="15" t="s">
-        <v>90</v>
+        <v>82</v>
+      </c>
+      <c r="J45" s="17" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.3">
@@ -3511,10 +3574,10 @@
         <v>19</v>
       </c>
       <c r="I46" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="J46" s="15" t="s">
-        <v>88</v>
+        <v>82</v>
+      </c>
+      <c r="J46" s="17" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
@@ -3523,13 +3586,13 @@
         <v>45</v>
       </c>
       <c r="C47" s="12">
-        <v>45678</v>
+        <v>45673</v>
       </c>
       <c r="D47" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E47" s="12">
-        <v>45678</v>
+        <v>45680</v>
       </c>
       <c r="F47" s="13">
         <v>30</v>
@@ -3538,13 +3601,13 @@
         <v>14</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I47" s="14" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J47" s="15" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.3">
@@ -3553,59 +3616,97 @@
         <v>46</v>
       </c>
       <c r="C48" s="12">
-        <v>45684</v>
+        <v>45679</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E48" s="12"/>
-      <c r="F48" s="13"/>
+        <v>12</v>
+      </c>
+      <c r="E48" s="12">
+        <v>45680</v>
+      </c>
+      <c r="F48" s="13">
+        <v>33</v>
+      </c>
       <c r="G48" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H48" s="13" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I48" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="J48" s="15"/>
+        <v>89</v>
+      </c>
+      <c r="J48" s="15" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B49" s="11">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="C49" s="12"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="13"/>
-      <c r="H49" s="13"/>
-      <c r="I49" s="14"/>
-      <c r="J49" s="15"/>
+      <c r="C49" s="12">
+        <v>45678</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E49" s="12">
+        <v>45678</v>
+      </c>
+      <c r="F49" s="13">
+        <v>30</v>
+      </c>
+      <c r="G49" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H49" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I49" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="J49" s="15" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B50" s="11">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="C50" s="12"/>
-      <c r="D50" s="13"/>
-      <c r="E50" s="12"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13"/>
-      <c r="H50" s="13"/>
-      <c r="I50" s="14"/>
-      <c r="J50" s="15"/>
-    </row>
-    <row r="51" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C50" s="12">
+        <v>45678</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E50" s="12">
+        <v>45678</v>
+      </c>
+      <c r="F50" s="13">
+        <v>30</v>
+      </c>
+      <c r="G50" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H50" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I50" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="J50" s="15" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B51" s="11">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="C51" s="12">
-        <v>45645</v>
+        <v>45684</v>
       </c>
       <c r="D51" s="13" t="s">
         <v>10</v>
@@ -3616,40 +3717,26 @@
         <v>14</v>
       </c>
       <c r="H51" s="13" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I51" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="J51" s="17" t="s">
-        <v>64</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="J51" s="15"/>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B52" s="11">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="C52" s="12">
-        <v>45654</v>
-      </c>
-      <c r="D52" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C52" s="12"/>
+      <c r="D52" s="13"/>
       <c r="E52" s="12"/>
       <c r="F52" s="13"/>
-      <c r="G52" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H52" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I52" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="J52" s="15" t="s">
-        <v>71</v>
-      </c>
+      <c r="G52" s="13"/>
+      <c r="H52" s="13"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="15"/>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B53" s="11">
@@ -3665,19 +3752,31 @@
       <c r="I53" s="14"/>
       <c r="J53" s="15"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B54" s="11">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="C54" s="12"/>
-      <c r="D54" s="13"/>
+      <c r="C54" s="12">
+        <v>45645</v>
+      </c>
+      <c r="D54" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E54" s="12"/>
       <c r="F54" s="13"/>
-      <c r="G54" s="13"/>
-      <c r="H54" s="13"/>
-      <c r="I54" s="14"/>
-      <c r="J54" s="15"/>
+      <c r="G54" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H54" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I54" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="J54" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B55" s="11">
@@ -3685,7 +3784,7 @@
         <v>53</v>
       </c>
       <c r="C55" s="12">
-        <v>45698</v>
+        <v>45654</v>
       </c>
       <c r="D55" s="13" t="s">
         <v>10</v>
@@ -3696,13 +3795,13 @@
         <v>14</v>
       </c>
       <c r="H55" s="13" t="s">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="I55" s="14" t="s">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="J55" s="15" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.3">
@@ -3710,60 +3809,28 @@
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="C56" s="12">
-        <v>45698</v>
-      </c>
-      <c r="D56" s="13" t="s">
-        <v>11</v>
-      </c>
+      <c r="C56" s="12"/>
+      <c r="D56" s="13"/>
       <c r="E56" s="12"/>
-      <c r="F56" s="13">
-        <f>$B$55</f>
-        <v>53</v>
-      </c>
-      <c r="G56" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H56" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I56" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="J56" s="15" t="s">
-        <v>107</v>
-      </c>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="15"/>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B57" s="11">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="C57" s="12">
-        <v>45698</v>
-      </c>
-      <c r="D57" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E57" s="12">
-        <v>45698</v>
-      </c>
-      <c r="F57" s="13">
-        <f>$B$56</f>
-        <v>54</v>
-      </c>
-      <c r="G57" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H57" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I57" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="J57" s="15" t="s">
-        <v>108</v>
-      </c>
+      <c r="C57" s="12"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="12"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="14"/>
+      <c r="J57" s="15"/>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B58" s="11">
@@ -3777,21 +3844,18 @@
         <v>10</v>
       </c>
       <c r="E58" s="12"/>
-      <c r="F58" s="13">
-        <f>$B$56</f>
-        <v>54</v>
-      </c>
+      <c r="F58" s="13"/>
       <c r="G58" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H58" s="13" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="I58" s="14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J58" s="15" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.3">
@@ -3803,12 +3867,12 @@
         <v>45698</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E59" s="12"/>
       <c r="F59" s="13">
-        <f>$B$56</f>
-        <v>54</v>
+        <f>$B$58</f>
+        <v>56</v>
       </c>
       <c r="G59" s="13" t="s">
         <v>14</v>
@@ -3820,7 +3884,7 @@
         <v>106</v>
       </c>
       <c r="J59" s="15" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.3">
@@ -3828,42 +3892,89 @@
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="C60" s="12"/>
-      <c r="D60" s="13"/>
-      <c r="E60" s="12"/>
-      <c r="F60" s="13"/>
-      <c r="G60" s="13"/>
-      <c r="H60" s="13"/>
-      <c r="I60" s="14"/>
-      <c r="J60" s="15"/>
+      <c r="C60" s="12">
+        <v>45698</v>
+      </c>
+      <c r="D60" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E60" s="12">
+        <v>45698</v>
+      </c>
+      <c r="F60" s="13">
+        <f>$B$59</f>
+        <v>57</v>
+      </c>
+      <c r="G60" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H60" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I60" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J60" s="15" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B61" s="11">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="C61" s="12"/>
-      <c r="D61" s="13"/>
+      <c r="C61" s="12">
+        <v>45698</v>
+      </c>
+      <c r="D61" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E61" s="12"/>
-      <c r="F61" s="13"/>
-      <c r="G61" s="13"/>
-      <c r="H61" s="13"/>
-      <c r="I61" s="14"/>
-      <c r="J61" s="15"/>
+      <c r="F61" s="13">
+        <f>$B$59</f>
+        <v>57</v>
+      </c>
+      <c r="G61" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H61" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I61" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J61" s="15" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B62" s="11">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="C62" s="12"/>
-      <c r="D62" s="13"/>
+      <c r="C62" s="12">
+        <v>45698</v>
+      </c>
+      <c r="D62" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E62" s="12"/>
-      <c r="F62" s="13"/>
-      <c r="G62" s="13"/>
-      <c r="H62" s="13"/>
-      <c r="I62" s="14"/>
-      <c r="J62" s="15"/>
+      <c r="F62" s="13">
+        <f>$B$59</f>
+        <v>57</v>
+      </c>
+      <c r="G62" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H62" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I62" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J62" s="15" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B63" s="11">
@@ -3991,24 +4102,66 @@
       <c r="I71" s="14"/>
       <c r="J71" s="15"/>
     </row>
-    <row r="72" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="18">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B72" s="11">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="C72" s="19"/>
-      <c r="D72" s="20"/>
-      <c r="E72" s="19"/>
-      <c r="F72" s="20"/>
-      <c r="G72" s="20"/>
-      <c r="H72" s="20"/>
-      <c r="I72" s="21"/>
-      <c r="J72" s="22"/>
+      <c r="C72" s="12"/>
+      <c r="D72" s="13"/>
+      <c r="E72" s="12"/>
+      <c r="F72" s="13"/>
+      <c r="G72" s="13"/>
+      <c r="H72" s="13"/>
+      <c r="I72" s="14"/>
+      <c r="J72" s="15"/>
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B73" s="11">
+        <f t="shared" si="0"/>
+        <v>71</v>
+      </c>
+      <c r="C73" s="12"/>
+      <c r="D73" s="13"/>
+      <c r="E73" s="12"/>
+      <c r="F73" s="13"/>
+      <c r="G73" s="13"/>
+      <c r="H73" s="13"/>
+      <c r="I73" s="14"/>
+      <c r="J73" s="15"/>
+    </row>
+    <row r="74" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B74" s="11">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="C74" s="12"/>
+      <c r="D74" s="13"/>
+      <c r="E74" s="12"/>
+      <c r="F74" s="13"/>
+      <c r="G74" s="13"/>
+      <c r="H74" s="13"/>
+      <c r="I74" s="14"/>
+      <c r="J74" s="15"/>
+    </row>
+    <row r="75" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B75" s="18">
+        <f t="shared" si="0"/>
+        <v>73</v>
+      </c>
+      <c r="C75" s="19"/>
+      <c r="D75" s="20"/>
+      <c r="E75" s="19"/>
+      <c r="F75" s="20"/>
+      <c r="G75" s="20"/>
+      <c r="H75" s="20"/>
+      <c r="I75" s="21"/>
+      <c r="J75" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:J72" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
+  <autoFilter ref="B2:J75" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B3:J72">
+  <conditionalFormatting sqref="B3:J75">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>
@@ -4025,25 +4178,25 @@
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D72</xm:sqref>
+          <xm:sqref>D3:D75</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G72</xm:sqref>
+          <xm:sqref>G3:G75</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B4A065F5-E745-4CD6-9C94-45B6B3E69BD7}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H3:H54 H56:H72</xm:sqref>
+          <xm:sqref>H59:H75 H3:H57</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D6F2F62E-6D63-4E2D-8772-1211A4C3A979}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$10</xm:f>
           </x14:formula1>
-          <xm:sqref>H55</xm:sqref>
+          <xm:sqref>H58</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{917905E2-42A4-4E9F-BC12-228D71640497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD8EB37-1B9D-4FEF-9231-2D7A8123E466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="選択情報" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$77</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="116">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -1572,6 +1572,32 @@
     </rPh>
     <rPh sb="20" eb="22">
       <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示処理情報の登録</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>生成ロジックの改修 : HtmlProductData</t>
+    <rPh sb="0" eb="2">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カイシュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2263,7 +2289,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="B1:K75"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -2461,7 +2487,7 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
-        <f t="shared" ref="B8:B75" si="0">B7+1</f>
+        <f t="shared" ref="A8:B77" si="0">B7+1</f>
         <v>6</v>
       </c>
       <c r="C8" s="12">
@@ -3178,7 +3204,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B33" s="11">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -3206,7 +3232,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B34" s="11">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -3236,7 +3262,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B35" s="11">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -3264,7 +3290,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B36" s="11">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -3295,7 +3321,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B37" s="11">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -3326,7 +3352,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B38" s="11">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -3355,7 +3381,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B39" s="11">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -3386,7 +3412,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B40" s="11">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -3417,7 +3443,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B41" s="11">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -3446,81 +3472,97 @@
         <v>113</v>
       </c>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42" s="11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="B42" s="11">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C42" s="12"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
-      <c r="H42" s="13"/>
-      <c r="I42" s="14"/>
-      <c r="J42" s="15"/>
-    </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C42" s="12">
+        <v>45705</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E42" s="12">
+        <v>45705</v>
+      </c>
+      <c r="F42" s="13">
+        <f>$B$41</f>
+        <v>39</v>
+      </c>
+      <c r="G42" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H42" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I42" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="J42" s="15" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43" s="11">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
       <c r="B43" s="11">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="C43" s="12">
-        <v>45673</v>
+        <v>45705</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E43" s="12">
-        <v>45684</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E43" s="12"/>
       <c r="F43" s="13">
-        <v>24</v>
+        <f>$B$41</f>
+        <v>39</v>
       </c>
       <c r="G43" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I43" s="14" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="J43" s="15" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" s="11">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
       <c r="B44" s="11">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="C44" s="12">
-        <v>45673</v>
-      </c>
-      <c r="D44" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E44" s="12">
-        <v>45680</v>
-      </c>
-      <c r="F44" s="13">
-        <v>29</v>
-      </c>
-      <c r="G44" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H44" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I44" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="J44" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="45" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C44" s="12"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="13"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="14"/>
+      <c r="J44" s="15"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" s="11">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
       <c r="B45" s="11">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -3532,10 +3574,10 @@
         <v>12</v>
       </c>
       <c r="E45" s="12">
-        <v>45678</v>
+        <v>45684</v>
       </c>
       <c r="F45" s="13">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G45" s="13" t="s">
         <v>14</v>
@@ -3544,28 +3586,32 @@
         <v>19</v>
       </c>
       <c r="I45" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="J45" s="17" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+      <c r="J45" s="15" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" s="11">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
       <c r="B46" s="11">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="C46" s="12">
-        <v>45678</v>
+        <v>45673</v>
       </c>
       <c r="D46" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E46" s="12">
-        <v>45678</v>
+        <v>45680</v>
       </c>
       <c r="F46" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G46" s="13" t="s">
         <v>14</v>
@@ -3577,10 +3623,10 @@
         <v>82</v>
       </c>
       <c r="J46" s="17" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B47" s="11">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -3592,7 +3638,7 @@
         <v>12</v>
       </c>
       <c r="E47" s="12">
-        <v>45680</v>
+        <v>45678</v>
       </c>
       <c r="F47" s="13">
         <v>30</v>
@@ -3606,26 +3652,26 @@
       <c r="I47" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="J47" s="15" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J47" s="17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B48" s="11">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="C48" s="12">
-        <v>45679</v>
+        <v>45678</v>
       </c>
       <c r="D48" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E48" s="12">
-        <v>45680</v>
+        <v>45678</v>
       </c>
       <c r="F48" s="13">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G48" s="13" t="s">
         <v>14</v>
@@ -3634,10 +3680,10 @@
         <v>19</v>
       </c>
       <c r="I48" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="J48" s="15" t="s">
-        <v>90</v>
+        <v>82</v>
+      </c>
+      <c r="J48" s="17" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.3">
@@ -3646,13 +3692,13 @@
         <v>47</v>
       </c>
       <c r="C49" s="12">
-        <v>45678</v>
+        <v>45673</v>
       </c>
       <c r="D49" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E49" s="12">
-        <v>45678</v>
+        <v>45680</v>
       </c>
       <c r="F49" s="13">
         <v>30</v>
@@ -3664,10 +3710,10 @@
         <v>19</v>
       </c>
       <c r="I49" s="14" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J49" s="15" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.3">
@@ -3676,28 +3722,28 @@
         <v>48</v>
       </c>
       <c r="C50" s="12">
-        <v>45678</v>
+        <v>45679</v>
       </c>
       <c r="D50" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E50" s="12">
-        <v>45678</v>
+        <v>45680</v>
       </c>
       <c r="F50" s="13">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G50" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H50" s="13" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I50" s="14" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="J50" s="15" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.3">
@@ -3706,186 +3752,191 @@
         <v>49</v>
       </c>
       <c r="C51" s="12">
-        <v>45684</v>
+        <v>45678</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E51" s="12"/>
-      <c r="F51" s="13"/>
+        <v>12</v>
+      </c>
+      <c r="E51" s="12">
+        <v>45678</v>
+      </c>
+      <c r="F51" s="13">
+        <v>30</v>
+      </c>
       <c r="G51" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H51" s="13" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I51" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="J51" s="15"/>
+        <v>87</v>
+      </c>
+      <c r="J51" s="15" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B52" s="11">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="C52" s="12"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="12"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="13"/>
-      <c r="I52" s="14"/>
-      <c r="J52" s="15"/>
+      <c r="C52" s="12">
+        <v>45678</v>
+      </c>
+      <c r="D52" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E52" s="12">
+        <v>45678</v>
+      </c>
+      <c r="F52" s="13">
+        <v>30</v>
+      </c>
+      <c r="G52" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H52" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I52" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="J52" s="15" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B53" s="11">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="C53" s="12"/>
-      <c r="D53" s="13"/>
+      <c r="C53" s="12">
+        <v>45684</v>
+      </c>
+      <c r="D53" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E53" s="12"/>
       <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
-      <c r="H53" s="13"/>
-      <c r="I53" s="14"/>
+      <c r="G53" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H53" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I53" s="14" t="s">
+        <v>91</v>
+      </c>
       <c r="J53" s="15"/>
     </row>
-    <row r="54" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B54" s="11">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="C54" s="12">
-        <v>45645</v>
-      </c>
-      <c r="D54" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C54" s="12"/>
+      <c r="D54" s="13"/>
       <c r="E54" s="12"/>
       <c r="F54" s="13"/>
-      <c r="G54" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H54" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I54" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="J54" s="17" t="s">
-        <v>64</v>
-      </c>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="14"/>
+      <c r="J54" s="15"/>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B55" s="11">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="C55" s="12">
-        <v>45654</v>
-      </c>
-      <c r="D55" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C55" s="12"/>
+      <c r="D55" s="13"/>
       <c r="E55" s="12"/>
       <c r="F55" s="13"/>
-      <c r="G55" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H55" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I55" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="J55" s="15" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="14"/>
+      <c r="J55" s="15"/>
+    </row>
+    <row r="56" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B56" s="11">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="C56" s="12"/>
-      <c r="D56" s="13"/>
+      <c r="C56" s="12">
+        <v>45645</v>
+      </c>
+      <c r="D56" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E56" s="12"/>
       <c r="F56" s="13"/>
-      <c r="G56" s="13"/>
-      <c r="H56" s="13"/>
-      <c r="I56" s="14"/>
-      <c r="J56" s="15"/>
+      <c r="G56" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H56" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I56" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="J56" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B57" s="11">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="C57" s="12"/>
-      <c r="D57" s="13"/>
+      <c r="C57" s="12">
+        <v>45654</v>
+      </c>
+      <c r="D57" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E57" s="12"/>
       <c r="F57" s="13"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="13"/>
-      <c r="I57" s="14"/>
-      <c r="J57" s="15"/>
+      <c r="G57" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H57" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I57" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="J57" s="15" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B58" s="11">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="C58" s="12">
-        <v>45698</v>
-      </c>
-      <c r="D58" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C58" s="12"/>
+      <c r="D58" s="13"/>
       <c r="E58" s="12"/>
       <c r="F58" s="13"/>
-      <c r="G58" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H58" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="I58" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="J58" s="15" t="s">
-        <v>105</v>
-      </c>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="14"/>
+      <c r="J58" s="15"/>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B59" s="11">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="C59" s="12">
-        <v>45698</v>
-      </c>
-      <c r="D59" s="13" t="s">
-        <v>11</v>
-      </c>
+      <c r="C59" s="12"/>
+      <c r="D59" s="13"/>
       <c r="E59" s="12"/>
-      <c r="F59" s="13">
-        <f>$B$58</f>
-        <v>56</v>
-      </c>
-      <c r="G59" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H59" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I59" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="J59" s="15" t="s">
-        <v>107</v>
-      </c>
+      <c r="F59" s="13"/>
+      <c r="G59" s="13"/>
+      <c r="H59" s="13"/>
+      <c r="I59" s="14"/>
+      <c r="J59" s="15"/>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B60" s="11">
@@ -3896,26 +3947,21 @@
         <v>45698</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E60" s="12">
-        <v>45698</v>
-      </c>
-      <c r="F60" s="13">
-        <f>$B$59</f>
-        <v>57</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E60" s="12"/>
+      <c r="F60" s="13"/>
       <c r="G60" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H60" s="13" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="I60" s="14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J60" s="15" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.3">
@@ -3927,12 +3973,12 @@
         <v>45698</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E61" s="12"/>
       <c r="F61" s="13">
-        <f>$B$59</f>
-        <v>57</v>
+        <f>$B$60</f>
+        <v>58</v>
       </c>
       <c r="G61" s="13" t="s">
         <v>14</v>
@@ -3944,7 +3990,7 @@
         <v>106</v>
       </c>
       <c r="J61" s="15" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.3">
@@ -3956,12 +4002,14 @@
         <v>45698</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E62" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E62" s="12">
+        <v>45698</v>
+      </c>
       <c r="F62" s="13">
-        <f>$B$59</f>
-        <v>57</v>
+        <f>$B$61</f>
+        <v>59</v>
       </c>
       <c r="G62" s="13" t="s">
         <v>14</v>
@@ -3973,7 +4021,7 @@
         <v>106</v>
       </c>
       <c r="J62" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.3">
@@ -3981,28 +4029,58 @@
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="C63" s="12"/>
-      <c r="D63" s="13"/>
+      <c r="C63" s="12">
+        <v>45698</v>
+      </c>
+      <c r="D63" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E63" s="12"/>
-      <c r="F63" s="13"/>
-      <c r="G63" s="13"/>
-      <c r="H63" s="13"/>
-      <c r="I63" s="14"/>
-      <c r="J63" s="15"/>
+      <c r="F63" s="13">
+        <f>$B$61</f>
+        <v>59</v>
+      </c>
+      <c r="G63" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H63" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I63" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J63" s="15" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B64" s="11">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="C64" s="12"/>
-      <c r="D64" s="13"/>
+      <c r="C64" s="12">
+        <v>45698</v>
+      </c>
+      <c r="D64" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E64" s="12"/>
-      <c r="F64" s="13"/>
-      <c r="G64" s="13"/>
-      <c r="H64" s="13"/>
-      <c r="I64" s="14"/>
-      <c r="J64" s="15"/>
+      <c r="F64" s="13">
+        <f>$B$61</f>
+        <v>59</v>
+      </c>
+      <c r="G64" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H64" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I64" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J64" s="15" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B65" s="11">
@@ -4144,24 +4222,52 @@
       <c r="I74" s="14"/>
       <c r="J74" s="15"/>
     </row>
-    <row r="75" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="18">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B75" s="11">
         <f t="shared" si="0"/>
         <v>73</v>
       </c>
-      <c r="C75" s="19"/>
-      <c r="D75" s="20"/>
-      <c r="E75" s="19"/>
-      <c r="F75" s="20"/>
-      <c r="G75" s="20"/>
-      <c r="H75" s="20"/>
-      <c r="I75" s="21"/>
-      <c r="J75" s="22"/>
+      <c r="C75" s="12"/>
+      <c r="D75" s="13"/>
+      <c r="E75" s="12"/>
+      <c r="F75" s="13"/>
+      <c r="G75" s="13"/>
+      <c r="H75" s="13"/>
+      <c r="I75" s="14"/>
+      <c r="J75" s="15"/>
+    </row>
+    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B76" s="11">
+        <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+      <c r="C76" s="12"/>
+      <c r="D76" s="13"/>
+      <c r="E76" s="12"/>
+      <c r="F76" s="13"/>
+      <c r="G76" s="13"/>
+      <c r="H76" s="13"/>
+      <c r="I76" s="14"/>
+      <c r="J76" s="15"/>
+    </row>
+    <row r="77" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B77" s="18">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="20"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="20"/>
+      <c r="G77" s="20"/>
+      <c r="H77" s="20"/>
+      <c r="I77" s="21"/>
+      <c r="J77" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:J75" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
+  <autoFilter ref="B2:J77" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B3:J75">
+  <conditionalFormatting sqref="B3:J41 A42:J46 B47:J77">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>
@@ -4178,25 +4284,25 @@
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D75</xm:sqref>
+          <xm:sqref>D3:D77</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G75</xm:sqref>
+          <xm:sqref>G3:G77</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B4A065F5-E745-4CD6-9C94-45B6B3E69BD7}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H59:H75 H3:H57</xm:sqref>
+          <xm:sqref>H61:H77 H3:H59</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D6F2F62E-6D63-4E2D-8772-1211A4C3A979}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$10</xm:f>
           </x14:formula1>
-          <xm:sqref>H58</xm:sqref>
+          <xm:sqref>H60</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD8EB37-1B9D-4FEF-9231-2D7A8123E466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{707685E8-9F63-44F7-9349-09E2D138721F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="選択情報" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$79</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="119">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -1598,6 +1598,66 @@
     </rPh>
     <rPh sb="7" eb="9">
       <t>カイシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>編集画面への遷移 : ProductAction01</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品編集画面</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品の追加・編集を行い、「登録」ボタン押下後、一覧画面へ遷移する。</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>センイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2289,7 +2349,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="A1:K77"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -2487,7 +2547,7 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
-        <f t="shared" ref="A8:B77" si="0">B7+1</f>
+        <f t="shared" ref="A8:B79" si="0">B7+1</f>
         <v>6</v>
       </c>
       <c r="C8" s="12">
@@ -3520,9 +3580,11 @@
         <v>45705</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E43" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E43" s="12">
+        <v>45706</v>
+      </c>
       <c r="F43" s="13">
         <f>$B$41</f>
         <v>39</v>
@@ -3541,94 +3603,87 @@
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" s="11">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
+      <c r="A44" s="11"/>
       <c r="B44" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B44" si="1">B43+1</f>
         <v>42</v>
       </c>
-      <c r="C44" s="12"/>
-      <c r="D44" s="13"/>
+      <c r="C44" s="12">
+        <v>45706</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>11</v>
+      </c>
       <c r="E44" s="12"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="13"/>
-      <c r="H44" s="13"/>
-      <c r="I44" s="14"/>
-      <c r="J44" s="15"/>
+      <c r="F44" s="13">
+        <f>$B$41</f>
+        <v>39</v>
+      </c>
+      <c r="G44" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H44" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I44" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="J44" s="15" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" s="11">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
+      <c r="A45" s="11"/>
       <c r="B45" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B45" si="2">B44+1</f>
         <v>43</v>
       </c>
       <c r="C45" s="12">
-        <v>45673</v>
+        <v>45706</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E45" s="12">
-        <v>45684</v>
-      </c>
-      <c r="F45" s="13">
-        <v>24</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E45" s="12"/>
+      <c r="F45" s="13"/>
       <c r="G45" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I45" s="14" t="s">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="J45" s="15" t="s">
-        <v>79</v>
+        <v>118</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="11">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>A43+1</f>
+        <v>3</v>
       </c>
       <c r="B46" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B46" si="3">B45+1</f>
         <v>44</v>
       </c>
-      <c r="C46" s="12">
-        <v>45673</v>
-      </c>
-      <c r="D46" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E46" s="12">
-        <v>45680</v>
-      </c>
-      <c r="F46" s="13">
-        <v>29</v>
-      </c>
-      <c r="G46" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H46" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I46" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="J46" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C46" s="12"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="14"/>
+      <c r="J46" s="15"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" s="11">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
       <c r="B47" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B47" si="4">B46+1</f>
         <v>45</v>
       </c>
       <c r="C47" s="12">
@@ -3638,10 +3693,10 @@
         <v>12</v>
       </c>
       <c r="E47" s="12">
-        <v>45678</v>
+        <v>45684</v>
       </c>
       <c r="F47" s="13">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G47" s="13" t="s">
         <v>14</v>
@@ -3650,28 +3705,32 @@
         <v>19</v>
       </c>
       <c r="I47" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="J47" s="17" t="s">
-        <v>83</v>
+        <v>78</v>
+      </c>
+      <c r="J47" s="15" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48" s="11">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
       <c r="B48" s="11">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="C48" s="12">
-        <v>45678</v>
+        <v>45673</v>
       </c>
       <c r="D48" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E48" s="12">
-        <v>45678</v>
+        <v>45680</v>
       </c>
       <c r="F48" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G48" s="13" t="s">
         <v>14</v>
@@ -3683,10 +3742,10 @@
         <v>82</v>
       </c>
       <c r="J48" s="17" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B49" s="11">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -3698,7 +3757,7 @@
         <v>12</v>
       </c>
       <c r="E49" s="12">
-        <v>45680</v>
+        <v>45678</v>
       </c>
       <c r="F49" s="13">
         <v>30</v>
@@ -3712,8 +3771,8 @@
       <c r="I49" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="J49" s="15" t="s">
-        <v>81</v>
+      <c r="J49" s="17" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.3">
@@ -3722,16 +3781,16 @@
         <v>48</v>
       </c>
       <c r="C50" s="12">
-        <v>45679</v>
+        <v>45678</v>
       </c>
       <c r="D50" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E50" s="12">
-        <v>45680</v>
+        <v>45678</v>
       </c>
       <c r="F50" s="13">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G50" s="13" t="s">
         <v>14</v>
@@ -3740,10 +3799,10 @@
         <v>19</v>
       </c>
       <c r="I50" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="J50" s="15" t="s">
-        <v>90</v>
+        <v>82</v>
+      </c>
+      <c r="J50" s="17" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.3">
@@ -3752,13 +3811,13 @@
         <v>49</v>
       </c>
       <c r="C51" s="12">
-        <v>45678</v>
+        <v>45673</v>
       </c>
       <c r="D51" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E51" s="12">
-        <v>45678</v>
+        <v>45680</v>
       </c>
       <c r="F51" s="13">
         <v>30</v>
@@ -3770,10 +3829,10 @@
         <v>19</v>
       </c>
       <c r="I51" s="14" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J51" s="15" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.3">
@@ -3782,28 +3841,28 @@
         <v>50</v>
       </c>
       <c r="C52" s="12">
-        <v>45678</v>
+        <v>45679</v>
       </c>
       <c r="D52" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E52" s="12">
-        <v>45678</v>
+        <v>45680</v>
       </c>
       <c r="F52" s="13">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G52" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H52" s="13" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I52" s="14" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="J52" s="15" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.3">
@@ -3812,186 +3871,191 @@
         <v>51</v>
       </c>
       <c r="C53" s="12">
-        <v>45684</v>
+        <v>45678</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E53" s="12"/>
-      <c r="F53" s="13"/>
+        <v>12</v>
+      </c>
+      <c r="E53" s="12">
+        <v>45678</v>
+      </c>
+      <c r="F53" s="13">
+        <v>30</v>
+      </c>
       <c r="G53" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H53" s="13" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I53" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="J53" s="15"/>
+        <v>87</v>
+      </c>
+      <c r="J53" s="15" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B54" s="11">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="C54" s="12"/>
-      <c r="D54" s="13"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="13"/>
-      <c r="H54" s="13"/>
-      <c r="I54" s="14"/>
-      <c r="J54" s="15"/>
+      <c r="C54" s="12">
+        <v>45678</v>
+      </c>
+      <c r="D54" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E54" s="12">
+        <v>45678</v>
+      </c>
+      <c r="F54" s="13">
+        <v>30</v>
+      </c>
+      <c r="G54" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H54" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I54" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="J54" s="15" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B55" s="11">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="C55" s="12"/>
-      <c r="D55" s="13"/>
+      <c r="C55" s="12">
+        <v>45684</v>
+      </c>
+      <c r="D55" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E55" s="12"/>
       <c r="F55" s="13"/>
-      <c r="G55" s="13"/>
-      <c r="H55" s="13"/>
-      <c r="I55" s="14"/>
+      <c r="G55" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H55" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I55" s="14" t="s">
+        <v>91</v>
+      </c>
       <c r="J55" s="15"/>
     </row>
-    <row r="56" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B56" s="11">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="C56" s="12">
-        <v>45645</v>
-      </c>
-      <c r="D56" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C56" s="12"/>
+      <c r="D56" s="13"/>
       <c r="E56" s="12"/>
       <c r="F56" s="13"/>
-      <c r="G56" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H56" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I56" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="J56" s="17" t="s">
-        <v>64</v>
-      </c>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="15"/>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B57" s="11">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="C57" s="12">
-        <v>45654</v>
-      </c>
-      <c r="D57" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C57" s="12"/>
+      <c r="D57" s="13"/>
       <c r="E57" s="12"/>
       <c r="F57" s="13"/>
-      <c r="G57" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H57" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I57" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="J57" s="15" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="14"/>
+      <c r="J57" s="15"/>
+    </row>
+    <row r="58" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B58" s="11">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="C58" s="12"/>
-      <c r="D58" s="13"/>
+      <c r="C58" s="12">
+        <v>45645</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E58" s="12"/>
       <c r="F58" s="13"/>
-      <c r="G58" s="13"/>
-      <c r="H58" s="13"/>
-      <c r="I58" s="14"/>
-      <c r="J58" s="15"/>
+      <c r="G58" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H58" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I58" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="J58" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B59" s="11">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="C59" s="12"/>
-      <c r="D59" s="13"/>
+      <c r="C59" s="12">
+        <v>45654</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E59" s="12"/>
       <c r="F59" s="13"/>
-      <c r="G59" s="13"/>
-      <c r="H59" s="13"/>
-      <c r="I59" s="14"/>
-      <c r="J59" s="15"/>
+      <c r="G59" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H59" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I59" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="J59" s="15" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B60" s="11">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="C60" s="12">
-        <v>45698</v>
-      </c>
-      <c r="D60" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C60" s="12"/>
+      <c r="D60" s="13"/>
       <c r="E60" s="12"/>
       <c r="F60" s="13"/>
-      <c r="G60" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H60" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="I60" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="J60" s="15" t="s">
-        <v>105</v>
-      </c>
+      <c r="G60" s="13"/>
+      <c r="H60" s="13"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="15"/>
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B61" s="11">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="C61" s="12">
-        <v>45698</v>
-      </c>
-      <c r="D61" s="13" t="s">
-        <v>11</v>
-      </c>
+      <c r="C61" s="12"/>
+      <c r="D61" s="13"/>
       <c r="E61" s="12"/>
-      <c r="F61" s="13">
-        <f>$B$60</f>
-        <v>58</v>
-      </c>
-      <c r="G61" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H61" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I61" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="J61" s="15" t="s">
-        <v>107</v>
-      </c>
+      <c r="F61" s="13"/>
+      <c r="G61" s="13"/>
+      <c r="H61" s="13"/>
+      <c r="I61" s="14"/>
+      <c r="J61" s="15"/>
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B62" s="11">
@@ -4002,26 +4066,21 @@
         <v>45698</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E62" s="12">
-        <v>45698</v>
-      </c>
-      <c r="F62" s="13">
-        <f>$B$61</f>
-        <v>59</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E62" s="12"/>
+      <c r="F62" s="13"/>
       <c r="G62" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H62" s="13" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="I62" s="14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J62" s="15" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.3">
@@ -4033,12 +4092,12 @@
         <v>45698</v>
       </c>
       <c r="D63" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E63" s="12"/>
       <c r="F63" s="13">
-        <f>$B$61</f>
-        <v>59</v>
+        <f>$B$62</f>
+        <v>60</v>
       </c>
       <c r="G63" s="13" t="s">
         <v>14</v>
@@ -4050,7 +4109,7 @@
         <v>106</v>
       </c>
       <c r="J63" s="15" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.3">
@@ -4062,12 +4121,14 @@
         <v>45698</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E64" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E64" s="12">
+        <v>45698</v>
+      </c>
       <c r="F64" s="13">
-        <f>$B$61</f>
-        <v>59</v>
+        <f>$B$63</f>
+        <v>61</v>
       </c>
       <c r="G64" s="13" t="s">
         <v>14</v>
@@ -4079,7 +4140,7 @@
         <v>106</v>
       </c>
       <c r="J64" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.3">
@@ -4087,28 +4148,58 @@
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="C65" s="12"/>
-      <c r="D65" s="13"/>
+      <c r="C65" s="12">
+        <v>45698</v>
+      </c>
+      <c r="D65" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E65" s="12"/>
-      <c r="F65" s="13"/>
-      <c r="G65" s="13"/>
-      <c r="H65" s="13"/>
-      <c r="I65" s="14"/>
-      <c r="J65" s="15"/>
+      <c r="F65" s="13">
+        <f>$B$63</f>
+        <v>61</v>
+      </c>
+      <c r="G65" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H65" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I65" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J65" s="15" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B66" s="11">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="C66" s="12"/>
-      <c r="D66" s="13"/>
+      <c r="C66" s="12">
+        <v>45698</v>
+      </c>
+      <c r="D66" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E66" s="12"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="13"/>
-      <c r="H66" s="13"/>
-      <c r="I66" s="14"/>
-      <c r="J66" s="15"/>
+      <c r="F66" s="13">
+        <f>$B$63</f>
+        <v>61</v>
+      </c>
+      <c r="G66" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H66" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I66" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J66" s="15" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B67" s="11">
@@ -4250,24 +4341,52 @@
       <c r="I76" s="14"/>
       <c r="J76" s="15"/>
     </row>
-    <row r="77" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="18">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B77" s="11">
         <f t="shared" si="0"/>
         <v>75</v>
       </c>
-      <c r="C77" s="19"/>
-      <c r="D77" s="20"/>
-      <c r="E77" s="19"/>
-      <c r="F77" s="20"/>
-      <c r="G77" s="20"/>
-      <c r="H77" s="20"/>
-      <c r="I77" s="21"/>
-      <c r="J77" s="22"/>
+      <c r="C77" s="12"/>
+      <c r="D77" s="13"/>
+      <c r="E77" s="12"/>
+      <c r="F77" s="13"/>
+      <c r="G77" s="13"/>
+      <c r="H77" s="13"/>
+      <c r="I77" s="14"/>
+      <c r="J77" s="15"/>
+    </row>
+    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B78" s="11">
+        <f t="shared" si="0"/>
+        <v>76</v>
+      </c>
+      <c r="C78" s="12"/>
+      <c r="D78" s="13"/>
+      <c r="E78" s="12"/>
+      <c r="F78" s="13"/>
+      <c r="G78" s="13"/>
+      <c r="H78" s="13"/>
+      <c r="I78" s="14"/>
+      <c r="J78" s="15"/>
+    </row>
+    <row r="79" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B79" s="18">
+        <f t="shared" si="0"/>
+        <v>77</v>
+      </c>
+      <c r="C79" s="19"/>
+      <c r="D79" s="20"/>
+      <c r="E79" s="19"/>
+      <c r="F79" s="20"/>
+      <c r="G79" s="20"/>
+      <c r="H79" s="20"/>
+      <c r="I79" s="21"/>
+      <c r="J79" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:J77" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
+  <autoFilter ref="B2:J79" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B3:J41 A42:J46 B47:J77">
+  <conditionalFormatting sqref="B3:J41 B49:J79 A42:J48">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>
@@ -4284,25 +4403,25 @@
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D77</xm:sqref>
+          <xm:sqref>D3:D79</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G77</xm:sqref>
+          <xm:sqref>G3:G79</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B4A065F5-E745-4CD6-9C94-45B6B3E69BD7}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H61:H77 H3:H59</xm:sqref>
+          <xm:sqref>H63:H79 H3:H61</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D6F2F62E-6D63-4E2D-8772-1211A4C3A979}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$10</xm:f>
           </x14:formula1>
-          <xm:sqref>H60</xm:sqref>
+          <xm:sqref>H62</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{707685E8-9F63-44F7-9349-09E2D138721F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{841C3F34-842F-4144-83FB-002966906A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="選択情報" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$81</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="120">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -1602,7 +1602,54 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>編集画面への遷移 : ProductAction01</t>
+    <t>商品編集画面</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品の追加・編集を行い、「登録」ボタン押下後、一覧画面へ遷移する。</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>編集画面への遷移 : ProductAction01 : productEntry01の処理を追加</t>
     <rPh sb="0" eb="2">
       <t>ヘンシュウ</t>
     </rPh>
@@ -1612,52 +1659,24 @@
     <rPh sb="6" eb="8">
       <t>センイ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>商品編集画面</t>
-    <rPh sb="0" eb="2">
-      <t>ショウヒン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ヘンシュウ</t>
-    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HTML生成用クラス構築 : HtmlProductEntry01</t>
     <rPh sb="4" eb="6">
-      <t>ガメン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>商品の追加・編集を行い、「登録」ボタン押下後、一覧画面へ遷移する。</t>
-    <rPh sb="0" eb="2">
-      <t>ショウヒン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>ゴ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>センイ</t>
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>コウチク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2349,7 +2368,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="A1:K79"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -2547,7 +2566,7 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
-        <f t="shared" ref="A8:B79" si="0">B7+1</f>
+        <f t="shared" ref="A8:B81" si="0">B7+1</f>
         <v>6</v>
       </c>
       <c r="C8" s="12">
@@ -3629,13 +3648,13 @@
         <v>97</v>
       </c>
       <c r="J44" s="15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="11"/>
       <c r="B45" s="11">
-        <f t="shared" ref="B45" si="2">B44+1</f>
+        <f t="shared" ref="B45:B51" si="2">B44+1</f>
         <v>43</v>
       </c>
       <c r="C45" s="12">
@@ -3653,101 +3672,82 @@
         <v>23</v>
       </c>
       <c r="I45" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="J45" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="J45" s="15" t="s">
-        <v>118</v>
-      </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A46" s="11">
+      <c r="A46" s="11"/>
+      <c r="B46" s="11">
+        <f t="shared" si="2"/>
+        <v>44</v>
+      </c>
+      <c r="C46" s="12">
+        <v>45706</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" s="12"/>
+      <c r="F46" s="13">
+        <f>$B$45</f>
+        <v>43</v>
+      </c>
+      <c r="G46" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H46" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I46" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="J46" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" s="11"/>
+      <c r="B47" s="11">
+        <f t="shared" si="2"/>
+        <v>45</v>
+      </c>
+      <c r="C47" s="12"/>
+      <c r="D47" s="13"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="13"/>
+      <c r="H47" s="13"/>
+      <c r="I47" s="14"/>
+      <c r="J47" s="15"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48" s="11">
         <f>A43+1</f>
         <v>3</v>
       </c>
-      <c r="B46" s="11">
-        <f t="shared" ref="B46" si="3">B45+1</f>
-        <v>44</v>
-      </c>
-      <c r="C46" s="12"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="13"/>
-      <c r="I46" s="14"/>
-      <c r="J46" s="15"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" s="11">
+      <c r="B48" s="11">
+        <f t="shared" si="2"/>
+        <v>46</v>
+      </c>
+      <c r="C48" s="12"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="13"/>
+      <c r="H48" s="13"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="15"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49" s="11">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B47" s="11">
-        <f t="shared" ref="B47" si="4">B46+1</f>
-        <v>45</v>
-      </c>
-      <c r="C47" s="12">
-        <v>45673</v>
-      </c>
-      <c r="D47" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E47" s="12">
-        <v>45684</v>
-      </c>
-      <c r="F47" s="13">
-        <v>24</v>
-      </c>
-      <c r="G47" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H47" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I47" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="J47" s="15" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A48" s="11">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="B48" s="11">
-        <f t="shared" si="0"/>
-        <v>46</v>
-      </c>
-      <c r="C48" s="12">
-        <v>45673</v>
-      </c>
-      <c r="D48" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E48" s="12">
-        <v>45680</v>
-      </c>
-      <c r="F48" s="13">
-        <v>29</v>
-      </c>
-      <c r="G48" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H48" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I48" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="J48" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="49" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B49" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>47</v>
       </c>
       <c r="C49" s="12">
@@ -3757,10 +3757,10 @@
         <v>12</v>
       </c>
       <c r="E49" s="12">
-        <v>45678</v>
+        <v>45684</v>
       </c>
       <c r="F49" s="13">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G49" s="13" t="s">
         <v>14</v>
@@ -3769,28 +3769,32 @@
         <v>19</v>
       </c>
       <c r="I49" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="J49" s="17" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+      <c r="J49" s="15" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50" s="11">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
       <c r="B50" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>48</v>
       </c>
       <c r="C50" s="12">
-        <v>45678</v>
+        <v>45673</v>
       </c>
       <c r="D50" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E50" s="12">
-        <v>45678</v>
+        <v>45680</v>
       </c>
       <c r="F50" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G50" s="13" t="s">
         <v>14</v>
@@ -3802,12 +3806,12 @@
         <v>82</v>
       </c>
       <c r="J50" s="17" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B51" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>49</v>
       </c>
       <c r="C51" s="12">
@@ -3817,7 +3821,7 @@
         <v>12</v>
       </c>
       <c r="E51" s="12">
-        <v>45680</v>
+        <v>45678</v>
       </c>
       <c r="F51" s="13">
         <v>30</v>
@@ -3831,26 +3835,26 @@
       <c r="I51" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="J51" s="15" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J51" s="17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B52" s="11">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="C52" s="12">
-        <v>45679</v>
+        <v>45678</v>
       </c>
       <c r="D52" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E52" s="12">
-        <v>45680</v>
+        <v>45678</v>
       </c>
       <c r="F52" s="13">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G52" s="13" t="s">
         <v>14</v>
@@ -3859,25 +3863,25 @@
         <v>19</v>
       </c>
       <c r="I52" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="J52" s="15" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+      <c r="J52" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B53" s="11">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
       <c r="C53" s="12">
-        <v>45678</v>
+        <v>45673</v>
       </c>
       <c r="D53" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E53" s="12">
-        <v>45678</v>
+        <v>45680</v>
       </c>
       <c r="F53" s="13">
         <v>30</v>
@@ -3889,230 +3893,235 @@
         <v>19</v>
       </c>
       <c r="I53" s="14" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J53" s="15" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B54" s="11">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
       <c r="C54" s="12">
-        <v>45678</v>
+        <v>45679</v>
       </c>
       <c r="D54" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E54" s="12">
+        <v>45680</v>
+      </c>
+      <c r="F54" s="13">
+        <v>33</v>
+      </c>
+      <c r="G54" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H54" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I54" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="J54" s="15" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B55" s="11">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="C55" s="12">
         <v>45678</v>
       </c>
-      <c r="F54" s="13">
+      <c r="D55" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E55" s="12">
+        <v>45678</v>
+      </c>
+      <c r="F55" s="13">
         <v>30</v>
       </c>
-      <c r="G54" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H54" s="13" t="s">
+      <c r="G55" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H55" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I55" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="J55" s="15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B56" s="11">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="C56" s="12">
+        <v>45678</v>
+      </c>
+      <c r="D56" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E56" s="12">
+        <v>45678</v>
+      </c>
+      <c r="F56" s="13">
+        <v>30</v>
+      </c>
+      <c r="G56" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H56" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="I54" s="14" t="s">
+      <c r="I56" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="J54" s="15" t="s">
+      <c r="J56" s="15" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B55" s="11">
-        <f t="shared" si="0"/>
-        <v>53</v>
-      </c>
-      <c r="C55" s="12">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B57" s="11">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="C57" s="12">
         <v>45684</v>
       </c>
-      <c r="D55" s="13" t="s">
+      <c r="D57" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E55" s="12"/>
-      <c r="F55" s="13"/>
-      <c r="G55" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H55" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="I55" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="J55" s="15"/>
-    </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B56" s="11">
-        <f t="shared" si="0"/>
-        <v>54</v>
-      </c>
-      <c r="C56" s="12"/>
-      <c r="D56" s="13"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="13"/>
-      <c r="G56" s="13"/>
-      <c r="H56" s="13"/>
-      <c r="I56" s="14"/>
-      <c r="J56" s="15"/>
-    </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B57" s="11">
-        <f t="shared" si="0"/>
-        <v>55</v>
-      </c>
-      <c r="C57" s="12"/>
-      <c r="D57" s="13"/>
       <c r="E57" s="12"/>
       <c r="F57" s="13"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="13"/>
-      <c r="I57" s="14"/>
+      <c r="G57" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H57" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I57" s="14" t="s">
+        <v>91</v>
+      </c>
       <c r="J57" s="15"/>
     </row>
-    <row r="58" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B58" s="11">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="C58" s="12">
-        <v>45645</v>
-      </c>
-      <c r="D58" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C58" s="12"/>
+      <c r="D58" s="13"/>
       <c r="E58" s="12"/>
       <c r="F58" s="13"/>
-      <c r="G58" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H58" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I58" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="J58" s="17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="14"/>
+      <c r="J58" s="15"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B59" s="11">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="C59" s="12">
-        <v>45654</v>
-      </c>
-      <c r="D59" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C59" s="12"/>
+      <c r="D59" s="13"/>
       <c r="E59" s="12"/>
       <c r="F59" s="13"/>
-      <c r="G59" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H59" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I59" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="J59" s="15" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="G59" s="13"/>
+      <c r="H59" s="13"/>
+      <c r="I59" s="14"/>
+      <c r="J59" s="15"/>
+    </row>
+    <row r="60" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B60" s="11">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="C60" s="12"/>
-      <c r="D60" s="13"/>
+      <c r="C60" s="12">
+        <v>45645</v>
+      </c>
+      <c r="D60" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E60" s="12"/>
       <c r="F60" s="13"/>
-      <c r="G60" s="13"/>
-      <c r="H60" s="13"/>
-      <c r="I60" s="14"/>
-      <c r="J60" s="15"/>
-    </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="G60" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H60" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I60" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="J60" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B61" s="11">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="C61" s="12"/>
-      <c r="D61" s="13"/>
+      <c r="C61" s="12">
+        <v>45654</v>
+      </c>
+      <c r="D61" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E61" s="12"/>
       <c r="F61" s="13"/>
-      <c r="G61" s="13"/>
-      <c r="H61" s="13"/>
-      <c r="I61" s="14"/>
-      <c r="J61" s="15"/>
-    </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="G61" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H61" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I61" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="J61" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B62" s="11">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="C62" s="12">
-        <v>45698</v>
-      </c>
-      <c r="D62" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C62" s="12"/>
+      <c r="D62" s="13"/>
       <c r="E62" s="12"/>
       <c r="F62" s="13"/>
-      <c r="G62" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H62" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="I62" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="J62" s="15" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="G62" s="13"/>
+      <c r="H62" s="13"/>
+      <c r="I62" s="14"/>
+      <c r="J62" s="15"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B63" s="11">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="C63" s="12">
-        <v>45698</v>
-      </c>
-      <c r="D63" s="13" t="s">
-        <v>11</v>
-      </c>
+      <c r="C63" s="12"/>
+      <c r="D63" s="13"/>
       <c r="E63" s="12"/>
-      <c r="F63" s="13">
-        <f>$B$62</f>
-        <v>60</v>
-      </c>
-      <c r="G63" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H63" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I63" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="J63" s="15" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F63" s="13"/>
+      <c r="G63" s="13"/>
+      <c r="H63" s="13"/>
+      <c r="I63" s="14"/>
+      <c r="J63" s="15"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B64" s="11">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -4121,26 +4130,21 @@
         <v>45698</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E64" s="12">
-        <v>45698</v>
-      </c>
-      <c r="F64" s="13">
-        <f>$B$63</f>
-        <v>61</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E64" s="12"/>
+      <c r="F64" s="13"/>
       <c r="G64" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H64" s="13" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="I64" s="14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J64" s="15" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.3">
@@ -4152,12 +4156,12 @@
         <v>45698</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E65" s="12"/>
       <c r="F65" s="13">
-        <f>$B$63</f>
-        <v>61</v>
+        <f>$B$64</f>
+        <v>62</v>
       </c>
       <c r="G65" s="13" t="s">
         <v>14</v>
@@ -4169,7 +4173,7 @@
         <v>106</v>
       </c>
       <c r="J65" s="15" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.3">
@@ -4181,12 +4185,14 @@
         <v>45698</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E66" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E66" s="12">
+        <v>45698</v>
+      </c>
       <c r="F66" s="13">
-        <f>$B$63</f>
-        <v>61</v>
+        <f>$B$65</f>
+        <v>63</v>
       </c>
       <c r="G66" s="13" t="s">
         <v>14</v>
@@ -4198,7 +4204,7 @@
         <v>106</v>
       </c>
       <c r="J66" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.3">
@@ -4206,28 +4212,58 @@
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="C67" s="12"/>
-      <c r="D67" s="13"/>
+      <c r="C67" s="12">
+        <v>45698</v>
+      </c>
+      <c r="D67" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E67" s="12"/>
-      <c r="F67" s="13"/>
-      <c r="G67" s="13"/>
-      <c r="H67" s="13"/>
-      <c r="I67" s="14"/>
-      <c r="J67" s="15"/>
+      <c r="F67" s="13">
+        <f>$B$65</f>
+        <v>63</v>
+      </c>
+      <c r="G67" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H67" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I67" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J67" s="15" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B68" s="11">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="C68" s="12"/>
-      <c r="D68" s="13"/>
+      <c r="C68" s="12">
+        <v>45698</v>
+      </c>
+      <c r="D68" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E68" s="12"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="13"/>
-      <c r="H68" s="13"/>
-      <c r="I68" s="14"/>
-      <c r="J68" s="15"/>
+      <c r="F68" s="13">
+        <f>$B$65</f>
+        <v>63</v>
+      </c>
+      <c r="G68" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H68" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I68" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J68" s="15" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="69" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B69" s="11">
@@ -4369,24 +4405,52 @@
       <c r="I78" s="14"/>
       <c r="J78" s="15"/>
     </row>
-    <row r="79" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B79" s="18">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B79" s="11">
         <f t="shared" si="0"/>
         <v>77</v>
       </c>
-      <c r="C79" s="19"/>
-      <c r="D79" s="20"/>
-      <c r="E79" s="19"/>
-      <c r="F79" s="20"/>
-      <c r="G79" s="20"/>
-      <c r="H79" s="20"/>
-      <c r="I79" s="21"/>
-      <c r="J79" s="22"/>
+      <c r="C79" s="12"/>
+      <c r="D79" s="13"/>
+      <c r="E79" s="12"/>
+      <c r="F79" s="13"/>
+      <c r="G79" s="13"/>
+      <c r="H79" s="13"/>
+      <c r="I79" s="14"/>
+      <c r="J79" s="15"/>
+    </row>
+    <row r="80" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B80" s="11">
+        <f t="shared" si="0"/>
+        <v>78</v>
+      </c>
+      <c r="C80" s="12"/>
+      <c r="D80" s="13"/>
+      <c r="E80" s="12"/>
+      <c r="F80" s="13"/>
+      <c r="G80" s="13"/>
+      <c r="H80" s="13"/>
+      <c r="I80" s="14"/>
+      <c r="J80" s="15"/>
+    </row>
+    <row r="81" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B81" s="18">
+        <f t="shared" si="0"/>
+        <v>79</v>
+      </c>
+      <c r="C81" s="19"/>
+      <c r="D81" s="20"/>
+      <c r="E81" s="19"/>
+      <c r="F81" s="20"/>
+      <c r="G81" s="20"/>
+      <c r="H81" s="20"/>
+      <c r="I81" s="21"/>
+      <c r="J81" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:J79" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
+  <autoFilter ref="B2:J81" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B3:J41 B49:J79 A42:J48">
+  <conditionalFormatting sqref="B3:J41 A42:J45 A46:A50 B46:J81">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>
@@ -4403,25 +4467,25 @@
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D79</xm:sqref>
+          <xm:sqref>D3:D81</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G79</xm:sqref>
+          <xm:sqref>G3:G81</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B4A065F5-E745-4CD6-9C94-45B6B3E69BD7}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H63:H79 H3:H61</xm:sqref>
+          <xm:sqref>H65:H81 H3:H63</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D6F2F62E-6D63-4E2D-8772-1211A4C3A979}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$10</xm:f>
           </x14:formula1>
-          <xm:sqref>H62</xm:sqref>
+          <xm:sqref>H64</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{841C3F34-842F-4144-83FB-002966906A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{835BD660-7517-43E6-9CB1-34DA7B307664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="選択情報" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$83</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="121">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -1677,6 +1677,19 @@
     </rPh>
     <rPh sb="10" eb="12">
       <t>コウチク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遷移ボタン追加 : メインメニューへ戻る</t>
+    <rPh sb="0" eb="2">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>モド</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2368,7 +2381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="A1:K81"/>
+  <dimension ref="A1:K83"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -2566,7 +2579,7 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
-        <f t="shared" ref="A8:B81" si="0">B7+1</f>
+        <f t="shared" ref="A8:B83" si="0">B7+1</f>
         <v>6</v>
       </c>
       <c r="C8" s="12">
@@ -3077,20 +3090,21 @@
         <v>67</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B26" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B26" si="1">B25+1</f>
         <v>24</v>
       </c>
       <c r="C26" s="12">
-        <v>45652</v>
+        <v>45708</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E26" s="12"/>
       <c r="F26" s="13">
-        <v>21</v>
+        <f>$B$24</f>
+        <v>22</v>
       </c>
       <c r="G26" s="13" t="s">
         <v>14</v>
@@ -3099,58 +3113,40 @@
         <v>23</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="J26" s="17" t="s">
-        <v>76</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B27" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B27" si="2">B26+1</f>
         <v>25</v>
       </c>
-      <c r="C27" s="12">
-        <v>45654</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E27" s="12">
-        <v>45665</v>
-      </c>
-      <c r="F27" s="13">
-        <v>24</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="I27" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="J27" s="15" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="C27" s="12"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="17"/>
+    </row>
+    <row r="28" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B28" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B28" si="3">B27+1</f>
         <v>26</v>
       </c>
       <c r="C28" s="12">
-        <v>45666</v>
+        <v>45652</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E28" s="12">
-        <v>45672</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E28" s="12"/>
       <c r="F28" s="13">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G28" s="13" t="s">
         <v>14</v>
@@ -3159,15 +3155,15 @@
         <v>23</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="J28" s="17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B29" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B29" si="4">B28+1</f>
         <v>27</v>
       </c>
       <c r="C29" s="12">
@@ -3177,10 +3173,10 @@
         <v>12</v>
       </c>
       <c r="E29" s="12">
-        <v>45686</v>
+        <v>45665</v>
       </c>
       <c r="F29" s="13">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>14</v>
@@ -3189,28 +3185,28 @@
         <v>23</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J29" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B30" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B30" si="5">B29+1</f>
         <v>28</v>
       </c>
       <c r="C30" s="12">
-        <v>45684</v>
+        <v>45666</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E30" s="12">
-        <v>45686</v>
+        <v>45672</v>
       </c>
       <c r="F30" s="13">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>14</v>
@@ -3219,19 +3215,19 @@
         <v>23</v>
       </c>
       <c r="I30" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="J30" s="15" t="s">
-        <v>93</v>
+        <v>74</v>
+      </c>
+      <c r="J30" s="17" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B31" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B31" si="6">B30+1</f>
         <v>29</v>
       </c>
       <c r="C31" s="12">
-        <v>45684</v>
+        <v>45654</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>12</v>
@@ -3240,7 +3236,7 @@
         <v>45686</v>
       </c>
       <c r="F31" s="13">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>14</v>
@@ -3249,26 +3245,28 @@
         <v>23</v>
       </c>
       <c r="I31" s="14" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="J31" s="15" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B32" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B32" si="7">B31+1</f>
         <v>30</v>
       </c>
       <c r="C32" s="12">
-        <v>45672</v>
+        <v>45684</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E32" s="12">
+        <v>45686</v>
+      </c>
       <c r="F32" s="13">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G32" s="13" t="s">
         <v>14</v>
@@ -3277,26 +3275,28 @@
         <v>23</v>
       </c>
       <c r="I32" s="14" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="J32" s="15" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B33" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B33" si="8">B32+1</f>
         <v>31</v>
       </c>
       <c r="C33" s="12">
+        <v>45684</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33" s="12">
         <v>45686</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E33" s="12"/>
       <c r="F33" s="13">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>14</v>
@@ -3305,28 +3305,26 @@
         <v>23</v>
       </c>
       <c r="I33" s="14" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="J33" s="15" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B34" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B34" si="9">B33+1</f>
         <v>32</v>
       </c>
       <c r="C34" s="12">
-        <v>45686</v>
+        <v>45672</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E34" s="12">
-        <v>45691</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E34" s="12"/>
       <c r="F34" s="13">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G34" s="13" t="s">
         <v>14</v>
@@ -3338,23 +3336,23 @@
         <v>66</v>
       </c>
       <c r="J34" s="15" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B35" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B35" si="10">B34+1</f>
         <v>33</v>
       </c>
       <c r="C35" s="12">
-        <v>45691</v>
+        <v>45686</v>
       </c>
       <c r="D35" s="13" t="s">
         <v>11</v>
       </c>
       <c r="E35" s="12"/>
       <c r="F35" s="13">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G35" s="13" t="s">
         <v>14</v>
@@ -3363,19 +3361,19 @@
         <v>23</v>
       </c>
       <c r="I35" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="J35" s="17" t="s">
-        <v>98</v>
+        <v>66</v>
+      </c>
+      <c r="J35" s="15" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B36" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B36" si="11">B35+1</f>
         <v>34</v>
       </c>
       <c r="C36" s="12">
-        <v>45691</v>
+        <v>45686</v>
       </c>
       <c r="D36" s="13" t="s">
         <v>12</v>
@@ -3384,8 +3382,7 @@
         <v>45691</v>
       </c>
       <c r="F36" s="13">
-        <f>$B$35</f>
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G36" s="13" t="s">
         <v>14</v>
@@ -3394,29 +3391,26 @@
         <v>23</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="J36" s="15" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B37" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B37" si="12">B36+1</f>
         <v>35</v>
       </c>
       <c r="C37" s="12">
         <v>45691</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E37" s="12">
-        <v>45692</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E37" s="12"/>
       <c r="F37" s="13">
-        <f>$B$35</f>
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G37" s="13" t="s">
         <v>14</v>
@@ -3427,25 +3421,27 @@
       <c r="I37" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="J37" s="15" t="s">
-        <v>100</v>
+      <c r="J37" s="17" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B38" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B38" si="13">B37+1</f>
         <v>36</v>
       </c>
       <c r="C38" s="12">
         <v>45691</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E38" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E38" s="12">
+        <v>45691</v>
+      </c>
       <c r="F38" s="13">
-        <f>$B$35</f>
-        <v>33</v>
+        <f>$B$37</f>
+        <v>35</v>
       </c>
       <c r="G38" s="13" t="s">
         <v>14</v>
@@ -3457,26 +3453,26 @@
         <v>97</v>
       </c>
       <c r="J38" s="15" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B39" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B39" si="14">B38+1</f>
         <v>37</v>
       </c>
       <c r="C39" s="12">
-        <v>45700</v>
+        <v>45691</v>
       </c>
       <c r="D39" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E39" s="12">
-        <v>45700</v>
+        <v>45692</v>
       </c>
       <c r="F39" s="13">
-        <f>$B$38</f>
-        <v>36</v>
+        <f>$B$37</f>
+        <v>35</v>
       </c>
       <c r="G39" s="13" t="s">
         <v>14</v>
@@ -3488,26 +3484,24 @@
         <v>97</v>
       </c>
       <c r="J39" s="15" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B40" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B40" si="15">B39+1</f>
         <v>38</v>
       </c>
       <c r="C40" s="12">
-        <v>45701</v>
+        <v>45691</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E40" s="12">
-        <v>45701</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E40" s="12"/>
       <c r="F40" s="13">
-        <f>$B$38</f>
-        <v>36</v>
+        <f>$B$37</f>
+        <v>35</v>
       </c>
       <c r="G40" s="13" t="s">
         <v>14</v>
@@ -3519,24 +3513,26 @@
         <v>97</v>
       </c>
       <c r="J40" s="15" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B41" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B41" si="16">B40+1</f>
         <v>39</v>
       </c>
       <c r="C41" s="12">
-        <v>45701</v>
+        <v>45700</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E41" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E41" s="12">
+        <v>45700</v>
+      </c>
       <c r="F41" s="13">
-        <f>$B$38</f>
-        <v>36</v>
+        <f>$B$40</f>
+        <v>38</v>
       </c>
       <c r="G41" s="13" t="s">
         <v>14</v>
@@ -3548,30 +3544,26 @@
         <v>97</v>
       </c>
       <c r="J41" s="15" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="11">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="B42" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B42" si="17">B41+1</f>
         <v>40</v>
       </c>
       <c r="C42" s="12">
-        <v>45705</v>
+        <v>45701</v>
       </c>
       <c r="D42" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E42" s="12">
-        <v>45705</v>
+        <v>45701</v>
       </c>
       <c r="F42" s="13">
-        <f>$B$41</f>
-        <v>39</v>
+        <f>$B$40</f>
+        <v>38</v>
       </c>
       <c r="G42" s="13" t="s">
         <v>14</v>
@@ -3583,30 +3575,24 @@
         <v>97</v>
       </c>
       <c r="J42" s="15" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" s="11">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
       <c r="B43" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B43" si="18">B42+1</f>
         <v>41</v>
       </c>
       <c r="C43" s="12">
-        <v>45705</v>
+        <v>45701</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E43" s="12">
-        <v>45706</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E43" s="12"/>
       <c r="F43" s="13">
-        <f>$B$41</f>
-        <v>39</v>
+        <f>$B$40</f>
+        <v>38</v>
       </c>
       <c r="G43" s="13" t="s">
         <v>14</v>
@@ -3618,25 +3604,30 @@
         <v>97</v>
       </c>
       <c r="J43" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" s="11"/>
+      <c r="A44" s="11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="B44" s="11">
-        <f t="shared" ref="B44" si="1">B43+1</f>
+        <f t="shared" ref="B44" si="19">B43+1</f>
         <v>42</v>
       </c>
       <c r="C44" s="12">
-        <v>45706</v>
+        <v>45705</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E44" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E44" s="12">
+        <v>45705</v>
+      </c>
       <c r="F44" s="13">
-        <f>$B$41</f>
-        <v>39</v>
+        <f>$B$43</f>
+        <v>41</v>
       </c>
       <c r="G44" s="13" t="s">
         <v>14</v>
@@ -3648,23 +3639,31 @@
         <v>97</v>
       </c>
       <c r="J44" s="15" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" s="11"/>
+      <c r="A45" s="11">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
       <c r="B45" s="11">
-        <f t="shared" ref="B45:B51" si="2">B44+1</f>
+        <f t="shared" ref="B45" si="20">B44+1</f>
         <v>43</v>
       </c>
       <c r="C45" s="12">
+        <v>45705</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45" s="12">
         <v>45706</v>
       </c>
-      <c r="D45" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" s="12"/>
-      <c r="F45" s="13"/>
+      <c r="F45" s="13">
+        <f>$B$43</f>
+        <v>41</v>
+      </c>
       <c r="G45" s="13" t="s">
         <v>14</v>
       </c>
@@ -3672,28 +3671,28 @@
         <v>23</v>
       </c>
       <c r="I45" s="14" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="J45" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="11"/>
       <c r="B46" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="B46" si="21">B45+1</f>
         <v>44</v>
       </c>
       <c r="C46" s="12">
         <v>45706</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E46" s="12"/>
       <c r="F46" s="13">
-        <f>$B$45</f>
-        <v>43</v>
+        <f>$B$43</f>
+        <v>41</v>
       </c>
       <c r="G46" s="13" t="s">
         <v>14</v>
@@ -3702,116 +3701,109 @@
         <v>23</v>
       </c>
       <c r="I46" s="14" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="J46" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="11"/>
       <c r="B47" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="B47:B53" si="22">B46+1</f>
         <v>45</v>
       </c>
-      <c r="C47" s="12"/>
-      <c r="D47" s="13"/>
+      <c r="C47" s="12">
+        <v>45706</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E47" s="12"/>
       <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="13"/>
-      <c r="I47" s="14"/>
-      <c r="J47" s="15"/>
+      <c r="G47" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H47" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I47" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="J47" s="15" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A48" s="11">
-        <f>A43+1</f>
-        <v>3</v>
-      </c>
+      <c r="A48" s="11"/>
       <c r="B48" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="22"/>
         <v>46</v>
       </c>
-      <c r="C48" s="12"/>
-      <c r="D48" s="13"/>
+      <c r="C48" s="12">
+        <v>45706</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E48" s="12"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
-      <c r="I48" s="14"/>
-      <c r="J48" s="15"/>
+      <c r="F48" s="13">
+        <f>$B$47</f>
+        <v>45</v>
+      </c>
+      <c r="G48" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H48" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I48" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="J48" s="15" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A49" s="11">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
+      <c r="A49" s="11"/>
       <c r="B49" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="22"/>
         <v>47</v>
       </c>
-      <c r="C49" s="12">
-        <v>45673</v>
-      </c>
-      <c r="D49" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E49" s="12">
-        <v>45684</v>
-      </c>
-      <c r="F49" s="13">
-        <v>24</v>
-      </c>
-      <c r="G49" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H49" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I49" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="J49" s="15" t="s">
-        <v>79</v>
-      </c>
+      <c r="C49" s="12"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="13"/>
+      <c r="H49" s="13"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="15"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="11">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>A45+1</f>
+        <v>3</v>
       </c>
       <c r="B50" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="22"/>
         <v>48</v>
       </c>
-      <c r="C50" s="12">
-        <v>45673</v>
-      </c>
-      <c r="D50" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E50" s="12">
-        <v>45680</v>
-      </c>
-      <c r="F50" s="13">
-        <v>29</v>
-      </c>
-      <c r="G50" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H50" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I50" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="J50" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C50" s="12"/>
+      <c r="D50" s="13"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="13"/>
+      <c r="H50" s="13"/>
+      <c r="I50" s="14"/>
+      <c r="J50" s="15"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" s="11">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
       <c r="B51" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="22"/>
         <v>49</v>
       </c>
       <c r="C51" s="12">
@@ -3821,10 +3813,10 @@
         <v>12</v>
       </c>
       <c r="E51" s="12">
-        <v>45678</v>
+        <v>45684</v>
       </c>
       <c r="F51" s="13">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G51" s="13" t="s">
         <v>14</v>
@@ -3833,28 +3825,32 @@
         <v>19</v>
       </c>
       <c r="I51" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="J51" s="17" t="s">
-        <v>83</v>
+        <v>78</v>
+      </c>
+      <c r="J51" s="15" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52" s="11">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
       <c r="B52" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="22"/>
         <v>50</v>
       </c>
       <c r="C52" s="12">
-        <v>45678</v>
+        <v>45673</v>
       </c>
       <c r="D52" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E52" s="12">
-        <v>45678</v>
+        <v>45680</v>
       </c>
       <c r="F52" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G52" s="13" t="s">
         <v>14</v>
@@ -3866,12 +3862,12 @@
         <v>82</v>
       </c>
       <c r="J52" s="17" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B53" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="22"/>
         <v>51</v>
       </c>
       <c r="C53" s="12">
@@ -3881,7 +3877,7 @@
         <v>12</v>
       </c>
       <c r="E53" s="12">
-        <v>45680</v>
+        <v>45678</v>
       </c>
       <c r="F53" s="13">
         <v>30</v>
@@ -3895,8 +3891,8 @@
       <c r="I53" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="J53" s="15" t="s">
-        <v>81</v>
+      <c r="J53" s="17" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
@@ -3905,16 +3901,16 @@
         <v>52</v>
       </c>
       <c r="C54" s="12">
-        <v>45679</v>
+        <v>45678</v>
       </c>
       <c r="D54" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E54" s="12">
-        <v>45680</v>
+        <v>45678</v>
       </c>
       <c r="F54" s="13">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G54" s="13" t="s">
         <v>14</v>
@@ -3923,10 +3919,10 @@
         <v>19</v>
       </c>
       <c r="I54" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="J54" s="15" t="s">
-        <v>90</v>
+        <v>82</v>
+      </c>
+      <c r="J54" s="17" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
@@ -3935,13 +3931,13 @@
         <v>53</v>
       </c>
       <c r="C55" s="12">
-        <v>45678</v>
+        <v>45673</v>
       </c>
       <c r="D55" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E55" s="12">
-        <v>45678</v>
+        <v>45680</v>
       </c>
       <c r="F55" s="13">
         <v>30</v>
@@ -3953,10 +3949,10 @@
         <v>19</v>
       </c>
       <c r="I55" s="14" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J55" s="15" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
@@ -3965,28 +3961,28 @@
         <v>54</v>
       </c>
       <c r="C56" s="12">
-        <v>45678</v>
+        <v>45679</v>
       </c>
       <c r="D56" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E56" s="12">
-        <v>45678</v>
+        <v>45680</v>
       </c>
       <c r="F56" s="13">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G56" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H56" s="13" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I56" s="14" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="J56" s="15" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
@@ -3995,186 +3991,191 @@
         <v>55</v>
       </c>
       <c r="C57" s="12">
-        <v>45684</v>
+        <v>45678</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E57" s="12"/>
-      <c r="F57" s="13"/>
+        <v>12</v>
+      </c>
+      <c r="E57" s="12">
+        <v>45678</v>
+      </c>
+      <c r="F57" s="13">
+        <v>30</v>
+      </c>
       <c r="G57" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H57" s="13" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I57" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="J57" s="15"/>
+        <v>87</v>
+      </c>
+      <c r="J57" s="15" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B58" s="11">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="C58" s="12"/>
-      <c r="D58" s="13"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="13"/>
-      <c r="H58" s="13"/>
-      <c r="I58" s="14"/>
-      <c r="J58" s="15"/>
+      <c r="C58" s="12">
+        <v>45678</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" s="12">
+        <v>45678</v>
+      </c>
+      <c r="F58" s="13">
+        <v>30</v>
+      </c>
+      <c r="G58" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H58" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I58" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="J58" s="15" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B59" s="11">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="C59" s="12"/>
-      <c r="D59" s="13"/>
+      <c r="C59" s="12">
+        <v>45684</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E59" s="12"/>
       <c r="F59" s="13"/>
-      <c r="G59" s="13"/>
-      <c r="H59" s="13"/>
-      <c r="I59" s="14"/>
+      <c r="G59" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H59" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I59" s="14" t="s">
+        <v>91</v>
+      </c>
       <c r="J59" s="15"/>
     </row>
-    <row r="60" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B60" s="11">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="C60" s="12">
-        <v>45645</v>
-      </c>
-      <c r="D60" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C60" s="12"/>
+      <c r="D60" s="13"/>
       <c r="E60" s="12"/>
       <c r="F60" s="13"/>
-      <c r="G60" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H60" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I60" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="J60" s="17" t="s">
-        <v>64</v>
-      </c>
+      <c r="G60" s="13"/>
+      <c r="H60" s="13"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="15"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B61" s="11">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="C61" s="12">
-        <v>45654</v>
-      </c>
-      <c r="D61" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C61" s="12"/>
+      <c r="D61" s="13"/>
       <c r="E61" s="12"/>
       <c r="F61" s="13"/>
-      <c r="G61" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H61" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I61" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="J61" s="15" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G61" s="13"/>
+      <c r="H61" s="13"/>
+      <c r="I61" s="14"/>
+      <c r="J61" s="15"/>
+    </row>
+    <row r="62" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B62" s="11">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="C62" s="12"/>
-      <c r="D62" s="13"/>
+      <c r="C62" s="12">
+        <v>45645</v>
+      </c>
+      <c r="D62" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E62" s="12"/>
       <c r="F62" s="13"/>
-      <c r="G62" s="13"/>
-      <c r="H62" s="13"/>
-      <c r="I62" s="14"/>
-      <c r="J62" s="15"/>
+      <c r="G62" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H62" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I62" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="J62" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B63" s="11">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="C63" s="12"/>
-      <c r="D63" s="13"/>
+      <c r="C63" s="12">
+        <v>45654</v>
+      </c>
+      <c r="D63" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E63" s="12"/>
       <c r="F63" s="13"/>
-      <c r="G63" s="13"/>
-      <c r="H63" s="13"/>
-      <c r="I63" s="14"/>
-      <c r="J63" s="15"/>
+      <c r="G63" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H63" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I63" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="J63" s="15" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B64" s="11">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="C64" s="12">
-        <v>45698</v>
-      </c>
-      <c r="D64" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C64" s="12"/>
+      <c r="D64" s="13"/>
       <c r="E64" s="12"/>
       <c r="F64" s="13"/>
-      <c r="G64" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H64" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="I64" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="J64" s="15" t="s">
-        <v>105</v>
-      </c>
+      <c r="G64" s="13"/>
+      <c r="H64" s="13"/>
+      <c r="I64" s="14"/>
+      <c r="J64" s="15"/>
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B65" s="11">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="C65" s="12">
-        <v>45698</v>
-      </c>
-      <c r="D65" s="13" t="s">
-        <v>11</v>
-      </c>
+      <c r="C65" s="12"/>
+      <c r="D65" s="13"/>
       <c r="E65" s="12"/>
-      <c r="F65" s="13">
-        <f>$B$64</f>
-        <v>62</v>
-      </c>
-      <c r="G65" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H65" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I65" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="J65" s="15" t="s">
-        <v>107</v>
-      </c>
+      <c r="F65" s="13"/>
+      <c r="G65" s="13"/>
+      <c r="H65" s="13"/>
+      <c r="I65" s="14"/>
+      <c r="J65" s="15"/>
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B66" s="11">
@@ -4185,26 +4186,21 @@
         <v>45698</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E66" s="12">
-        <v>45698</v>
-      </c>
-      <c r="F66" s="13">
-        <f>$B$65</f>
-        <v>63</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E66" s="12"/>
+      <c r="F66" s="13"/>
       <c r="G66" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H66" s="13" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="I66" s="14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J66" s="15" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.3">
@@ -4216,12 +4212,12 @@
         <v>45698</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E67" s="12"/>
       <c r="F67" s="13">
-        <f>$B$65</f>
-        <v>63</v>
+        <f>$B$66</f>
+        <v>64</v>
       </c>
       <c r="G67" s="13" t="s">
         <v>14</v>
@@ -4233,7 +4229,7 @@
         <v>106</v>
       </c>
       <c r="J67" s="15" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.3">
@@ -4245,12 +4241,14 @@
         <v>45698</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E68" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E68" s="12">
+        <v>45698</v>
+      </c>
       <c r="F68" s="13">
-        <f>$B$65</f>
-        <v>63</v>
+        <f>$B$67</f>
+        <v>65</v>
       </c>
       <c r="G68" s="13" t="s">
         <v>14</v>
@@ -4262,7 +4260,7 @@
         <v>106</v>
       </c>
       <c r="J68" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="69" spans="2:10" x14ac:dyDescent="0.3">
@@ -4270,28 +4268,58 @@
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
-      <c r="C69" s="12"/>
-      <c r="D69" s="13"/>
+      <c r="C69" s="12">
+        <v>45698</v>
+      </c>
+      <c r="D69" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E69" s="12"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="13"/>
-      <c r="H69" s="13"/>
-      <c r="I69" s="14"/>
-      <c r="J69" s="15"/>
+      <c r="F69" s="13">
+        <f>$B$67</f>
+        <v>65</v>
+      </c>
+      <c r="G69" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H69" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I69" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J69" s="15" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="70" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B70" s="11">
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
-      <c r="C70" s="12"/>
-      <c r="D70" s="13"/>
+      <c r="C70" s="12">
+        <v>45698</v>
+      </c>
+      <c r="D70" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E70" s="12"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="13"/>
-      <c r="H70" s="13"/>
-      <c r="I70" s="14"/>
-      <c r="J70" s="15"/>
+      <c r="F70" s="13">
+        <f>$B$67</f>
+        <v>65</v>
+      </c>
+      <c r="G70" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H70" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I70" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J70" s="15" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="71" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B71" s="11">
@@ -4433,24 +4461,52 @@
       <c r="I80" s="14"/>
       <c r="J80" s="15"/>
     </row>
-    <row r="81" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B81" s="18">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B81" s="11">
         <f t="shared" si="0"/>
         <v>79</v>
       </c>
-      <c r="C81" s="19"/>
-      <c r="D81" s="20"/>
-      <c r="E81" s="19"/>
-      <c r="F81" s="20"/>
-      <c r="G81" s="20"/>
-      <c r="H81" s="20"/>
-      <c r="I81" s="21"/>
-      <c r="J81" s="22"/>
+      <c r="C81" s="12"/>
+      <c r="D81" s="13"/>
+      <c r="E81" s="12"/>
+      <c r="F81" s="13"/>
+      <c r="G81" s="13"/>
+      <c r="H81" s="13"/>
+      <c r="I81" s="14"/>
+      <c r="J81" s="15"/>
+    </row>
+    <row r="82" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B82" s="11">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="C82" s="12"/>
+      <c r="D82" s="13"/>
+      <c r="E82" s="12"/>
+      <c r="F82" s="13"/>
+      <c r="G82" s="13"/>
+      <c r="H82" s="13"/>
+      <c r="I82" s="14"/>
+      <c r="J82" s="15"/>
+    </row>
+    <row r="83" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B83" s="18">
+        <f t="shared" si="0"/>
+        <v>81</v>
+      </c>
+      <c r="C83" s="19"/>
+      <c r="D83" s="20"/>
+      <c r="E83" s="19"/>
+      <c r="F83" s="20"/>
+      <c r="G83" s="20"/>
+      <c r="H83" s="20"/>
+      <c r="I83" s="21"/>
+      <c r="J83" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:J81" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
+  <autoFilter ref="B2:J83" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B3:J41 A42:J45 A46:A50 B46:J81">
+  <conditionalFormatting sqref="A47:J47 A48:A52 B48:J83 A44:A46 B3:J46">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>
@@ -4467,25 +4523,25 @@
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D81</xm:sqref>
+          <xm:sqref>D3:D83</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G81</xm:sqref>
+          <xm:sqref>G3:G83</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B4A065F5-E745-4CD6-9C94-45B6B3E69BD7}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H65:H81 H3:H63</xm:sqref>
+          <xm:sqref>H67:H83 H3:H65</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D6F2F62E-6D63-4E2D-8772-1211A4C3A979}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$10</xm:f>
           </x14:formula1>
-          <xm:sqref>H64</xm:sqref>
+          <xm:sqref>H66</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{835BD660-7517-43E6-9CB1-34DA7B307664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38C664A6-EA44-425C-A408-FF575C218A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="選択情報" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$82</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2381,7 +2381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="A1:K83"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -2579,7 +2579,7 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
-        <f t="shared" ref="A8:B83" si="0">B7+1</f>
+        <f t="shared" ref="A8:B82" si="0">B7+1</f>
         <v>6</v>
       </c>
       <c r="C8" s="12">
@@ -3092,16 +3092,18 @@
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B26" s="11">
-        <f t="shared" ref="B26" si="1">B25+1</f>
+        <f t="shared" ref="B26:B27" si="1">B25+1</f>
         <v>24</v>
       </c>
       <c r="C26" s="12">
         <v>45708</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E26" s="12">
+        <v>45709</v>
+      </c>
       <c r="F26" s="13">
         <f>$B$24</f>
         <v>22</v>
@@ -3119,34 +3121,52 @@
         <v>120</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B27" s="11">
-        <f t="shared" ref="B27" si="2">B26+1</f>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="C27" s="12"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="17"/>
-    </row>
-    <row r="28" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C27" s="12">
+        <v>45652</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" s="12">
+        <v>45713</v>
+      </c>
+      <c r="F27" s="13">
+        <v>21</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I27" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="J27" s="17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B28" s="11">
-        <f t="shared" ref="B28" si="3">B27+1</f>
+        <f t="shared" ref="B28" si="2">B27+1</f>
         <v>26</v>
       </c>
       <c r="C28" s="12">
-        <v>45652</v>
+        <v>45654</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E28" s="12">
+        <v>45665</v>
+      </c>
       <c r="F28" s="13">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G28" s="13" t="s">
         <v>14</v>
@@ -3155,28 +3175,28 @@
         <v>23</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="J28" s="17" t="s">
-        <v>76</v>
+        <v>68</v>
+      </c>
+      <c r="J28" s="15" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B29" s="11">
-        <f t="shared" ref="B29" si="4">B28+1</f>
+        <f t="shared" ref="B29" si="3">B28+1</f>
         <v>27</v>
       </c>
       <c r="C29" s="12">
-        <v>45654</v>
+        <v>45666</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E29" s="12">
-        <v>45665</v>
+        <v>45672</v>
       </c>
       <c r="F29" s="13">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>14</v>
@@ -3185,28 +3205,28 @@
         <v>23</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="J29" s="15" t="s">
-        <v>72</v>
+        <v>74</v>
+      </c>
+      <c r="J29" s="17" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B30" s="11">
-        <f t="shared" ref="B30" si="5">B29+1</f>
+        <f t="shared" ref="B30" si="4">B29+1</f>
         <v>28</v>
       </c>
       <c r="C30" s="12">
-        <v>45666</v>
+        <v>45654</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E30" s="12">
-        <v>45672</v>
+        <v>45686</v>
       </c>
       <c r="F30" s="13">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>14</v>
@@ -3215,19 +3235,19 @@
         <v>23</v>
       </c>
       <c r="I30" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="J30" s="17" t="s">
-        <v>75</v>
+        <v>69</v>
+      </c>
+      <c r="J30" s="15" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B31" s="11">
-        <f t="shared" ref="B31" si="6">B30+1</f>
+        <f t="shared" ref="B31" si="5">B30+1</f>
         <v>29</v>
       </c>
       <c r="C31" s="12">
-        <v>45654</v>
+        <v>45684</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>12</v>
@@ -3236,7 +3256,7 @@
         <v>45686</v>
       </c>
       <c r="F31" s="13">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>14</v>
@@ -3245,15 +3265,15 @@
         <v>23</v>
       </c>
       <c r="I31" s="14" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="J31" s="15" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B32" s="11">
-        <f t="shared" ref="B32" si="7">B31+1</f>
+        <f t="shared" ref="B32" si="6">B31+1</f>
         <v>30</v>
       </c>
       <c r="C32" s="12">
@@ -3278,25 +3298,25 @@
         <v>92</v>
       </c>
       <c r="J32" s="15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B33" s="11">
-        <f t="shared" ref="B33" si="8">B32+1</f>
+        <f t="shared" ref="B33" si="7">B32+1</f>
         <v>31</v>
       </c>
       <c r="C33" s="12">
-        <v>45684</v>
+        <v>45672</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E33" s="12">
-        <v>45686</v>
+        <v>45713</v>
       </c>
       <c r="F33" s="13">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>14</v>
@@ -3305,26 +3325,28 @@
         <v>23</v>
       </c>
       <c r="I33" s="14" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="J33" s="15" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B34" s="11">
-        <f t="shared" ref="B34" si="9">B33+1</f>
+        <f t="shared" ref="B34" si="8">B33+1</f>
         <v>32</v>
       </c>
       <c r="C34" s="12">
-        <v>45672</v>
+        <v>45686</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E34" s="12">
+        <v>45709</v>
+      </c>
       <c r="F34" s="13">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G34" s="13" t="s">
         <v>14</v>
@@ -3336,21 +3358,23 @@
         <v>66</v>
       </c>
       <c r="J34" s="15" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B35" s="11">
-        <f t="shared" ref="B35" si="10">B34+1</f>
+        <f t="shared" ref="B35" si="9">B34+1</f>
         <v>33</v>
       </c>
       <c r="C35" s="12">
         <v>45686</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E35" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E35" s="12">
+        <v>45691</v>
+      </c>
       <c r="F35" s="13">
         <v>30</v>
       </c>
@@ -3364,25 +3388,25 @@
         <v>66</v>
       </c>
       <c r="J35" s="15" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B36" s="11">
-        <f t="shared" ref="B36" si="11">B35+1</f>
+        <f t="shared" ref="B36" si="10">B35+1</f>
         <v>34</v>
       </c>
       <c r="C36" s="12">
-        <v>45686</v>
+        <v>45691</v>
       </c>
       <c r="D36" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E36" s="12">
-        <v>45691</v>
+        <v>45709</v>
       </c>
       <c r="F36" s="13">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G36" s="13" t="s">
         <v>14</v>
@@ -3391,26 +3415,29 @@
         <v>23</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="J36" s="15" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+      <c r="J36" s="17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B37" s="11">
-        <f t="shared" ref="B37" si="12">B36+1</f>
+        <f t="shared" ref="B37" si="11">B36+1</f>
         <v>35</v>
       </c>
       <c r="C37" s="12">
         <v>45691</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E37" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E37" s="12">
+        <v>45691</v>
+      </c>
       <c r="F37" s="13">
-        <v>31</v>
+        <f>$B$36</f>
+        <v>34</v>
       </c>
       <c r="G37" s="13" t="s">
         <v>14</v>
@@ -3421,13 +3448,13 @@
       <c r="I37" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="J37" s="17" t="s">
-        <v>98</v>
+      <c r="J37" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B38" s="11">
-        <f t="shared" ref="B38" si="13">B37+1</f>
+        <f t="shared" ref="B38" si="12">B37+1</f>
         <v>36</v>
       </c>
       <c r="C38" s="12">
@@ -3437,11 +3464,11 @@
         <v>12</v>
       </c>
       <c r="E38" s="12">
-        <v>45691</v>
+        <v>45692</v>
       </c>
       <c r="F38" s="13">
-        <f>$B$37</f>
-        <v>35</v>
+        <f>$B$36</f>
+        <v>34</v>
       </c>
       <c r="G38" s="13" t="s">
         <v>14</v>
@@ -3453,12 +3480,12 @@
         <v>97</v>
       </c>
       <c r="J38" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B39" s="11">
-        <f t="shared" ref="B39" si="14">B38+1</f>
+        <f t="shared" ref="B39" si="13">B38+1</f>
         <v>37</v>
       </c>
       <c r="C39" s="12">
@@ -3468,11 +3495,11 @@
         <v>12</v>
       </c>
       <c r="E39" s="12">
-        <v>45692</v>
+        <v>45713</v>
       </c>
       <c r="F39" s="13">
-        <f>$B$37</f>
-        <v>35</v>
+        <f>$B$36</f>
+        <v>34</v>
       </c>
       <c r="G39" s="13" t="s">
         <v>14</v>
@@ -3484,24 +3511,26 @@
         <v>97</v>
       </c>
       <c r="J39" s="15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B40" s="11">
-        <f t="shared" ref="B40" si="15">B39+1</f>
+        <f t="shared" ref="B40" si="14">B39+1</f>
         <v>38</v>
       </c>
       <c r="C40" s="12">
-        <v>45691</v>
+        <v>45700</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E40" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E40" s="12">
+        <v>45700</v>
+      </c>
       <c r="F40" s="13">
-        <f>$B$37</f>
-        <v>35</v>
+        <f>$B$39</f>
+        <v>37</v>
       </c>
       <c r="G40" s="13" t="s">
         <v>14</v>
@@ -3513,26 +3542,26 @@
         <v>97</v>
       </c>
       <c r="J40" s="15" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B41" s="11">
-        <f t="shared" ref="B41" si="16">B40+1</f>
+        <f t="shared" ref="B41" si="15">B40+1</f>
         <v>39</v>
       </c>
       <c r="C41" s="12">
-        <v>45700</v>
+        <v>45701</v>
       </c>
       <c r="D41" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E41" s="12">
-        <v>45700</v>
+        <v>45701</v>
       </c>
       <c r="F41" s="13">
-        <f>$B$40</f>
-        <v>38</v>
+        <f>$B$39</f>
+        <v>37</v>
       </c>
       <c r="G41" s="13" t="s">
         <v>14</v>
@@ -3544,12 +3573,12 @@
         <v>97</v>
       </c>
       <c r="J41" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B42" s="11">
-        <f t="shared" ref="B42" si="17">B41+1</f>
+        <f t="shared" ref="B42" si="16">B41+1</f>
         <v>40</v>
       </c>
       <c r="C42" s="12">
@@ -3559,11 +3588,11 @@
         <v>12</v>
       </c>
       <c r="E42" s="12">
-        <v>45701</v>
+        <v>45713</v>
       </c>
       <c r="F42" s="13">
-        <f>$B$40</f>
-        <v>38</v>
+        <f>$B$39</f>
+        <v>37</v>
       </c>
       <c r="G42" s="13" t="s">
         <v>14</v>
@@ -3575,24 +3604,30 @@
         <v>97</v>
       </c>
       <c r="J42" s="15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43" s="11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="B43" s="11">
-        <f t="shared" ref="B43" si="18">B42+1</f>
+        <f t="shared" ref="B43" si="17">B42+1</f>
         <v>41</v>
       </c>
       <c r="C43" s="12">
-        <v>45701</v>
+        <v>45705</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E43" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E43" s="12">
+        <v>45705</v>
+      </c>
       <c r="F43" s="13">
-        <f>$B$40</f>
-        <v>38</v>
+        <f>$B$42</f>
+        <v>40</v>
       </c>
       <c r="G43" s="13" t="s">
         <v>14</v>
@@ -3604,16 +3639,16 @@
         <v>97</v>
       </c>
       <c r="J43" s="15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B44" s="11">
-        <f t="shared" ref="B44" si="19">B43+1</f>
+        <f t="shared" ref="B44" si="18">B43+1</f>
         <v>42</v>
       </c>
       <c r="C44" s="12">
@@ -3623,11 +3658,11 @@
         <v>12</v>
       </c>
       <c r="E44" s="12">
-        <v>45705</v>
+        <v>45706</v>
       </c>
       <c r="F44" s="13">
-        <f>$B$43</f>
-        <v>41</v>
+        <f>$B$42</f>
+        <v>40</v>
       </c>
       <c r="G44" s="13" t="s">
         <v>14</v>
@@ -3639,30 +3674,25 @@
         <v>97</v>
       </c>
       <c r="J44" s="15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" s="11">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
+      <c r="A45" s="11"/>
       <c r="B45" s="11">
-        <f t="shared" ref="B45" si="20">B44+1</f>
+        <f t="shared" ref="B45" si="19">B44+1</f>
         <v>43</v>
       </c>
       <c r="C45" s="12">
-        <v>45705</v>
+        <v>45706</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E45" s="12">
-        <v>45706</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E45" s="12"/>
       <c r="F45" s="13">
-        <f>$B$43</f>
-        <v>41</v>
+        <f>$B$42</f>
+        <v>40</v>
       </c>
       <c r="G45" s="13" t="s">
         <v>14</v>
@@ -3674,26 +3704,23 @@
         <v>97</v>
       </c>
       <c r="J45" s="15" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="11"/>
       <c r="B46" s="11">
-        <f t="shared" ref="B46" si="21">B45+1</f>
+        <f t="shared" ref="B46:B52" si="20">B45+1</f>
         <v>44</v>
       </c>
       <c r="C46" s="12">
         <v>45706</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E46" s="12"/>
-      <c r="F46" s="13">
-        <f>$B$43</f>
-        <v>41</v>
-      </c>
+      <c r="F46" s="13"/>
       <c r="G46" s="13" t="s">
         <v>14</v>
       </c>
@@ -3701,16 +3728,16 @@
         <v>23</v>
       </c>
       <c r="I46" s="14" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="J46" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="11"/>
       <c r="B47" s="11">
-        <f t="shared" ref="B47:B53" si="22">B46+1</f>
+        <f t="shared" si="20"/>
         <v>45</v>
       </c>
       <c r="C47" s="12">
@@ -3720,7 +3747,10 @@
         <v>10</v>
       </c>
       <c r="E47" s="12"/>
-      <c r="F47" s="13"/>
+      <c r="F47" s="13">
+        <f>$B$46</f>
+        <v>44</v>
+      </c>
       <c r="G47" s="13" t="s">
         <v>14</v>
       </c>
@@ -3731,43 +3761,31 @@
         <v>116</v>
       </c>
       <c r="J47" s="15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="11"/>
       <c r="B48" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>46</v>
       </c>
-      <c r="C48" s="12">
-        <v>45706</v>
-      </c>
-      <c r="D48" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C48" s="12"/>
+      <c r="D48" s="13"/>
       <c r="E48" s="12"/>
-      <c r="F48" s="13">
-        <f>$B$47</f>
-        <v>45</v>
-      </c>
-      <c r="G48" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H48" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="I48" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="J48" s="15" t="s">
-        <v>119</v>
-      </c>
+      <c r="F48" s="13"/>
+      <c r="G48" s="13"/>
+      <c r="H48" s="13"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="15"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A49" s="11"/>
+      <c r="A49" s="11">
+        <f>A44+1</f>
+        <v>3</v>
+      </c>
       <c r="B49" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>47</v>
       </c>
       <c r="C49" s="12"/>
@@ -3781,29 +3799,45 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="11">
-        <f>A45+1</f>
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
       <c r="B50" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>48</v>
       </c>
-      <c r="C50" s="12"/>
-      <c r="D50" s="13"/>
-      <c r="E50" s="12"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13"/>
-      <c r="H50" s="13"/>
-      <c r="I50" s="14"/>
-      <c r="J50" s="15"/>
+      <c r="C50" s="12">
+        <v>45673</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E50" s="12">
+        <v>45684</v>
+      </c>
+      <c r="F50" s="13">
+        <v>24</v>
+      </c>
+      <c r="G50" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H50" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I50" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J50" s="15" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="11">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B51" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>49</v>
       </c>
       <c r="C51" s="12">
@@ -3813,10 +3847,10 @@
         <v>12</v>
       </c>
       <c r="E51" s="12">
-        <v>45684</v>
+        <v>45680</v>
       </c>
       <c r="F51" s="13">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G51" s="13" t="s">
         <v>14</v>
@@ -3825,19 +3859,15 @@
         <v>19</v>
       </c>
       <c r="I51" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="J51" s="15" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" s="11">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="J51" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B52" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>50</v>
       </c>
       <c r="C52" s="12">
@@ -3847,10 +3877,10 @@
         <v>12</v>
       </c>
       <c r="E52" s="12">
-        <v>45680</v>
+        <v>45678</v>
       </c>
       <c r="F52" s="13">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G52" s="13" t="s">
         <v>14</v>
@@ -3862,16 +3892,16 @@
         <v>82</v>
       </c>
       <c r="J52" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B53" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="0"/>
         <v>51</v>
       </c>
       <c r="C53" s="12">
-        <v>45673</v>
+        <v>45678</v>
       </c>
       <c r="D53" s="13" t="s">
         <v>12</v>
@@ -3892,7 +3922,7 @@
         <v>82</v>
       </c>
       <c r="J53" s="17" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
@@ -3901,13 +3931,13 @@
         <v>52</v>
       </c>
       <c r="C54" s="12">
-        <v>45678</v>
+        <v>45673</v>
       </c>
       <c r="D54" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E54" s="12">
-        <v>45678</v>
+        <v>45680</v>
       </c>
       <c r="F54" s="13">
         <v>30</v>
@@ -3921,8 +3951,8 @@
       <c r="I54" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="J54" s="17" t="s">
-        <v>86</v>
+      <c r="J54" s="15" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
@@ -3931,7 +3961,7 @@
         <v>53</v>
       </c>
       <c r="C55" s="12">
-        <v>45673</v>
+        <v>45679</v>
       </c>
       <c r="D55" s="13" t="s">
         <v>12</v>
@@ -3940,7 +3970,7 @@
         <v>45680</v>
       </c>
       <c r="F55" s="13">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G55" s="13" t="s">
         <v>14</v>
@@ -3949,10 +3979,10 @@
         <v>19</v>
       </c>
       <c r="I55" s="14" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="J55" s="15" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
@@ -3961,16 +3991,16 @@
         <v>54</v>
       </c>
       <c r="C56" s="12">
-        <v>45679</v>
+        <v>45678</v>
       </c>
       <c r="D56" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E56" s="12">
-        <v>45680</v>
+        <v>45678</v>
       </c>
       <c r="F56" s="13">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G56" s="13" t="s">
         <v>14</v>
@@ -3979,10 +4009,10 @@
         <v>19</v>
       </c>
       <c r="I56" s="14" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J56" s="15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
@@ -4006,13 +4036,13 @@
         <v>14</v>
       </c>
       <c r="H57" s="13" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I57" s="14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J57" s="15" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
@@ -4021,17 +4051,13 @@
         <v>56</v>
       </c>
       <c r="C58" s="12">
-        <v>45678</v>
+        <v>45684</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E58" s="12">
-        <v>45678</v>
-      </c>
-      <c r="F58" s="13">
-        <v>30</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E58" s="12"/>
+      <c r="F58" s="13"/>
       <c r="G58" s="13" t="s">
         <v>14</v>
       </c>
@@ -4039,34 +4065,22 @@
         <v>23</v>
       </c>
       <c r="I58" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="J58" s="15" t="s">
-        <v>85</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="J58" s="15"/>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B59" s="11">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="C59" s="12">
-        <v>45684</v>
-      </c>
-      <c r="D59" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C59" s="12"/>
+      <c r="D59" s="13"/>
       <c r="E59" s="12"/>
       <c r="F59" s="13"/>
-      <c r="G59" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H59" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="I59" s="14" t="s">
-        <v>91</v>
-      </c>
+      <c r="G59" s="13"/>
+      <c r="H59" s="13"/>
+      <c r="I59" s="14"/>
       <c r="J59" s="15"/>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
@@ -4083,27 +4097,39 @@
       <c r="I60" s="14"/>
       <c r="J60" s="15"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B61" s="11">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="C61" s="12"/>
-      <c r="D61" s="13"/>
+      <c r="C61" s="12">
+        <v>45645</v>
+      </c>
+      <c r="D61" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E61" s="12"/>
       <c r="F61" s="13"/>
-      <c r="G61" s="13"/>
-      <c r="H61" s="13"/>
-      <c r="I61" s="14"/>
-      <c r="J61" s="15"/>
-    </row>
-    <row r="62" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G61" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H61" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I61" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="J61" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B62" s="11">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="C62" s="12">
-        <v>45645</v>
+        <v>45654</v>
       </c>
       <c r="D62" s="13" t="s">
         <v>10</v>
@@ -4117,10 +4143,10 @@
         <v>19</v>
       </c>
       <c r="I62" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="J62" s="17" t="s">
-        <v>64</v>
+        <v>70</v>
+      </c>
+      <c r="J62" s="15" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
@@ -4128,26 +4154,14 @@
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="C63" s="12">
-        <v>45654</v>
-      </c>
-      <c r="D63" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C63" s="12"/>
+      <c r="D63" s="13"/>
       <c r="E63" s="12"/>
       <c r="F63" s="13"/>
-      <c r="G63" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H63" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I63" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="J63" s="15" t="s">
-        <v>71</v>
-      </c>
+      <c r="G63" s="13"/>
+      <c r="H63" s="13"/>
+      <c r="I63" s="14"/>
+      <c r="J63" s="15"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B64" s="11">
@@ -4168,14 +4182,26 @@
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="C65" s="12"/>
-      <c r="D65" s="13"/>
+      <c r="C65" s="12">
+        <v>45698</v>
+      </c>
+      <c r="D65" s="13" t="s">
+        <v>11</v>
+      </c>
       <c r="E65" s="12"/>
       <c r="F65" s="13"/>
-      <c r="G65" s="13"/>
-      <c r="H65" s="13"/>
-      <c r="I65" s="14"/>
-      <c r="J65" s="15"/>
+      <c r="G65" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H65" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I65" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="J65" s="15" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B66" s="11">
@@ -4186,21 +4212,24 @@
         <v>45698</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E66" s="12"/>
-      <c r="F66" s="13"/>
+      <c r="F66" s="13">
+        <f>$B$65</f>
+        <v>63</v>
+      </c>
       <c r="G66" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H66" s="13" t="s">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="I66" s="14" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J66" s="15" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.3">
@@ -4212,9 +4241,11 @@
         <v>45698</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E67" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E67" s="12">
+        <v>45698</v>
+      </c>
       <c r="F67" s="13">
         <f>$B$66</f>
         <v>64</v>
@@ -4229,7 +4260,7 @@
         <v>106</v>
       </c>
       <c r="J67" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.3">
@@ -4241,14 +4272,12 @@
         <v>45698</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E68" s="12">
-        <v>45698</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E68" s="12"/>
       <c r="F68" s="13">
-        <f>$B$67</f>
-        <v>65</v>
+        <f>$B$66</f>
+        <v>64</v>
       </c>
       <c r="G68" s="13" t="s">
         <v>14</v>
@@ -4260,7 +4289,7 @@
         <v>106</v>
       </c>
       <c r="J68" s="15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="69" spans="2:10" x14ac:dyDescent="0.3">
@@ -4276,8 +4305,8 @@
       </c>
       <c r="E69" s="12"/>
       <c r="F69" s="13">
-        <f>$B$67</f>
-        <v>65</v>
+        <f>$B$66</f>
+        <v>64</v>
       </c>
       <c r="G69" s="13" t="s">
         <v>14</v>
@@ -4289,7 +4318,7 @@
         <v>106</v>
       </c>
       <c r="J69" s="15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="70" spans="2:10" x14ac:dyDescent="0.3">
@@ -4297,29 +4326,14 @@
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
-      <c r="C70" s="12">
-        <v>45698</v>
-      </c>
-      <c r="D70" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C70" s="12"/>
+      <c r="D70" s="13"/>
       <c r="E70" s="12"/>
-      <c r="F70" s="13">
-        <f>$B$67</f>
-        <v>65</v>
-      </c>
-      <c r="G70" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H70" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I70" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="J70" s="15" t="s">
-        <v>110</v>
-      </c>
+      <c r="F70" s="13"/>
+      <c r="G70" s="13"/>
+      <c r="H70" s="13"/>
+      <c r="I70" s="14"/>
+      <c r="J70" s="15"/>
     </row>
     <row r="71" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B71" s="11">
@@ -4475,38 +4489,24 @@
       <c r="I81" s="14"/>
       <c r="J81" s="15"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B82" s="11">
+    <row r="82" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B82" s="18">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="C82" s="12"/>
-      <c r="D82" s="13"/>
-      <c r="E82" s="12"/>
-      <c r="F82" s="13"/>
-      <c r="G82" s="13"/>
-      <c r="H82" s="13"/>
-      <c r="I82" s="14"/>
-      <c r="J82" s="15"/>
-    </row>
-    <row r="83" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="18">
-        <f t="shared" si="0"/>
-        <v>81</v>
-      </c>
-      <c r="C83" s="19"/>
-      <c r="D83" s="20"/>
-      <c r="E83" s="19"/>
-      <c r="F83" s="20"/>
-      <c r="G83" s="20"/>
-      <c r="H83" s="20"/>
-      <c r="I83" s="21"/>
-      <c r="J83" s="22"/>
+      <c r="C82" s="19"/>
+      <c r="D82" s="20"/>
+      <c r="E82" s="19"/>
+      <c r="F82" s="20"/>
+      <c r="G82" s="20"/>
+      <c r="H82" s="20"/>
+      <c r="I82" s="21"/>
+      <c r="J82" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:J83" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
+  <autoFilter ref="B2:J82" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A47:J47 A48:A52 B48:J83 A44:A46 B3:J46">
+  <conditionalFormatting sqref="A43:A45 A46:J46 A47:A51 B47:J82 B3:J45">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>
@@ -4519,29 +4519,29 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B4A065F5-E745-4CD6-9C94-45B6B3E69BD7}">
+          <x14:formula1>
+            <xm:f>選択情報!$D$3:$D$6</xm:f>
+          </x14:formula1>
+          <xm:sqref>H66:H82 H3:H64</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D6F2F62E-6D63-4E2D-8772-1211A4C3A979}">
+          <x14:formula1>
+            <xm:f>選択情報!$D$3:$D$10</xm:f>
+          </x14:formula1>
+          <xm:sqref>H65</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C61EF0EC-B820-4CEA-8AA2-04B5D172AE2C}">
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D83</xm:sqref>
+          <xm:sqref>D3:D82</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G83</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B4A065F5-E745-4CD6-9C94-45B6B3E69BD7}">
-          <x14:formula1>
-            <xm:f>選択情報!$D$3:$D$6</xm:f>
-          </x14:formula1>
-          <xm:sqref>H67:H83 H3:H65</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D6F2F62E-6D63-4E2D-8772-1211A4C3A979}">
-          <x14:formula1>
-            <xm:f>選択情報!$D$3:$D$10</xm:f>
-          </x14:formula1>
-          <xm:sqref>H66</xm:sqref>
+          <xm:sqref>G3:G82</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38C664A6-EA44-425C-A408-FF575C218A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C5C529D-0327-4B27-BAF3-473D9571F810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="123">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -1478,47 +1478,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>表示メニュー情報の初期登録化</t>
-    <rPh sb="0" eb="2">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ショキ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>HtmlMenuの修正（メニュー情報を読込、行毎にボタンを出力する。）</t>
-    <rPh sb="9" eb="11">
-      <t>シュウセイ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ヨミコミ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>ギョウ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>ゴト</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>シュツリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>週品情報読込 : M_Product.load(env, productId)</t>
     <rPh sb="0" eb="2">
       <t>シュウヒン</t>
@@ -1690,6 +1649,79 @@
     </rPh>
     <rPh sb="18" eb="19">
       <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面情報 : メニュー情報の登録 → 確認用として教育用メニューを登録</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>カクニンヨウ</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>キョウイクヨウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HtmlMenu01の改修 : 表示情報の取込</t>
+    <rPh sb="11" eb="13">
+      <t>カイシュウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>トリコミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示メニュー情報の採番情報登録</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>サイバン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HtmlMenu01 : メニュー表示のデータ化（教育用）</t>
+    <rPh sb="17" eb="19">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>キョウイクヨウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3118,7 +3150,7 @@
         <v>60</v>
       </c>
       <c r="J26" s="17" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -3542,7 +3574,7 @@
         <v>97</v>
       </c>
       <c r="J40" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
@@ -3573,7 +3605,7 @@
         <v>97</v>
       </c>
       <c r="J41" s="15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
@@ -3604,7 +3636,7 @@
         <v>97</v>
       </c>
       <c r="J42" s="15" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
@@ -3639,7 +3671,7 @@
         <v>97</v>
       </c>
       <c r="J43" s="15" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
@@ -3674,7 +3706,7 @@
         <v>97</v>
       </c>
       <c r="J44" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
@@ -3704,7 +3736,7 @@
         <v>97</v>
       </c>
       <c r="J45" s="15" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
@@ -3728,10 +3760,10 @@
         <v>23</v>
       </c>
       <c r="I46" s="14" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J46" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
@@ -3758,10 +3790,10 @@
         <v>23</v>
       </c>
       <c r="I47" s="14" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J47" s="15" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
@@ -4272,9 +4304,11 @@
         <v>45698</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E68" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E68" s="12">
+        <v>45714</v>
+      </c>
       <c r="F68" s="13">
         <f>$B$66</f>
         <v>64</v>
@@ -4289,7 +4323,7 @@
         <v>106</v>
       </c>
       <c r="J68" s="15" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="69" spans="2:10" x14ac:dyDescent="0.3">
@@ -4301,9 +4335,11 @@
         <v>45698</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E69" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E69" s="12">
+        <v>45714</v>
+      </c>
       <c r="F69" s="13">
         <f>$B$66</f>
         <v>64</v>
@@ -4318,7 +4354,7 @@
         <v>106</v>
       </c>
       <c r="J69" s="15" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
     </row>
     <row r="70" spans="2:10" x14ac:dyDescent="0.3">
@@ -4326,28 +4362,58 @@
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
-      <c r="C70" s="12"/>
-      <c r="D70" s="13"/>
-      <c r="E70" s="12"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="13"/>
-      <c r="H70" s="13"/>
-      <c r="I70" s="14"/>
-      <c r="J70" s="15"/>
+      <c r="C70" s="12">
+        <v>45714</v>
+      </c>
+      <c r="D70" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E70" s="12">
+        <v>45714</v>
+      </c>
+      <c r="F70" s="13">
+        <f>$B$66</f>
+        <v>64</v>
+      </c>
+      <c r="G70" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H70" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I70" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J70" s="15" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="71" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B71" s="11">
         <f t="shared" si="0"/>
         <v>69</v>
       </c>
-      <c r="C71" s="12"/>
+      <c r="C71" s="12">
+        <v>45714</v>
+      </c>
       <c r="D71" s="13"/>
       <c r="E71" s="12"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="13"/>
-      <c r="H71" s="13"/>
-      <c r="I71" s="14"/>
-      <c r="J71" s="15"/>
+      <c r="F71" s="13">
+        <f>$B$66</f>
+        <v>64</v>
+      </c>
+      <c r="G71" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H71" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I71" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J71" s="15" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="72" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B72" s="11">
@@ -4506,7 +4572,7 @@
   </sheetData>
   <autoFilter ref="B2:J82" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A43:A45 A46:J46 A47:A51 B47:J82 B3:J45">
+  <conditionalFormatting sqref="B3:J45 A43:A45 A46:J46 A47:A51 B47:J82">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>
@@ -4523,7 +4589,7 @@
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H66:H82 H3:H64</xm:sqref>
+          <xm:sqref>H3:H64 H66:H82</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D6F2F62E-6D63-4E2D-8772-1211A4C3A979}">
           <x14:formula1>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C5C529D-0327-4B27-BAF3-473D9571F810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B49112F6-CAFC-449F-9D08-49C10CFEFCEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="125">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -1713,15 +1713,47 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>HtmlMenu01 : メニュー表示のデータ化（教育用）</t>
+    <t>HtmlMenu01 : メニュー表示を表示メニュー情報から設定（教育管理Lv.01)</t>
     <rPh sb="17" eb="19">
       <t>ヒョウジ</t>
     </rPh>
-    <rPh sb="23" eb="24">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="25" eb="28">
-      <t>キョウイクヨウ</t>
+    <rPh sb="20" eb="22">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>キョウイク</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HtmlMenu01 : メニュー遷移用Functionの設定</t>
+    <rPh sb="17" eb="20">
+      <t>センイヨウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HtmlMenu01 : 受注、生産メニュー設定</t>
+    <rPh sb="13" eb="15">
+      <t>ジュチュウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>セイサン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>セッテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4279,7 +4311,7 @@
         <v>45698</v>
       </c>
       <c r="F67" s="13">
-        <f>$B$66</f>
+        <f t="shared" ref="F67:F73" si="21">$B$66</f>
         <v>64</v>
       </c>
       <c r="G67" s="13" t="s">
@@ -4310,7 +4342,7 @@
         <v>45714</v>
       </c>
       <c r="F68" s="13">
-        <f>$B$66</f>
+        <f t="shared" si="21"/>
         <v>64</v>
       </c>
       <c r="G68" s="13" t="s">
@@ -4341,7 +4373,7 @@
         <v>45714</v>
       </c>
       <c r="F69" s="13">
-        <f>$B$66</f>
+        <f t="shared" si="21"/>
         <v>64</v>
       </c>
       <c r="G69" s="13" t="s">
@@ -4372,7 +4404,7 @@
         <v>45714</v>
       </c>
       <c r="F70" s="13">
-        <f>$B$66</f>
+        <f t="shared" si="21"/>
         <v>64</v>
       </c>
       <c r="G70" s="13" t="s">
@@ -4396,10 +4428,14 @@
       <c r="C71" s="12">
         <v>45714</v>
       </c>
-      <c r="D71" s="13"/>
-      <c r="E71" s="12"/>
+      <c r="D71" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E71" s="12">
+        <v>45715</v>
+      </c>
       <c r="F71" s="13">
-        <f>$B$66</f>
+        <f t="shared" si="21"/>
         <v>64</v>
       </c>
       <c r="G71" s="13" t="s">
@@ -4420,28 +4456,60 @@
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="C72" s="12"/>
-      <c r="D72" s="13"/>
-      <c r="E72" s="12"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="13"/>
-      <c r="H72" s="13"/>
-      <c r="I72" s="14"/>
-      <c r="J72" s="15"/>
+      <c r="C72" s="12">
+        <v>45715</v>
+      </c>
+      <c r="D72" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E72" s="12">
+        <v>45715</v>
+      </c>
+      <c r="F72" s="13">
+        <f t="shared" si="21"/>
+        <v>64</v>
+      </c>
+      <c r="G72" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H72" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I72" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J72" s="15" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="73" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B73" s="11">
         <f t="shared" si="0"/>
         <v>71</v>
       </c>
-      <c r="C73" s="12"/>
-      <c r="D73" s="13"/>
+      <c r="C73" s="12">
+        <v>45715</v>
+      </c>
+      <c r="D73" s="13" t="s">
+        <v>11</v>
+      </c>
       <c r="E73" s="12"/>
-      <c r="F73" s="13"/>
-      <c r="G73" s="13"/>
-      <c r="H73" s="13"/>
-      <c r="I73" s="14"/>
-      <c r="J73" s="15"/>
+      <c r="F73" s="13">
+        <f t="shared" si="21"/>
+        <v>64</v>
+      </c>
+      <c r="G73" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H73" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I73" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J73" s="15" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B74" s="11">

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B49112F6-CAFC-449F-9D08-49C10CFEFCEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB412601-58DD-4BA8-AF60-1CB285241980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="130">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -1754,6 +1754,71 @@
     </rPh>
     <rPh sb="22" eb="24">
       <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HtmlMenu01 : プロジェクトメニューを2行目に設定する。</t>
+    <rPh sb="25" eb="27">
+      <t>ギョウメ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示メニュー情報</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>行番号項目の追加 : menu_row_no : 初期値"1"</t>
+    <rPh sb="0" eb="3">
+      <t>ギョウバンゴウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>ショキチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示情報読込修正</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヨミコミ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロジェクトメニューボタン用情報登録</t>
+    <rPh sb="13" eb="14">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>トウロク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4311,7 +4376,7 @@
         <v>45698</v>
       </c>
       <c r="F67" s="13">
-        <f t="shared" ref="F67:F73" si="21">$B$66</f>
+        <f t="shared" ref="F67:F74" si="21">$B$66</f>
         <v>64</v>
       </c>
       <c r="G67" s="13" t="s">
@@ -4491,9 +4556,11 @@
         <v>45715</v>
       </c>
       <c r="D73" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E73" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E73" s="12">
+        <v>45714</v>
+      </c>
       <c r="F73" s="13">
         <f t="shared" si="21"/>
         <v>64</v>
@@ -4516,56 +4583,118 @@
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="C74" s="12"/>
-      <c r="D74" s="13"/>
+      <c r="C74" s="12">
+        <v>45717</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>11</v>
+      </c>
       <c r="E74" s="12"/>
-      <c r="F74" s="13"/>
-      <c r="G74" s="13"/>
-      <c r="H74" s="13"/>
-      <c r="I74" s="14"/>
-      <c r="J74" s="15"/>
+      <c r="F74" s="13">
+        <f t="shared" si="21"/>
+        <v>64</v>
+      </c>
+      <c r="G74" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H74" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I74" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J74" s="15" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="75" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B75" s="11">
         <f t="shared" si="0"/>
         <v>73</v>
       </c>
-      <c r="C75" s="12"/>
-      <c r="D75" s="13"/>
-      <c r="E75" s="12"/>
-      <c r="F75" s="13"/>
-      <c r="G75" s="13"/>
-      <c r="H75" s="13"/>
-      <c r="I75" s="14"/>
-      <c r="J75" s="15"/>
+      <c r="C75" s="12">
+        <v>45717</v>
+      </c>
+      <c r="D75" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E75" s="12">
+        <v>45717</v>
+      </c>
+      <c r="F75" s="13">
+        <f>$B$74</f>
+        <v>72</v>
+      </c>
+      <c r="G75" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H75" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I75" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="J75" s="15" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="76" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B76" s="11">
         <f t="shared" si="0"/>
         <v>74</v>
       </c>
-      <c r="C76" s="12"/>
-      <c r="D76" s="13"/>
+      <c r="C76" s="12">
+        <v>45717</v>
+      </c>
+      <c r="D76" s="13" t="s">
+        <v>11</v>
+      </c>
       <c r="E76" s="12"/>
-      <c r="F76" s="13"/>
-      <c r="G76" s="13"/>
-      <c r="H76" s="13"/>
-      <c r="I76" s="14"/>
-      <c r="J76" s="15"/>
+      <c r="F76" s="13">
+        <f>$B$74</f>
+        <v>72</v>
+      </c>
+      <c r="G76" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H76" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I76" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="J76" s="15" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="77" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B77" s="11">
         <f t="shared" si="0"/>
         <v>75</v>
       </c>
-      <c r="C77" s="12"/>
-      <c r="D77" s="13"/>
+      <c r="C77" s="12">
+        <v>45717</v>
+      </c>
+      <c r="D77" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E77" s="12"/>
-      <c r="F77" s="13"/>
-      <c r="G77" s="13"/>
-      <c r="H77" s="13"/>
-      <c r="I77" s="14"/>
-      <c r="J77" s="15"/>
+      <c r="F77" s="13">
+        <f>$B$74</f>
+        <v>72</v>
+      </c>
+      <c r="G77" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H77" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I77" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="J77" s="15" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="78" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B78" s="11">

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB412601-58DD-4BA8-AF60-1CB285241980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD7D6748-6ED3-4C6D-BE39-3699352A4214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="134">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -1818,6 +1818,40 @@
       <t>ジョウホウ</t>
     </rPh>
     <rPh sb="16" eb="18">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロジェクト管理</t>
+    <rPh sb="6" eb="8">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HtmlProjectMenu01構築</t>
+    <rPh sb="17" eb="19">
+      <t>コウチク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロジェクト管理メニュー</t>
+    <rPh sb="6" eb="8">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示情報 : プロジェクトメニューLv.01登録</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
       <t>トウロク</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -4341,9 +4375,11 @@
         <v>45698</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E66" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E66" s="12">
+        <v>45717</v>
+      </c>
       <c r="F66" s="13">
         <f>$B$65</f>
         <v>63</v>
@@ -4587,9 +4623,11 @@
         <v>45717</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E74" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E74" s="12">
+        <v>45717</v>
+      </c>
       <c r="F74" s="13">
         <f t="shared" si="21"/>
         <v>64</v>
@@ -4647,9 +4685,11 @@
         <v>45717</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E76" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E76" s="12">
+        <v>45717</v>
+      </c>
       <c r="F76" s="13">
         <f>$B$74</f>
         <v>72</v>
@@ -4676,9 +4716,11 @@
         <v>45717</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E77" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E77" s="12">
+        <v>45717</v>
+      </c>
       <c r="F77" s="13">
         <f>$B$74</f>
         <v>72</v>
@@ -4701,28 +4743,58 @@
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
-      <c r="C78" s="12"/>
-      <c r="D78" s="13"/>
+      <c r="C78" s="12">
+        <v>45717</v>
+      </c>
+      <c r="D78" s="13" t="s">
+        <v>11</v>
+      </c>
       <c r="E78" s="12"/>
-      <c r="F78" s="13"/>
-      <c r="G78" s="13"/>
-      <c r="H78" s="13"/>
-      <c r="I78" s="14"/>
-      <c r="J78" s="15"/>
+      <c r="F78" s="13">
+        <f>$B$65</f>
+        <v>63</v>
+      </c>
+      <c r="G78" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H78" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I78" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="J78" s="15" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="79" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B79" s="11">
         <f t="shared" si="0"/>
         <v>77</v>
       </c>
-      <c r="C79" s="12"/>
-      <c r="D79" s="13"/>
+      <c r="C79" s="12">
+        <v>45717</v>
+      </c>
+      <c r="D79" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E79" s="12"/>
-      <c r="F79" s="13"/>
-      <c r="G79" s="13"/>
-      <c r="H79" s="13"/>
-      <c r="I79" s="14"/>
-      <c r="J79" s="15"/>
+      <c r="F79" s="13">
+        <f>$B$78</f>
+        <v>76</v>
+      </c>
+      <c r="G79" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H79" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I79" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="J79" s="15" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="80" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B80" s="11">
@@ -4786,13 +4858,13 @@
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H3:H64 H66:H82</xm:sqref>
+          <xm:sqref>H3:H64 H66:H77 H80:H82</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D6F2F62E-6D63-4E2D-8772-1211A4C3A979}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$10</xm:f>
           </x14:formula1>
-          <xm:sqref>H65</xm:sqref>
+          <xm:sqref>H65 H78:H79</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C61EF0EC-B820-4CEA-8AA2-04B5D172AE2C}">
           <x14:formula1>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD7D6748-6ED3-4C6D-BE39-3699352A4214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0D2BED1-A051-4E00-A47C-28C12BDCD04A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="選択情報" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$90</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="135">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -1853,6 +1853,16 @@
     </rPh>
     <rPh sb="22" eb="24">
       <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HtmlProjectMenu01 : タイトル迄表示</t>
+    <rPh sb="24" eb="25">
+      <t>マデ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2544,7 +2554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="A1:K82"/>
+  <dimension ref="A1:K90"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -2742,7 +2752,7 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
-        <f t="shared" ref="A8:B82" si="0">B7+1</f>
+        <f t="shared" ref="A8:B90" si="0">B7+1</f>
         <v>6</v>
       </c>
       <c r="C8" s="12">
@@ -4776,9 +4786,11 @@
         <v>45717</v>
       </c>
       <c r="D79" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E79" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E79" s="12">
+        <v>45717</v>
+      </c>
       <c r="F79" s="13">
         <f>$B$78</f>
         <v>76</v>
@@ -4801,18 +4813,33 @@
         <f t="shared" si="0"/>
         <v>78</v>
       </c>
-      <c r="C80" s="12"/>
-      <c r="D80" s="13"/>
+      <c r="C80" s="12">
+        <v>45717</v>
+      </c>
+      <c r="D80" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E80" s="12"/>
-      <c r="F80" s="13"/>
-      <c r="G80" s="13"/>
-      <c r="H80" s="13"/>
-      <c r="I80" s="14"/>
-      <c r="J80" s="15"/>
+      <c r="F80" s="13">
+        <f>$B$78</f>
+        <v>76</v>
+      </c>
+      <c r="G80" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H80" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I80" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="J80" s="15" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="81" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B81" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B81" si="22">B80+1</f>
         <v>79</v>
       </c>
       <c r="C81" s="12"/>
@@ -4824,24 +4851,136 @@
       <c r="I81" s="14"/>
       <c r="J81" s="15"/>
     </row>
-    <row r="82" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B82" s="18">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B82" s="11">
+        <f t="shared" ref="B82" si="23">B81+1</f>
+        <v>80</v>
+      </c>
+      <c r="C82" s="12"/>
+      <c r="D82" s="13"/>
+      <c r="E82" s="12"/>
+      <c r="F82" s="13"/>
+      <c r="G82" s="13"/>
+      <c r="H82" s="13"/>
+      <c r="I82" s="14"/>
+      <c r="J82" s="15"/>
+    </row>
+    <row r="83" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B83" s="11">
+        <f t="shared" ref="B83" si="24">B82+1</f>
+        <v>81</v>
+      </c>
+      <c r="C83" s="12"/>
+      <c r="D83" s="13"/>
+      <c r="E83" s="12"/>
+      <c r="F83" s="13"/>
+      <c r="G83" s="13"/>
+      <c r="H83" s="13"/>
+      <c r="I83" s="14"/>
+      <c r="J83" s="15"/>
+    </row>
+    <row r="84" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B84" s="11">
+        <f t="shared" ref="B84" si="25">B83+1</f>
+        <v>82</v>
+      </c>
+      <c r="C84" s="12"/>
+      <c r="D84" s="13"/>
+      <c r="E84" s="12"/>
+      <c r="F84" s="13"/>
+      <c r="G84" s="13"/>
+      <c r="H84" s="13"/>
+      <c r="I84" s="14"/>
+      <c r="J84" s="15"/>
+    </row>
+    <row r="85" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B85" s="11">
+        <f t="shared" ref="B85" si="26">B84+1</f>
+        <v>83</v>
+      </c>
+      <c r="C85" s="12"/>
+      <c r="D85" s="13"/>
+      <c r="E85" s="12"/>
+      <c r="F85" s="13"/>
+      <c r="G85" s="13"/>
+      <c r="H85" s="13"/>
+      <c r="I85" s="14"/>
+      <c r="J85" s="15"/>
+    </row>
+    <row r="86" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B86" s="11">
+        <f t="shared" ref="B86" si="27">B85+1</f>
+        <v>84</v>
+      </c>
+      <c r="C86" s="12"/>
+      <c r="D86" s="13"/>
+      <c r="E86" s="12"/>
+      <c r="F86" s="13"/>
+      <c r="G86" s="13"/>
+      <c r="H86" s="13"/>
+      <c r="I86" s="14"/>
+      <c r="J86" s="15"/>
+    </row>
+    <row r="87" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B87" s="11">
+        <f t="shared" ref="B87" si="28">B86+1</f>
+        <v>85</v>
+      </c>
+      <c r="C87" s="12"/>
+      <c r="D87" s="13"/>
+      <c r="E87" s="12"/>
+      <c r="F87" s="13"/>
+      <c r="G87" s="13"/>
+      <c r="H87" s="13"/>
+      <c r="I87" s="14"/>
+      <c r="J87" s="15"/>
+    </row>
+    <row r="88" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B88" s="11">
+        <f t="shared" ref="B88" si="29">B87+1</f>
+        <v>86</v>
+      </c>
+      <c r="C88" s="12"/>
+      <c r="D88" s="13"/>
+      <c r="E88" s="12"/>
+      <c r="F88" s="13"/>
+      <c r="G88" s="13"/>
+      <c r="H88" s="13"/>
+      <c r="I88" s="14"/>
+      <c r="J88" s="15"/>
+    </row>
+    <row r="89" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B89" s="11">
+        <f t="shared" ref="B89" si="30">B88+1</f>
+        <v>87</v>
+      </c>
+      <c r="C89" s="12"/>
+      <c r="D89" s="13"/>
+      <c r="E89" s="12"/>
+      <c r="F89" s="13"/>
+      <c r="G89" s="13"/>
+      <c r="H89" s="13"/>
+      <c r="I89" s="14"/>
+      <c r="J89" s="15"/>
+    </row>
+    <row r="90" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B90" s="18">
         <f t="shared" si="0"/>
-        <v>80</v>
-      </c>
-      <c r="C82" s="19"/>
-      <c r="D82" s="20"/>
-      <c r="E82" s="19"/>
-      <c r="F82" s="20"/>
-      <c r="G82" s="20"/>
-      <c r="H82" s="20"/>
-      <c r="I82" s="21"/>
-      <c r="J82" s="22"/>
+        <v>88</v>
+      </c>
+      <c r="C90" s="19"/>
+      <c r="D90" s="20"/>
+      <c r="E90" s="19"/>
+      <c r="F90" s="20"/>
+      <c r="G90" s="20"/>
+      <c r="H90" s="20"/>
+      <c r="I90" s="21"/>
+      <c r="J90" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:J82" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
+  <autoFilter ref="B2:J90" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B3:J45 A43:A45 A46:J46 A47:A51 B47:J82">
+  <conditionalFormatting sqref="B3:J45 A43:A45 A46:J46 A47:A51 B47:J90">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>
@@ -4858,25 +4997,25 @@
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H3:H64 H66:H77 H80:H82</xm:sqref>
+          <xm:sqref>H3:H64 H66:H77 H81:H90</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D6F2F62E-6D63-4E2D-8772-1211A4C3A979}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$10</xm:f>
           </x14:formula1>
-          <xm:sqref>H65 H78:H79</xm:sqref>
+          <xm:sqref>H65 H78:H80</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C61EF0EC-B820-4CEA-8AA2-04B5D172AE2C}">
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D82</xm:sqref>
+          <xm:sqref>D3:D90</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G82</xm:sqref>
+          <xm:sqref>G3:G90</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0D2BED1-A051-4E00-A47C-28C12BDCD04A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54996957-2DE8-4F7E-8266-FF3EDAFF766E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="142">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -1863,6 +1863,79 @@
     </rPh>
     <rPh sb="25" eb="27">
       <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示メニュー情報</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロジェクト一覧メニューボタン登録</t>
+    <rPh sb="6" eb="8">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HtmlProjectMenu01 :　一覧メニューボタン表示</t>
+    <rPh sb="20" eb="22">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示処理情報</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メインメニューへ戻るボタン登録</t>
+    <rPh sb="8" eb="9">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メインメニューへ戻るボタン遷移構築</t>
+    <rPh sb="8" eb="9">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>コウチク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ProjectAction01構築</t>
+    <rPh sb="15" eb="17">
+      <t>コウチク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4817,9 +4890,11 @@
         <v>45717</v>
       </c>
       <c r="D80" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E80" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E80" s="12">
+        <v>45717</v>
+      </c>
       <c r="F80" s="13">
         <f>$B$78</f>
         <v>76</v>
@@ -4842,70 +4917,145 @@
         <f t="shared" ref="B81" si="22">B80+1</f>
         <v>79</v>
       </c>
-      <c r="C81" s="12"/>
-      <c r="D81" s="13"/>
+      <c r="C81" s="12">
+        <v>45717</v>
+      </c>
+      <c r="D81" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E81" s="12"/>
-      <c r="F81" s="13"/>
-      <c r="G81" s="13"/>
-      <c r="H81" s="13"/>
-      <c r="I81" s="14"/>
-      <c r="J81" s="15"/>
+      <c r="F81" s="13">
+        <f>$B$78</f>
+        <v>76</v>
+      </c>
+      <c r="G81" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H81" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I81" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="J81" s="15" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="82" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B82" s="11">
         <f t="shared" ref="B82" si="23">B81+1</f>
         <v>80</v>
       </c>
-      <c r="C82" s="12"/>
-      <c r="D82" s="13"/>
+      <c r="C82" s="12">
+        <v>45717</v>
+      </c>
+      <c r="D82" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E82" s="12"/>
-      <c r="F82" s="13"/>
-      <c r="G82" s="13"/>
-      <c r="H82" s="13"/>
-      <c r="I82" s="14"/>
-      <c r="J82" s="15"/>
+      <c r="F82" s="13">
+        <f>$B$78</f>
+        <v>76</v>
+      </c>
+      <c r="G82" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H82" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I82" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="J82" s="15" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B83" s="11">
         <f t="shared" ref="B83" si="24">B82+1</f>
         <v>81</v>
       </c>
-      <c r="C83" s="12"/>
-      <c r="D83" s="13"/>
+      <c r="C83" s="12">
+        <v>45717</v>
+      </c>
+      <c r="D83" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E83" s="12"/>
-      <c r="F83" s="13"/>
-      <c r="G83" s="13"/>
-      <c r="H83" s="13"/>
-      <c r="I83" s="14"/>
-      <c r="J83" s="15"/>
+      <c r="F83" s="13">
+        <f>$B$78</f>
+        <v>76</v>
+      </c>
+      <c r="G83" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H83" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I83" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="J83" s="15" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="84" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B84" s="11">
         <f t="shared" ref="B84" si="25">B83+1</f>
         <v>82</v>
       </c>
-      <c r="C84" s="12"/>
-      <c r="D84" s="13"/>
+      <c r="C84" s="12">
+        <v>45717</v>
+      </c>
+      <c r="D84" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E84" s="12"/>
-      <c r="F84" s="13"/>
-      <c r="G84" s="13"/>
-      <c r="H84" s="13"/>
-      <c r="I84" s="14"/>
-      <c r="J84" s="15"/>
+      <c r="F84" s="13">
+        <f>$B$78</f>
+        <v>76</v>
+      </c>
+      <c r="G84" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H84" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I84" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="J84" s="15" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B85" s="11">
         <f t="shared" ref="B85" si="26">B84+1</f>
         <v>83</v>
       </c>
-      <c r="C85" s="12"/>
-      <c r="D85" s="13"/>
+      <c r="C85" s="12">
+        <v>45717</v>
+      </c>
+      <c r="D85" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E85" s="12"/>
-      <c r="F85" s="13"/>
-      <c r="G85" s="13"/>
-      <c r="H85" s="13"/>
-      <c r="I85" s="14"/>
-      <c r="J85" s="15"/>
+      <c r="F85" s="13">
+        <f>$B$78</f>
+        <v>76</v>
+      </c>
+      <c r="G85" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H85" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I85" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="J85" s="15" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B86" s="11">
@@ -4997,13 +5147,13 @@
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H3:H64 H66:H77 H81:H90</xm:sqref>
+          <xm:sqref>H3:H64 H66:H77 H86:H90</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D6F2F62E-6D63-4E2D-8772-1211A4C3A979}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$10</xm:f>
           </x14:formula1>
-          <xm:sqref>H65 H78:H80</xm:sqref>
+          <xm:sqref>H65 H78:H85</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C61EF0EC-B820-4CEA-8AA2-04B5D172AE2C}">
           <x14:formula1>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54996957-2DE8-4F7E-8266-FF3EDAFF766E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B3D76B4-9EAD-47C0-93C4-7BCC7337A4DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="作業項目" sheetId="1" r:id="rId1"/>
     <sheet name="選択情報" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作業項目!$B$2:$J$99</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="148">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -1935,6 +1935,126 @@
   <si>
     <t>ProjectAction01構築</t>
     <rPh sb="15" eb="17">
+      <t>コウチク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デモ用受注情報初期登録</t>
+    <rPh sb="2" eb="3">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジュチュウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>ショキトウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>受注管理 Lv.01</t>
+    <rPh sb="0" eb="2">
+      <t>ジュチュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>受注管理 Lv.01の追加構築、受注一覧項目追加、一覧からの照会、編集遷移の改修</t>
+    <rPh sb="0" eb="2">
+      <t>ジュチュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>コウチク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジュチュウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ショウカイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>カイシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>受注一覧に台数と金額項目を追加する。(Number,Amoutへの対応）</t>
+    <rPh sb="0" eb="2">
+      <t>ジュチュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ダイスウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>キンガク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一覧からの照会遷移</t>
+    <rPh sb="0" eb="2">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ショウカイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>照会画面構築</t>
+    <rPh sb="0" eb="2">
+      <t>ショウカイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
       <t>コウチク</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -2627,7 +2747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="A1:K90"/>
+  <dimension ref="A1:K99"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -2825,7 +2945,7 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
-        <f t="shared" ref="A8:B90" si="0">B7+1</f>
+        <f t="shared" ref="A8:B99" si="0">B7+1</f>
         <v>6</v>
       </c>
       <c r="C8" s="12">
@@ -4865,7 +4985,7 @@
         <v>45717</v>
       </c>
       <c r="F79" s="13">
-        <f>$B$78</f>
+        <f t="shared" ref="F79:F85" si="22">$B$78</f>
         <v>76</v>
       </c>
       <c r="G79" s="13" t="s">
@@ -4896,7 +5016,7 @@
         <v>45717</v>
       </c>
       <c r="F80" s="13">
-        <f>$B$78</f>
+        <f t="shared" si="22"/>
         <v>76</v>
       </c>
       <c r="G80" s="13" t="s">
@@ -4914,18 +5034,20 @@
     </row>
     <row r="81" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B81" s="11">
-        <f t="shared" ref="B81" si="22">B80+1</f>
+        <f t="shared" ref="B81" si="23">B80+1</f>
         <v>79</v>
       </c>
       <c r="C81" s="12">
         <v>45717</v>
       </c>
       <c r="D81" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E81" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E81" s="12">
+        <v>45717</v>
+      </c>
       <c r="F81" s="13">
-        <f>$B$78</f>
+        <f t="shared" si="22"/>
         <v>76</v>
       </c>
       <c r="G81" s="13" t="s">
@@ -4943,7 +5065,7 @@
     </row>
     <row r="82" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B82" s="11">
-        <f t="shared" ref="B82" si="23">B81+1</f>
+        <f t="shared" ref="B82" si="24">B81+1</f>
         <v>80</v>
       </c>
       <c r="C82" s="12">
@@ -4954,7 +5076,7 @@
       </c>
       <c r="E82" s="12"/>
       <c r="F82" s="13">
-        <f>$B$78</f>
+        <f t="shared" si="22"/>
         <v>76</v>
       </c>
       <c r="G82" s="13" t="s">
@@ -4972,7 +5094,7 @@
     </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B83" s="11">
-        <f t="shared" ref="B83" si="24">B82+1</f>
+        <f t="shared" ref="B83" si="25">B82+1</f>
         <v>81</v>
       </c>
       <c r="C83" s="12">
@@ -4983,7 +5105,7 @@
       </c>
       <c r="E83" s="12"/>
       <c r="F83" s="13">
-        <f>$B$78</f>
+        <f t="shared" si="22"/>
         <v>76</v>
       </c>
       <c r="G83" s="13" t="s">
@@ -5001,7 +5123,7 @@
     </row>
     <row r="84" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B84" s="11">
-        <f t="shared" ref="B84" si="25">B83+1</f>
+        <f t="shared" ref="B84" si="26">B83+1</f>
         <v>82</v>
       </c>
       <c r="C84" s="12">
@@ -5012,7 +5134,7 @@
       </c>
       <c r="E84" s="12"/>
       <c r="F84" s="13">
-        <f>$B$78</f>
+        <f t="shared" si="22"/>
         <v>76</v>
       </c>
       <c r="G84" s="13" t="s">
@@ -5030,7 +5152,7 @@
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B85" s="11">
-        <f t="shared" ref="B85" si="26">B84+1</f>
+        <f t="shared" ref="B85" si="27">B84+1</f>
         <v>83</v>
       </c>
       <c r="C85" s="12">
@@ -5041,7 +5163,7 @@
       </c>
       <c r="E85" s="12"/>
       <c r="F85" s="13">
-        <f>$B$78</f>
+        <f t="shared" si="22"/>
         <v>76</v>
       </c>
       <c r="G85" s="13" t="s">
@@ -5059,7 +5181,7 @@
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B86" s="11">
-        <f t="shared" ref="B86" si="27">B85+1</f>
+        <f t="shared" ref="B86:B97" si="28">B85+1</f>
         <v>84</v>
       </c>
       <c r="C86" s="12"/>
@@ -5073,64 +5195,264 @@
     </row>
     <row r="87" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B87" s="11">
-        <f t="shared" ref="B87" si="28">B86+1</f>
+        <f t="shared" si="28"/>
         <v>85</v>
       </c>
-      <c r="C87" s="12"/>
-      <c r="D87" s="13"/>
+      <c r="C87" s="12">
+        <v>45719</v>
+      </c>
+      <c r="D87" s="13" t="s">
+        <v>11</v>
+      </c>
       <c r="E87" s="12"/>
       <c r="F87" s="13"/>
-      <c r="G87" s="13"/>
-      <c r="H87" s="13"/>
-      <c r="I87" s="14"/>
-      <c r="J87" s="15"/>
+      <c r="G87" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H87" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I87" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="J87" s="15" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="88" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B88" s="11">
-        <f t="shared" ref="B88" si="29">B87+1</f>
+        <f t="shared" si="28"/>
         <v>86</v>
       </c>
-      <c r="C88" s="12"/>
-      <c r="D88" s="13"/>
-      <c r="E88" s="12"/>
-      <c r="F88" s="13"/>
-      <c r="G88" s="13"/>
-      <c r="H88" s="13"/>
-      <c r="I88" s="14"/>
-      <c r="J88" s="15"/>
+      <c r="C88" s="12">
+        <v>45719</v>
+      </c>
+      <c r="D88" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E88" s="12">
+        <v>45719</v>
+      </c>
+      <c r="F88" s="13">
+        <f>$B$87</f>
+        <v>85</v>
+      </c>
+      <c r="G88" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H88" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I88" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="J88" s="15" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="89" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B89" s="11">
-        <f t="shared" ref="B89" si="30">B88+1</f>
+        <f t="shared" si="28"/>
         <v>87</v>
       </c>
-      <c r="C89" s="12"/>
-      <c r="D89" s="13"/>
+      <c r="C89" s="12">
+        <v>45719</v>
+      </c>
+      <c r="D89" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E89" s="12"/>
-      <c r="F89" s="13"/>
-      <c r="G89" s="13"/>
-      <c r="H89" s="13"/>
-      <c r="I89" s="14"/>
-      <c r="J89" s="15"/>
-    </row>
-    <row r="90" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B90" s="18">
+      <c r="F89" s="13">
+        <f>$B$87</f>
+        <v>85</v>
+      </c>
+      <c r="G89" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H89" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I89" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="J89" s="15" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="90" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B90" s="11">
+        <f t="shared" si="28"/>
+        <v>88</v>
+      </c>
+      <c r="C90" s="12">
+        <v>45719</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E90" s="12"/>
+      <c r="F90" s="13">
+        <f>$B$87</f>
+        <v>85</v>
+      </c>
+      <c r="G90" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H90" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I90" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="J90" s="15" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="91" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B91" s="11">
+        <f t="shared" si="28"/>
+        <v>89</v>
+      </c>
+      <c r="C91" s="12">
+        <v>45719</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E91" s="12"/>
+      <c r="F91" s="13">
+        <f>$B$87</f>
+        <v>85</v>
+      </c>
+      <c r="G91" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H91" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I91" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="J91" s="15" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="92" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B92" s="11">
+        <f t="shared" si="28"/>
+        <v>90</v>
+      </c>
+      <c r="C92" s="12"/>
+      <c r="D92" s="13"/>
+      <c r="E92" s="12"/>
+      <c r="F92" s="13"/>
+      <c r="G92" s="13"/>
+      <c r="H92" s="13"/>
+      <c r="I92" s="14"/>
+      <c r="J92" s="15"/>
+    </row>
+    <row r="93" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B93" s="11">
+        <f t="shared" si="28"/>
+        <v>91</v>
+      </c>
+      <c r="C93" s="12"/>
+      <c r="D93" s="13"/>
+      <c r="E93" s="12"/>
+      <c r="F93" s="13"/>
+      <c r="G93" s="13"/>
+      <c r="H93" s="13"/>
+      <c r="I93" s="14"/>
+      <c r="J93" s="15"/>
+    </row>
+    <row r="94" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B94" s="11">
+        <f t="shared" si="28"/>
+        <v>92</v>
+      </c>
+      <c r="C94" s="12"/>
+      <c r="D94" s="13"/>
+      <c r="E94" s="12"/>
+      <c r="F94" s="13"/>
+      <c r="G94" s="13"/>
+      <c r="H94" s="13"/>
+      <c r="I94" s="14"/>
+      <c r="J94" s="15"/>
+    </row>
+    <row r="95" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B95" s="11">
+        <f t="shared" si="28"/>
+        <v>93</v>
+      </c>
+      <c r="C95" s="12"/>
+      <c r="D95" s="13"/>
+      <c r="E95" s="12"/>
+      <c r="F95" s="13"/>
+      <c r="G95" s="13"/>
+      <c r="H95" s="13"/>
+      <c r="I95" s="14"/>
+      <c r="J95" s="15"/>
+    </row>
+    <row r="96" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B96" s="11">
+        <f t="shared" si="28"/>
+        <v>94</v>
+      </c>
+      <c r="C96" s="12"/>
+      <c r="D96" s="13"/>
+      <c r="E96" s="12"/>
+      <c r="F96" s="13"/>
+      <c r="G96" s="13"/>
+      <c r="H96" s="13"/>
+      <c r="I96" s="14"/>
+      <c r="J96" s="15"/>
+    </row>
+    <row r="97" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B97" s="11">
+        <f t="shared" si="28"/>
+        <v>95</v>
+      </c>
+      <c r="C97" s="12"/>
+      <c r="D97" s="13"/>
+      <c r="E97" s="12"/>
+      <c r="F97" s="13"/>
+      <c r="G97" s="13"/>
+      <c r="H97" s="13"/>
+      <c r="I97" s="14"/>
+      <c r="J97" s="15"/>
+    </row>
+    <row r="98" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B98" s="11">
+        <f t="shared" ref="B98" si="29">B97+1</f>
+        <v>96</v>
+      </c>
+      <c r="C98" s="12"/>
+      <c r="D98" s="13"/>
+      <c r="E98" s="12"/>
+      <c r="F98" s="13"/>
+      <c r="G98" s="13"/>
+      <c r="H98" s="13"/>
+      <c r="I98" s="14"/>
+      <c r="J98" s="15"/>
+    </row>
+    <row r="99" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B99" s="18">
         <f t="shared" si="0"/>
-        <v>88</v>
-      </c>
-      <c r="C90" s="19"/>
-      <c r="D90" s="20"/>
-      <c r="E90" s="19"/>
-      <c r="F90" s="20"/>
-      <c r="G90" s="20"/>
-      <c r="H90" s="20"/>
-      <c r="I90" s="21"/>
-      <c r="J90" s="22"/>
+        <v>97</v>
+      </c>
+      <c r="C99" s="19"/>
+      <c r="D99" s="20"/>
+      <c r="E99" s="19"/>
+      <c r="F99" s="20"/>
+      <c r="G99" s="20"/>
+      <c r="H99" s="20"/>
+      <c r="I99" s="21"/>
+      <c r="J99" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:J90" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
+  <autoFilter ref="B2:J99" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B3:J45 A43:A45 A46:J46 A47:A51 B47:J90">
+  <conditionalFormatting sqref="B3:J45 A43:A45 A46:J46 A47:A51 B47:J99">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>
@@ -5147,25 +5469,25 @@
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H3:H64 H66:H77 H86:H90</xm:sqref>
+          <xm:sqref>H3:H64 H66:H77 H97:H99</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D6F2F62E-6D63-4E2D-8772-1211A4C3A979}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$10</xm:f>
           </x14:formula1>
-          <xm:sqref>H65 H78:H85</xm:sqref>
+          <xm:sqref>H65 H78:H96</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C61EF0EC-B820-4CEA-8AA2-04B5D172AE2C}">
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D90</xm:sqref>
+          <xm:sqref>D3:D99</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G90</xm:sqref>
+          <xm:sqref>G3:G99</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B3D76B4-9EAD-47C0-93C4-7BCC7337A4DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD05229B-96D9-4D3D-A93A-E5878A560DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="149">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -2056,6 +2056,16 @@
     </rPh>
     <rPh sb="4" eb="6">
       <t>コウチク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メニューへ戻るボタン追加</t>
+    <rPh sb="5" eb="6">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ツイカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5259,9 +5269,11 @@
         <v>45719</v>
       </c>
       <c r="D89" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E89" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E89" s="12">
+        <v>45720</v>
+      </c>
       <c r="F89" s="13">
         <f>$B$87</f>
         <v>85</v>
@@ -5342,14 +5354,29 @@
         <f t="shared" si="28"/>
         <v>90</v>
       </c>
-      <c r="C92" s="12"/>
-      <c r="D92" s="13"/>
+      <c r="C92" s="12">
+        <v>45720</v>
+      </c>
+      <c r="D92" s="13" t="s">
+        <v>11</v>
+      </c>
       <c r="E92" s="12"/>
-      <c r="F92" s="13"/>
-      <c r="G92" s="13"/>
-      <c r="H92" s="13"/>
-      <c r="I92" s="14"/>
-      <c r="J92" s="15"/>
+      <c r="F92" s="13">
+        <f>$B$87</f>
+        <v>85</v>
+      </c>
+      <c r="G92" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H92" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I92" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="J92" s="15" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="93" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B93" s="11">

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD05229B-96D9-4D3D-A93A-E5878A560DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5B59483-12D5-4F7C-A07C-B3150A90E17D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="選択情報" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作業項目!$B$2:$J$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作業項目!$B$2:$J$102</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="153">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -2060,12 +2060,58 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>メニューへ戻るボタン追加</t>
-    <rPh sb="5" eb="6">
-      <t>モド</t>
-    </rPh>
-    <rPh sb="10" eb="12">
+    <t>メインメニュー画面</t>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>システム管理メニュー Lv.01追加</t>
+    <rPh sb="4" eb="6">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
       <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示メニュー情報 : システム管理メニュー追加(3行目)</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ギョウメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ActionServlet01 : システム管理メニューへの遷移追加</t>
+    <rPh sb="22" eb="24">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HtmlSystemMenuクラス構築</t>
+    <rPh sb="17" eb="19">
+      <t>コウチク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2757,7 +2803,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="A1:K99"/>
+  <dimension ref="A1:K102"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -2955,7 +3001,7 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
-        <f t="shared" ref="A8:B99" si="0">B7+1</f>
+        <f t="shared" ref="A8:B102" si="0">B7+1</f>
         <v>6</v>
       </c>
       <c r="C8" s="12">
@@ -4511,7 +4557,10 @@
         <v>10</v>
       </c>
       <c r="E62" s="12"/>
-      <c r="F62" s="13"/>
+      <c r="F62" s="13">
+        <f>$B$61</f>
+        <v>59</v>
+      </c>
       <c r="G62" s="13" t="s">
         <v>14</v>
       </c>
@@ -4527,75 +4576,106 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B63" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B63" si="21">B62+1</f>
         <v>61</v>
       </c>
-      <c r="C63" s="12"/>
-      <c r="D63" s="13"/>
+      <c r="C63" s="12">
+        <v>45722</v>
+      </c>
+      <c r="D63" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E63" s="12"/>
-      <c r="F63" s="13"/>
-      <c r="G63" s="13"/>
-      <c r="H63" s="13"/>
-      <c r="I63" s="14"/>
-      <c r="J63" s="15"/>
+      <c r="F63" s="13">
+        <f>$B$61</f>
+        <v>59</v>
+      </c>
+      <c r="G63" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H63" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I63" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="J63" s="15" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B64" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B64" si="22">B63+1</f>
         <v>62</v>
       </c>
-      <c r="C64" s="12"/>
-      <c r="D64" s="13"/>
+      <c r="C64" s="12">
+        <v>45722</v>
+      </c>
+      <c r="D64" s="13" t="s">
+        <v>12</v>
+      </c>
       <c r="E64" s="12"/>
-      <c r="F64" s="13"/>
-      <c r="G64" s="13"/>
-      <c r="H64" s="13"/>
-      <c r="I64" s="14"/>
-      <c r="J64" s="15"/>
+      <c r="F64" s="13">
+        <f>$B$61</f>
+        <v>59</v>
+      </c>
+      <c r="G64" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H64" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I64" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="J64" s="15" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B65" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B65:B68" si="23">B64+1</f>
         <v>63</v>
       </c>
       <c r="C65" s="12">
-        <v>45698</v>
+        <v>45722</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E65" s="12"/>
-      <c r="F65" s="13"/>
+      <c r="F65" s="13">
+        <f>$B$61</f>
+        <v>59</v>
+      </c>
       <c r="G65" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H65" s="13" t="s">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="I65" s="14" t="s">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="J65" s="15" t="s">
-        <v>105</v>
+        <v>151</v>
       </c>
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B66" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="23"/>
         <v>64</v>
       </c>
       <c r="C66" s="12">
-        <v>45698</v>
+        <v>45722</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E66" s="12">
-        <v>45717</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E66" s="12"/>
       <c r="F66" s="13">
-        <f>$B$65</f>
-        <v>63</v>
+        <f>$B$61</f>
+        <v>59</v>
       </c>
       <c r="G66" s="13" t="s">
         <v>14</v>
@@ -4604,73 +4684,39 @@
         <v>19</v>
       </c>
       <c r="I66" s="14" t="s">
-        <v>106</v>
+        <v>148</v>
       </c>
       <c r="J66" s="15" t="s">
-        <v>107</v>
+        <v>152</v>
       </c>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B67" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="23"/>
         <v>65</v>
       </c>
-      <c r="C67" s="12">
-        <v>45698</v>
-      </c>
-      <c r="D67" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E67" s="12">
-        <v>45698</v>
-      </c>
-      <c r="F67" s="13">
-        <f t="shared" ref="F67:F74" si="21">$B$66</f>
-        <v>64</v>
-      </c>
-      <c r="G67" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H67" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I67" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="J67" s="15" t="s">
-        <v>108</v>
-      </c>
+      <c r="C67" s="12"/>
+      <c r="D67" s="13"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="13"/>
+      <c r="G67" s="13"/>
+      <c r="H67" s="13"/>
+      <c r="I67" s="14"/>
+      <c r="J67" s="15"/>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B68" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="23"/>
         <v>66</v>
       </c>
-      <c r="C68" s="12">
-        <v>45698</v>
-      </c>
-      <c r="D68" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E68" s="12">
-        <v>45714</v>
-      </c>
-      <c r="F68" s="13">
-        <f t="shared" si="21"/>
-        <v>64</v>
-      </c>
-      <c r="G68" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H68" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I68" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="J68" s="15" t="s">
-        <v>119</v>
-      </c>
+      <c r="C68" s="12"/>
+      <c r="D68" s="13"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="13"/>
+      <c r="G68" s="13"/>
+      <c r="H68" s="13"/>
+      <c r="I68" s="14"/>
+      <c r="J68" s="15"/>
     </row>
     <row r="69" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B69" s="11">
@@ -4681,26 +4727,21 @@
         <v>45698</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E69" s="12">
-        <v>45714</v>
-      </c>
-      <c r="F69" s="13">
-        <f t="shared" si="21"/>
-        <v>64</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E69" s="12"/>
+      <c r="F69" s="13"/>
       <c r="G69" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H69" s="13" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="I69" s="14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J69" s="15" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
     </row>
     <row r="70" spans="2:10" x14ac:dyDescent="0.3">
@@ -4709,17 +4750,17 @@
         <v>68</v>
       </c>
       <c r="C70" s="12">
-        <v>45714</v>
+        <v>45698</v>
       </c>
       <c r="D70" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E70" s="12">
-        <v>45714</v>
+        <v>45717</v>
       </c>
       <c r="F70" s="13">
-        <f t="shared" si="21"/>
-        <v>64</v>
+        <f>$B$69</f>
+        <v>67</v>
       </c>
       <c r="G70" s="13" t="s">
         <v>14</v>
@@ -4731,7 +4772,7 @@
         <v>106</v>
       </c>
       <c r="J70" s="15" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
     </row>
     <row r="71" spans="2:10" x14ac:dyDescent="0.3">
@@ -4740,17 +4781,17 @@
         <v>69</v>
       </c>
       <c r="C71" s="12">
-        <v>45714</v>
+        <v>45698</v>
       </c>
       <c r="D71" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E71" s="12">
-        <v>45715</v>
+        <v>45698</v>
       </c>
       <c r="F71" s="13">
-        <f t="shared" si="21"/>
-        <v>64</v>
+        <f t="shared" ref="F71:F78" si="24">$B$70</f>
+        <v>68</v>
       </c>
       <c r="G71" s="13" t="s">
         <v>14</v>
@@ -4762,7 +4803,7 @@
         <v>106</v>
       </c>
       <c r="J71" s="15" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
     </row>
     <row r="72" spans="2:10" x14ac:dyDescent="0.3">
@@ -4771,17 +4812,17 @@
         <v>70</v>
       </c>
       <c r="C72" s="12">
-        <v>45715</v>
+        <v>45698</v>
       </c>
       <c r="D72" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E72" s="12">
-        <v>45715</v>
+        <v>45714</v>
       </c>
       <c r="F72" s="13">
-        <f t="shared" si="21"/>
-        <v>64</v>
+        <f t="shared" si="24"/>
+        <v>68</v>
       </c>
       <c r="G72" s="13" t="s">
         <v>14</v>
@@ -4793,7 +4834,7 @@
         <v>106</v>
       </c>
       <c r="J72" s="15" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="73" spans="2:10" x14ac:dyDescent="0.3">
@@ -4802,7 +4843,7 @@
         <v>71</v>
       </c>
       <c r="C73" s="12">
-        <v>45715</v>
+        <v>45698</v>
       </c>
       <c r="D73" s="13" t="s">
         <v>12</v>
@@ -4811,8 +4852,8 @@
         <v>45714</v>
       </c>
       <c r="F73" s="13">
-        <f t="shared" si="21"/>
-        <v>64</v>
+        <f t="shared" si="24"/>
+        <v>68</v>
       </c>
       <c r="G73" s="13" t="s">
         <v>14</v>
@@ -4824,7 +4865,7 @@
         <v>106</v>
       </c>
       <c r="J73" s="15" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.3">
@@ -4833,17 +4874,17 @@
         <v>72</v>
       </c>
       <c r="C74" s="12">
-        <v>45717</v>
+        <v>45714</v>
       </c>
       <c r="D74" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E74" s="12">
-        <v>45717</v>
+        <v>45714</v>
       </c>
       <c r="F74" s="13">
-        <f t="shared" si="21"/>
-        <v>64</v>
+        <f t="shared" si="24"/>
+        <v>68</v>
       </c>
       <c r="G74" s="13" t="s">
         <v>14</v>
@@ -4855,7 +4896,7 @@
         <v>106</v>
       </c>
       <c r="J74" s="15" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="75" spans="2:10" x14ac:dyDescent="0.3">
@@ -4864,17 +4905,17 @@
         <v>73</v>
       </c>
       <c r="C75" s="12">
-        <v>45717</v>
+        <v>45714</v>
       </c>
       <c r="D75" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E75" s="12">
-        <v>45717</v>
+        <v>45715</v>
       </c>
       <c r="F75" s="13">
-        <f>$B$74</f>
-        <v>72</v>
+        <f t="shared" si="24"/>
+        <v>68</v>
       </c>
       <c r="G75" s="13" t="s">
         <v>14</v>
@@ -4883,10 +4924,10 @@
         <v>19</v>
       </c>
       <c r="I75" s="14" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="J75" s="15" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="76" spans="2:10" x14ac:dyDescent="0.3">
@@ -4895,17 +4936,17 @@
         <v>74</v>
       </c>
       <c r="C76" s="12">
-        <v>45717</v>
+        <v>45715</v>
       </c>
       <c r="D76" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E76" s="12">
-        <v>45717</v>
+        <v>45715</v>
       </c>
       <c r="F76" s="13">
-        <f>$B$74</f>
-        <v>72</v>
+        <f t="shared" si="24"/>
+        <v>68</v>
       </c>
       <c r="G76" s="13" t="s">
         <v>14</v>
@@ -4914,10 +4955,10 @@
         <v>19</v>
       </c>
       <c r="I76" s="14" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="J76" s="15" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="77" spans="2:10" x14ac:dyDescent="0.3">
@@ -4926,17 +4967,17 @@
         <v>75</v>
       </c>
       <c r="C77" s="12">
-        <v>45717</v>
+        <v>45715</v>
       </c>
       <c r="D77" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E77" s="12">
-        <v>45717</v>
+        <v>45714</v>
       </c>
       <c r="F77" s="13">
-        <f>$B$74</f>
-        <v>72</v>
+        <f t="shared" si="24"/>
+        <v>68</v>
       </c>
       <c r="G77" s="13" t="s">
         <v>14</v>
@@ -4945,10 +4986,10 @@
         <v>19</v>
       </c>
       <c r="I77" s="14" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="J77" s="15" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="78" spans="2:10" x14ac:dyDescent="0.3">
@@ -4960,24 +5001,26 @@
         <v>45717</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E78" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E78" s="12">
+        <v>45717</v>
+      </c>
       <c r="F78" s="13">
-        <f>$B$65</f>
-        <v>63</v>
+        <f t="shared" si="24"/>
+        <v>68</v>
       </c>
       <c r="G78" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H78" s="13" t="s">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="I78" s="14" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="J78" s="15" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="79" spans="2:10" x14ac:dyDescent="0.3">
@@ -4995,20 +5038,20 @@
         <v>45717</v>
       </c>
       <c r="F79" s="13">
-        <f t="shared" ref="F79:F85" si="22">$B$78</f>
+        <f>$B$78</f>
         <v>76</v>
       </c>
       <c r="G79" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H79" s="13" t="s">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="I79" s="14" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="J79" s="15" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="80" spans="2:10" x14ac:dyDescent="0.3">
@@ -5026,25 +5069,25 @@
         <v>45717</v>
       </c>
       <c r="F80" s="13">
-        <f t="shared" si="22"/>
+        <f>$B$78</f>
         <v>76</v>
       </c>
       <c r="G80" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H80" s="13" t="s">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="I80" s="14" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="J80" s="15" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="81" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B81" s="11">
-        <f t="shared" ref="B81" si="23">B80+1</f>
+        <f t="shared" si="0"/>
         <v>79</v>
       </c>
       <c r="C81" s="12">
@@ -5057,7 +5100,7 @@
         <v>45717</v>
       </c>
       <c r="F81" s="13">
-        <f t="shared" si="22"/>
+        <f>$B$78</f>
         <v>76</v>
       </c>
       <c r="G81" s="13" t="s">
@@ -5067,27 +5110,27 @@
         <v>19</v>
       </c>
       <c r="I81" s="14" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="J81" s="15" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="82" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B82" s="11">
-        <f t="shared" ref="B82" si="24">B81+1</f>
+        <f t="shared" si="0"/>
         <v>80</v>
       </c>
       <c r="C82" s="12">
         <v>45717</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E82" s="12"/>
       <c r="F82" s="13">
-        <f t="shared" si="22"/>
-        <v>76</v>
+        <f>$B$69</f>
+        <v>67</v>
       </c>
       <c r="G82" s="13" t="s">
         <v>14</v>
@@ -5096,56 +5139,60 @@
         <v>102</v>
       </c>
       <c r="I82" s="14" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="J82" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B83" s="11">
-        <f t="shared" ref="B83" si="25">B82+1</f>
+        <f t="shared" si="0"/>
         <v>81</v>
       </c>
       <c r="C83" s="12">
         <v>45717</v>
       </c>
       <c r="D83" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E83" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E83" s="12">
+        <v>45717</v>
+      </c>
       <c r="F83" s="13">
-        <f t="shared" si="22"/>
-        <v>76</v>
+        <f t="shared" ref="F83:F89" si="25">$B$82</f>
+        <v>80</v>
       </c>
       <c r="G83" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H83" s="13" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="I83" s="14" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="J83" s="15" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="84" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B84" s="11">
-        <f t="shared" ref="B84" si="26">B83+1</f>
+        <f t="shared" si="0"/>
         <v>82</v>
       </c>
       <c r="C84" s="12">
         <v>45717</v>
       </c>
       <c r="D84" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E84" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E84" s="12">
+        <v>45717</v>
+      </c>
       <c r="F84" s="13">
-        <f t="shared" si="22"/>
-        <v>76</v>
+        <f t="shared" si="25"/>
+        <v>80</v>
       </c>
       <c r="G84" s="13" t="s">
         <v>14</v>
@@ -5157,185 +5204,183 @@
         <v>132</v>
       </c>
       <c r="J84" s="15" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B85" s="11">
-        <f t="shared" ref="B85" si="27">B84+1</f>
+        <f t="shared" ref="B85" si="26">B84+1</f>
         <v>83</v>
       </c>
       <c r="C85" s="12">
         <v>45717</v>
       </c>
       <c r="D85" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E85" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E85" s="12">
+        <v>45717</v>
+      </c>
       <c r="F85" s="13">
-        <f t="shared" si="22"/>
-        <v>76</v>
+        <f t="shared" si="25"/>
+        <v>80</v>
       </c>
       <c r="G85" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H85" s="13" t="s">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="I85" s="14" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J85" s="15" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B86" s="11">
-        <f t="shared" ref="B86:B97" si="28">B85+1</f>
+        <f t="shared" ref="B86" si="27">B85+1</f>
         <v>84</v>
       </c>
-      <c r="C86" s="12"/>
-      <c r="D86" s="13"/>
+      <c r="C86" s="12">
+        <v>45717</v>
+      </c>
+      <c r="D86" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E86" s="12"/>
-      <c r="F86" s="13"/>
-      <c r="G86" s="13"/>
-      <c r="H86" s="13"/>
-      <c r="I86" s="14"/>
-      <c r="J86" s="15"/>
+      <c r="F86" s="13">
+        <f t="shared" si="25"/>
+        <v>80</v>
+      </c>
+      <c r="G86" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H86" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I86" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="J86" s="15" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="87" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B87" s="11">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="B87" si="28">B86+1</f>
         <v>85</v>
       </c>
       <c r="C87" s="12">
-        <v>45719</v>
+        <v>45717</v>
       </c>
       <c r="D87" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E87" s="12"/>
-      <c r="F87" s="13"/>
+      <c r="F87" s="13">
+        <f t="shared" si="25"/>
+        <v>80</v>
+      </c>
       <c r="G87" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H87" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I87" s="15" t="s">
-        <v>143</v>
+        <v>19</v>
+      </c>
+      <c r="I87" s="14" t="s">
+        <v>138</v>
       </c>
       <c r="J87" s="15" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
     <row r="88" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B88" s="11">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="B88" si="29">B87+1</f>
         <v>86</v>
       </c>
       <c r="C88" s="12">
-        <v>45719</v>
+        <v>45717</v>
       </c>
       <c r="D88" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E88" s="12">
-        <v>45719</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E88" s="12"/>
       <c r="F88" s="13">
-        <f>$B$87</f>
-        <v>85</v>
+        <f t="shared" si="25"/>
+        <v>80</v>
       </c>
       <c r="G88" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H88" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I88" s="15" t="s">
-        <v>143</v>
+        <v>102</v>
+      </c>
+      <c r="I88" s="14" t="s">
+        <v>132</v>
       </c>
       <c r="J88" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="89" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B89" s="11">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="B89" si="30">B88+1</f>
         <v>87</v>
       </c>
       <c r="C89" s="12">
-        <v>45719</v>
+        <v>45717</v>
       </c>
       <c r="D89" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E89" s="12">
-        <v>45720</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E89" s="12"/>
       <c r="F89" s="13">
-        <f>$B$87</f>
-        <v>85</v>
+        <f t="shared" si="25"/>
+        <v>80</v>
       </c>
       <c r="G89" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H89" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I89" s="15" t="s">
-        <v>143</v>
+        <v>102</v>
+      </c>
+      <c r="I89" s="14" t="s">
+        <v>132</v>
       </c>
       <c r="J89" s="15" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="90" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B90" s="11">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="B90:B101" si="31">B89+1</f>
         <v>88</v>
       </c>
-      <c r="C90" s="12">
-        <v>45719</v>
-      </c>
-      <c r="D90" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C90" s="12"/>
+      <c r="D90" s="13"/>
       <c r="E90" s="12"/>
-      <c r="F90" s="13">
-        <f>$B$87</f>
-        <v>85</v>
-      </c>
-      <c r="G90" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H90" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I90" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="J90" s="15" t="s">
-        <v>146</v>
-      </c>
+      <c r="F90" s="13"/>
+      <c r="G90" s="13"/>
+      <c r="H90" s="13"/>
+      <c r="I90" s="14"/>
+      <c r="J90" s="15"/>
     </row>
     <row r="91" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B91" s="11">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>89</v>
       </c>
       <c r="C91" s="12">
         <v>45719</v>
       </c>
       <c r="D91" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E91" s="12"/>
-      <c r="F91" s="13">
-        <f>$B$87</f>
-        <v>85</v>
-      </c>
+      <c r="F91" s="13"/>
       <c r="G91" s="13" t="s">
         <v>14</v>
       </c>
@@ -5346,24 +5391,26 @@
         <v>143</v>
       </c>
       <c r="J91" s="15" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="92" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B92" s="11">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>90</v>
       </c>
       <c r="C92" s="12">
-        <v>45720</v>
+        <v>45719</v>
       </c>
       <c r="D92" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E92" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E92" s="12">
+        <v>45719</v>
+      </c>
       <c r="F92" s="13">
-        <f>$B$87</f>
-        <v>85</v>
+        <f>$B$91</f>
+        <v>89</v>
       </c>
       <c r="G92" s="13" t="s">
         <v>14</v>
@@ -5375,54 +5422,101 @@
         <v>143</v>
       </c>
       <c r="J92" s="15" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="93" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B93" s="11">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>91</v>
       </c>
-      <c r="C93" s="12"/>
-      <c r="D93" s="13"/>
-      <c r="E93" s="12"/>
-      <c r="F93" s="13"/>
-      <c r="G93" s="13"/>
-      <c r="H93" s="13"/>
-      <c r="I93" s="14"/>
-      <c r="J93" s="15"/>
+      <c r="C93" s="12">
+        <v>45719</v>
+      </c>
+      <c r="D93" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E93" s="12">
+        <v>45720</v>
+      </c>
+      <c r="F93" s="13">
+        <f>$B$91</f>
+        <v>89</v>
+      </c>
+      <c r="G93" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H93" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I93" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="J93" s="15" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="94" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B94" s="11">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>92</v>
       </c>
-      <c r="C94" s="12"/>
-      <c r="D94" s="13"/>
+      <c r="C94" s="12">
+        <v>45719</v>
+      </c>
+      <c r="D94" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E94" s="12"/>
-      <c r="F94" s="13"/>
-      <c r="G94" s="13"/>
-      <c r="H94" s="13"/>
-      <c r="I94" s="14"/>
-      <c r="J94" s="15"/>
+      <c r="F94" s="13">
+        <f>$B$91</f>
+        <v>89</v>
+      </c>
+      <c r="G94" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H94" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I94" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="J94" s="15" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="95" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B95" s="11">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>93</v>
       </c>
-      <c r="C95" s="12"/>
-      <c r="D95" s="13"/>
+      <c r="C95" s="12">
+        <v>45719</v>
+      </c>
+      <c r="D95" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E95" s="12"/>
-      <c r="F95" s="13"/>
-      <c r="G95" s="13"/>
-      <c r="H95" s="13"/>
-      <c r="I95" s="14"/>
-      <c r="J95" s="15"/>
+      <c r="F95" s="13">
+        <f>$B$91</f>
+        <v>89</v>
+      </c>
+      <c r="G95" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H95" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I95" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="J95" s="15" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="96" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B96" s="11">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>94</v>
       </c>
       <c r="C96" s="12"/>
@@ -5436,7 +5530,7 @@
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97" s="11">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>95</v>
       </c>
       <c r="C97" s="12"/>
@@ -5450,7 +5544,7 @@
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98" s="11">
-        <f t="shared" ref="B98" si="29">B97+1</f>
+        <f t="shared" si="31"/>
         <v>96</v>
       </c>
       <c r="C98" s="12"/>
@@ -5462,24 +5556,66 @@
       <c r="I98" s="14"/>
       <c r="J98" s="15"/>
     </row>
-    <row r="99" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="18">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B99" s="11">
+        <f t="shared" si="31"/>
+        <v>97</v>
+      </c>
+      <c r="C99" s="12"/>
+      <c r="D99" s="13"/>
+      <c r="E99" s="12"/>
+      <c r="F99" s="13"/>
+      <c r="G99" s="13"/>
+      <c r="H99" s="13"/>
+      <c r="I99" s="14"/>
+      <c r="J99" s="15"/>
+    </row>
+    <row r="100" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B100" s="11">
+        <f t="shared" si="31"/>
+        <v>98</v>
+      </c>
+      <c r="C100" s="12"/>
+      <c r="D100" s="13"/>
+      <c r="E100" s="12"/>
+      <c r="F100" s="13"/>
+      <c r="G100" s="13"/>
+      <c r="H100" s="13"/>
+      <c r="I100" s="14"/>
+      <c r="J100" s="15"/>
+    </row>
+    <row r="101" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B101" s="11">
+        <f t="shared" si="31"/>
+        <v>99</v>
+      </c>
+      <c r="C101" s="12"/>
+      <c r="D101" s="13"/>
+      <c r="E101" s="12"/>
+      <c r="F101" s="13"/>
+      <c r="G101" s="13"/>
+      <c r="H101" s="13"/>
+      <c r="I101" s="14"/>
+      <c r="J101" s="15"/>
+    </row>
+    <row r="102" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B102" s="18">
         <f t="shared" si="0"/>
-        <v>97</v>
-      </c>
-      <c r="C99" s="19"/>
-      <c r="D99" s="20"/>
-      <c r="E99" s="19"/>
-      <c r="F99" s="20"/>
-      <c r="G99" s="20"/>
-      <c r="H99" s="20"/>
-      <c r="I99" s="21"/>
-      <c r="J99" s="22"/>
+        <v>100</v>
+      </c>
+      <c r="C102" s="19"/>
+      <c r="D102" s="20"/>
+      <c r="E102" s="19"/>
+      <c r="F102" s="20"/>
+      <c r="G102" s="20"/>
+      <c r="H102" s="20"/>
+      <c r="I102" s="21"/>
+      <c r="J102" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:J99" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
+  <autoFilter ref="B2:J102" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B3:J45 A43:A45 A46:J46 A47:A51 B47:J99">
+  <conditionalFormatting sqref="B3:J45 A43:A45 A46:J46 A47:A51 B47:J102">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>
@@ -5496,25 +5632,25 @@
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H3:H64 H66:H77 H97:H99</xm:sqref>
+          <xm:sqref>H100:H102 H70:H81 H3:H62 H68</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D6F2F62E-6D63-4E2D-8772-1211A4C3A979}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$10</xm:f>
           </x14:formula1>
-          <xm:sqref>H65 H78:H96</xm:sqref>
+          <xm:sqref>H69 H82:H99 H63:H67</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C61EF0EC-B820-4CEA-8AA2-04B5D172AE2C}">
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D99</xm:sqref>
+          <xm:sqref>D3:D102</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G99</xm:sqref>
+          <xm:sqref>G3:G102</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5B59483-12D5-4F7C-A07C-B3150A90E17D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42978670-18F8-4873-AB7C-138BCE2C5E4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="選択情報" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作業項目!$B$2:$J$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作業項目!$B$2:$J$103</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="155">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -2112,6 +2112,47 @@
     <t>HtmlSystemMenuクラス構築</t>
     <rPh sb="17" eb="19">
       <t>コウチク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示情報 : システム管理メニュー追加</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示メニュー情報 : システム管理メニューLv.01 : テーブル一覧、エンティティ一覧、画面一覧</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>イチラン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2803,7 +2844,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -3001,7 +3042,7 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
-        <f t="shared" ref="A8:B102" si="0">B7+1</f>
+        <f t="shared" ref="A8:B103" si="0">B7+1</f>
         <v>6</v>
       </c>
       <c r="C8" s="12">
@@ -4605,7 +4646,7 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B64" s="11">
-        <f t="shared" ref="B64" si="22">B63+1</f>
+        <f t="shared" ref="B64:B66" si="22">B63+1</f>
         <v>62</v>
       </c>
       <c r="C64" s="12">
@@ -4634,14 +4675,14 @@
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B65" s="11">
-        <f t="shared" ref="B65:B68" si="23">B64+1</f>
+        <f t="shared" si="22"/>
         <v>63</v>
       </c>
       <c r="C65" s="12">
-        <v>45722</v>
+        <v>45726</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E65" s="12"/>
       <c r="F65" s="13">
@@ -4658,19 +4699,19 @@
         <v>148</v>
       </c>
       <c r="J65" s="15" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B66" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>64</v>
       </c>
       <c r="C66" s="12">
         <v>45722</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E66" s="12"/>
       <c r="F66" s="13">
@@ -4687,62 +4728,80 @@
         <v>148</v>
       </c>
       <c r="J66" s="15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B67" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="B67:B69" si="23">B66+1</f>
         <v>65</v>
       </c>
-      <c r="C67" s="12"/>
-      <c r="D67" s="13"/>
+      <c r="C67" s="12">
+        <v>45722</v>
+      </c>
+      <c r="D67" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E67" s="12"/>
-      <c r="F67" s="13"/>
-      <c r="G67" s="13"/>
-      <c r="H67" s="13"/>
-      <c r="I67" s="14"/>
-      <c r="J67" s="15"/>
+      <c r="F67" s="13">
+        <f>$B$61</f>
+        <v>59</v>
+      </c>
+      <c r="G67" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H67" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I67" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="J67" s="15" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B68" s="11">
         <f t="shared" si="23"/>
         <v>66</v>
       </c>
-      <c r="C68" s="12"/>
-      <c r="D68" s="13"/>
+      <c r="C68" s="12">
+        <v>45726</v>
+      </c>
+      <c r="D68" s="13" t="s">
+        <v>11</v>
+      </c>
       <c r="E68" s="12"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="13"/>
-      <c r="H68" s="13"/>
-      <c r="I68" s="14"/>
-      <c r="J68" s="15"/>
+      <c r="F68" s="13">
+        <f>$B$67</f>
+        <v>65</v>
+      </c>
+      <c r="G68" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H68" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I68" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="J68" s="15" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="69" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B69" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="23"/>
         <v>67</v>
       </c>
-      <c r="C69" s="12">
-        <v>45698</v>
-      </c>
-      <c r="D69" s="13" t="s">
-        <v>11</v>
-      </c>
+      <c r="C69" s="12"/>
+      <c r="D69" s="13"/>
       <c r="E69" s="12"/>
       <c r="F69" s="13"/>
-      <c r="G69" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H69" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="I69" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="J69" s="15" t="s">
-        <v>105</v>
-      </c>
+      <c r="G69" s="13"/>
+      <c r="H69" s="13"/>
+      <c r="I69" s="14"/>
+      <c r="J69" s="15"/>
     </row>
     <row r="70" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B70" s="11">
@@ -4753,26 +4812,21 @@
         <v>45698</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E70" s="12">
-        <v>45717</v>
-      </c>
-      <c r="F70" s="13">
-        <f>$B$69</f>
-        <v>67</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E70" s="12"/>
+      <c r="F70" s="13"/>
       <c r="G70" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H70" s="13" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="I70" s="14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J70" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="71" spans="2:10" x14ac:dyDescent="0.3">
@@ -4787,10 +4841,10 @@
         <v>12</v>
       </c>
       <c r="E71" s="12">
-        <v>45698</v>
+        <v>45717</v>
       </c>
       <c r="F71" s="13">
-        <f t="shared" ref="F71:F78" si="24">$B$70</f>
+        <f>$B$70</f>
         <v>68</v>
       </c>
       <c r="G71" s="13" t="s">
@@ -4803,7 +4857,7 @@
         <v>106</v>
       </c>
       <c r="J71" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="72" spans="2:10" x14ac:dyDescent="0.3">
@@ -4818,11 +4872,11 @@
         <v>12</v>
       </c>
       <c r="E72" s="12">
-        <v>45714</v>
+        <v>45698</v>
       </c>
       <c r="F72" s="13">
-        <f t="shared" si="24"/>
-        <v>68</v>
+        <f t="shared" ref="F72:F79" si="24">$B$71</f>
+        <v>69</v>
       </c>
       <c r="G72" s="13" t="s">
         <v>14</v>
@@ -4834,7 +4888,7 @@
         <v>106</v>
       </c>
       <c r="J72" s="15" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
     </row>
     <row r="73" spans="2:10" x14ac:dyDescent="0.3">
@@ -4853,7 +4907,7 @@
       </c>
       <c r="F73" s="13">
         <f t="shared" si="24"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G73" s="13" t="s">
         <v>14</v>
@@ -4865,7 +4919,7 @@
         <v>106</v>
       </c>
       <c r="J73" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.3">
@@ -4874,7 +4928,7 @@
         <v>72</v>
       </c>
       <c r="C74" s="12">
-        <v>45714</v>
+        <v>45698</v>
       </c>
       <c r="D74" s="13" t="s">
         <v>12</v>
@@ -4884,7 +4938,7 @@
       </c>
       <c r="F74" s="13">
         <f t="shared" si="24"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G74" s="13" t="s">
         <v>14</v>
@@ -4896,7 +4950,7 @@
         <v>106</v>
       </c>
       <c r="J74" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="75" spans="2:10" x14ac:dyDescent="0.3">
@@ -4911,11 +4965,11 @@
         <v>12</v>
       </c>
       <c r="E75" s="12">
-        <v>45715</v>
+        <v>45714</v>
       </c>
       <c r="F75" s="13">
         <f t="shared" si="24"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G75" s="13" t="s">
         <v>14</v>
@@ -4927,7 +4981,7 @@
         <v>106</v>
       </c>
       <c r="J75" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="76" spans="2:10" x14ac:dyDescent="0.3">
@@ -4936,7 +4990,7 @@
         <v>74</v>
       </c>
       <c r="C76" s="12">
-        <v>45715</v>
+        <v>45714</v>
       </c>
       <c r="D76" s="13" t="s">
         <v>12</v>
@@ -4946,7 +5000,7 @@
       </c>
       <c r="F76" s="13">
         <f t="shared" si="24"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G76" s="13" t="s">
         <v>14</v>
@@ -4958,7 +5012,7 @@
         <v>106</v>
       </c>
       <c r="J76" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="77" spans="2:10" x14ac:dyDescent="0.3">
@@ -4973,11 +5027,11 @@
         <v>12</v>
       </c>
       <c r="E77" s="12">
-        <v>45714</v>
+        <v>45715</v>
       </c>
       <c r="F77" s="13">
         <f t="shared" si="24"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G77" s="13" t="s">
         <v>14</v>
@@ -4989,7 +5043,7 @@
         <v>106</v>
       </c>
       <c r="J77" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="78" spans="2:10" x14ac:dyDescent="0.3">
@@ -4998,17 +5052,17 @@
         <v>76</v>
       </c>
       <c r="C78" s="12">
-        <v>45717</v>
+        <v>45715</v>
       </c>
       <c r="D78" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E78" s="12">
-        <v>45717</v>
+        <v>45714</v>
       </c>
       <c r="F78" s="13">
         <f t="shared" si="24"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G78" s="13" t="s">
         <v>14</v>
@@ -5020,7 +5074,7 @@
         <v>106</v>
       </c>
       <c r="J78" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="79" spans="2:10" x14ac:dyDescent="0.3">
@@ -5038,8 +5092,8 @@
         <v>45717</v>
       </c>
       <c r="F79" s="13">
-        <f>$B$78</f>
-        <v>76</v>
+        <f t="shared" si="24"/>
+        <v>69</v>
       </c>
       <c r="G79" s="13" t="s">
         <v>14</v>
@@ -5048,10 +5102,10 @@
         <v>19</v>
       </c>
       <c r="I79" s="14" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="J79" s="15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="80" spans="2:10" x14ac:dyDescent="0.3">
@@ -5069,8 +5123,8 @@
         <v>45717</v>
       </c>
       <c r="F80" s="13">
-        <f>$B$78</f>
-        <v>76</v>
+        <f>$B$79</f>
+        <v>77</v>
       </c>
       <c r="G80" s="13" t="s">
         <v>14</v>
@@ -5082,7 +5136,7 @@
         <v>126</v>
       </c>
       <c r="J80" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="81" spans="2:10" x14ac:dyDescent="0.3">
@@ -5100,8 +5154,8 @@
         <v>45717</v>
       </c>
       <c r="F81" s="13">
-        <f>$B$78</f>
-        <v>76</v>
+        <f>$B$79</f>
+        <v>77</v>
       </c>
       <c r="G81" s="13" t="s">
         <v>14</v>
@@ -5113,7 +5167,7 @@
         <v>126</v>
       </c>
       <c r="J81" s="15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="82" spans="2:10" x14ac:dyDescent="0.3">
@@ -5125,24 +5179,26 @@
         <v>45717</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E82" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E82" s="12">
+        <v>45717</v>
+      </c>
       <c r="F82" s="13">
-        <f>$B$69</f>
-        <v>67</v>
+        <f>$B$79</f>
+        <v>77</v>
       </c>
       <c r="G82" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H82" s="13" t="s">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="I82" s="14" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="J82" s="15" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.3">
@@ -5154,14 +5210,12 @@
         <v>45717</v>
       </c>
       <c r="D83" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E83" s="12">
-        <v>45717</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E83" s="12"/>
       <c r="F83" s="13">
-        <f t="shared" ref="F83:F89" si="25">$B$82</f>
-        <v>80</v>
+        <f>$B$70</f>
+        <v>68</v>
       </c>
       <c r="G83" s="13" t="s">
         <v>14</v>
@@ -5170,10 +5224,10 @@
         <v>102</v>
       </c>
       <c r="I83" s="14" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="J83" s="15" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="84" spans="2:10" x14ac:dyDescent="0.3">
@@ -5191,8 +5245,8 @@
         <v>45717</v>
       </c>
       <c r="F84" s="13">
-        <f t="shared" si="25"/>
-        <v>80</v>
+        <f t="shared" ref="F84:F90" si="25">$B$83</f>
+        <v>81</v>
       </c>
       <c r="G84" s="13" t="s">
         <v>14</v>
@@ -5204,12 +5258,12 @@
         <v>132</v>
       </c>
       <c r="J84" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B85" s="11">
-        <f t="shared" ref="B85" si="26">B84+1</f>
+        <f t="shared" si="0"/>
         <v>83</v>
       </c>
       <c r="C85" s="12">
@@ -5223,53 +5277,55 @@
       </c>
       <c r="F85" s="13">
         <f t="shared" si="25"/>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G85" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H85" s="13" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="I85" s="14" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="J85" s="15" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B86" s="11">
-        <f t="shared" ref="B86" si="27">B85+1</f>
+        <f t="shared" ref="B86" si="26">B85+1</f>
         <v>84</v>
       </c>
       <c r="C86" s="12">
         <v>45717</v>
       </c>
       <c r="D86" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E86" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E86" s="12">
+        <v>45717</v>
+      </c>
       <c r="F86" s="13">
         <f t="shared" si="25"/>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G86" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H86" s="13" t="s">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="I86" s="14" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J86" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="87" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B87" s="11">
-        <f t="shared" ref="B87" si="28">B86+1</f>
+        <f t="shared" ref="B87" si="27">B86+1</f>
         <v>85</v>
       </c>
       <c r="C87" s="12">
@@ -5281,24 +5337,24 @@
       <c r="E87" s="12"/>
       <c r="F87" s="13">
         <f t="shared" si="25"/>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G87" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H87" s="13" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="I87" s="14" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="J87" s="15" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="88" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B88" s="11">
-        <f t="shared" ref="B88" si="29">B87+1</f>
+        <f t="shared" ref="B88" si="28">B87+1</f>
         <v>86</v>
       </c>
       <c r="C88" s="12">
@@ -5310,24 +5366,24 @@
       <c r="E88" s="12"/>
       <c r="F88" s="13">
         <f t="shared" si="25"/>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G88" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H88" s="13" t="s">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="I88" s="14" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="J88" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="89" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B89" s="11">
-        <f t="shared" ref="B89" si="30">B88+1</f>
+        <f t="shared" ref="B89" si="29">B88+1</f>
         <v>87</v>
       </c>
       <c r="C89" s="12">
@@ -5339,7 +5395,7 @@
       <c r="E89" s="12"/>
       <c r="F89" s="13">
         <f t="shared" si="25"/>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G89" s="13" t="s">
         <v>14</v>
@@ -5351,48 +5407,51 @@
         <v>132</v>
       </c>
       <c r="J89" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="90" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B90" s="11">
-        <f t="shared" ref="B90:B101" si="31">B89+1</f>
+        <f t="shared" ref="B90" si="30">B89+1</f>
         <v>88</v>
       </c>
-      <c r="C90" s="12"/>
-      <c r="D90" s="13"/>
+      <c r="C90" s="12">
+        <v>45717</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E90" s="12"/>
-      <c r="F90" s="13"/>
-      <c r="G90" s="13"/>
-      <c r="H90" s="13"/>
-      <c r="I90" s="14"/>
-      <c r="J90" s="15"/>
+      <c r="F90" s="13">
+        <f t="shared" si="25"/>
+        <v>81</v>
+      </c>
+      <c r="G90" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H90" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I90" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="J90" s="15" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="91" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B91" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="B91:B102" si="31">B90+1</f>
         <v>89</v>
       </c>
-      <c r="C91" s="12">
-        <v>45719</v>
-      </c>
-      <c r="D91" s="13" t="s">
-        <v>11</v>
-      </c>
+      <c r="C91" s="12"/>
+      <c r="D91" s="13"/>
       <c r="E91" s="12"/>
       <c r="F91" s="13"/>
-      <c r="G91" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H91" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I91" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="J91" s="15" t="s">
-        <v>144</v>
-      </c>
+      <c r="G91" s="13"/>
+      <c r="H91" s="13"/>
+      <c r="I91" s="14"/>
+      <c r="J91" s="15"/>
     </row>
     <row r="92" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B92" s="11">
@@ -5403,15 +5462,10 @@
         <v>45719</v>
       </c>
       <c r="D92" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E92" s="12">
-        <v>45719</v>
-      </c>
-      <c r="F92" s="13">
-        <f>$B$91</f>
-        <v>89</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E92" s="12"/>
+      <c r="F92" s="13"/>
       <c r="G92" s="13" t="s">
         <v>14</v>
       </c>
@@ -5422,7 +5476,7 @@
         <v>143</v>
       </c>
       <c r="J92" s="15" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="93" spans="2:10" x14ac:dyDescent="0.3">
@@ -5437,11 +5491,11 @@
         <v>12</v>
       </c>
       <c r="E93" s="12">
-        <v>45720</v>
+        <v>45719</v>
       </c>
       <c r="F93" s="13">
-        <f>$B$91</f>
-        <v>89</v>
+        <f>$B$92</f>
+        <v>90</v>
       </c>
       <c r="G93" s="13" t="s">
         <v>14</v>
@@ -5453,7 +5507,7 @@
         <v>143</v>
       </c>
       <c r="J93" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="94" spans="2:10" x14ac:dyDescent="0.3">
@@ -5465,12 +5519,14 @@
         <v>45719</v>
       </c>
       <c r="D94" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E94" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E94" s="12">
+        <v>45720</v>
+      </c>
       <c r="F94" s="13">
-        <f>$B$91</f>
-        <v>89</v>
+        <f>$B$92</f>
+        <v>90</v>
       </c>
       <c r="G94" s="13" t="s">
         <v>14</v>
@@ -5482,7 +5538,7 @@
         <v>143</v>
       </c>
       <c r="J94" s="15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="95" spans="2:10" x14ac:dyDescent="0.3">
@@ -5498,8 +5554,8 @@
       </c>
       <c r="E95" s="12"/>
       <c r="F95" s="13">
-        <f>$B$91</f>
-        <v>89</v>
+        <f>$B$92</f>
+        <v>90</v>
       </c>
       <c r="G95" s="13" t="s">
         <v>14</v>
@@ -5511,7 +5567,7 @@
         <v>143</v>
       </c>
       <c r="J95" s="15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="96" spans="2:10" x14ac:dyDescent="0.3">
@@ -5519,14 +5575,29 @@
         <f t="shared" si="31"/>
         <v>94</v>
       </c>
-      <c r="C96" s="12"/>
-      <c r="D96" s="13"/>
+      <c r="C96" s="12">
+        <v>45719</v>
+      </c>
+      <c r="D96" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E96" s="12"/>
-      <c r="F96" s="13"/>
-      <c r="G96" s="13"/>
-      <c r="H96" s="13"/>
-      <c r="I96" s="14"/>
-      <c r="J96" s="15"/>
+      <c r="F96" s="13">
+        <f>$B$92</f>
+        <v>90</v>
+      </c>
+      <c r="G96" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H96" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I96" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="J96" s="15" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97" s="11">
@@ -5598,24 +5669,38 @@
       <c r="I101" s="14"/>
       <c r="J101" s="15"/>
     </row>
-    <row r="102" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B102" s="18">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B102" s="11">
+        <f t="shared" si="31"/>
+        <v>100</v>
+      </c>
+      <c r="C102" s="12"/>
+      <c r="D102" s="13"/>
+      <c r="E102" s="12"/>
+      <c r="F102" s="13"/>
+      <c r="G102" s="13"/>
+      <c r="H102" s="13"/>
+      <c r="I102" s="14"/>
+      <c r="J102" s="15"/>
+    </row>
+    <row r="103" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B103" s="18">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="C102" s="19"/>
-      <c r="D102" s="20"/>
-      <c r="E102" s="19"/>
-      <c r="F102" s="20"/>
-      <c r="G102" s="20"/>
-      <c r="H102" s="20"/>
-      <c r="I102" s="21"/>
-      <c r="J102" s="22"/>
+        <v>101</v>
+      </c>
+      <c r="C103" s="19"/>
+      <c r="D103" s="20"/>
+      <c r="E103" s="19"/>
+      <c r="F103" s="20"/>
+      <c r="G103" s="20"/>
+      <c r="H103" s="20"/>
+      <c r="I103" s="21"/>
+      <c r="J103" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:J102" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
+  <autoFilter ref="B2:J103" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B3:J45 A43:A45 A46:J46 A47:A51 B47:J102">
+  <conditionalFormatting sqref="B3:J45 A43:A45 A46:J46 A47:A51 B47:J103">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>
@@ -5632,25 +5717,25 @@
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H100:H102 H70:H81 H3:H62 H68</xm:sqref>
+          <xm:sqref>H101:H103 H71:H82 H3:H62 H69</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D6F2F62E-6D63-4E2D-8772-1211A4C3A979}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$10</xm:f>
           </x14:formula1>
-          <xm:sqref>H69 H82:H99 H63:H67</xm:sqref>
+          <xm:sqref>H70 H83:H100 H63:H68</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C61EF0EC-B820-4CEA-8AA2-04B5D172AE2C}">
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D102</xm:sqref>
+          <xm:sqref>D3:D103</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G102</xm:sqref>
+          <xm:sqref>G3:G103</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42978670-18F8-4873-AB7C-138BCE2C5E4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6322BFD6-2F47-4760-B2EA-41DC555B2F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="選択情報" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作業項目!$B$2:$J$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作業項目!$B$2:$J$106</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="156">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -2153,6 +2153,22 @@
     </rPh>
     <rPh sb="47" eb="49">
       <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SystemAction01構築 : テーブル一覧への分岐追加</t>
+    <rPh sb="14" eb="16">
+      <t>コウチク</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ブンキ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ツイカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2844,7 +2860,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:K106"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -3042,7 +3058,7 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
-        <f t="shared" ref="A8:B103" si="0">B7+1</f>
+        <f t="shared" ref="A8:B106" si="0">B7+1</f>
         <v>6</v>
       </c>
       <c r="C8" s="12">
@@ -4599,7 +4615,7 @@
       </c>
       <c r="E62" s="12"/>
       <c r="F62" s="13">
-        <f>$B$61</f>
+        <f t="shared" ref="F62:F67" si="21">$B$61</f>
         <v>59</v>
       </c>
       <c r="G62" s="13" t="s">
@@ -4617,7 +4633,7 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B63" s="11">
-        <f t="shared" ref="B63" si="21">B62+1</f>
+        <f t="shared" ref="B63" si="22">B62+1</f>
         <v>61</v>
       </c>
       <c r="C63" s="12">
@@ -4628,7 +4644,7 @@
       </c>
       <c r="E63" s="12"/>
       <c r="F63" s="13">
-        <f>$B$61</f>
+        <f t="shared" si="21"/>
         <v>59</v>
       </c>
       <c r="G63" s="13" t="s">
@@ -4646,7 +4662,7 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B64" s="11">
-        <f t="shared" ref="B64:B66" si="22">B63+1</f>
+        <f t="shared" ref="B64:B66" si="23">B63+1</f>
         <v>62</v>
       </c>
       <c r="C64" s="12">
@@ -4657,7 +4673,7 @@
       </c>
       <c r="E64" s="12"/>
       <c r="F64" s="13">
-        <f>$B$61</f>
+        <f t="shared" si="21"/>
         <v>59</v>
       </c>
       <c r="G64" s="13" t="s">
@@ -4675,7 +4691,7 @@
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B65" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>63</v>
       </c>
       <c r="C65" s="12">
@@ -4686,7 +4702,7 @@
       </c>
       <c r="E65" s="12"/>
       <c r="F65" s="13">
-        <f>$B$61</f>
+        <f t="shared" si="21"/>
         <v>59</v>
       </c>
       <c r="G65" s="13" t="s">
@@ -4704,7 +4720,7 @@
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B66" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>64</v>
       </c>
       <c r="C66" s="12">
@@ -4715,7 +4731,7 @@
       </c>
       <c r="E66" s="12"/>
       <c r="F66" s="13">
-        <f>$B$61</f>
+        <f t="shared" si="21"/>
         <v>59</v>
       </c>
       <c r="G66" s="13" t="s">
@@ -4733,18 +4749,18 @@
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B67" s="11">
-        <f t="shared" ref="B67:B69" si="23">B66+1</f>
+        <f t="shared" ref="B67:B73" si="24">B66+1</f>
         <v>65</v>
       </c>
       <c r="C67" s="12">
         <v>45722</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E67" s="12"/>
       <c r="F67" s="13">
-        <f>$B$61</f>
+        <f t="shared" si="21"/>
         <v>59</v>
       </c>
       <c r="G67" s="13" t="s">
@@ -4762,14 +4778,14 @@
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B68" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>66</v>
       </c>
       <c r="C68" s="12">
         <v>45726</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E68" s="12"/>
       <c r="F68" s="13">
@@ -4791,135 +4807,99 @@
     </row>
     <row r="69" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B69" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>67</v>
       </c>
-      <c r="C69" s="12"/>
-      <c r="D69" s="13"/>
+      <c r="C69" s="12">
+        <v>45729</v>
+      </c>
+      <c r="D69" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E69" s="12"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="13"/>
-      <c r="H69" s="13"/>
-      <c r="I69" s="14"/>
-      <c r="J69" s="15"/>
+      <c r="F69" s="13">
+        <f>$B$63</f>
+        <v>61</v>
+      </c>
+      <c r="G69" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H69" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I69" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="J69" s="15" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="70" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B70" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="24"/>
         <v>68</v>
       </c>
-      <c r="C70" s="12">
-        <v>45698</v>
-      </c>
-      <c r="D70" s="13" t="s">
-        <v>11</v>
-      </c>
+      <c r="C70" s="12"/>
+      <c r="D70" s="13"/>
       <c r="E70" s="12"/>
       <c r="F70" s="13"/>
-      <c r="G70" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H70" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="I70" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="J70" s="15" t="s">
-        <v>105</v>
-      </c>
+      <c r="G70" s="13"/>
+      <c r="H70" s="13"/>
+      <c r="I70" s="14"/>
+      <c r="J70" s="15"/>
     </row>
     <row r="71" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B71" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="24"/>
         <v>69</v>
       </c>
-      <c r="C71" s="12">
-        <v>45698</v>
-      </c>
-      <c r="D71" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E71" s="12">
-        <v>45717</v>
-      </c>
-      <c r="F71" s="13">
-        <f>$B$70</f>
-        <v>68</v>
-      </c>
-      <c r="G71" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H71" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I71" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="J71" s="15" t="s">
-        <v>107</v>
-      </c>
+      <c r="C71" s="12"/>
+      <c r="D71" s="13"/>
+      <c r="E71" s="12"/>
+      <c r="F71" s="13"/>
+      <c r="G71" s="13"/>
+      <c r="H71" s="13"/>
+      <c r="I71" s="14"/>
+      <c r="J71" s="15"/>
     </row>
     <row r="72" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B72" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="24"/>
         <v>70</v>
       </c>
-      <c r="C72" s="12">
-        <v>45698</v>
-      </c>
-      <c r="D72" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E72" s="12">
-        <v>45698</v>
-      </c>
-      <c r="F72" s="13">
-        <f t="shared" ref="F72:F79" si="24">$B$71</f>
-        <v>69</v>
-      </c>
-      <c r="G72" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H72" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I72" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="J72" s="15" t="s">
-        <v>108</v>
-      </c>
+      <c r="C72" s="12"/>
+      <c r="D72" s="13"/>
+      <c r="E72" s="12"/>
+      <c r="F72" s="13"/>
+      <c r="G72" s="13"/>
+      <c r="H72" s="13"/>
+      <c r="I72" s="14"/>
+      <c r="J72" s="15"/>
     </row>
     <row r="73" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B73" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="24"/>
         <v>71</v>
       </c>
       <c r="C73" s="12">
         <v>45698</v>
       </c>
       <c r="D73" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E73" s="12">
-        <v>45714</v>
-      </c>
-      <c r="F73" s="13">
-        <f t="shared" si="24"/>
-        <v>69</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E73" s="12"/>
+      <c r="F73" s="13"/>
       <c r="G73" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H73" s="13" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="I73" s="14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J73" s="15" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.3">
@@ -4934,11 +4914,11 @@
         <v>12</v>
       </c>
       <c r="E74" s="12">
-        <v>45714</v>
+        <v>45717</v>
       </c>
       <c r="F74" s="13">
-        <f t="shared" si="24"/>
-        <v>69</v>
+        <f>$B$73</f>
+        <v>71</v>
       </c>
       <c r="G74" s="13" t="s">
         <v>14</v>
@@ -4950,7 +4930,7 @@
         <v>106</v>
       </c>
       <c r="J74" s="15" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
     </row>
     <row r="75" spans="2:10" x14ac:dyDescent="0.3">
@@ -4959,17 +4939,17 @@
         <v>73</v>
       </c>
       <c r="C75" s="12">
-        <v>45714</v>
+        <v>45698</v>
       </c>
       <c r="D75" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E75" s="12">
-        <v>45714</v>
+        <v>45698</v>
       </c>
       <c r="F75" s="13">
-        <f t="shared" si="24"/>
-        <v>69</v>
+        <f t="shared" ref="F75:F82" si="25">$B$74</f>
+        <v>72</v>
       </c>
       <c r="G75" s="13" t="s">
         <v>14</v>
@@ -4981,7 +4961,7 @@
         <v>106</v>
       </c>
       <c r="J75" s="15" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
     </row>
     <row r="76" spans="2:10" x14ac:dyDescent="0.3">
@@ -4990,17 +4970,17 @@
         <v>74</v>
       </c>
       <c r="C76" s="12">
+        <v>45698</v>
+      </c>
+      <c r="D76" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E76" s="12">
         <v>45714</v>
       </c>
-      <c r="D76" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E76" s="12">
-        <v>45715</v>
-      </c>
       <c r="F76" s="13">
-        <f t="shared" si="24"/>
-        <v>69</v>
+        <f t="shared" si="25"/>
+        <v>72</v>
       </c>
       <c r="G76" s="13" t="s">
         <v>14</v>
@@ -5012,7 +4992,7 @@
         <v>106</v>
       </c>
       <c r="J76" s="15" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="77" spans="2:10" x14ac:dyDescent="0.3">
@@ -5021,17 +5001,17 @@
         <v>75</v>
       </c>
       <c r="C77" s="12">
-        <v>45715</v>
+        <v>45698</v>
       </c>
       <c r="D77" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E77" s="12">
-        <v>45715</v>
+        <v>45714</v>
       </c>
       <c r="F77" s="13">
-        <f t="shared" si="24"/>
-        <v>69</v>
+        <f t="shared" si="25"/>
+        <v>72</v>
       </c>
       <c r="G77" s="13" t="s">
         <v>14</v>
@@ -5043,7 +5023,7 @@
         <v>106</v>
       </c>
       <c r="J77" s="15" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="78" spans="2:10" x14ac:dyDescent="0.3">
@@ -5052,7 +5032,7 @@
         <v>76</v>
       </c>
       <c r="C78" s="12">
-        <v>45715</v>
+        <v>45714</v>
       </c>
       <c r="D78" s="13" t="s">
         <v>12</v>
@@ -5061,8 +5041,8 @@
         <v>45714</v>
       </c>
       <c r="F78" s="13">
-        <f t="shared" si="24"/>
-        <v>69</v>
+        <f t="shared" si="25"/>
+        <v>72</v>
       </c>
       <c r="G78" s="13" t="s">
         <v>14</v>
@@ -5074,7 +5054,7 @@
         <v>106</v>
       </c>
       <c r="J78" s="15" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="79" spans="2:10" x14ac:dyDescent="0.3">
@@ -5083,17 +5063,17 @@
         <v>77</v>
       </c>
       <c r="C79" s="12">
-        <v>45717</v>
+        <v>45714</v>
       </c>
       <c r="D79" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E79" s="12">
-        <v>45717</v>
+        <v>45715</v>
       </c>
       <c r="F79" s="13">
-        <f t="shared" si="24"/>
-        <v>69</v>
+        <f t="shared" si="25"/>
+        <v>72</v>
       </c>
       <c r="G79" s="13" t="s">
         <v>14</v>
@@ -5105,7 +5085,7 @@
         <v>106</v>
       </c>
       <c r="J79" s="15" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="80" spans="2:10" x14ac:dyDescent="0.3">
@@ -5114,17 +5094,17 @@
         <v>78</v>
       </c>
       <c r="C80" s="12">
-        <v>45717</v>
+        <v>45715</v>
       </c>
       <c r="D80" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E80" s="12">
-        <v>45717</v>
+        <v>45715</v>
       </c>
       <c r="F80" s="13">
-        <f>$B$79</f>
-        <v>77</v>
+        <f t="shared" si="25"/>
+        <v>72</v>
       </c>
       <c r="G80" s="13" t="s">
         <v>14</v>
@@ -5133,10 +5113,10 @@
         <v>19</v>
       </c>
       <c r="I80" s="14" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="J80" s="15" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="81" spans="2:10" x14ac:dyDescent="0.3">
@@ -5145,17 +5125,17 @@
         <v>79</v>
       </c>
       <c r="C81" s="12">
-        <v>45717</v>
+        <v>45715</v>
       </c>
       <c r="D81" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E81" s="12">
-        <v>45717</v>
+        <v>45714</v>
       </c>
       <c r="F81" s="13">
-        <f>$B$79</f>
-        <v>77</v>
+        <f t="shared" si="25"/>
+        <v>72</v>
       </c>
       <c r="G81" s="13" t="s">
         <v>14</v>
@@ -5164,10 +5144,10 @@
         <v>19</v>
       </c>
       <c r="I81" s="14" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="J81" s="15" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="82" spans="2:10" x14ac:dyDescent="0.3">
@@ -5185,8 +5165,8 @@
         <v>45717</v>
       </c>
       <c r="F82" s="13">
-        <f>$B$79</f>
-        <v>77</v>
+        <f t="shared" si="25"/>
+        <v>72</v>
       </c>
       <c r="G82" s="13" t="s">
         <v>14</v>
@@ -5195,10 +5175,10 @@
         <v>19</v>
       </c>
       <c r="I82" s="14" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="J82" s="15" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.3">
@@ -5210,24 +5190,26 @@
         <v>45717</v>
       </c>
       <c r="D83" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E83" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E83" s="12">
+        <v>45717</v>
+      </c>
       <c r="F83" s="13">
-        <f>$B$70</f>
-        <v>68</v>
+        <f>$B$82</f>
+        <v>80</v>
       </c>
       <c r="G83" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H83" s="13" t="s">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="I83" s="14" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="J83" s="15" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="84" spans="2:10" x14ac:dyDescent="0.3">
@@ -5245,20 +5227,20 @@
         <v>45717</v>
       </c>
       <c r="F84" s="13">
-        <f t="shared" ref="F84:F90" si="25">$B$83</f>
-        <v>81</v>
+        <f>$B$82</f>
+        <v>80</v>
       </c>
       <c r="G84" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H84" s="13" t="s">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="I84" s="14" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="J84" s="15" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.3">
@@ -5276,68 +5258,68 @@
         <v>45717</v>
       </c>
       <c r="F85" s="13">
-        <f t="shared" si="25"/>
-        <v>81</v>
+        <f>$B$82</f>
+        <v>80</v>
       </c>
       <c r="G85" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H85" s="13" t="s">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="I85" s="14" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="J85" s="15" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B86" s="11">
-        <f t="shared" ref="B86" si="26">B85+1</f>
+        <f t="shared" si="0"/>
         <v>84</v>
       </c>
       <c r="C86" s="12">
         <v>45717</v>
       </c>
       <c r="D86" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E86" s="12">
-        <v>45717</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E86" s="12"/>
       <c r="F86" s="13">
-        <f t="shared" si="25"/>
-        <v>81</v>
+        <f>$B$73</f>
+        <v>71</v>
       </c>
       <c r="G86" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H86" s="13" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="I86" s="14" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J86" s="15" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="87" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B87" s="11">
-        <f t="shared" ref="B87" si="27">B86+1</f>
+        <f t="shared" si="0"/>
         <v>85</v>
       </c>
       <c r="C87" s="12">
         <v>45717</v>
       </c>
       <c r="D87" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E87" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E87" s="12">
+        <v>45717</v>
+      </c>
       <c r="F87" s="13">
-        <f t="shared" si="25"/>
-        <v>81</v>
+        <f t="shared" ref="F87:F93" si="26">$B$86</f>
+        <v>84</v>
       </c>
       <c r="G87" s="13" t="s">
         <v>14</v>
@@ -5349,70 +5331,74 @@
         <v>132</v>
       </c>
       <c r="J87" s="15" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="88" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B88" s="11">
-        <f t="shared" ref="B88" si="28">B87+1</f>
+        <f t="shared" si="0"/>
         <v>86</v>
       </c>
       <c r="C88" s="12">
         <v>45717</v>
       </c>
       <c r="D88" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E88" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E88" s="12">
+        <v>45717</v>
+      </c>
       <c r="F88" s="13">
-        <f t="shared" si="25"/>
-        <v>81</v>
+        <f t="shared" si="26"/>
+        <v>84</v>
       </c>
       <c r="G88" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H88" s="13" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="I88" s="14" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="J88" s="15" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="89" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B89" s="11">
-        <f t="shared" ref="B89" si="29">B88+1</f>
+        <f t="shared" ref="B89" si="27">B88+1</f>
         <v>87</v>
       </c>
       <c r="C89" s="12">
         <v>45717</v>
       </c>
       <c r="D89" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E89" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E89" s="12">
+        <v>45717</v>
+      </c>
       <c r="F89" s="13">
-        <f t="shared" si="25"/>
-        <v>81</v>
+        <f t="shared" si="26"/>
+        <v>84</v>
       </c>
       <c r="G89" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H89" s="13" t="s">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="I89" s="14" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J89" s="15" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="90" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B90" s="11">
-        <f t="shared" ref="B90" si="30">B89+1</f>
+        <f t="shared" ref="B90" si="28">B89+1</f>
         <v>88</v>
       </c>
       <c r="C90" s="12">
@@ -5423,8 +5409,8 @@
       </c>
       <c r="E90" s="12"/>
       <c r="F90" s="13">
-        <f t="shared" si="25"/>
-        <v>81</v>
+        <f t="shared" si="26"/>
+        <v>84</v>
       </c>
       <c r="G90" s="13" t="s">
         <v>14</v>
@@ -5436,127 +5422,123 @@
         <v>132</v>
       </c>
       <c r="J90" s="15" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="91" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B91" s="11">
-        <f t="shared" ref="B91:B102" si="31">B90+1</f>
+        <f t="shared" ref="B91" si="29">B90+1</f>
         <v>89</v>
       </c>
-      <c r="C91" s="12"/>
-      <c r="D91" s="13"/>
+      <c r="C91" s="12">
+        <v>45717</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E91" s="12"/>
-      <c r="F91" s="13"/>
-      <c r="G91" s="13"/>
-      <c r="H91" s="13"/>
-      <c r="I91" s="14"/>
-      <c r="J91" s="15"/>
+      <c r="F91" s="13">
+        <f t="shared" si="26"/>
+        <v>84</v>
+      </c>
+      <c r="G91" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H91" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I91" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="J91" s="15" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="92" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B92" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="B92" si="30">B91+1</f>
         <v>90</v>
       </c>
       <c r="C92" s="12">
-        <v>45719</v>
+        <v>45717</v>
       </c>
       <c r="D92" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E92" s="12"/>
-      <c r="F92" s="13"/>
+      <c r="F92" s="13">
+        <f t="shared" si="26"/>
+        <v>84</v>
+      </c>
       <c r="G92" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H92" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I92" s="15" t="s">
-        <v>143</v>
+        <v>102</v>
+      </c>
+      <c r="I92" s="14" t="s">
+        <v>132</v>
       </c>
       <c r="J92" s="15" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="93" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B93" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="B93" si="31">B92+1</f>
         <v>91</v>
       </c>
       <c r="C93" s="12">
-        <v>45719</v>
+        <v>45717</v>
       </c>
       <c r="D93" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E93" s="12">
-        <v>45719</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E93" s="12"/>
       <c r="F93" s="13">
-        <f>$B$92</f>
-        <v>90</v>
+        <f t="shared" si="26"/>
+        <v>84</v>
       </c>
       <c r="G93" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H93" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I93" s="15" t="s">
-        <v>143</v>
+        <v>102</v>
+      </c>
+      <c r="I93" s="14" t="s">
+        <v>132</v>
       </c>
       <c r="J93" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="94" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B94" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="B94:B105" si="32">B93+1</f>
         <v>92</v>
       </c>
-      <c r="C94" s="12">
-        <v>45719</v>
-      </c>
-      <c r="D94" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E94" s="12">
-        <v>45720</v>
-      </c>
-      <c r="F94" s="13">
-        <f>$B$92</f>
-        <v>90</v>
-      </c>
-      <c r="G94" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H94" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I94" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="J94" s="15" t="s">
-        <v>145</v>
-      </c>
+      <c r="C94" s="12"/>
+      <c r="D94" s="13"/>
+      <c r="E94" s="12"/>
+      <c r="F94" s="13"/>
+      <c r="G94" s="13"/>
+      <c r="H94" s="13"/>
+      <c r="I94" s="14"/>
+      <c r="J94" s="15"/>
     </row>
     <row r="95" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B95" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>93</v>
       </c>
       <c r="C95" s="12">
         <v>45719</v>
       </c>
       <c r="D95" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E95" s="12"/>
-      <c r="F95" s="13">
-        <f>$B$92</f>
-        <v>90</v>
-      </c>
+      <c r="F95" s="13"/>
       <c r="G95" s="13" t="s">
         <v>14</v>
       </c>
@@ -5567,24 +5549,26 @@
         <v>143</v>
       </c>
       <c r="J95" s="15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="96" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B96" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>94</v>
       </c>
       <c r="C96" s="12">
         <v>45719</v>
       </c>
       <c r="D96" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E96" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E96" s="12">
+        <v>45719</v>
+      </c>
       <c r="F96" s="13">
-        <f>$B$92</f>
-        <v>90</v>
+        <f>$B$95</f>
+        <v>93</v>
       </c>
       <c r="G96" s="13" t="s">
         <v>14</v>
@@ -5596,54 +5580,101 @@
         <v>143</v>
       </c>
       <c r="J96" s="15" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>95</v>
       </c>
-      <c r="C97" s="12"/>
-      <c r="D97" s="13"/>
-      <c r="E97" s="12"/>
-      <c r="F97" s="13"/>
-      <c r="G97" s="13"/>
-      <c r="H97" s="13"/>
-      <c r="I97" s="14"/>
-      <c r="J97" s="15"/>
+      <c r="C97" s="12">
+        <v>45719</v>
+      </c>
+      <c r="D97" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E97" s="12">
+        <v>45720</v>
+      </c>
+      <c r="F97" s="13">
+        <f>$B$95</f>
+        <v>93</v>
+      </c>
+      <c r="G97" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H97" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I97" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="J97" s="15" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>96</v>
       </c>
-      <c r="C98" s="12"/>
-      <c r="D98" s="13"/>
+      <c r="C98" s="12">
+        <v>45719</v>
+      </c>
+      <c r="D98" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E98" s="12"/>
-      <c r="F98" s="13"/>
-      <c r="G98" s="13"/>
-      <c r="H98" s="13"/>
-      <c r="I98" s="14"/>
-      <c r="J98" s="15"/>
+      <c r="F98" s="13">
+        <f>$B$95</f>
+        <v>93</v>
+      </c>
+      <c r="G98" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H98" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I98" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="J98" s="15" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B99" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>97</v>
       </c>
-      <c r="C99" s="12"/>
-      <c r="D99" s="13"/>
+      <c r="C99" s="12">
+        <v>45719</v>
+      </c>
+      <c r="D99" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E99" s="12"/>
-      <c r="F99" s="13"/>
-      <c r="G99" s="13"/>
-      <c r="H99" s="13"/>
-      <c r="I99" s="14"/>
-      <c r="J99" s="15"/>
+      <c r="F99" s="13">
+        <f>$B$95</f>
+        <v>93</v>
+      </c>
+      <c r="G99" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H99" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I99" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="J99" s="15" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="100" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B100" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>98</v>
       </c>
       <c r="C100" s="12"/>
@@ -5657,7 +5688,7 @@
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B101" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>99</v>
       </c>
       <c r="C101" s="12"/>
@@ -5671,7 +5702,7 @@
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B102" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>100</v>
       </c>
       <c r="C102" s="12"/>
@@ -5683,24 +5714,66 @@
       <c r="I102" s="14"/>
       <c r="J102" s="15"/>
     </row>
-    <row r="103" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="18">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B103" s="11">
+        <f t="shared" si="32"/>
+        <v>101</v>
+      </c>
+      <c r="C103" s="12"/>
+      <c r="D103" s="13"/>
+      <c r="E103" s="12"/>
+      <c r="F103" s="13"/>
+      <c r="G103" s="13"/>
+      <c r="H103" s="13"/>
+      <c r="I103" s="14"/>
+      <c r="J103" s="15"/>
+    </row>
+    <row r="104" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B104" s="11">
+        <f t="shared" si="32"/>
+        <v>102</v>
+      </c>
+      <c r="C104" s="12"/>
+      <c r="D104" s="13"/>
+      <c r="E104" s="12"/>
+      <c r="F104" s="13"/>
+      <c r="G104" s="13"/>
+      <c r="H104" s="13"/>
+      <c r="I104" s="14"/>
+      <c r="J104" s="15"/>
+    </row>
+    <row r="105" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B105" s="11">
+        <f t="shared" si="32"/>
+        <v>103</v>
+      </c>
+      <c r="C105" s="12"/>
+      <c r="D105" s="13"/>
+      <c r="E105" s="12"/>
+      <c r="F105" s="13"/>
+      <c r="G105" s="13"/>
+      <c r="H105" s="13"/>
+      <c r="I105" s="14"/>
+      <c r="J105" s="15"/>
+    </row>
+    <row r="106" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B106" s="18">
         <f t="shared" si="0"/>
-        <v>101</v>
-      </c>
-      <c r="C103" s="19"/>
-      <c r="D103" s="20"/>
-      <c r="E103" s="19"/>
-      <c r="F103" s="20"/>
-      <c r="G103" s="20"/>
-      <c r="H103" s="20"/>
-      <c r="I103" s="21"/>
-      <c r="J103" s="22"/>
+        <v>104</v>
+      </c>
+      <c r="C106" s="19"/>
+      <c r="D106" s="20"/>
+      <c r="E106" s="19"/>
+      <c r="F106" s="20"/>
+      <c r="G106" s="20"/>
+      <c r="H106" s="20"/>
+      <c r="I106" s="21"/>
+      <c r="J106" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:J103" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
+  <autoFilter ref="B2:J106" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B3:J45 A43:A45 A46:J46 A47:A51 B47:J103">
+  <conditionalFormatting sqref="B3:J45 A43:A45 A46:J46 A47:A51 B47:J106">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>
@@ -5709,7 +5782,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
@@ -5717,25 +5790,25 @@
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H101:H103 H71:H82 H3:H62 H69</xm:sqref>
+          <xm:sqref>H104:H106 H74:H85 H3:H62 H72</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D6F2F62E-6D63-4E2D-8772-1211A4C3A979}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$10</xm:f>
           </x14:formula1>
-          <xm:sqref>H70 H83:H100 H63:H68</xm:sqref>
+          <xm:sqref>H73 H86:H103 H63:H71</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C61EF0EC-B820-4CEA-8AA2-04B5D172AE2C}">
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D103</xm:sqref>
+          <xm:sqref>D3:D106</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G103</xm:sqref>
+          <xm:sqref>G3:G106</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6322BFD6-2F47-4760-B2EA-41DC555B2F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A98B1E6-BB36-4CE1-9AF4-E7A4BBE78B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="選択情報" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作業項目!$B$2:$J$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作業項目!$B$2:$J$108</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="159">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -781,44 +781,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>システム管理用のメニューを生成する。（当面は単独で表示する。総合メニューとは連携しない）
-表示項目はユーザー一覧、テーブル一覧とする。</t>
-    <rPh sb="4" eb="7">
-      <t>カンリヨウ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>セイセイ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>トウメン</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>タンドク</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>ソウゴウ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>レンケイ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="47" eb="49">
-      <t>コウモク</t>
-    </rPh>
-    <rPh sb="54" eb="56">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="61" eb="63">
-      <t>イチラン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>「メニューへ戻る」ボタン構築</t>
     <rPh sb="6" eb="7">
       <t>モド</t>
@@ -886,38 +848,6 @@
     </rPh>
     <rPh sb="4" eb="8">
       <t>ショキトウロク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>テーブル情報テーブル構築</t>
-    <rPh sb="4" eb="6">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>コウチク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>テーブル名 : sys_table、項目 : テーブル情報ID、テーブル識別コード、名前、説明</t>
-    <rPh sb="4" eb="5">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>コウモク</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>シキベツ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>ナマエ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>セツメイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2169,6 +2099,106 @@
     </rPh>
     <rPh sb="29" eb="31">
       <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テーブル一覧画面</t>
+    <rPh sb="4" eb="6">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>システム管理用のメニューを生成する。（当面は単独で表示する。総合メニューとは連携しない）
+表示項目は テーブル一覧、エンティティ一覧、画面一覧とする。</t>
+    <rPh sb="4" eb="7">
+      <t>カンリヨウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>トウメン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>タンドク</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ソウゴウ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>レンケイ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>コウモク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HtmlSysTableList01クラス構築</t>
+    <rPh sb="21" eb="23">
+      <t>コウチク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テーブル情報</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テーブル構築 : テーブル名 : sys_table、項目 : テーブル情報ID、テーブル識別コード、名前、説明</t>
+    <rPh sb="13" eb="14">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>シキベツ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示情報 : テーブル一覧画面情報の初期登録</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="18" eb="22">
+      <t>ショキトウロク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2860,7 +2890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="A1:K106"/>
+  <dimension ref="A1:K108"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -3058,7 +3088,7 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
-        <f t="shared" ref="A8:B106" si="0">B7+1</f>
+        <f t="shared" ref="A8:B108" si="0">B7+1</f>
         <v>6</v>
       </c>
       <c r="C8" s="12">
@@ -3536,7 +3566,7 @@
         <v>60</v>
       </c>
       <c r="J24" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.3">
@@ -3566,7 +3596,7 @@
         <v>60</v>
       </c>
       <c r="J25" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.3">
@@ -3597,7 +3627,7 @@
         <v>60</v>
       </c>
       <c r="J26" s="17" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -3624,10 +3654,10 @@
         <v>23</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J27" s="17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.3">
@@ -3654,10 +3684,10 @@
         <v>23</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J28" s="15" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.3">
@@ -3684,10 +3714,10 @@
         <v>23</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.3">
@@ -3714,10 +3744,10 @@
         <v>23</v>
       </c>
       <c r="I30" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J30" s="15" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.3">
@@ -3744,10 +3774,10 @@
         <v>23</v>
       </c>
       <c r="I31" s="14" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J31" s="15" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.3">
@@ -3774,10 +3804,10 @@
         <v>23</v>
       </c>
       <c r="I32" s="14" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J32" s="15" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
@@ -3804,10 +3834,10 @@
         <v>23</v>
       </c>
       <c r="I33" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J33" s="15" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
@@ -3834,10 +3864,10 @@
         <v>23</v>
       </c>
       <c r="I34" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J34" s="15" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
@@ -3864,10 +3894,10 @@
         <v>23</v>
       </c>
       <c r="I35" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J35" s="15" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -3894,10 +3924,10 @@
         <v>23</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J36" s="17" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
@@ -3925,10 +3955,10 @@
         <v>23</v>
       </c>
       <c r="I37" s="14" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J37" s="15" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
@@ -3956,10 +3986,10 @@
         <v>23</v>
       </c>
       <c r="I38" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="J38" s="15" t="s">
         <v>97</v>
-      </c>
-      <c r="J38" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
@@ -3987,10 +4017,10 @@
         <v>23</v>
       </c>
       <c r="I39" s="14" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J39" s="15" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
@@ -4018,10 +4048,10 @@
         <v>23</v>
       </c>
       <c r="I40" s="14" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J40" s="15" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
@@ -4049,10 +4079,10 @@
         <v>23</v>
       </c>
       <c r="I41" s="14" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J41" s="15" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
@@ -4080,10 +4110,10 @@
         <v>23</v>
       </c>
       <c r="I42" s="14" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J42" s="15" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
@@ -4115,10 +4145,10 @@
         <v>23</v>
       </c>
       <c r="I43" s="14" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J43" s="15" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
@@ -4150,10 +4180,10 @@
         <v>23</v>
       </c>
       <c r="I44" s="14" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J44" s="15" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
@@ -4180,10 +4210,10 @@
         <v>23</v>
       </c>
       <c r="I45" s="14" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J45" s="15" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
@@ -4207,10 +4237,10 @@
         <v>23</v>
       </c>
       <c r="I46" s="14" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J46" s="15" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
@@ -4237,10 +4267,10 @@
         <v>23</v>
       </c>
       <c r="I47" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="J47" s="15" t="s">
         <v>114</v>
-      </c>
-      <c r="J47" s="15" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
@@ -4304,10 +4334,10 @@
         <v>19</v>
       </c>
       <c r="I50" s="14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="J50" s="15" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
@@ -4338,10 +4368,10 @@
         <v>19</v>
       </c>
       <c r="I51" s="14" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J51" s="17" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -4368,10 +4398,10 @@
         <v>19</v>
       </c>
       <c r="I52" s="14" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J52" s="17" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
@@ -4398,10 +4428,10 @@
         <v>19</v>
       </c>
       <c r="I53" s="14" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J53" s="17" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
@@ -4428,10 +4458,10 @@
         <v>19</v>
       </c>
       <c r="I54" s="14" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J54" s="15" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
@@ -4458,10 +4488,10 @@
         <v>19</v>
       </c>
       <c r="I55" s="14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="J55" s="15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
@@ -4488,10 +4518,10 @@
         <v>19</v>
       </c>
       <c r="I56" s="14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J56" s="15" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
@@ -4518,10 +4548,10 @@
         <v>23</v>
       </c>
       <c r="I57" s="14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="J57" s="15" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
@@ -4544,7 +4574,7 @@
         <v>23</v>
       </c>
       <c r="I58" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J58" s="15"/>
     </row>
@@ -4585,7 +4615,7 @@
         <v>45645</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E61" s="12"/>
       <c r="F61" s="13"/>
@@ -4599,7 +4629,7 @@
         <v>63</v>
       </c>
       <c r="J61" s="17" t="s">
-        <v>64</v>
+        <v>154</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
@@ -4608,14 +4638,14 @@
         <v>60</v>
       </c>
       <c r="C62" s="12">
-        <v>45654</v>
+        <v>45722</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E62" s="12"/>
       <c r="F62" s="13">
-        <f t="shared" ref="F62:F67" si="21">$B$61</f>
+        <f t="shared" ref="F62:F66" si="21">$B$61</f>
         <v>59</v>
       </c>
       <c r="G62" s="13" t="s">
@@ -4625,22 +4655,22 @@
         <v>19</v>
       </c>
       <c r="I62" s="14" t="s">
-        <v>70</v>
+        <v>145</v>
       </c>
       <c r="J62" s="15" t="s">
-        <v>71</v>
+        <v>146</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B63" s="11">
-        <f t="shared" ref="B63" si="22">B62+1</f>
+        <f t="shared" ref="B63:B65" si="22">B62+1</f>
         <v>61</v>
       </c>
       <c r="C63" s="12">
         <v>45722</v>
       </c>
       <c r="D63" s="13" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E63" s="12"/>
       <c r="F63" s="13">
@@ -4654,19 +4684,19 @@
         <v>19</v>
       </c>
       <c r="I63" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="J63" s="15" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B64" s="11">
-        <f t="shared" ref="B64:B66" si="23">B63+1</f>
+        <f t="shared" si="22"/>
         <v>62</v>
       </c>
       <c r="C64" s="12">
-        <v>45722</v>
+        <v>45726</v>
       </c>
       <c r="D64" s="13" t="s">
         <v>12</v>
@@ -4683,7 +4713,7 @@
         <v>19</v>
       </c>
       <c r="I64" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="J64" s="15" t="s">
         <v>150</v>
@@ -4691,11 +4721,11 @@
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B65" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>63</v>
       </c>
       <c r="C65" s="12">
-        <v>45726</v>
+        <v>45722</v>
       </c>
       <c r="D65" s="13" t="s">
         <v>12</v>
@@ -4712,15 +4742,15 @@
         <v>19</v>
       </c>
       <c r="I65" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="J65" s="15" t="s">
         <v>148</v>
-      </c>
-      <c r="J65" s="15" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B66" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="B66:B75" si="23">B65+1</f>
         <v>64</v>
       </c>
       <c r="C66" s="12">
@@ -4741,27 +4771,27 @@
         <v>19</v>
       </c>
       <c r="I66" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="J66" s="15" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B67" s="11">
-        <f t="shared" ref="B67:B73" si="24">B66+1</f>
+        <f t="shared" si="23"/>
         <v>65</v>
       </c>
       <c r="C67" s="12">
-        <v>45722</v>
+        <v>45726</v>
       </c>
       <c r="D67" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E67" s="12"/>
       <c r="F67" s="13">
-        <f t="shared" si="21"/>
-        <v>59</v>
+        <f>$B$66</f>
+        <v>64</v>
       </c>
       <c r="G67" s="13" t="s">
         <v>14</v>
@@ -4770,27 +4800,27 @@
         <v>19</v>
       </c>
       <c r="I67" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="J67" s="15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B68" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>66</v>
       </c>
       <c r="C68" s="12">
-        <v>45726</v>
+        <v>45729</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E68" s="12"/>
       <c r="F68" s="13">
-        <f>$B$67</f>
-        <v>65</v>
+        <f>$B$62</f>
+        <v>60</v>
       </c>
       <c r="G68" s="13" t="s">
         <v>14</v>
@@ -4799,15 +4829,15 @@
         <v>19</v>
       </c>
       <c r="I68" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="J68" s="15" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="69" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B69" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>67</v>
       </c>
       <c r="C69" s="12">
@@ -4818,8 +4848,8 @@
       </c>
       <c r="E69" s="12"/>
       <c r="F69" s="13">
-        <f>$B$63</f>
-        <v>61</v>
+        <f>$B$62</f>
+        <v>60</v>
       </c>
       <c r="G69" s="13" t="s">
         <v>14</v>
@@ -4828,7 +4858,7 @@
         <v>19</v>
       </c>
       <c r="I69" s="14" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="J69" s="15" t="s">
         <v>155</v>
@@ -4836,36 +4866,66 @@
     </row>
     <row r="70" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B70" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>68</v>
       </c>
-      <c r="C70" s="12"/>
-      <c r="D70" s="13"/>
+      <c r="C70" s="12">
+        <v>45729</v>
+      </c>
+      <c r="D70" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E70" s="12"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="13"/>
-      <c r="H70" s="13"/>
-      <c r="I70" s="14"/>
-      <c r="J70" s="15"/>
+      <c r="F70" s="13">
+        <f>$B$62</f>
+        <v>60</v>
+      </c>
+      <c r="G70" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H70" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I70" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="J70" s="15" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="71" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B71" s="11">
-        <f t="shared" si="24"/>
-        <v>69</v>
-      </c>
-      <c r="C71" s="12"/>
-      <c r="D71" s="13"/>
+        <f>B69+1</f>
+        <v>68</v>
+      </c>
+      <c r="C71" s="12">
+        <v>45729</v>
+      </c>
+      <c r="D71" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E71" s="12"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="13"/>
-      <c r="H71" s="13"/>
-      <c r="I71" s="14"/>
-      <c r="J71" s="15"/>
+      <c r="F71" s="13">
+        <f>$B$69</f>
+        <v>67</v>
+      </c>
+      <c r="G71" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H71" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I71" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="J71" s="15" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="72" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B72" s="11">
-        <f t="shared" si="24"/>
-        <v>70</v>
+        <f t="shared" si="23"/>
+        <v>69</v>
       </c>
       <c r="C72" s="12"/>
       <c r="D72" s="13"/>
@@ -4878,96 +4938,62 @@
     </row>
     <row r="73" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B73" s="11">
-        <f t="shared" si="24"/>
-        <v>71</v>
-      </c>
-      <c r="C73" s="12">
-        <v>45698</v>
-      </c>
-      <c r="D73" s="13" t="s">
-        <v>11</v>
-      </c>
+        <f t="shared" si="23"/>
+        <v>70</v>
+      </c>
+      <c r="C73" s="12"/>
+      <c r="D73" s="13"/>
       <c r="E73" s="12"/>
       <c r="F73" s="13"/>
-      <c r="G73" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H73" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="I73" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="J73" s="15" t="s">
-        <v>105</v>
-      </c>
+      <c r="G73" s="13"/>
+      <c r="H73" s="13"/>
+      <c r="I73" s="14"/>
+      <c r="J73" s="15"/>
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B74" s="11">
-        <f t="shared" si="0"/>
-        <v>72</v>
-      </c>
-      <c r="C74" s="12">
-        <v>45698</v>
-      </c>
-      <c r="D74" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E74" s="12">
-        <v>45717</v>
-      </c>
-      <c r="F74" s="13">
-        <f>$B$73</f>
+        <f t="shared" si="23"/>
         <v>71</v>
       </c>
-      <c r="G74" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H74" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I74" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="J74" s="15" t="s">
-        <v>107</v>
-      </c>
+      <c r="C74" s="12"/>
+      <c r="D74" s="13"/>
+      <c r="E74" s="12"/>
+      <c r="F74" s="13"/>
+      <c r="G74" s="13"/>
+      <c r="H74" s="13"/>
+      <c r="I74" s="14"/>
+      <c r="J74" s="15"/>
     </row>
     <row r="75" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B75" s="11">
-        <f t="shared" si="0"/>
-        <v>73</v>
+        <f t="shared" si="23"/>
+        <v>72</v>
       </c>
       <c r="C75" s="12">
         <v>45698</v>
       </c>
       <c r="D75" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E75" s="12">
-        <v>45698</v>
-      </c>
-      <c r="F75" s="13">
-        <f t="shared" ref="F75:F82" si="25">$B$74</f>
-        <v>72</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E75" s="12"/>
+      <c r="F75" s="13"/>
       <c r="G75" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H75" s="13" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="I75" s="14" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="J75" s="15" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="76" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B76" s="11">
         <f t="shared" si="0"/>
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C76" s="12">
         <v>45698</v>
@@ -4976,10 +5002,10 @@
         <v>12</v>
       </c>
       <c r="E76" s="12">
-        <v>45714</v>
+        <v>45717</v>
       </c>
       <c r="F76" s="13">
-        <f t="shared" si="25"/>
+        <f>$B$75</f>
         <v>72</v>
       </c>
       <c r="G76" s="13" t="s">
@@ -4989,16 +5015,16 @@
         <v>19</v>
       </c>
       <c r="I76" s="14" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="J76" s="15" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
     </row>
     <row r="77" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B77" s="11">
         <f t="shared" si="0"/>
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C77" s="12">
         <v>45698</v>
@@ -5007,11 +5033,11 @@
         <v>12</v>
       </c>
       <c r="E77" s="12">
-        <v>45714</v>
+        <v>45698</v>
       </c>
       <c r="F77" s="13">
-        <f t="shared" si="25"/>
-        <v>72</v>
+        <f t="shared" ref="F77:F84" si="24">$B$76</f>
+        <v>73</v>
       </c>
       <c r="G77" s="13" t="s">
         <v>14</v>
@@ -5020,19 +5046,19 @@
         <v>19</v>
       </c>
       <c r="I77" s="14" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="J77" s="15" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
     </row>
     <row r="78" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B78" s="11">
         <f t="shared" si="0"/>
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C78" s="12">
-        <v>45714</v>
+        <v>45698</v>
       </c>
       <c r="D78" s="13" t="s">
         <v>12</v>
@@ -5041,8 +5067,8 @@
         <v>45714</v>
       </c>
       <c r="F78" s="13">
-        <f t="shared" si="25"/>
-        <v>72</v>
+        <f t="shared" si="24"/>
+        <v>73</v>
       </c>
       <c r="G78" s="13" t="s">
         <v>14</v>
@@ -5051,29 +5077,29 @@
         <v>19</v>
       </c>
       <c r="I78" s="14" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="J78" s="15" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="79" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B79" s="11">
         <f t="shared" si="0"/>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C79" s="12">
+        <v>45698</v>
+      </c>
+      <c r="D79" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E79" s="12">
         <v>45714</v>
       </c>
-      <c r="D79" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E79" s="12">
-        <v>45715</v>
-      </c>
       <c r="F79" s="13">
-        <f t="shared" si="25"/>
-        <v>72</v>
+        <f t="shared" si="24"/>
+        <v>73</v>
       </c>
       <c r="G79" s="13" t="s">
         <v>14</v>
@@ -5082,29 +5108,29 @@
         <v>19</v>
       </c>
       <c r="I79" s="14" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="J79" s="15" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="80" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B80" s="11">
         <f t="shared" si="0"/>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C80" s="12">
-        <v>45715</v>
+        <v>45714</v>
       </c>
       <c r="D80" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E80" s="12">
-        <v>45715</v>
+        <v>45714</v>
       </c>
       <c r="F80" s="13">
-        <f t="shared" si="25"/>
-        <v>72</v>
+        <f t="shared" si="24"/>
+        <v>73</v>
       </c>
       <c r="G80" s="13" t="s">
         <v>14</v>
@@ -5113,29 +5139,29 @@
         <v>19</v>
       </c>
       <c r="I80" s="14" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="J80" s="15" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="81" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B81" s="11">
         <f t="shared" si="0"/>
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C81" s="12">
+        <v>45714</v>
+      </c>
+      <c r="D81" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E81" s="12">
         <v>45715</v>
       </c>
-      <c r="D81" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E81" s="12">
-        <v>45714</v>
-      </c>
       <c r="F81" s="13">
-        <f t="shared" si="25"/>
-        <v>72</v>
+        <f t="shared" si="24"/>
+        <v>73</v>
       </c>
       <c r="G81" s="13" t="s">
         <v>14</v>
@@ -5144,29 +5170,29 @@
         <v>19</v>
       </c>
       <c r="I81" s="14" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="J81" s="15" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="82" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B82" s="11">
         <f t="shared" si="0"/>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C82" s="12">
-        <v>45717</v>
+        <v>45715</v>
       </c>
       <c r="D82" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E82" s="12">
-        <v>45717</v>
+        <v>45715</v>
       </c>
       <c r="F82" s="13">
-        <f t="shared" si="25"/>
-        <v>72</v>
+        <f t="shared" si="24"/>
+        <v>73</v>
       </c>
       <c r="G82" s="13" t="s">
         <v>14</v>
@@ -5175,29 +5201,29 @@
         <v>19</v>
       </c>
       <c r="I82" s="14" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="J82" s="15" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B83" s="11">
         <f t="shared" si="0"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C83" s="12">
-        <v>45717</v>
+        <v>45715</v>
       </c>
       <c r="D83" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E83" s="12">
-        <v>45717</v>
+        <v>45714</v>
       </c>
       <c r="F83" s="13">
-        <f>$B$82</f>
-        <v>80</v>
+        <f t="shared" si="24"/>
+        <v>73</v>
       </c>
       <c r="G83" s="13" t="s">
         <v>14</v>
@@ -5206,16 +5232,16 @@
         <v>19</v>
       </c>
       <c r="I83" s="14" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="J83" s="15" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="84" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B84" s="11">
         <f t="shared" si="0"/>
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C84" s="12">
         <v>45717</v>
@@ -5227,8 +5253,8 @@
         <v>45717</v>
       </c>
       <c r="F84" s="13">
-        <f>$B$82</f>
-        <v>80</v>
+        <f t="shared" si="24"/>
+        <v>73</v>
       </c>
       <c r="G84" s="13" t="s">
         <v>14</v>
@@ -5237,16 +5263,16 @@
         <v>19</v>
       </c>
       <c r="I84" s="14" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="J84" s="15" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B85" s="11">
         <f t="shared" si="0"/>
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C85" s="12">
         <v>45717</v>
@@ -5258,8 +5284,8 @@
         <v>45717</v>
       </c>
       <c r="F85" s="13">
-        <f>$B$82</f>
-        <v>80</v>
+        <f>$B$84</f>
+        <v>81</v>
       </c>
       <c r="G85" s="13" t="s">
         <v>14</v>
@@ -5268,45 +5294,47 @@
         <v>19</v>
       </c>
       <c r="I85" s="14" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="J85" s="15" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B86" s="11">
         <f t="shared" si="0"/>
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C86" s="12">
         <v>45717</v>
       </c>
       <c r="D86" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E86" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E86" s="12">
+        <v>45717</v>
+      </c>
       <c r="F86" s="13">
-        <f>$B$73</f>
-        <v>71</v>
+        <f>$B$84</f>
+        <v>81</v>
       </c>
       <c r="G86" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H86" s="13" t="s">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="I86" s="14" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="J86" s="15" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="87" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B87" s="11">
         <f t="shared" si="0"/>
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C87" s="12">
         <v>45717</v>
@@ -5318,57 +5346,55 @@
         <v>45717</v>
       </c>
       <c r="F87" s="13">
-        <f t="shared" ref="F87:F93" si="26">$B$86</f>
-        <v>84</v>
+        <f>$B$84</f>
+        <v>81</v>
       </c>
       <c r="G87" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H87" s="13" t="s">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="I87" s="14" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="J87" s="15" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="88" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B88" s="11">
         <f t="shared" si="0"/>
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C88" s="12">
         <v>45717</v>
       </c>
       <c r="D88" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E88" s="12">
-        <v>45717</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E88" s="12"/>
       <c r="F88" s="13">
-        <f t="shared" si="26"/>
-        <v>84</v>
+        <f>$B$75</f>
+        <v>72</v>
       </c>
       <c r="G88" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H88" s="13" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I88" s="14" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="J88" s="15" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="89" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B89" s="11">
-        <f t="shared" ref="B89" si="27">B88+1</f>
-        <v>87</v>
+        <f t="shared" si="0"/>
+        <v>86</v>
       </c>
       <c r="C89" s="12">
         <v>45717</v>
@@ -5380,66 +5406,70 @@
         <v>45717</v>
       </c>
       <c r="F89" s="13">
-        <f t="shared" si="26"/>
-        <v>84</v>
+        <f t="shared" ref="F89:F95" si="25">$B$88</f>
+        <v>85</v>
       </c>
       <c r="G89" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H89" s="13" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="I89" s="14" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="J89" s="15" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="90" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B90" s="11">
-        <f t="shared" ref="B90" si="28">B89+1</f>
-        <v>88</v>
+        <f t="shared" si="0"/>
+        <v>87</v>
       </c>
       <c r="C90" s="12">
         <v>45717</v>
       </c>
       <c r="D90" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E90" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E90" s="12">
+        <v>45717</v>
+      </c>
       <c r="F90" s="13">
-        <f t="shared" si="26"/>
-        <v>84</v>
+        <f t="shared" si="25"/>
+        <v>85</v>
       </c>
       <c r="G90" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H90" s="13" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I90" s="14" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J90" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="91" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B91" s="11">
-        <f t="shared" ref="B91" si="29">B90+1</f>
-        <v>89</v>
+        <f t="shared" ref="B91" si="26">B90+1</f>
+        <v>88</v>
       </c>
       <c r="C91" s="12">
         <v>45717</v>
       </c>
       <c r="D91" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E91" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E91" s="12">
+        <v>45717</v>
+      </c>
       <c r="F91" s="13">
-        <f t="shared" si="26"/>
-        <v>84</v>
+        <f t="shared" si="25"/>
+        <v>85</v>
       </c>
       <c r="G91" s="13" t="s">
         <v>14</v>
@@ -5448,16 +5478,16 @@
         <v>19</v>
       </c>
       <c r="I91" s="14" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="J91" s="15" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="92" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B92" s="11">
-        <f t="shared" ref="B92" si="30">B91+1</f>
-        <v>90</v>
+        <f t="shared" ref="B92" si="27">B91+1</f>
+        <v>89</v>
       </c>
       <c r="C92" s="12">
         <v>45717</v>
@@ -5467,26 +5497,26 @@
       </c>
       <c r="E92" s="12"/>
       <c r="F92" s="13">
-        <f t="shared" si="26"/>
-        <v>84</v>
+        <f t="shared" si="25"/>
+        <v>85</v>
       </c>
       <c r="G92" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H92" s="13" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I92" s="14" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J92" s="15" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="93" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B93" s="11">
-        <f t="shared" ref="B93" si="31">B92+1</f>
-        <v>91</v>
+        <f t="shared" ref="B93" si="28">B92+1</f>
+        <v>90</v>
       </c>
       <c r="C93" s="12">
         <v>45717</v>
@@ -5496,111 +5526,107 @@
       </c>
       <c r="E93" s="12"/>
       <c r="F93" s="13">
-        <f t="shared" si="26"/>
-        <v>84</v>
+        <f t="shared" si="25"/>
+        <v>85</v>
       </c>
       <c r="G93" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H93" s="13" t="s">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="I93" s="14" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J93" s="15" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="94" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B94" s="11">
-        <f t="shared" ref="B94:B105" si="32">B93+1</f>
-        <v>92</v>
-      </c>
-      <c r="C94" s="12"/>
-      <c r="D94" s="13"/>
+        <f t="shared" ref="B94" si="29">B93+1</f>
+        <v>91</v>
+      </c>
+      <c r="C94" s="12">
+        <v>45717</v>
+      </c>
+      <c r="D94" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E94" s="12"/>
-      <c r="F94" s="13"/>
-      <c r="G94" s="13"/>
-      <c r="H94" s="13"/>
-      <c r="I94" s="14"/>
-      <c r="J94" s="15"/>
+      <c r="F94" s="13">
+        <f t="shared" si="25"/>
+        <v>85</v>
+      </c>
+      <c r="G94" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H94" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="I94" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="J94" s="15" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="95" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B95" s="11">
-        <f t="shared" si="32"/>
-        <v>93</v>
+        <f t="shared" ref="B95" si="30">B94+1</f>
+        <v>92</v>
       </c>
       <c r="C95" s="12">
-        <v>45719</v>
+        <v>45717</v>
       </c>
       <c r="D95" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E95" s="12"/>
-      <c r="F95" s="13"/>
+      <c r="F95" s="13">
+        <f t="shared" si="25"/>
+        <v>85</v>
+      </c>
       <c r="G95" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H95" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I95" s="15" t="s">
-        <v>143</v>
+        <v>99</v>
+      </c>
+      <c r="I95" s="14" t="s">
+        <v>129</v>
       </c>
       <c r="J95" s="15" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="96" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B96" s="11">
-        <f t="shared" si="32"/>
-        <v>94</v>
-      </c>
-      <c r="C96" s="12">
-        <v>45719</v>
-      </c>
-      <c r="D96" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E96" s="12">
-        <v>45719</v>
-      </c>
-      <c r="F96" s="13">
-        <f>$B$95</f>
+        <f t="shared" ref="B96:B107" si="31">B95+1</f>
         <v>93</v>
       </c>
-      <c r="G96" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H96" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I96" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="J96" s="15" t="s">
-        <v>142</v>
-      </c>
+      <c r="C96" s="12"/>
+      <c r="D96" s="13"/>
+      <c r="E96" s="12"/>
+      <c r="F96" s="13"/>
+      <c r="G96" s="13"/>
+      <c r="H96" s="13"/>
+      <c r="I96" s="14"/>
+      <c r="J96" s="15"/>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97" s="11">
-        <f t="shared" si="32"/>
-        <v>95</v>
+        <f t="shared" si="31"/>
+        <v>94</v>
       </c>
       <c r="C97" s="12">
         <v>45719</v>
       </c>
       <c r="D97" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E97" s="12">
-        <v>45720</v>
-      </c>
-      <c r="F97" s="13">
-        <f>$B$95</f>
-        <v>93</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E97" s="12"/>
+      <c r="F97" s="13"/>
       <c r="G97" s="13" t="s">
         <v>14</v>
       </c>
@@ -5608,27 +5634,29 @@
         <v>21</v>
       </c>
       <c r="I97" s="15" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="J97" s="15" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98" s="11">
-        <f t="shared" si="32"/>
-        <v>96</v>
+        <f t="shared" si="31"/>
+        <v>95</v>
       </c>
       <c r="C98" s="12">
         <v>45719</v>
       </c>
       <c r="D98" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E98" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E98" s="12">
+        <v>45719</v>
+      </c>
       <c r="F98" s="13">
-        <f>$B$95</f>
-        <v>93</v>
+        <f>$B$97</f>
+        <v>94</v>
       </c>
       <c r="G98" s="13" t="s">
         <v>14</v>
@@ -5637,27 +5665,29 @@
         <v>21</v>
       </c>
       <c r="I98" s="15" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="J98" s="15" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B99" s="11">
-        <f t="shared" si="32"/>
-        <v>97</v>
+        <f t="shared" si="31"/>
+        <v>96</v>
       </c>
       <c r="C99" s="12">
         <v>45719</v>
       </c>
       <c r="D99" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E99" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E99" s="12">
+        <v>45720</v>
+      </c>
       <c r="F99" s="13">
-        <f>$B$95</f>
-        <v>93</v>
+        <f>$B$97</f>
+        <v>94</v>
       </c>
       <c r="G99" s="13" t="s">
         <v>14</v>
@@ -5666,44 +5696,74 @@
         <v>21</v>
       </c>
       <c r="I99" s="15" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="J99" s="15" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="100" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B100" s="11">
-        <f t="shared" si="32"/>
-        <v>98</v>
-      </c>
-      <c r="C100" s="12"/>
-      <c r="D100" s="13"/>
+        <f t="shared" si="31"/>
+        <v>97</v>
+      </c>
+      <c r="C100" s="12">
+        <v>45719</v>
+      </c>
+      <c r="D100" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E100" s="12"/>
-      <c r="F100" s="13"/>
-      <c r="G100" s="13"/>
-      <c r="H100" s="13"/>
-      <c r="I100" s="14"/>
-      <c r="J100" s="15"/>
+      <c r="F100" s="13">
+        <f>$B$97</f>
+        <v>94</v>
+      </c>
+      <c r="G100" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H100" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I100" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="J100" s="15" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B101" s="11">
-        <f t="shared" si="32"/>
-        <v>99</v>
-      </c>
-      <c r="C101" s="12"/>
-      <c r="D101" s="13"/>
+        <f t="shared" si="31"/>
+        <v>98</v>
+      </c>
+      <c r="C101" s="12">
+        <v>45719</v>
+      </c>
+      <c r="D101" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E101" s="12"/>
-      <c r="F101" s="13"/>
-      <c r="G101" s="13"/>
-      <c r="H101" s="13"/>
-      <c r="I101" s="14"/>
-      <c r="J101" s="15"/>
+      <c r="F101" s="13">
+        <f>$B$97</f>
+        <v>94</v>
+      </c>
+      <c r="G101" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H101" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I101" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="J101" s="15" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B102" s="11">
-        <f t="shared" si="32"/>
-        <v>100</v>
+        <f t="shared" si="31"/>
+        <v>99</v>
       </c>
       <c r="C102" s="12"/>
       <c r="D102" s="13"/>
@@ -5716,8 +5776,8 @@
     </row>
     <row r="103" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B103" s="11">
-        <f t="shared" si="32"/>
-        <v>101</v>
+        <f t="shared" si="31"/>
+        <v>100</v>
       </c>
       <c r="C103" s="12"/>
       <c r="D103" s="13"/>
@@ -5730,8 +5790,8 @@
     </row>
     <row r="104" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B104" s="11">
-        <f t="shared" si="32"/>
-        <v>102</v>
+        <f t="shared" si="31"/>
+        <v>101</v>
       </c>
       <c r="C104" s="12"/>
       <c r="D104" s="13"/>
@@ -5744,8 +5804,8 @@
     </row>
     <row r="105" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B105" s="11">
-        <f t="shared" si="32"/>
-        <v>103</v>
+        <f t="shared" si="31"/>
+        <v>102</v>
       </c>
       <c r="C105" s="12"/>
       <c r="D105" s="13"/>
@@ -5756,24 +5816,52 @@
       <c r="I105" s="14"/>
       <c r="J105" s="15"/>
     </row>
-    <row r="106" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B106" s="18">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B106" s="11">
+        <f t="shared" si="31"/>
+        <v>103</v>
+      </c>
+      <c r="C106" s="12"/>
+      <c r="D106" s="13"/>
+      <c r="E106" s="12"/>
+      <c r="F106" s="13"/>
+      <c r="G106" s="13"/>
+      <c r="H106" s="13"/>
+      <c r="I106" s="14"/>
+      <c r="J106" s="15"/>
+    </row>
+    <row r="107" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B107" s="11">
+        <f t="shared" si="31"/>
+        <v>104</v>
+      </c>
+      <c r="C107" s="12"/>
+      <c r="D107" s="13"/>
+      <c r="E107" s="12"/>
+      <c r="F107" s="13"/>
+      <c r="G107" s="13"/>
+      <c r="H107" s="13"/>
+      <c r="I107" s="14"/>
+      <c r="J107" s="15"/>
+    </row>
+    <row r="108" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B108" s="18">
         <f t="shared" si="0"/>
-        <v>104</v>
-      </c>
-      <c r="C106" s="19"/>
-      <c r="D106" s="20"/>
-      <c r="E106" s="19"/>
-      <c r="F106" s="20"/>
-      <c r="G106" s="20"/>
-      <c r="H106" s="20"/>
-      <c r="I106" s="21"/>
-      <c r="J106" s="22"/>
+        <v>105</v>
+      </c>
+      <c r="C108" s="19"/>
+      <c r="D108" s="20"/>
+      <c r="E108" s="19"/>
+      <c r="F108" s="20"/>
+      <c r="G108" s="20"/>
+      <c r="H108" s="20"/>
+      <c r="I108" s="21"/>
+      <c r="J108" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:J106" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
+  <autoFilter ref="B2:J108" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B3:J45 A43:A45 A46:J46 A47:A51 B47:J106">
+  <conditionalFormatting sqref="B3:J45 A43:A45 A46:J46 A47:A51 B47:J108">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>
@@ -5790,25 +5878,25 @@
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H104:H106 H74:H85 H3:H62 H72</xm:sqref>
+          <xm:sqref>H106:H108 H76:H87 H3:H61 H74</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D6F2F62E-6D63-4E2D-8772-1211A4C3A979}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$10</xm:f>
           </x14:formula1>
-          <xm:sqref>H73 H86:H103 H63:H71</xm:sqref>
+          <xm:sqref>H75 H88:H105 H62:H73</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C61EF0EC-B820-4CEA-8AA2-04B5D172AE2C}">
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D106</xm:sqref>
+          <xm:sqref>D3:D108</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G106</xm:sqref>
+          <xm:sqref>G3:G108</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5872,7 +5960,7 @@
     </row>
     <row r="7" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D7" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A98B1E6-BB36-4CE1-9AF4-E7A4BBE78B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79BDAEA-BF3C-41B5-89CD-31EF6B53DD4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -20,6 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作業項目!$B$2:$J$108</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="160">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -2199,6 +2200,16 @@
     </rPh>
     <rPh sb="18" eb="22">
       <t>ショキトウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HtmlSysTableList01クラス : テーブル表示追加</t>
+    <rPh sb="28" eb="30">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ツイカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2888,6 +2899,26 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="12">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{173B67FF-03C2-42DB-9315-4AD202080CA9}">
+  <we:reference id="wa104381701" version="1.0.0.4" store="ja-JP" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA104381701" version="1.0.0.4" store="WA104381701" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
   <dimension ref="A1:K108"/>
@@ -4672,7 +4703,9 @@
       <c r="D63" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="E63" s="12"/>
+      <c r="E63" s="12">
+        <v>45729</v>
+      </c>
       <c r="F63" s="13">
         <f t="shared" si="21"/>
         <v>59</v>
@@ -4701,7 +4734,9 @@
       <c r="D64" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="E64" s="12"/>
+      <c r="E64" s="12">
+        <v>45729</v>
+      </c>
       <c r="F64" s="13">
         <f t="shared" si="21"/>
         <v>59</v>
@@ -4730,7 +4765,9 @@
       <c r="D65" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="E65" s="12"/>
+      <c r="E65" s="12">
+        <v>45729</v>
+      </c>
       <c r="F65" s="13">
         <f t="shared" si="21"/>
         <v>59</v>
@@ -4759,7 +4796,9 @@
       <c r="D66" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="E66" s="12"/>
+      <c r="E66" s="12">
+        <v>45729</v>
+      </c>
       <c r="F66" s="13">
         <f t="shared" si="21"/>
         <v>59</v>
@@ -4788,7 +4827,9 @@
       <c r="D67" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="E67" s="12"/>
+      <c r="E67" s="12">
+        <v>45729</v>
+      </c>
       <c r="F67" s="13">
         <f>$B$66</f>
         <v>64</v>
@@ -4815,9 +4856,11 @@
         <v>45729</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E68" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E68" s="12">
+        <v>45730</v>
+      </c>
       <c r="F68" s="13">
         <f>$B$62</f>
         <v>60</v>
@@ -4844,7 +4887,7 @@
         <v>45729</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E69" s="12"/>
       <c r="F69" s="13">
@@ -4902,7 +4945,7 @@
         <v>45729</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E71" s="12"/>
       <c r="F71" s="13">
@@ -4927,14 +4970,29 @@
         <f t="shared" si="23"/>
         <v>69</v>
       </c>
-      <c r="C72" s="12"/>
-      <c r="D72" s="13"/>
+      <c r="C72" s="12">
+        <v>45730</v>
+      </c>
+      <c r="D72" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E72" s="12"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="13"/>
-      <c r="H72" s="13"/>
-      <c r="I72" s="14"/>
-      <c r="J72" s="15"/>
+      <c r="F72" s="13">
+        <f>$B$69</f>
+        <v>67</v>
+      </c>
+      <c r="G72" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H72" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I72" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="J72" s="15" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="73" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B73" s="11">

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79BDAEA-BF3C-41B5-89CD-31EF6B53DD4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFD3EE92-40EA-44C9-9E4B-276DB01BD47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -20,7 +20,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作業項目!$B$2:$J$108</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2204,11 +2203,14 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>HtmlSysTableList01クラス : テーブル表示追加</t>
+    <t>HtmlSysTableList01クラス : テーブル一覧表示追加</t>
     <rPh sb="28" eb="30">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="30" eb="32">
       <t>ヒョウジ</t>
     </rPh>
-    <rPh sb="30" eb="32">
+    <rPh sb="32" eb="34">
       <t>ツイカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -4945,7 +4947,7 @@
         <v>45729</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E71" s="12"/>
       <c r="F71" s="13">

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFD3EE92-40EA-44C9-9E4B-276DB01BD47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C580CE1D-4CF7-408C-9918-4C575978679C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="161">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -2212,6 +2212,25 @@
     </rPh>
     <rPh sb="32" eb="34">
       <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テーブル情報初期登録 : 表示情報の登録</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>ショキトウロク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>トウロク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5001,14 +5020,29 @@
         <f t="shared" si="23"/>
         <v>70</v>
       </c>
-      <c r="C73" s="12"/>
-      <c r="D73" s="13"/>
+      <c r="C73" s="12">
+        <v>45731</v>
+      </c>
+      <c r="D73" s="13" t="s">
+        <v>11</v>
+      </c>
       <c r="E73" s="12"/>
-      <c r="F73" s="13"/>
-      <c r="G73" s="13"/>
-      <c r="H73" s="13"/>
-      <c r="I73" s="14"/>
-      <c r="J73" s="15"/>
+      <c r="F73" s="13">
+        <f>$B$69</f>
+        <v>67</v>
+      </c>
+      <c r="G73" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H73" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I73" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="J73" s="15" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B74" s="11">

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C580CE1D-4CF7-408C-9918-4C575978679C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ED299D3-C3BD-4E57-9023-D389D6D96C44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="選択情報" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作業項目!$B$2:$J$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作業項目!$B$2:$J$112</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="164">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -1977,19 +1977,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>照会画面構築</t>
-    <rPh sb="0" eb="2">
-      <t>ショウカイ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>コウチク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>メインメニュー画面</t>
     <rPh sb="7" eb="9">
       <t>ガメン</t>
@@ -2216,21 +2203,73 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>表示情報 : 照会画面初期登録</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ショウカイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>ショキトウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レベルわけ方法</t>
+    <rPh sb="5" eb="7">
+      <t>ホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>方法の検討</t>
+    <rPh sb="0" eb="2">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ケントウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>テーブル情報初期登録 : 表示情報の登録</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示詳細情報 : テーブル一覧項目の追加 : テーブル情報ID、CD、名前、説明</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショウサイ</t>
+    </rPh>
     <rPh sb="4" eb="6">
       <t>ジョウホウ</t>
     </rPh>
-    <rPh sb="6" eb="10">
-      <t>ショキトウロク</t>
-    </rPh>
     <rPh sb="13" eb="15">
-      <t>ヒョウジ</t>
+      <t>イチラン</t>
     </rPh>
     <rPh sb="15" eb="17">
-      <t>ジョウホウ</t>
+      <t>コウモク</t>
     </rPh>
     <rPh sb="18" eb="20">
-      <t>トウロク</t>
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>セツメイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2942,7 +2981,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="A1:K108"/>
+  <dimension ref="A1:K112"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -3140,7 +3179,7 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
-        <f t="shared" ref="A8:B108" si="0">B7+1</f>
+        <f t="shared" ref="A8:B112" si="0">B7+1</f>
         <v>6</v>
       </c>
       <c r="C8" s="12">
@@ -4681,7 +4720,7 @@
         <v>63</v>
       </c>
       <c r="J61" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
@@ -4707,10 +4746,10 @@
         <v>19</v>
       </c>
       <c r="I62" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="J62" s="15" t="s">
         <v>145</v>
-      </c>
-      <c r="J62" s="15" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
@@ -4738,10 +4777,10 @@
         <v>19</v>
       </c>
       <c r="I63" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J63" s="15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
@@ -4769,10 +4808,10 @@
         <v>19</v>
       </c>
       <c r="I64" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J64" s="15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.3">
@@ -4800,15 +4839,15 @@
         <v>19</v>
       </c>
       <c r="I65" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J65" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B66" s="11">
-        <f t="shared" ref="B66:B75" si="23">B65+1</f>
+        <f t="shared" ref="B66:B79" si="23">B65+1</f>
         <v>64</v>
       </c>
       <c r="C66" s="12">
@@ -4831,10 +4870,10 @@
         <v>19</v>
       </c>
       <c r="I66" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J66" s="15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.3">
@@ -4862,10 +4901,10 @@
         <v>19</v>
       </c>
       <c r="I67" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J67" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.3">
@@ -4893,10 +4932,10 @@
         <v>19</v>
       </c>
       <c r="I68" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J68" s="15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="69" spans="2:10" x14ac:dyDescent="0.3">
@@ -4922,10 +4961,10 @@
         <v>19</v>
       </c>
       <c r="I69" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J69" s="15" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="70" spans="2:10" x14ac:dyDescent="0.3">
@@ -4951,10 +4990,10 @@
         <v>19</v>
       </c>
       <c r="I70" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J70" s="15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="71" spans="2:10" x14ac:dyDescent="0.3">
@@ -4980,10 +5019,10 @@
         <v>19</v>
       </c>
       <c r="I71" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="J71" s="15" t="s">
         <v>156</v>
-      </c>
-      <c r="J71" s="15" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="72" spans="2:10" x14ac:dyDescent="0.3">
@@ -5009,10 +5048,10 @@
         <v>19</v>
       </c>
       <c r="I72" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J72" s="15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="73" spans="2:10" x14ac:dyDescent="0.3">
@@ -5024,9 +5063,11 @@
         <v>45731</v>
       </c>
       <c r="D73" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E73" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E73" s="12">
+        <v>45734</v>
+      </c>
       <c r="F73" s="13">
         <f>$B$69</f>
         <v>67</v>
@@ -5038,10 +5079,10 @@
         <v>19</v>
       </c>
       <c r="I73" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J73" s="15" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.3">
@@ -5049,163 +5090,110 @@
         <f t="shared" si="23"/>
         <v>71</v>
       </c>
-      <c r="C74" s="12"/>
-      <c r="D74" s="13"/>
+      <c r="C74" s="12">
+        <v>45734</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>11</v>
+      </c>
       <c r="E74" s="12"/>
-      <c r="F74" s="13"/>
-      <c r="G74" s="13"/>
-      <c r="H74" s="13"/>
-      <c r="I74" s="14"/>
-      <c r="J74" s="15"/>
+      <c r="F74" s="13">
+        <f>$B$69</f>
+        <v>67</v>
+      </c>
+      <c r="G74" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H74" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I74" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="J74" s="15" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="75" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B75" s="11">
         <f t="shared" si="23"/>
         <v>72</v>
       </c>
-      <c r="C75" s="12">
-        <v>45698</v>
-      </c>
-      <c r="D75" s="13" t="s">
-        <v>11</v>
-      </c>
+      <c r="C75" s="12"/>
+      <c r="D75" s="13"/>
       <c r="E75" s="12"/>
       <c r="F75" s="13"/>
-      <c r="G75" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H75" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="I75" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="J75" s="15" t="s">
-        <v>102</v>
-      </c>
+      <c r="G75" s="13"/>
+      <c r="H75" s="13"/>
+      <c r="I75" s="14"/>
+      <c r="J75" s="15"/>
     </row>
     <row r="76" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B76" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="23"/>
         <v>73</v>
       </c>
-      <c r="C76" s="12">
-        <v>45698</v>
-      </c>
-      <c r="D76" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E76" s="12">
-        <v>45717</v>
-      </c>
-      <c r="F76" s="13">
-        <f>$B$75</f>
-        <v>72</v>
-      </c>
-      <c r="G76" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H76" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I76" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="J76" s="15" t="s">
-        <v>104</v>
-      </c>
+      <c r="C76" s="12"/>
+      <c r="D76" s="13"/>
+      <c r="E76" s="12"/>
+      <c r="F76" s="13"/>
+      <c r="G76" s="13"/>
+      <c r="H76" s="13"/>
+      <c r="I76" s="14"/>
+      <c r="J76" s="15"/>
     </row>
     <row r="77" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B77" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="23"/>
         <v>74</v>
       </c>
-      <c r="C77" s="12">
-        <v>45698</v>
-      </c>
-      <c r="D77" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E77" s="12">
-        <v>45698</v>
-      </c>
-      <c r="F77" s="13">
-        <f t="shared" ref="F77:F84" si="24">$B$76</f>
-        <v>73</v>
-      </c>
-      <c r="G77" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H77" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I77" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="J77" s="15" t="s">
-        <v>105</v>
-      </c>
+      <c r="C77" s="12"/>
+      <c r="D77" s="13"/>
+      <c r="E77" s="12"/>
+      <c r="F77" s="13"/>
+      <c r="G77" s="13"/>
+      <c r="H77" s="13"/>
+      <c r="I77" s="14"/>
+      <c r="J77" s="15"/>
     </row>
     <row r="78" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B78" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="23"/>
         <v>75</v>
       </c>
-      <c r="C78" s="12">
-        <v>45698</v>
-      </c>
-      <c r="D78" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E78" s="12">
-        <v>45714</v>
-      </c>
-      <c r="F78" s="13">
-        <f t="shared" si="24"/>
-        <v>73</v>
-      </c>
-      <c r="G78" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H78" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I78" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="J78" s="15" t="s">
-        <v>116</v>
-      </c>
+      <c r="C78" s="12"/>
+      <c r="D78" s="13"/>
+      <c r="E78" s="12"/>
+      <c r="F78" s="13"/>
+      <c r="G78" s="13"/>
+      <c r="H78" s="13"/>
+      <c r="I78" s="14"/>
+      <c r="J78" s="15"/>
     </row>
     <row r="79" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B79" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="23"/>
         <v>76</v>
       </c>
       <c r="C79" s="12">
         <v>45698</v>
       </c>
       <c r="D79" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E79" s="12">
-        <v>45714</v>
-      </c>
-      <c r="F79" s="13">
-        <f t="shared" si="24"/>
-        <v>73</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E79" s="12"/>
+      <c r="F79" s="13"/>
       <c r="G79" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H79" s="13" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="I79" s="14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J79" s="15" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
     </row>
     <row r="80" spans="2:10" x14ac:dyDescent="0.3">
@@ -5214,17 +5202,17 @@
         <v>77</v>
       </c>
       <c r="C80" s="12">
-        <v>45714</v>
+        <v>45698</v>
       </c>
       <c r="D80" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E80" s="12">
-        <v>45714</v>
+        <v>45717</v>
       </c>
       <c r="F80" s="13">
-        <f t="shared" si="24"/>
-        <v>73</v>
+        <f>$B$79</f>
+        <v>76</v>
       </c>
       <c r="G80" s="13" t="s">
         <v>14</v>
@@ -5236,7 +5224,7 @@
         <v>103</v>
       </c>
       <c r="J80" s="15" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
     </row>
     <row r="81" spans="2:10" x14ac:dyDescent="0.3">
@@ -5245,17 +5233,17 @@
         <v>78</v>
       </c>
       <c r="C81" s="12">
-        <v>45714</v>
+        <v>45698</v>
       </c>
       <c r="D81" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E81" s="12">
-        <v>45715</v>
+        <v>45698</v>
       </c>
       <c r="F81" s="13">
-        <f t="shared" si="24"/>
-        <v>73</v>
+        <f t="shared" ref="F81:F88" si="24">$B$80</f>
+        <v>77</v>
       </c>
       <c r="G81" s="13" t="s">
         <v>14</v>
@@ -5267,7 +5255,7 @@
         <v>103</v>
       </c>
       <c r="J81" s="15" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
     </row>
     <row r="82" spans="2:10" x14ac:dyDescent="0.3">
@@ -5276,17 +5264,17 @@
         <v>79</v>
       </c>
       <c r="C82" s="12">
-        <v>45715</v>
+        <v>45698</v>
       </c>
       <c r="D82" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E82" s="12">
-        <v>45715</v>
+        <v>45714</v>
       </c>
       <c r="F82" s="13">
         <f t="shared" si="24"/>
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G82" s="13" t="s">
         <v>14</v>
@@ -5298,7 +5286,7 @@
         <v>103</v>
       </c>
       <c r="J82" s="15" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.3">
@@ -5307,7 +5295,7 @@
         <v>80</v>
       </c>
       <c r="C83" s="12">
-        <v>45715</v>
+        <v>45698</v>
       </c>
       <c r="D83" s="13" t="s">
         <v>12</v>
@@ -5317,7 +5305,7 @@
       </c>
       <c r="F83" s="13">
         <f t="shared" si="24"/>
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G83" s="13" t="s">
         <v>14</v>
@@ -5329,7 +5317,7 @@
         <v>103</v>
       </c>
       <c r="J83" s="15" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="84" spans="2:10" x14ac:dyDescent="0.3">
@@ -5338,17 +5326,17 @@
         <v>81</v>
       </c>
       <c r="C84" s="12">
-        <v>45717</v>
+        <v>45714</v>
       </c>
       <c r="D84" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E84" s="12">
-        <v>45717</v>
+        <v>45714</v>
       </c>
       <c r="F84" s="13">
         <f t="shared" si="24"/>
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G84" s="13" t="s">
         <v>14</v>
@@ -5360,7 +5348,7 @@
         <v>103</v>
       </c>
       <c r="J84" s="15" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.3">
@@ -5369,17 +5357,17 @@
         <v>82</v>
       </c>
       <c r="C85" s="12">
-        <v>45717</v>
+        <v>45714</v>
       </c>
       <c r="D85" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E85" s="12">
-        <v>45717</v>
+        <v>45715</v>
       </c>
       <c r="F85" s="13">
-        <f>$B$84</f>
-        <v>81</v>
+        <f t="shared" si="24"/>
+        <v>77</v>
       </c>
       <c r="G85" s="13" t="s">
         <v>14</v>
@@ -5388,10 +5376,10 @@
         <v>19</v>
       </c>
       <c r="I85" s="14" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="J85" s="15" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.3">
@@ -5400,17 +5388,17 @@
         <v>83</v>
       </c>
       <c r="C86" s="12">
-        <v>45717</v>
+        <v>45715</v>
       </c>
       <c r="D86" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E86" s="12">
-        <v>45717</v>
+        <v>45715</v>
       </c>
       <c r="F86" s="13">
-        <f>$B$84</f>
-        <v>81</v>
+        <f t="shared" si="24"/>
+        <v>77</v>
       </c>
       <c r="G86" s="13" t="s">
         <v>14</v>
@@ -5419,10 +5407,10 @@
         <v>19</v>
       </c>
       <c r="I86" s="14" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="J86" s="15" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="87" spans="2:10" x14ac:dyDescent="0.3">
@@ -5431,17 +5419,17 @@
         <v>84</v>
       </c>
       <c r="C87" s="12">
-        <v>45717</v>
+        <v>45715</v>
       </c>
       <c r="D87" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E87" s="12">
-        <v>45717</v>
+        <v>45714</v>
       </c>
       <c r="F87" s="13">
-        <f>$B$84</f>
-        <v>81</v>
+        <f t="shared" si="24"/>
+        <v>77</v>
       </c>
       <c r="G87" s="13" t="s">
         <v>14</v>
@@ -5450,10 +5438,10 @@
         <v>19</v>
       </c>
       <c r="I87" s="14" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="J87" s="15" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="88" spans="2:10" x14ac:dyDescent="0.3">
@@ -5465,24 +5453,26 @@
         <v>45717</v>
       </c>
       <c r="D88" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E88" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E88" s="12">
+        <v>45717</v>
+      </c>
       <c r="F88" s="13">
-        <f>$B$75</f>
-        <v>72</v>
+        <f t="shared" si="24"/>
+        <v>77</v>
       </c>
       <c r="G88" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H88" s="13" t="s">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="I88" s="14" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="J88" s="15" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="89" spans="2:10" x14ac:dyDescent="0.3">
@@ -5500,20 +5490,20 @@
         <v>45717</v>
       </c>
       <c r="F89" s="13">
-        <f t="shared" ref="F89:F95" si="25">$B$88</f>
+        <f>$B$88</f>
         <v>85</v>
       </c>
       <c r="G89" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H89" s="13" t="s">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="I89" s="14" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="J89" s="15" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="90" spans="2:10" x14ac:dyDescent="0.3">
@@ -5531,25 +5521,25 @@
         <v>45717</v>
       </c>
       <c r="F90" s="13">
-        <f t="shared" si="25"/>
+        <f>$B$88</f>
         <v>85</v>
       </c>
       <c r="G90" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H90" s="13" t="s">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="I90" s="14" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="J90" s="15" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="91" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B91" s="11">
-        <f t="shared" ref="B91" si="26">B90+1</f>
+        <f t="shared" si="0"/>
         <v>88</v>
       </c>
       <c r="C91" s="12">
@@ -5562,7 +5552,7 @@
         <v>45717</v>
       </c>
       <c r="F91" s="13">
-        <f t="shared" si="25"/>
+        <f>$B$88</f>
         <v>85</v>
       </c>
       <c r="G91" s="13" t="s">
@@ -5572,27 +5562,27 @@
         <v>19</v>
       </c>
       <c r="I91" s="14" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="J91" s="15" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="92" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B92" s="11">
-        <f t="shared" ref="B92" si="27">B91+1</f>
+        <f t="shared" si="0"/>
         <v>89</v>
       </c>
       <c r="C92" s="12">
         <v>45717</v>
       </c>
       <c r="D92" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E92" s="12"/>
       <c r="F92" s="13">
-        <f t="shared" si="25"/>
-        <v>85</v>
+        <f>$B$79</f>
+        <v>76</v>
       </c>
       <c r="G92" s="13" t="s">
         <v>14</v>
@@ -5601,56 +5591,60 @@
         <v>99</v>
       </c>
       <c r="I92" s="14" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J92" s="15" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="93" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B93" s="11">
-        <f t="shared" ref="B93" si="28">B92+1</f>
+        <f t="shared" si="0"/>
         <v>90</v>
       </c>
       <c r="C93" s="12">
         <v>45717</v>
       </c>
       <c r="D93" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E93" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E93" s="12">
+        <v>45717</v>
+      </c>
       <c r="F93" s="13">
-        <f t="shared" si="25"/>
-        <v>85</v>
+        <f t="shared" ref="F93:F99" si="25">$B$92</f>
+        <v>89</v>
       </c>
       <c r="G93" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H93" s="13" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="I93" s="14" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="J93" s="15" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="94" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B94" s="11">
-        <f t="shared" ref="B94" si="29">B93+1</f>
+        <f t="shared" si="0"/>
         <v>91</v>
       </c>
       <c r="C94" s="12">
         <v>45717</v>
       </c>
       <c r="D94" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E94" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E94" s="12">
+        <v>45717</v>
+      </c>
       <c r="F94" s="13">
         <f t="shared" si="25"/>
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G94" s="13" t="s">
         <v>14</v>
@@ -5662,168 +5656,169 @@
         <v>129</v>
       </c>
       <c r="J94" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="95" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B95" s="11">
-        <f t="shared" ref="B95" si="30">B94+1</f>
+        <f t="shared" ref="B95" si="26">B94+1</f>
         <v>92</v>
       </c>
       <c r="C95" s="12">
         <v>45717</v>
       </c>
       <c r="D95" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E95" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E95" s="12">
+        <v>45717</v>
+      </c>
       <c r="F95" s="13">
         <f t="shared" si="25"/>
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G95" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H95" s="13" t="s">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="I95" s="14" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J95" s="15" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="96" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B96" s="11">
-        <f t="shared" ref="B96:B107" si="31">B95+1</f>
+        <f t="shared" ref="B96" si="27">B95+1</f>
         <v>93</v>
       </c>
-      <c r="C96" s="12"/>
-      <c r="D96" s="13"/>
+      <c r="C96" s="12">
+        <v>45717</v>
+      </c>
+      <c r="D96" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E96" s="12"/>
-      <c r="F96" s="13"/>
-      <c r="G96" s="13"/>
-      <c r="H96" s="13"/>
-      <c r="I96" s="14"/>
-      <c r="J96" s="15"/>
+      <c r="F96" s="13">
+        <f t="shared" si="25"/>
+        <v>89</v>
+      </c>
+      <c r="G96" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H96" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="I96" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="J96" s="15" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="B97" si="28">B96+1</f>
         <v>94</v>
       </c>
       <c r="C97" s="12">
-        <v>45719</v>
+        <v>45717</v>
       </c>
       <c r="D97" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E97" s="12"/>
-      <c r="F97" s="13"/>
+      <c r="F97" s="13">
+        <f t="shared" si="25"/>
+        <v>89</v>
+      </c>
       <c r="G97" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H97" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I97" s="15" t="s">
-        <v>140</v>
+        <v>19</v>
+      </c>
+      <c r="I97" s="14" t="s">
+        <v>135</v>
       </c>
       <c r="J97" s="15" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="B98" si="29">B97+1</f>
         <v>95</v>
       </c>
       <c r="C98" s="12">
-        <v>45719</v>
+        <v>45717</v>
       </c>
       <c r="D98" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E98" s="12">
-        <v>45719</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E98" s="12"/>
       <c r="F98" s="13">
-        <f>$B$97</f>
-        <v>94</v>
+        <f t="shared" si="25"/>
+        <v>89</v>
       </c>
       <c r="G98" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H98" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I98" s="15" t="s">
-        <v>140</v>
+        <v>99</v>
+      </c>
+      <c r="I98" s="14" t="s">
+        <v>129</v>
       </c>
       <c r="J98" s="15" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B99" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="B99" si="30">B98+1</f>
         <v>96</v>
       </c>
       <c r="C99" s="12">
-        <v>45719</v>
+        <v>45717</v>
       </c>
       <c r="D99" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E99" s="12">
-        <v>45720</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E99" s="12"/>
       <c r="F99" s="13">
-        <f>$B$97</f>
-        <v>94</v>
+        <f t="shared" si="25"/>
+        <v>89</v>
       </c>
       <c r="G99" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H99" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I99" s="15" t="s">
-        <v>140</v>
+        <v>99</v>
+      </c>
+      <c r="I99" s="14" t="s">
+        <v>129</v>
       </c>
       <c r="J99" s="15" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="100" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B100" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="B100:B111" si="31">B99+1</f>
         <v>97</v>
       </c>
-      <c r="C100" s="12">
-        <v>45719</v>
-      </c>
-      <c r="D100" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C100" s="12"/>
+      <c r="D100" s="13"/>
       <c r="E100" s="12"/>
-      <c r="F100" s="13">
-        <f>$B$97</f>
-        <v>94</v>
-      </c>
-      <c r="G100" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H100" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I100" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="J100" s="15" t="s">
-        <v>143</v>
-      </c>
+      <c r="F100" s="13"/>
+      <c r="G100" s="13"/>
+      <c r="H100" s="13"/>
+      <c r="I100" s="14"/>
+      <c r="J100" s="15"/>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B101" s="11">
@@ -5834,13 +5829,10 @@
         <v>45719</v>
       </c>
       <c r="D101" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E101" s="12"/>
-      <c r="F101" s="13">
-        <f>$B$97</f>
-        <v>94</v>
-      </c>
+      <c r="F101" s="13"/>
       <c r="G101" s="13" t="s">
         <v>14</v>
       </c>
@@ -5851,7 +5843,7 @@
         <v>140</v>
       </c>
       <c r="J101" s="15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.3">
@@ -5859,56 +5851,120 @@
         <f t="shared" si="31"/>
         <v>99</v>
       </c>
-      <c r="C102" s="12"/>
-      <c r="D102" s="13"/>
-      <c r="E102" s="12"/>
-      <c r="F102" s="13"/>
-      <c r="G102" s="13"/>
-      <c r="H102" s="13"/>
-      <c r="I102" s="14"/>
-      <c r="J102" s="15"/>
+      <c r="C102" s="12">
+        <v>45719</v>
+      </c>
+      <c r="D102" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E102" s="12">
+        <v>45719</v>
+      </c>
+      <c r="F102" s="13">
+        <f>$B$101</f>
+        <v>98</v>
+      </c>
+      <c r="G102" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H102" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I102" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="J102" s="15" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="103" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B103" s="11">
         <f t="shared" si="31"/>
         <v>100</v>
       </c>
-      <c r="C103" s="12"/>
-      <c r="D103" s="13"/>
-      <c r="E103" s="12"/>
-      <c r="F103" s="13"/>
-      <c r="G103" s="13"/>
-      <c r="H103" s="13"/>
-      <c r="I103" s="14"/>
-      <c r="J103" s="15"/>
+      <c r="C103" s="12">
+        <v>45719</v>
+      </c>
+      <c r="D103" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E103" s="12">
+        <v>45720</v>
+      </c>
+      <c r="F103" s="13">
+        <f>$B$101</f>
+        <v>98</v>
+      </c>
+      <c r="G103" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H103" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I103" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="J103" s="15" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="104" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B104" s="11">
         <f t="shared" si="31"/>
         <v>101</v>
       </c>
-      <c r="C104" s="12"/>
-      <c r="D104" s="13"/>
+      <c r="C104" s="12">
+        <v>45719</v>
+      </c>
+      <c r="D104" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E104" s="12"/>
-      <c r="F104" s="13"/>
-      <c r="G104" s="13"/>
-      <c r="H104" s="13"/>
-      <c r="I104" s="14"/>
-      <c r="J104" s="15"/>
+      <c r="F104" s="13">
+        <f>$B$101</f>
+        <v>98</v>
+      </c>
+      <c r="G104" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H104" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I104" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="J104" s="15" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="105" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B105" s="11">
         <f t="shared" si="31"/>
         <v>102</v>
       </c>
-      <c r="C105" s="12"/>
-      <c r="D105" s="13"/>
+      <c r="C105" s="12">
+        <v>45719</v>
+      </c>
+      <c r="D105" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E105" s="12"/>
-      <c r="F105" s="13"/>
-      <c r="G105" s="13"/>
-      <c r="H105" s="13"/>
-      <c r="I105" s="14"/>
-      <c r="J105" s="15"/>
+      <c r="F105" s="13">
+        <f>$B$101</f>
+        <v>98</v>
+      </c>
+      <c r="G105" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H105" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I105" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="J105" s="15" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="106" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B106" s="11">
@@ -5938,24 +5994,92 @@
       <c r="I107" s="14"/>
       <c r="J107" s="15"/>
     </row>
-    <row r="108" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B108" s="18">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B108" s="11">
+        <f t="shared" si="31"/>
+        <v>105</v>
+      </c>
+      <c r="C108" s="12"/>
+      <c r="D108" s="13"/>
+      <c r="E108" s="12"/>
+      <c r="F108" s="13"/>
+      <c r="G108" s="13"/>
+      <c r="H108" s="13"/>
+      <c r="I108" s="14"/>
+      <c r="J108" s="15"/>
+    </row>
+    <row r="109" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B109" s="11">
+        <f t="shared" si="31"/>
+        <v>106</v>
+      </c>
+      <c r="C109" s="12">
+        <v>45734</v>
+      </c>
+      <c r="D109" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E109" s="12"/>
+      <c r="F109" s="13"/>
+      <c r="G109" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H109" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I109" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="J109" s="15" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="110" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B110" s="11">
+        <f t="shared" si="31"/>
+        <v>107</v>
+      </c>
+      <c r="C110" s="12"/>
+      <c r="D110" s="13"/>
+      <c r="E110" s="12"/>
+      <c r="F110" s="13"/>
+      <c r="G110" s="13"/>
+      <c r="H110" s="13"/>
+      <c r="I110" s="14"/>
+      <c r="J110" s="15"/>
+    </row>
+    <row r="111" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B111" s="11">
+        <f t="shared" si="31"/>
+        <v>108</v>
+      </c>
+      <c r="C111" s="12"/>
+      <c r="D111" s="13"/>
+      <c r="E111" s="12"/>
+      <c r="F111" s="13"/>
+      <c r="G111" s="13"/>
+      <c r="H111" s="13"/>
+      <c r="I111" s="14"/>
+      <c r="J111" s="15"/>
+    </row>
+    <row r="112" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B112" s="18">
         <f t="shared" si="0"/>
-        <v>105</v>
-      </c>
-      <c r="C108" s="19"/>
-      <c r="D108" s="20"/>
-      <c r="E108" s="19"/>
-      <c r="F108" s="20"/>
-      <c r="G108" s="20"/>
-      <c r="H108" s="20"/>
-      <c r="I108" s="21"/>
-      <c r="J108" s="22"/>
+        <v>109</v>
+      </c>
+      <c r="C112" s="19"/>
+      <c r="D112" s="20"/>
+      <c r="E112" s="19"/>
+      <c r="F112" s="20"/>
+      <c r="G112" s="20"/>
+      <c r="H112" s="20"/>
+      <c r="I112" s="21"/>
+      <c r="J112" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:J108" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
+  <autoFilter ref="B2:J112" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B3:J45 A43:A45 A46:J46 A47:A51 B47:J108">
+  <conditionalFormatting sqref="B3:J45 A43:A45 A46:J46 A47:A51 B47:J112">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>
@@ -5972,25 +6096,25 @@
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H106:H108 H76:H87 H3:H61 H74</xm:sqref>
+          <xm:sqref>H110:H112 H80:H91 H3:H61 H78</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D6F2F62E-6D63-4E2D-8772-1211A4C3A979}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$10</xm:f>
           </x14:formula1>
-          <xm:sqref>H75 H88:H105 H62:H73</xm:sqref>
+          <xm:sqref>H79 H92:H109 H62:H77</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C61EF0EC-B820-4CEA-8AA2-04B5D172AE2C}">
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D108</xm:sqref>
+          <xm:sqref>D3:D112</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G108</xm:sqref>
+          <xm:sqref>G3:G112</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ED299D3-C3BD-4E57-9023-D389D6D96C44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC1B9134-CCAA-432E-BB4C-1D2CDC963D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="165">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -2270,6 +2270,16 @@
     </rPh>
     <rPh sb="38" eb="40">
       <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一覧にクリックを追加する。</t>
+    <rPh sb="0" eb="2">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ツイカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5971,14 +5981,29 @@
         <f t="shared" si="31"/>
         <v>103</v>
       </c>
-      <c r="C106" s="12"/>
-      <c r="D106" s="13"/>
+      <c r="C106" s="12">
+        <v>45735</v>
+      </c>
+      <c r="D106" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E106" s="12"/>
-      <c r="F106" s="13"/>
-      <c r="G106" s="13"/>
-      <c r="H106" s="13"/>
-      <c r="I106" s="14"/>
-      <c r="J106" s="15"/>
+      <c r="F106" s="13">
+        <f>$B$104</f>
+        <v>101</v>
+      </c>
+      <c r="G106" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H106" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I106" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="J106" s="15" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="107" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B107" s="11">
@@ -6102,7 +6127,7 @@
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$10</xm:f>
           </x14:formula1>
-          <xm:sqref>H79 H92:H109 H62:H77</xm:sqref>
+          <xm:sqref>H79 H62:H77 H92:H109</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C61EF0EC-B820-4CEA-8AA2-04B5D172AE2C}">
           <x14:formula1>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC1B9134-CCAA-432E-BB4C-1D2CDC963D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70668C6A-6B60-4B02-8461-FBBF7C67B32D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="選択情報" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作業項目!$B$2:$J$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作業項目!$B$2:$J$113</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="167">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -2280,6 +2280,32 @@
     </rPh>
     <rPh sb="8" eb="10">
       <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HtmlOrderDisp01構築</t>
+    <rPh sb="15" eb="17">
+      <t>コウチク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示詳細情報 : 受注情報ID、受注日、相手先名、商品名、受注数、受注金額</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジュチュウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジョウホウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2991,7 +3017,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="A1:K112"/>
+  <dimension ref="A1:K113"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -3189,7 +3215,7 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
-        <f t="shared" ref="A8:B112" si="0">B7+1</f>
+        <f t="shared" ref="A8:B113" si="0">B7+1</f>
         <v>6</v>
       </c>
       <c r="C8" s="12">
@@ -5818,7 +5844,7 @@
     </row>
     <row r="100" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B100" s="11">
-        <f t="shared" ref="B100:B111" si="31">B99+1</f>
+        <f t="shared" ref="B100:B112" si="31">B99+1</f>
         <v>97</v>
       </c>
       <c r="C100" s="12"/>
@@ -5956,12 +5982,12 @@
         <v>45719</v>
       </c>
       <c r="D105" s="13" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E105" s="12"/>
       <c r="F105" s="13">
-        <f>$B$101</f>
-        <v>98</v>
+        <f>$B$108</f>
+        <v>105</v>
       </c>
       <c r="G105" s="13" t="s">
         <v>14</v>
@@ -5985,12 +6011,12 @@
         <v>45735</v>
       </c>
       <c r="D106" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E106" s="12"/>
       <c r="F106" s="13">
-        <f>$B$104</f>
-        <v>101</v>
+        <f>$B$108</f>
+        <v>105</v>
       </c>
       <c r="G106" s="13" t="s">
         <v>14</v>
@@ -6002,7 +6028,7 @@
         <v>140</v>
       </c>
       <c r="J106" s="15" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="107" spans="2:10" x14ac:dyDescent="0.3">
@@ -6010,68 +6036,98 @@
         <f t="shared" si="31"/>
         <v>104</v>
       </c>
-      <c r="C107" s="12"/>
-      <c r="D107" s="13"/>
+      <c r="C107" s="12">
+        <v>45735</v>
+      </c>
+      <c r="D107" s="13" t="s">
+        <v>12</v>
+      </c>
       <c r="E107" s="12"/>
-      <c r="F107" s="13"/>
-      <c r="G107" s="13"/>
-      <c r="H107" s="13"/>
-      <c r="I107" s="14"/>
-      <c r="J107" s="15"/>
+      <c r="F107" s="13">
+        <f>$B$104</f>
+        <v>101</v>
+      </c>
+      <c r="G107" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H107" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I107" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="J107" s="15" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="108" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B108" s="11">
         <f t="shared" si="31"/>
         <v>105</v>
       </c>
-      <c r="C108" s="12"/>
-      <c r="D108" s="13"/>
+      <c r="C108" s="12">
+        <v>45735</v>
+      </c>
+      <c r="D108" s="13" t="s">
+        <v>11</v>
+      </c>
       <c r="E108" s="12"/>
-      <c r="F108" s="13"/>
-      <c r="G108" s="13"/>
-      <c r="H108" s="13"/>
-      <c r="I108" s="14"/>
-      <c r="J108" s="15"/>
+      <c r="F108" s="13">
+        <f>$B$104</f>
+        <v>101</v>
+      </c>
+      <c r="G108" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H108" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I108" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="J108" s="15" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="109" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B109" s="11">
         <f t="shared" si="31"/>
         <v>106</v>
       </c>
-      <c r="C109" s="12">
-        <v>45734</v>
-      </c>
-      <c r="D109" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C109" s="12"/>
+      <c r="D109" s="13"/>
       <c r="E109" s="12"/>
       <c r="F109" s="13"/>
-      <c r="G109" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="H109" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I109" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="J109" s="15" t="s">
-        <v>161</v>
-      </c>
+      <c r="G109" s="13"/>
+      <c r="H109" s="13"/>
+      <c r="I109" s="14"/>
+      <c r="J109" s="15"/>
     </row>
     <row r="110" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B110" s="11">
         <f t="shared" si="31"/>
         <v>107</v>
       </c>
-      <c r="C110" s="12"/>
-      <c r="D110" s="13"/>
+      <c r="C110" s="12">
+        <v>45734</v>
+      </c>
+      <c r="D110" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E110" s="12"/>
       <c r="F110" s="13"/>
-      <c r="G110" s="13"/>
-      <c r="H110" s="13"/>
-      <c r="I110" s="14"/>
-      <c r="J110" s="15"/>
+      <c r="G110" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H110" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I110" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="J110" s="15" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="111" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B111" s="11">
@@ -6087,24 +6143,38 @@
       <c r="I111" s="14"/>
       <c r="J111" s="15"/>
     </row>
-    <row r="112" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B112" s="18">
+    <row r="112" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B112" s="11">
+        <f t="shared" si="31"/>
+        <v>109</v>
+      </c>
+      <c r="C112" s="12"/>
+      <c r="D112" s="13"/>
+      <c r="E112" s="12"/>
+      <c r="F112" s="13"/>
+      <c r="G112" s="13"/>
+      <c r="H112" s="13"/>
+      <c r="I112" s="14"/>
+      <c r="J112" s="15"/>
+    </row>
+    <row r="113" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B113" s="18">
         <f t="shared" si="0"/>
-        <v>109</v>
-      </c>
-      <c r="C112" s="19"/>
-      <c r="D112" s="20"/>
-      <c r="E112" s="19"/>
-      <c r="F112" s="20"/>
-      <c r="G112" s="20"/>
-      <c r="H112" s="20"/>
-      <c r="I112" s="21"/>
-      <c r="J112" s="22"/>
+        <v>110</v>
+      </c>
+      <c r="C113" s="19"/>
+      <c r="D113" s="20"/>
+      <c r="E113" s="19"/>
+      <c r="F113" s="20"/>
+      <c r="G113" s="20"/>
+      <c r="H113" s="20"/>
+      <c r="I113" s="21"/>
+      <c r="J113" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:J112" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
+  <autoFilter ref="B2:J113" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B3:J45 A43:A45 A46:J46 A47:A51 B47:J112">
+  <conditionalFormatting sqref="B3:J45 A43:A45 A46:J46 A47:A51 B47:J113">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>
@@ -6121,25 +6191,25 @@
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H110:H112 H80:H91 H3:H61 H78</xm:sqref>
+          <xm:sqref>H111:H113 H80:H91 H3:H61 H78</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D6F2F62E-6D63-4E2D-8772-1211A4C3A979}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$10</xm:f>
           </x14:formula1>
-          <xm:sqref>H79 H62:H77 H92:H109</xm:sqref>
+          <xm:sqref>H79 H62:H77 H92:H110</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C61EF0EC-B820-4CEA-8AA2-04B5D172AE2C}">
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D112</xm:sqref>
+          <xm:sqref>D3:D113</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G112</xm:sqref>
+          <xm:sqref>G3:G113</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70668C6A-6B60-4B02-8461-FBBF7C67B32D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A25391E1-42FB-443E-B2F1-13B7E07CA7BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="選択情報" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作業項目!$B$2:$J$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作業項目!$B$2:$J$119</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="172">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -2284,28 +2284,84 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>HtmlOrderDisp01構築</t>
+    <t>表示詳細情報 : 受注情報ID、受注日、相手先名、商品名、受注数、受注金額</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジュチュウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HtmlOrderDisp01構築 : タイトル表示</t>
     <rPh sb="15" eb="17">
       <t>コウチク</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>表示詳細情報 : 受注情報ID、受注日、相手先名、商品名、受注数、受注金額</t>
-    <rPh sb="0" eb="2">
+    <rPh sb="24" eb="26">
       <t>ヒョウジ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>受注一覧</t>
+    <rPh sb="0" eb="2">
+      <t>ジュチュウ</t>
+    </rPh>
     <rPh sb="2" eb="4">
-      <t>ショウサイ</t>
-    </rPh>
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メニュー遷移追加</t>
     <rPh sb="4" eb="6">
-      <t>ジョウホウ</t>
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>受注照会</t>
+    <rPh sb="0" eb="2">
+      <t>ジュチュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショウカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「新規登録」ボタン追加</t>
+    <rPh sb="1" eb="5">
+      <t>シンキトウロク</t>
     </rPh>
     <rPh sb="9" eb="11">
-      <t>ジュチュウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ジョウホウ</t>
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「一覧へ戻る」ボタン追加</t>
+    <rPh sb="1" eb="3">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ツイカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2340,7 +2396,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -2567,13 +2623,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2644,6 +2713,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3017,7 +3089,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="A1:K113"/>
+  <dimension ref="A1:K119"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -3215,7 +3287,7 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
-        <f t="shared" ref="A8:B113" si="0">B7+1</f>
+        <f t="shared" ref="A8:B119" si="0">B7+1</f>
         <v>6</v>
       </c>
       <c r="C8" s="12">
@@ -5844,7 +5916,7 @@
     </row>
     <row r="100" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B100" s="11">
-        <f t="shared" ref="B100:B112" si="31">B99+1</f>
+        <f t="shared" ref="B100:B118" si="31">B99+1</f>
         <v>97</v>
       </c>
       <c r="C100" s="12"/>
@@ -5953,7 +6025,7 @@
         <v>45719</v>
       </c>
       <c r="D104" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E104" s="12"/>
       <c r="F104" s="13">
@@ -6028,7 +6100,7 @@
         <v>140</v>
       </c>
       <c r="J106" s="15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="107" spans="2:10" x14ac:dyDescent="0.3">
@@ -6086,7 +6158,7 @@
         <v>140</v>
       </c>
       <c r="J108" s="15" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="109" spans="2:10" x14ac:dyDescent="0.3">
@@ -6094,14 +6166,29 @@
         <f t="shared" si="31"/>
         <v>106</v>
       </c>
-      <c r="C109" s="12"/>
-      <c r="D109" s="13"/>
+      <c r="C109" s="12">
+        <v>45737</v>
+      </c>
+      <c r="D109" s="13" t="s">
+        <v>11</v>
+      </c>
       <c r="E109" s="12"/>
-      <c r="F109" s="13"/>
-      <c r="G109" s="13"/>
-      <c r="H109" s="13"/>
-      <c r="I109" s="14"/>
-      <c r="J109" s="15"/>
+      <c r="F109" s="13">
+        <f>$B$101</f>
+        <v>98</v>
+      </c>
+      <c r="G109" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H109" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I109" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="J109" s="15" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="110" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B110" s="11">
@@ -6109,24 +6196,27 @@
         <v>107</v>
       </c>
       <c r="C110" s="12">
-        <v>45734</v>
+        <v>45737</v>
       </c>
       <c r="D110" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E110" s="12"/>
-      <c r="F110" s="13"/>
+      <c r="F110" s="13">
+        <f>$B$108</f>
+        <v>105</v>
+      </c>
       <c r="G110" s="13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H110" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I110" s="14" t="s">
-        <v>160</v>
+        <v>21</v>
+      </c>
+      <c r="I110" s="24" t="s">
+        <v>169</v>
       </c>
       <c r="J110" s="15" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
     </row>
     <row r="111" spans="2:10" x14ac:dyDescent="0.3">
@@ -6134,14 +6224,29 @@
         <f t="shared" si="31"/>
         <v>108</v>
       </c>
-      <c r="C111" s="12"/>
-      <c r="D111" s="13"/>
+      <c r="C111" s="12">
+        <v>45737</v>
+      </c>
+      <c r="D111" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E111" s="12"/>
-      <c r="F111" s="13"/>
-      <c r="G111" s="13"/>
-      <c r="H111" s="13"/>
-      <c r="I111" s="14"/>
-      <c r="J111" s="15"/>
+      <c r="F111" s="13">
+        <f>$B$108</f>
+        <v>105</v>
+      </c>
+      <c r="G111" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H111" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I111" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="J111" s="15" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="112" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B112" s="11">
@@ -6154,27 +6259,123 @@
       <c r="F112" s="13"/>
       <c r="G112" s="13"/>
       <c r="H112" s="13"/>
-      <c r="I112" s="14"/>
+      <c r="I112" s="24"/>
       <c r="J112" s="15"/>
     </row>
-    <row r="113" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B113" s="18">
+    <row r="113" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B113" s="11">
+        <f t="shared" si="31"/>
+        <v>110</v>
+      </c>
+      <c r="C113" s="12"/>
+      <c r="D113" s="13"/>
+      <c r="E113" s="12"/>
+      <c r="F113" s="13"/>
+      <c r="G113" s="13"/>
+      <c r="H113" s="13"/>
+      <c r="I113" s="24"/>
+      <c r="J113" s="15"/>
+    </row>
+    <row r="114" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B114" s="11">
+        <f t="shared" si="31"/>
+        <v>111</v>
+      </c>
+      <c r="C114" s="12"/>
+      <c r="D114" s="13"/>
+      <c r="E114" s="12"/>
+      <c r="F114" s="13"/>
+      <c r="G114" s="13"/>
+      <c r="H114" s="13"/>
+      <c r="I114" s="24"/>
+      <c r="J114" s="15"/>
+    </row>
+    <row r="115" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B115" s="11">
+        <f t="shared" si="31"/>
+        <v>112</v>
+      </c>
+      <c r="C115" s="12"/>
+      <c r="D115" s="13"/>
+      <c r="E115" s="12"/>
+      <c r="F115" s="13"/>
+      <c r="G115" s="13"/>
+      <c r="H115" s="13"/>
+      <c r="I115" s="14"/>
+      <c r="J115" s="15"/>
+    </row>
+    <row r="116" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B116" s="11">
+        <f t="shared" si="31"/>
+        <v>113</v>
+      </c>
+      <c r="C116" s="12">
+        <v>45734</v>
+      </c>
+      <c r="D116" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E116" s="12"/>
+      <c r="F116" s="13"/>
+      <c r="G116" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H116" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I116" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="J116" s="15" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="117" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B117" s="11">
+        <f t="shared" si="31"/>
+        <v>114</v>
+      </c>
+      <c r="C117" s="12"/>
+      <c r="D117" s="13"/>
+      <c r="E117" s="12"/>
+      <c r="F117" s="13"/>
+      <c r="G117" s="13"/>
+      <c r="H117" s="13"/>
+      <c r="I117" s="14"/>
+      <c r="J117" s="15"/>
+    </row>
+    <row r="118" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B118" s="11">
+        <f t="shared" si="31"/>
+        <v>115</v>
+      </c>
+      <c r="C118" s="12"/>
+      <c r="D118" s="13"/>
+      <c r="E118" s="12"/>
+      <c r="F118" s="13"/>
+      <c r="G118" s="13"/>
+      <c r="H118" s="13"/>
+      <c r="I118" s="14"/>
+      <c r="J118" s="15"/>
+    </row>
+    <row r="119" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B119" s="18">
         <f t="shared" si="0"/>
-        <v>110</v>
-      </c>
-      <c r="C113" s="19"/>
-      <c r="D113" s="20"/>
-      <c r="E113" s="19"/>
-      <c r="F113" s="20"/>
-      <c r="G113" s="20"/>
-      <c r="H113" s="20"/>
-      <c r="I113" s="21"/>
-      <c r="J113" s="22"/>
+        <v>116</v>
+      </c>
+      <c r="C119" s="19"/>
+      <c r="D119" s="20"/>
+      <c r="E119" s="19"/>
+      <c r="F119" s="20"/>
+      <c r="G119" s="20"/>
+      <c r="H119" s="20"/>
+      <c r="I119" s="21"/>
+      <c r="J119" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:J113" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
+  <autoFilter ref="B2:J119" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B3:J45 A43:A45 A46:J46 A47:A51 B47:J113">
+  <conditionalFormatting sqref="B3:J45 A43:A45 A46:J46 A47:A51 B47:J119">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>
@@ -6191,25 +6392,25 @@
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H111:H113 H80:H91 H3:H61 H78</xm:sqref>
+          <xm:sqref>H117:H119 H80:H91 H3:H61 H78</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D6F2F62E-6D63-4E2D-8772-1211A4C3A979}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$10</xm:f>
           </x14:formula1>
-          <xm:sqref>H79 H62:H77 H92:H110</xm:sqref>
+          <xm:sqref>H79 H62:H77 H92:H116</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C61EF0EC-B820-4CEA-8AA2-04B5D172AE2C}">
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D113</xm:sqref>
+          <xm:sqref>D3:D119</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G113</xm:sqref>
+          <xm:sqref>G3:G119</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\workspace\busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A25391E1-42FB-443E-B2F1-13B7E07CA7BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D6938BF-1692-45D9-A101-6FDCA8567048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -6056,7 +6056,9 @@
       <c r="D105" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="E105" s="12"/>
+      <c r="E105" s="12">
+        <v>45719</v>
+      </c>
       <c r="F105" s="13">
         <f>$B$108</f>
         <v>105</v>
@@ -6114,7 +6116,9 @@
       <c r="D107" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="E107" s="12"/>
+      <c r="E107" s="12">
+        <v>45735</v>
+      </c>
       <c r="F107" s="13">
         <f>$B$104</f>
         <v>101</v>
@@ -6170,9 +6174,11 @@
         <v>45737</v>
       </c>
       <c r="D109" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E109" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E109" s="12">
+        <v>45738</v>
+      </c>
       <c r="F109" s="13">
         <f>$B$101</f>
         <v>98</v>
@@ -6199,9 +6205,11 @@
         <v>45737</v>
       </c>
       <c r="D110" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E110" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E110" s="12">
+        <v>45738</v>
+      </c>
       <c r="F110" s="13">
         <f>$B$108</f>
         <v>105</v>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -5,19 +5,20 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\workspace\busiframe\document\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D6938BF-1692-45D9-A101-6FDCA8567048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E2F979-F145-4DEF-B4B2-C4C6249032C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
+    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
   <sheets>
     <sheet name="作業項目" sheetId="1" r:id="rId1"/>
     <sheet name="選択情報" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作業項目!$B$2:$J$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作業項目!$B$2:$J$124</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="183">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -2284,35 +2285,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>表示詳細情報 : 受注情報ID、受注日、相手先名、商品名、受注数、受注金額</t>
-    <rPh sb="0" eb="2">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ショウサイ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ジュチュウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ジョウホウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>HtmlOrderDisp01構築 : タイトル表示</t>
-    <rPh sb="15" eb="17">
-      <t>コウチク</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>受注一覧</t>
     <rPh sb="0" eb="2">
       <t>ジュチュウ</t>
@@ -2361,6 +2333,218 @@
       <t>モド</t>
     </rPh>
     <rPh sb="10" eb="12">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>表示詳細情報 : 受注情報ID、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>受注日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>、相手先名、商品名、受注数、受注金額</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジュチュウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HtmlOrderDisp01構築 : タイトル表示、受注日表示</t>
+    <rPh sb="15" eb="17">
+      <t>コウチク</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="27" eb="30">
+      <t>ジュチュウビ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>詳細情報項目に対して実際のテーブル項目からの値の取得</t>
+    <rPh sb="0" eb="2">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>シュトク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>原則</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンソク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1画面1テーブル、親子関係は付属の一覧画面で表現する。</t>
+    <rPh sb="1" eb="3">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>オヤコ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カンケイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>フゾク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テーブル情報ID</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示詳細情報</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>項目情報ID</t>
+    <rPh sb="0" eb="2">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2025/3/24</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示情報</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テーブル項目情報</t>
+    <rPh sb="4" eb="6">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テーブル項目情報テーブル構築 : sys_column : テーブル項目情報ID,テーブル項目情報CD,テーブル情報ID,属性,桁数,名前,説明</t>
+    <rPh sb="4" eb="8">
+      <t>コウモクジョウホウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>コウチク</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>ケタスウ</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テーブルID項目の追加 : table_id</t>
+    <rPh sb="6" eb="8">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
       <t>ツイカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -2373,7 +2557,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm/dd"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -2385,6 +2569,13 @@
       <sz val="6"/>
       <name val="Meiryo UI"/>
       <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -2642,7 +2833,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2716,6 +2907,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3089,7 +3286,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="A1:K119"/>
+  <dimension ref="A1:K124"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -3287,7 +3484,7 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
-        <f t="shared" ref="A8:B119" si="0">B7+1</f>
+        <f t="shared" ref="A8:B124" si="0">B7+1</f>
         <v>6</v>
       </c>
       <c r="C8" s="12">
@@ -4955,7 +5152,7 @@
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B66" s="11">
-        <f t="shared" ref="B66:B79" si="23">B65+1</f>
+        <f t="shared" ref="B66:B84" si="23">B65+1</f>
         <v>64</v>
       </c>
       <c r="C66" s="12">
@@ -5241,28 +5438,52 @@
         <f t="shared" si="23"/>
         <v>73</v>
       </c>
-      <c r="C76" s="12"/>
-      <c r="D76" s="13"/>
+      <c r="C76" s="12">
+        <v>45740</v>
+      </c>
+      <c r="D76" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E76" s="12"/>
       <c r="F76" s="13"/>
-      <c r="G76" s="13"/>
-      <c r="H76" s="13"/>
-      <c r="I76" s="14"/>
-      <c r="J76" s="15"/>
-    </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="G76" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H76" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I76" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="J76" s="15" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B77" s="11">
         <f t="shared" si="23"/>
         <v>74</v>
       </c>
-      <c r="C77" s="12"/>
-      <c r="D77" s="13"/>
+      <c r="C77" s="12">
+        <v>45740</v>
+      </c>
+      <c r="D77" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E77" s="12"/>
       <c r="F77" s="13"/>
-      <c r="G77" s="13"/>
-      <c r="H77" s="13"/>
-      <c r="I77" s="14"/>
-      <c r="J77" s="15"/>
+      <c r="G77" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H77" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I77" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="J77" s="17" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="78" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B78" s="11">
@@ -5283,180 +5504,95 @@
         <f t="shared" si="23"/>
         <v>76</v>
       </c>
-      <c r="C79" s="12">
-        <v>45698</v>
-      </c>
-      <c r="D79" s="13" t="s">
-        <v>11</v>
-      </c>
+      <c r="C79" s="12"/>
+      <c r="D79" s="13"/>
       <c r="E79" s="12"/>
       <c r="F79" s="13"/>
-      <c r="G79" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H79" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="I79" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="J79" s="15" t="s">
-        <v>102</v>
-      </c>
+      <c r="G79" s="13"/>
+      <c r="H79" s="13"/>
+      <c r="I79" s="14"/>
+      <c r="J79" s="15"/>
     </row>
     <row r="80" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B80" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="23"/>
         <v>77</v>
       </c>
-      <c r="C80" s="12">
-        <v>45698</v>
-      </c>
-      <c r="D80" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E80" s="12">
-        <v>45717</v>
-      </c>
-      <c r="F80" s="13">
-        <f>$B$79</f>
-        <v>76</v>
-      </c>
-      <c r="G80" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H80" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I80" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="J80" s="15" t="s">
-        <v>104</v>
-      </c>
+      <c r="C80" s="12"/>
+      <c r="D80" s="13"/>
+      <c r="E80" s="12"/>
+      <c r="F80" s="13"/>
+      <c r="G80" s="13"/>
+      <c r="H80" s="13"/>
+      <c r="I80" s="14"/>
+      <c r="J80" s="15"/>
     </row>
     <row r="81" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B81" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="23"/>
         <v>78</v>
       </c>
-      <c r="C81" s="12">
-        <v>45698</v>
-      </c>
-      <c r="D81" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E81" s="12">
-        <v>45698</v>
-      </c>
-      <c r="F81" s="13">
-        <f t="shared" ref="F81:F88" si="24">$B$80</f>
-        <v>77</v>
-      </c>
-      <c r="G81" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H81" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I81" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="J81" s="15" t="s">
-        <v>105</v>
-      </c>
+      <c r="C81" s="12"/>
+      <c r="D81" s="13"/>
+      <c r="E81" s="12"/>
+      <c r="F81" s="13"/>
+      <c r="G81" s="13"/>
+      <c r="H81" s="13"/>
+      <c r="I81" s="14"/>
+      <c r="J81" s="15"/>
     </row>
     <row r="82" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B82" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="23"/>
         <v>79</v>
       </c>
-      <c r="C82" s="12">
-        <v>45698</v>
-      </c>
-      <c r="D82" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E82" s="12">
-        <v>45714</v>
-      </c>
-      <c r="F82" s="13">
-        <f t="shared" si="24"/>
-        <v>77</v>
-      </c>
-      <c r="G82" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H82" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I82" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="J82" s="15" t="s">
-        <v>116</v>
-      </c>
+      <c r="C82" s="12"/>
+      <c r="D82" s="13"/>
+      <c r="E82" s="12"/>
+      <c r="F82" s="13"/>
+      <c r="G82" s="13"/>
+      <c r="H82" s="13"/>
+      <c r="I82" s="14"/>
+      <c r="J82" s="15"/>
     </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B83" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="23"/>
         <v>80</v>
       </c>
-      <c r="C83" s="12">
-        <v>45698</v>
-      </c>
-      <c r="D83" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E83" s="12">
-        <v>45714</v>
-      </c>
-      <c r="F83" s="13">
-        <f t="shared" si="24"/>
-        <v>77</v>
-      </c>
-      <c r="G83" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H83" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I83" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="J83" s="15" t="s">
-        <v>117</v>
-      </c>
+      <c r="C83" s="12"/>
+      <c r="D83" s="13"/>
+      <c r="E83" s="12"/>
+      <c r="F83" s="13"/>
+      <c r="G83" s="13"/>
+      <c r="H83" s="13"/>
+      <c r="I83" s="14"/>
+      <c r="J83" s="15"/>
     </row>
     <row r="84" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B84" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="23"/>
         <v>81</v>
       </c>
       <c r="C84" s="12">
-        <v>45714</v>
+        <v>45698</v>
       </c>
       <c r="D84" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E84" s="12">
-        <v>45714</v>
-      </c>
-      <c r="F84" s="13">
-        <f t="shared" si="24"/>
-        <v>77</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E84" s="12"/>
+      <c r="F84" s="13"/>
       <c r="G84" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H84" s="13" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="I84" s="14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J84" s="15" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.3">
@@ -5465,17 +5601,17 @@
         <v>82</v>
       </c>
       <c r="C85" s="12">
-        <v>45714</v>
+        <v>45698</v>
       </c>
       <c r="D85" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E85" s="12">
-        <v>45715</v>
+        <v>45717</v>
       </c>
       <c r="F85" s="13">
-        <f t="shared" si="24"/>
-        <v>77</v>
+        <f>$B$84</f>
+        <v>81</v>
       </c>
       <c r="G85" s="13" t="s">
         <v>14</v>
@@ -5487,7 +5623,7 @@
         <v>103</v>
       </c>
       <c r="J85" s="15" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.3">
@@ -5496,17 +5632,17 @@
         <v>83</v>
       </c>
       <c r="C86" s="12">
-        <v>45715</v>
+        <v>45698</v>
       </c>
       <c r="D86" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E86" s="12">
-        <v>45715</v>
+        <v>45698</v>
       </c>
       <c r="F86" s="13">
-        <f t="shared" si="24"/>
-        <v>77</v>
+        <f t="shared" ref="F86:F93" si="24">$B$85</f>
+        <v>82</v>
       </c>
       <c r="G86" s="13" t="s">
         <v>14</v>
@@ -5518,7 +5654,7 @@
         <v>103</v>
       </c>
       <c r="J86" s="15" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
     </row>
     <row r="87" spans="2:10" x14ac:dyDescent="0.3">
@@ -5527,7 +5663,7 @@
         <v>84</v>
       </c>
       <c r="C87" s="12">
-        <v>45715</v>
+        <v>45698</v>
       </c>
       <c r="D87" s="13" t="s">
         <v>12</v>
@@ -5537,7 +5673,7 @@
       </c>
       <c r="F87" s="13">
         <f t="shared" si="24"/>
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G87" s="13" t="s">
         <v>14</v>
@@ -5549,7 +5685,7 @@
         <v>103</v>
       </c>
       <c r="J87" s="15" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="88" spans="2:10" x14ac:dyDescent="0.3">
@@ -5558,17 +5694,17 @@
         <v>85</v>
       </c>
       <c r="C88" s="12">
-        <v>45717</v>
+        <v>45698</v>
       </c>
       <c r="D88" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E88" s="12">
-        <v>45717</v>
+        <v>45714</v>
       </c>
       <c r="F88" s="13">
         <f t="shared" si="24"/>
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G88" s="13" t="s">
         <v>14</v>
@@ -5580,7 +5716,7 @@
         <v>103</v>
       </c>
       <c r="J88" s="15" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="89" spans="2:10" x14ac:dyDescent="0.3">
@@ -5589,17 +5725,17 @@
         <v>86</v>
       </c>
       <c r="C89" s="12">
-        <v>45717</v>
+        <v>45714</v>
       </c>
       <c r="D89" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E89" s="12">
-        <v>45717</v>
+        <v>45714</v>
       </c>
       <c r="F89" s="13">
-        <f>$B$88</f>
-        <v>85</v>
+        <f t="shared" si="24"/>
+        <v>82</v>
       </c>
       <c r="G89" s="13" t="s">
         <v>14</v>
@@ -5608,10 +5744,10 @@
         <v>19</v>
       </c>
       <c r="I89" s="14" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="J89" s="15" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="90" spans="2:10" x14ac:dyDescent="0.3">
@@ -5620,17 +5756,17 @@
         <v>87</v>
       </c>
       <c r="C90" s="12">
-        <v>45717</v>
+        <v>45714</v>
       </c>
       <c r="D90" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E90" s="12">
-        <v>45717</v>
+        <v>45715</v>
       </c>
       <c r="F90" s="13">
-        <f>$B$88</f>
-        <v>85</v>
+        <f t="shared" si="24"/>
+        <v>82</v>
       </c>
       <c r="G90" s="13" t="s">
         <v>14</v>
@@ -5639,10 +5775,10 @@
         <v>19</v>
       </c>
       <c r="I90" s="14" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="J90" s="15" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="91" spans="2:10" x14ac:dyDescent="0.3">
@@ -5651,17 +5787,17 @@
         <v>88</v>
       </c>
       <c r="C91" s="12">
-        <v>45717</v>
+        <v>45715</v>
       </c>
       <c r="D91" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E91" s="12">
-        <v>45717</v>
+        <v>45715</v>
       </c>
       <c r="F91" s="13">
-        <f>$B$88</f>
-        <v>85</v>
+        <f t="shared" si="24"/>
+        <v>82</v>
       </c>
       <c r="G91" s="13" t="s">
         <v>14</v>
@@ -5670,10 +5806,10 @@
         <v>19</v>
       </c>
       <c r="I91" s="14" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="J91" s="15" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="92" spans="2:10" x14ac:dyDescent="0.3">
@@ -5682,27 +5818,29 @@
         <v>89</v>
       </c>
       <c r="C92" s="12">
-        <v>45717</v>
+        <v>45715</v>
       </c>
       <c r="D92" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E92" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E92" s="12">
+        <v>45714</v>
+      </c>
       <c r="F92" s="13">
-        <f>$B$79</f>
-        <v>76</v>
+        <f t="shared" si="24"/>
+        <v>82</v>
       </c>
       <c r="G92" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H92" s="13" t="s">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="I92" s="14" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="J92" s="15" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
     </row>
     <row r="93" spans="2:10" x14ac:dyDescent="0.3">
@@ -5720,20 +5858,20 @@
         <v>45717</v>
       </c>
       <c r="F93" s="13">
-        <f t="shared" ref="F93:F99" si="25">$B$92</f>
-        <v>89</v>
+        <f t="shared" si="24"/>
+        <v>82</v>
       </c>
       <c r="G93" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H93" s="13" t="s">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="I93" s="14" t="s">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="J93" s="15" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="94" spans="2:10" x14ac:dyDescent="0.3">
@@ -5751,25 +5889,25 @@
         <v>45717</v>
       </c>
       <c r="F94" s="13">
-        <f t="shared" si="25"/>
-        <v>89</v>
+        <f>$B$93</f>
+        <v>90</v>
       </c>
       <c r="G94" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H94" s="13" t="s">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="I94" s="14" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="J94" s="15" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
     </row>
     <row r="95" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B95" s="11">
-        <f t="shared" ref="B95" si="26">B94+1</f>
+        <f t="shared" si="0"/>
         <v>92</v>
       </c>
       <c r="C95" s="12">
@@ -5782,8 +5920,8 @@
         <v>45717</v>
       </c>
       <c r="F95" s="13">
-        <f t="shared" si="25"/>
-        <v>89</v>
+        <f>$B$93</f>
+        <v>90</v>
       </c>
       <c r="G95" s="13" t="s">
         <v>14</v>
@@ -5792,85 +5930,89 @@
         <v>19</v>
       </c>
       <c r="I95" s="14" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="J95" s="15" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="96" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B96" s="11">
-        <f t="shared" ref="B96" si="27">B95+1</f>
+        <f t="shared" si="0"/>
         <v>93</v>
       </c>
       <c r="C96" s="12">
         <v>45717</v>
       </c>
       <c r="D96" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E96" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E96" s="12">
+        <v>45717</v>
+      </c>
       <c r="F96" s="13">
-        <f t="shared" si="25"/>
-        <v>89</v>
+        <f>$B$93</f>
+        <v>90</v>
       </c>
       <c r="G96" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H96" s="13" t="s">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="I96" s="14" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="J96" s="15" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97" s="11">
-        <f t="shared" ref="B97" si="28">B96+1</f>
+        <f t="shared" si="0"/>
         <v>94</v>
       </c>
       <c r="C97" s="12">
         <v>45717</v>
       </c>
       <c r="D97" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E97" s="12"/>
       <c r="F97" s="13">
-        <f t="shared" si="25"/>
-        <v>89</v>
+        <f>$B$84</f>
+        <v>81</v>
       </c>
       <c r="G97" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H97" s="13" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="I97" s="14" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="J97" s="15" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98" s="11">
-        <f t="shared" ref="B98" si="29">B97+1</f>
+        <f t="shared" si="0"/>
         <v>95</v>
       </c>
       <c r="C98" s="12">
         <v>45717</v>
       </c>
       <c r="D98" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E98" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E98" s="12">
+        <v>45717</v>
+      </c>
       <c r="F98" s="13">
-        <f t="shared" si="25"/>
-        <v>89</v>
+        <f t="shared" ref="F98:F104" si="25">$B$97</f>
+        <v>94</v>
       </c>
       <c r="G98" s="13" t="s">
         <v>14</v>
@@ -5882,24 +6024,26 @@
         <v>129</v>
       </c>
       <c r="J98" s="15" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B99" s="11">
-        <f t="shared" ref="B99" si="30">B98+1</f>
+        <f t="shared" si="0"/>
         <v>96</v>
       </c>
       <c r="C99" s="12">
         <v>45717</v>
       </c>
       <c r="D99" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E99" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E99" s="12">
+        <v>45717</v>
+      </c>
       <c r="F99" s="13">
         <f t="shared" si="25"/>
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G99" s="13" t="s">
         <v>14</v>
@@ -5911,170 +6055,169 @@
         <v>129</v>
       </c>
       <c r="J99" s="15" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="100" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B100" s="11">
-        <f t="shared" ref="B100:B118" si="31">B99+1</f>
+        <f t="shared" ref="B100" si="26">B99+1</f>
         <v>97</v>
       </c>
-      <c r="C100" s="12"/>
-      <c r="D100" s="13"/>
-      <c r="E100" s="12"/>
-      <c r="F100" s="13"/>
-      <c r="G100" s="13"/>
-      <c r="H100" s="13"/>
-      <c r="I100" s="14"/>
-      <c r="J100" s="15"/>
+      <c r="C100" s="12">
+        <v>45717</v>
+      </c>
+      <c r="D100" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E100" s="12">
+        <v>45717</v>
+      </c>
+      <c r="F100" s="13">
+        <f t="shared" si="25"/>
+        <v>94</v>
+      </c>
+      <c r="G100" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H100" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I100" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="J100" s="15" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B101" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="B101" si="27">B100+1</f>
         <v>98</v>
       </c>
       <c r="C101" s="12">
-        <v>45719</v>
+        <v>45717</v>
       </c>
       <c r="D101" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E101" s="12"/>
-      <c r="F101" s="13"/>
+      <c r="F101" s="13">
+        <f t="shared" si="25"/>
+        <v>94</v>
+      </c>
       <c r="G101" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H101" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I101" s="15" t="s">
-        <v>140</v>
+        <v>99</v>
+      </c>
+      <c r="I101" s="14" t="s">
+        <v>129</v>
       </c>
       <c r="J101" s="15" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B102" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="B102" si="28">B101+1</f>
         <v>99</v>
       </c>
       <c r="C102" s="12">
-        <v>45719</v>
+        <v>45717</v>
       </c>
       <c r="D102" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E102" s="12">
-        <v>45719</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E102" s="12"/>
       <c r="F102" s="13">
-        <f>$B$101</f>
-        <v>98</v>
+        <f t="shared" si="25"/>
+        <v>94</v>
       </c>
       <c r="G102" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H102" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I102" s="15" t="s">
-        <v>140</v>
+        <v>19</v>
+      </c>
+      <c r="I102" s="14" t="s">
+        <v>135</v>
       </c>
       <c r="J102" s="15" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="103" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B103" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="B103" si="29">B102+1</f>
         <v>100</v>
       </c>
       <c r="C103" s="12">
-        <v>45719</v>
+        <v>45717</v>
       </c>
       <c r="D103" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E103" s="12">
-        <v>45720</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E103" s="12"/>
       <c r="F103" s="13">
-        <f>$B$101</f>
-        <v>98</v>
+        <f t="shared" si="25"/>
+        <v>94</v>
       </c>
       <c r="G103" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H103" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I103" s="15" t="s">
-        <v>140</v>
+        <v>99</v>
+      </c>
+      <c r="I103" s="14" t="s">
+        <v>129</v>
       </c>
       <c r="J103" s="15" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="104" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B104" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="B104" si="30">B103+1</f>
         <v>101</v>
       </c>
       <c r="C104" s="12">
-        <v>45719</v>
+        <v>45717</v>
       </c>
       <c r="D104" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E104" s="12"/>
       <c r="F104" s="13">
-        <f>$B$101</f>
-        <v>98</v>
+        <f t="shared" si="25"/>
+        <v>94</v>
       </c>
       <c r="G104" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H104" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I104" s="15" t="s">
-        <v>140</v>
+        <v>99</v>
+      </c>
+      <c r="I104" s="14" t="s">
+        <v>129</v>
       </c>
       <c r="J104" s="15" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="105" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B105" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="B105:B123" si="31">B104+1</f>
         <v>102</v>
       </c>
-      <c r="C105" s="12">
-        <v>45719</v>
-      </c>
-      <c r="D105" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E105" s="12">
-        <v>45719</v>
-      </c>
-      <c r="F105" s="13">
-        <f>$B$108</f>
-        <v>105</v>
-      </c>
-      <c r="G105" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H105" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I105" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="J105" s="15" t="s">
-        <v>159</v>
-      </c>
+      <c r="C105" s="12"/>
+      <c r="D105" s="13"/>
+      <c r="E105" s="12"/>
+      <c r="F105" s="13"/>
+      <c r="G105" s="13"/>
+      <c r="H105" s="13"/>
+      <c r="I105" s="14"/>
+      <c r="J105" s="15"/>
     </row>
     <row r="106" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B106" s="11">
@@ -6082,16 +6225,13 @@
         <v>103</v>
       </c>
       <c r="C106" s="12">
-        <v>45735</v>
+        <v>45719</v>
       </c>
       <c r="D106" s="13" t="s">
         <v>11</v>
       </c>
       <c r="E106" s="12"/>
-      <c r="F106" s="13">
-        <f>$B$108</f>
-        <v>105</v>
-      </c>
+      <c r="F106" s="13"/>
       <c r="G106" s="13" t="s">
         <v>14</v>
       </c>
@@ -6102,7 +6242,7 @@
         <v>140</v>
       </c>
       <c r="J106" s="15" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
     </row>
     <row r="107" spans="2:10" x14ac:dyDescent="0.3">
@@ -6111,17 +6251,17 @@
         <v>104</v>
       </c>
       <c r="C107" s="12">
-        <v>45735</v>
+        <v>45719</v>
       </c>
       <c r="D107" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E107" s="12">
-        <v>45735</v>
+        <v>45719</v>
       </c>
       <c r="F107" s="13">
-        <f>$B$104</f>
-        <v>101</v>
+        <f>$B$106</f>
+        <v>103</v>
       </c>
       <c r="G107" s="13" t="s">
         <v>14</v>
@@ -6133,7 +6273,7 @@
         <v>140</v>
       </c>
       <c r="J107" s="15" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
     </row>
     <row r="108" spans="2:10" x14ac:dyDescent="0.3">
@@ -6142,15 +6282,17 @@
         <v>105</v>
       </c>
       <c r="C108" s="12">
-        <v>45735</v>
+        <v>45719</v>
       </c>
       <c r="D108" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E108" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E108" s="12">
+        <v>45720</v>
+      </c>
       <c r="F108" s="13">
-        <f>$B$104</f>
-        <v>101</v>
+        <f>$B$106</f>
+        <v>103</v>
       </c>
       <c r="G108" s="13" t="s">
         <v>14</v>
@@ -6162,7 +6304,7 @@
         <v>140</v>
       </c>
       <c r="J108" s="15" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
     </row>
     <row r="109" spans="2:10" x14ac:dyDescent="0.3">
@@ -6171,17 +6313,15 @@
         <v>106</v>
       </c>
       <c r="C109" s="12">
-        <v>45737</v>
+        <v>45719</v>
       </c>
       <c r="D109" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E109" s="12">
-        <v>45738</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E109" s="12"/>
       <c r="F109" s="13">
-        <f>$B$101</f>
-        <v>98</v>
+        <f>$B$106</f>
+        <v>103</v>
       </c>
       <c r="G109" s="13" t="s">
         <v>14</v>
@@ -6190,10 +6330,10 @@
         <v>21</v>
       </c>
       <c r="I109" s="15" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="J109" s="15" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
     </row>
     <row r="110" spans="2:10" x14ac:dyDescent="0.3">
@@ -6202,17 +6342,17 @@
         <v>107</v>
       </c>
       <c r="C110" s="12">
-        <v>45737</v>
+        <v>45719</v>
       </c>
       <c r="D110" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E110" s="12">
-        <v>45738</v>
+        <v>45719</v>
       </c>
       <c r="F110" s="13">
-        <f>$B$108</f>
-        <v>105</v>
+        <f>$B$113</f>
+        <v>110</v>
       </c>
       <c r="G110" s="13" t="s">
         <v>14</v>
@@ -6220,11 +6360,11 @@
       <c r="H110" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I110" s="24" t="s">
-        <v>169</v>
+      <c r="I110" s="15" t="s">
+        <v>140</v>
       </c>
       <c r="J110" s="15" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
     </row>
     <row r="111" spans="2:10" x14ac:dyDescent="0.3">
@@ -6233,15 +6373,15 @@
         <v>108</v>
       </c>
       <c r="C111" s="12">
-        <v>45737</v>
+        <v>45735</v>
       </c>
       <c r="D111" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E111" s="12"/>
       <c r="F111" s="13">
-        <f>$B$108</f>
-        <v>105</v>
+        <f>$B$113</f>
+        <v>110</v>
       </c>
       <c r="G111" s="13" t="s">
         <v>14</v>
@@ -6249,8 +6389,8 @@
       <c r="H111" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I111" s="24" t="s">
-        <v>169</v>
+      <c r="I111" s="15" t="s">
+        <v>140</v>
       </c>
       <c r="J111" s="15" t="s">
         <v>170</v>
@@ -6261,56 +6401,122 @@
         <f t="shared" si="31"/>
         <v>109</v>
       </c>
-      <c r="C112" s="12"/>
-      <c r="D112" s="13"/>
-      <c r="E112" s="12"/>
-      <c r="F112" s="13"/>
-      <c r="G112" s="13"/>
-      <c r="H112" s="13"/>
-      <c r="I112" s="24"/>
-      <c r="J112" s="15"/>
+      <c r="C112" s="12">
+        <v>45735</v>
+      </c>
+      <c r="D112" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E112" s="12">
+        <v>45735</v>
+      </c>
+      <c r="F112" s="13">
+        <f>$B$109</f>
+        <v>106</v>
+      </c>
+      <c r="G112" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H112" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I112" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="J112" s="15" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B113" s="11">
         <f t="shared" si="31"/>
         <v>110</v>
       </c>
-      <c r="C113" s="12"/>
-      <c r="D113" s="13"/>
+      <c r="C113" s="12">
+        <v>45735</v>
+      </c>
+      <c r="D113" s="13" t="s">
+        <v>11</v>
+      </c>
       <c r="E113" s="12"/>
-      <c r="F113" s="13"/>
-      <c r="G113" s="13"/>
-      <c r="H113" s="13"/>
-      <c r="I113" s="24"/>
-      <c r="J113" s="15"/>
+      <c r="F113" s="13">
+        <f>$B$109</f>
+        <v>106</v>
+      </c>
+      <c r="G113" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H113" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I113" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="J113" s="15" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="114" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B114" s="11">
         <f t="shared" si="31"/>
         <v>111</v>
       </c>
-      <c r="C114" s="12"/>
-      <c r="D114" s="13"/>
-      <c r="E114" s="12"/>
-      <c r="F114" s="13"/>
-      <c r="G114" s="13"/>
-      <c r="H114" s="13"/>
-      <c r="I114" s="24"/>
-      <c r="J114" s="15"/>
+      <c r="C114" s="12">
+        <v>45737</v>
+      </c>
+      <c r="D114" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E114" s="12">
+        <v>45738</v>
+      </c>
+      <c r="F114" s="13">
+        <f>$B$106</f>
+        <v>103</v>
+      </c>
+      <c r="G114" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H114" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I114" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="J114" s="15" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="115" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B115" s="11">
         <f t="shared" si="31"/>
         <v>112</v>
       </c>
-      <c r="C115" s="12"/>
-      <c r="D115" s="13"/>
-      <c r="E115" s="12"/>
-      <c r="F115" s="13"/>
-      <c r="G115" s="13"/>
-      <c r="H115" s="13"/>
-      <c r="I115" s="14"/>
-      <c r="J115" s="15"/>
+      <c r="C115" s="12">
+        <v>45737</v>
+      </c>
+      <c r="D115" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E115" s="12">
+        <v>45738</v>
+      </c>
+      <c r="F115" s="13">
+        <f>$B$113</f>
+        <v>110</v>
+      </c>
+      <c r="G115" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H115" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I115" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="J115" s="15" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="116" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B116" s="11">
@@ -6318,24 +6524,27 @@
         <v>113</v>
       </c>
       <c r="C116" s="12">
-        <v>45734</v>
+        <v>45737</v>
       </c>
       <c r="D116" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E116" s="12"/>
-      <c r="F116" s="13"/>
+      <c r="F116" s="13">
+        <f>$B$113</f>
+        <v>110</v>
+      </c>
       <c r="G116" s="13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H116" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I116" s="14" t="s">
-        <v>160</v>
+        <v>21</v>
+      </c>
+      <c r="I116" s="24" t="s">
+        <v>167</v>
       </c>
       <c r="J116" s="15" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="117" spans="2:10" x14ac:dyDescent="0.3">
@@ -6349,7 +6558,7 @@
       <c r="F117" s="13"/>
       <c r="G117" s="13"/>
       <c r="H117" s="13"/>
-      <c r="I117" s="14"/>
+      <c r="I117" s="24"/>
       <c r="J117" s="15"/>
     </row>
     <row r="118" spans="2:10" x14ac:dyDescent="0.3">
@@ -6363,27 +6572,109 @@
       <c r="F118" s="13"/>
       <c r="G118" s="13"/>
       <c r="H118" s="13"/>
-      <c r="I118" s="14"/>
+      <c r="I118" s="24"/>
       <c r="J118" s="15"/>
     </row>
-    <row r="119" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B119" s="18">
+    <row r="119" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B119" s="11">
+        <f t="shared" si="31"/>
+        <v>116</v>
+      </c>
+      <c r="C119" s="12"/>
+      <c r="D119" s="13"/>
+      <c r="E119" s="12"/>
+      <c r="F119" s="13"/>
+      <c r="G119" s="13"/>
+      <c r="H119" s="13"/>
+      <c r="I119" s="24"/>
+      <c r="J119" s="15"/>
+    </row>
+    <row r="120" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B120" s="11">
+        <f t="shared" si="31"/>
+        <v>117</v>
+      </c>
+      <c r="C120" s="12"/>
+      <c r="D120" s="13"/>
+      <c r="E120" s="12"/>
+      <c r="F120" s="13"/>
+      <c r="G120" s="13"/>
+      <c r="H120" s="13"/>
+      <c r="I120" s="14"/>
+      <c r="J120" s="15"/>
+    </row>
+    <row r="121" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B121" s="11">
+        <f t="shared" si="31"/>
+        <v>118</v>
+      </c>
+      <c r="C121" s="12">
+        <v>45734</v>
+      </c>
+      <c r="D121" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E121" s="12"/>
+      <c r="F121" s="13"/>
+      <c r="G121" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H121" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I121" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="J121" s="15" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="122" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B122" s="11">
+        <f t="shared" si="31"/>
+        <v>119</v>
+      </c>
+      <c r="C122" s="12"/>
+      <c r="D122" s="13"/>
+      <c r="E122" s="12"/>
+      <c r="F122" s="13"/>
+      <c r="G122" s="13"/>
+      <c r="H122" s="13"/>
+      <c r="I122" s="14"/>
+      <c r="J122" s="15"/>
+    </row>
+    <row r="123" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B123" s="11">
+        <f t="shared" si="31"/>
+        <v>120</v>
+      </c>
+      <c r="C123" s="12"/>
+      <c r="D123" s="13"/>
+      <c r="E123" s="12"/>
+      <c r="F123" s="13"/>
+      <c r="G123" s="13"/>
+      <c r="H123" s="13"/>
+      <c r="I123" s="14"/>
+      <c r="J123" s="15"/>
+    </row>
+    <row r="124" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B124" s="18">
         <f t="shared" si="0"/>
-        <v>116</v>
-      </c>
-      <c r="C119" s="19"/>
-      <c r="D119" s="20"/>
-      <c r="E119" s="19"/>
-      <c r="F119" s="20"/>
-      <c r="G119" s="20"/>
-      <c r="H119" s="20"/>
-      <c r="I119" s="21"/>
-      <c r="J119" s="22"/>
+        <v>121</v>
+      </c>
+      <c r="C124" s="19"/>
+      <c r="D124" s="20"/>
+      <c r="E124" s="19"/>
+      <c r="F124" s="20"/>
+      <c r="G124" s="20"/>
+      <c r="H124" s="20"/>
+      <c r="I124" s="21"/>
+      <c r="J124" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:J119" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
+  <autoFilter ref="B2:J124" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B3:J45 A43:A45 A46:J46 A47:A51 B47:J119">
+  <conditionalFormatting sqref="B3:J45 A43:A45 A46:J46 A47:A51 B47:J124">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>
@@ -6400,25 +6691,25 @@
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H117:H119 H80:H91 H3:H61 H78</xm:sqref>
+          <xm:sqref>H122:H124 H85:H96 H3:H61 H83</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D6F2F62E-6D63-4E2D-8772-1211A4C3A979}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$10</xm:f>
           </x14:formula1>
-          <xm:sqref>H79 H62:H77 H92:H116</xm:sqref>
+          <xm:sqref>H84 H97:H121 H62:H82</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C61EF0EC-B820-4CEA-8AA2-04B5D172AE2C}">
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D119</xm:sqref>
+          <xm:sqref>D3:D124</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G119</xm:sqref>
+          <xm:sqref>G3:G124</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6489,4 +6780,50 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{010CCC86-5868-4A8F-A831-BB7D05E6FC68}">
+  <dimension ref="B2:Q7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="118" width="2.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B2" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q2" s="26" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
+        <v>173</v>
+      </c>
+      <c r="E4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="C6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="C7" t="s">
+        <v>176</v>
+      </c>
+      <c r="H7" t="s">
+        <v>177</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E2F979-F145-4DEF-B4B2-C4C6249032C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{420970AC-F5C9-4541-B7E4-FDABCBCA6061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作業項目!$B$2:$J$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作業項目!$B$2:$J$125</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="185">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -2547,6 +2547,29 @@
     <rPh sb="9" eb="11">
       <t>ツイカ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>load時の項目とTable情報取込追加</t>
+    <rPh sb="4" eb="5">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>トリコミ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>-</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2912,7 +2935,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3286,7 +3309,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="A1:K124"/>
+  <dimension ref="A1:K125"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -3484,7 +3507,7 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
-        <f t="shared" ref="A8:B124" si="0">B7+1</f>
+        <f t="shared" ref="A8:B125" si="0">B7+1</f>
         <v>6</v>
       </c>
       <c r="C8" s="12">
@@ -5152,7 +5175,7 @@
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B66" s="11">
-        <f t="shared" ref="B66:B84" si="23">B65+1</f>
+        <f t="shared" ref="B66:B85" si="23">B65+1</f>
         <v>64</v>
       </c>
       <c r="C66" s="12">
@@ -5442,10 +5465,12 @@
         <v>45740</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E76" s="12"/>
-      <c r="F76" s="13"/>
+      <c r="F76" s="13" t="s">
+        <v>184</v>
+      </c>
       <c r="G76" s="13" t="s">
         <v>14</v>
       </c>
@@ -5459,7 +5484,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="77" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B77" s="11">
         <f t="shared" si="23"/>
         <v>74</v>
@@ -5471,7 +5496,10 @@
         <v>10</v>
       </c>
       <c r="E77" s="12"/>
-      <c r="F77" s="13"/>
+      <c r="F77" s="13">
+        <f>$B$76</f>
+        <v>73</v>
+      </c>
       <c r="G77" s="13" t="s">
         <v>14</v>
       </c>
@@ -5479,25 +5507,37 @@
         <v>19</v>
       </c>
       <c r="I77" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="J77" s="17" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+      <c r="J77" s="15" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B78" s="11">
         <f t="shared" si="23"/>
         <v>75</v>
       </c>
-      <c r="C78" s="12"/>
-      <c r="D78" s="13"/>
+      <c r="C78" s="12">
+        <v>45740</v>
+      </c>
+      <c r="D78" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E78" s="12"/>
       <c r="F78" s="13"/>
-      <c r="G78" s="13"/>
-      <c r="H78" s="13"/>
-      <c r="I78" s="14"/>
-      <c r="J78" s="15"/>
+      <c r="G78" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H78" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I78" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="J78" s="17" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="79" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B79" s="11">
@@ -5574,56 +5614,39 @@
         <f t="shared" si="23"/>
         <v>81</v>
       </c>
-      <c r="C84" s="12">
-        <v>45698</v>
-      </c>
-      <c r="D84" s="13" t="s">
-        <v>11</v>
-      </c>
+      <c r="C84" s="12"/>
+      <c r="D84" s="13"/>
       <c r="E84" s="12"/>
       <c r="F84" s="13"/>
-      <c r="G84" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H84" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="I84" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="J84" s="15" t="s">
-        <v>102</v>
-      </c>
+      <c r="G84" s="13"/>
+      <c r="H84" s="13"/>
+      <c r="I84" s="14"/>
+      <c r="J84" s="15"/>
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B85" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="23"/>
         <v>82</v>
       </c>
       <c r="C85" s="12">
         <v>45698</v>
       </c>
       <c r="D85" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E85" s="12">
-        <v>45717</v>
-      </c>
-      <c r="F85" s="13">
-        <f>$B$84</f>
-        <v>81</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E85" s="12"/>
+      <c r="F85" s="13"/>
       <c r="G85" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H85" s="13" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="I85" s="14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J85" s="15" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.3">
@@ -5638,10 +5661,10 @@
         <v>12</v>
       </c>
       <c r="E86" s="12">
-        <v>45698</v>
+        <v>45717</v>
       </c>
       <c r="F86" s="13">
-        <f t="shared" ref="F86:F93" si="24">$B$85</f>
+        <f>$B$85</f>
         <v>82</v>
       </c>
       <c r="G86" s="13" t="s">
@@ -5654,7 +5677,7 @@
         <v>103</v>
       </c>
       <c r="J86" s="15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="87" spans="2:10" x14ac:dyDescent="0.3">
@@ -5669,11 +5692,11 @@
         <v>12</v>
       </c>
       <c r="E87" s="12">
-        <v>45714</v>
+        <v>45698</v>
       </c>
       <c r="F87" s="13">
-        <f t="shared" si="24"/>
-        <v>82</v>
+        <f t="shared" ref="F87:F94" si="24">$B$86</f>
+        <v>83</v>
       </c>
       <c r="G87" s="13" t="s">
         <v>14</v>
@@ -5685,7 +5708,7 @@
         <v>103</v>
       </c>
       <c r="J87" s="15" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
     </row>
     <row r="88" spans="2:10" x14ac:dyDescent="0.3">
@@ -5704,7 +5727,7 @@
       </c>
       <c r="F88" s="13">
         <f t="shared" si="24"/>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G88" s="13" t="s">
         <v>14</v>
@@ -5716,7 +5739,7 @@
         <v>103</v>
       </c>
       <c r="J88" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="89" spans="2:10" x14ac:dyDescent="0.3">
@@ -5725,7 +5748,7 @@
         <v>86</v>
       </c>
       <c r="C89" s="12">
-        <v>45714</v>
+        <v>45698</v>
       </c>
       <c r="D89" s="13" t="s">
         <v>12</v>
@@ -5735,7 +5758,7 @@
       </c>
       <c r="F89" s="13">
         <f t="shared" si="24"/>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G89" s="13" t="s">
         <v>14</v>
@@ -5747,7 +5770,7 @@
         <v>103</v>
       </c>
       <c r="J89" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="90" spans="2:10" x14ac:dyDescent="0.3">
@@ -5762,11 +5785,11 @@
         <v>12</v>
       </c>
       <c r="E90" s="12">
-        <v>45715</v>
+        <v>45714</v>
       </c>
       <c r="F90" s="13">
         <f t="shared" si="24"/>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G90" s="13" t="s">
         <v>14</v>
@@ -5778,7 +5801,7 @@
         <v>103</v>
       </c>
       <c r="J90" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="91" spans="2:10" x14ac:dyDescent="0.3">
@@ -5787,7 +5810,7 @@
         <v>88</v>
       </c>
       <c r="C91" s="12">
-        <v>45715</v>
+        <v>45714</v>
       </c>
       <c r="D91" s="13" t="s">
         <v>12</v>
@@ -5797,7 +5820,7 @@
       </c>
       <c r="F91" s="13">
         <f t="shared" si="24"/>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G91" s="13" t="s">
         <v>14</v>
@@ -5809,7 +5832,7 @@
         <v>103</v>
       </c>
       <c r="J91" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="92" spans="2:10" x14ac:dyDescent="0.3">
@@ -5824,11 +5847,11 @@
         <v>12</v>
       </c>
       <c r="E92" s="12">
-        <v>45714</v>
+        <v>45715</v>
       </c>
       <c r="F92" s="13">
         <f t="shared" si="24"/>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G92" s="13" t="s">
         <v>14</v>
@@ -5840,7 +5863,7 @@
         <v>103</v>
       </c>
       <c r="J92" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="93" spans="2:10" x14ac:dyDescent="0.3">
@@ -5849,17 +5872,17 @@
         <v>90</v>
       </c>
       <c r="C93" s="12">
-        <v>45717</v>
+        <v>45715</v>
       </c>
       <c r="D93" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E93" s="12">
-        <v>45717</v>
+        <v>45714</v>
       </c>
       <c r="F93" s="13">
         <f t="shared" si="24"/>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G93" s="13" t="s">
         <v>14</v>
@@ -5871,7 +5894,7 @@
         <v>103</v>
       </c>
       <c r="J93" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="94" spans="2:10" x14ac:dyDescent="0.3">
@@ -5889,8 +5912,8 @@
         <v>45717</v>
       </c>
       <c r="F94" s="13">
-        <f>$B$93</f>
-        <v>90</v>
+        <f t="shared" si="24"/>
+        <v>83</v>
       </c>
       <c r="G94" s="13" t="s">
         <v>14</v>
@@ -5899,10 +5922,10 @@
         <v>19</v>
       </c>
       <c r="I94" s="14" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="J94" s="15" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="95" spans="2:10" x14ac:dyDescent="0.3">
@@ -5920,8 +5943,8 @@
         <v>45717</v>
       </c>
       <c r="F95" s="13">
-        <f>$B$93</f>
-        <v>90</v>
+        <f>$B$94</f>
+        <v>91</v>
       </c>
       <c r="G95" s="13" t="s">
         <v>14</v>
@@ -5933,7 +5956,7 @@
         <v>123</v>
       </c>
       <c r="J95" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="96" spans="2:10" x14ac:dyDescent="0.3">
@@ -5951,8 +5974,8 @@
         <v>45717</v>
       </c>
       <c r="F96" s="13">
-        <f>$B$93</f>
-        <v>90</v>
+        <f>$B$94</f>
+        <v>91</v>
       </c>
       <c r="G96" s="13" t="s">
         <v>14</v>
@@ -5964,7 +5987,7 @@
         <v>123</v>
       </c>
       <c r="J96" s="15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.3">
@@ -5976,24 +5999,26 @@
         <v>45717</v>
       </c>
       <c r="D97" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E97" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E97" s="12">
+        <v>45717</v>
+      </c>
       <c r="F97" s="13">
-        <f>$B$84</f>
-        <v>81</v>
+        <f>$B$94</f>
+        <v>91</v>
       </c>
       <c r="G97" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H97" s="13" t="s">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="I97" s="14" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="J97" s="15" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.3">
@@ -6005,14 +6030,12 @@
         <v>45717</v>
       </c>
       <c r="D98" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E98" s="12">
-        <v>45717</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E98" s="12"/>
       <c r="F98" s="13">
-        <f t="shared" ref="F98:F104" si="25">$B$97</f>
-        <v>94</v>
+        <f>$B$85</f>
+        <v>82</v>
       </c>
       <c r="G98" s="13" t="s">
         <v>14</v>
@@ -6021,10 +6044,10 @@
         <v>99</v>
       </c>
       <c r="I98" s="14" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J98" s="15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.3">
@@ -6042,8 +6065,8 @@
         <v>45717</v>
       </c>
       <c r="F99" s="13">
-        <f t="shared" si="25"/>
-        <v>94</v>
+        <f t="shared" ref="F99:F105" si="25">$B$98</f>
+        <v>95</v>
       </c>
       <c r="G99" s="13" t="s">
         <v>14</v>
@@ -6055,12 +6078,12 @@
         <v>129</v>
       </c>
       <c r="J99" s="15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="100" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B100" s="11">
-        <f t="shared" ref="B100" si="26">B99+1</f>
+        <f t="shared" si="0"/>
         <v>97</v>
       </c>
       <c r="C100" s="12">
@@ -6074,53 +6097,55 @@
       </c>
       <c r="F100" s="13">
         <f t="shared" si="25"/>
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G100" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H100" s="13" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="I100" s="14" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J100" s="15" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B101" s="11">
-        <f t="shared" ref="B101" si="27">B100+1</f>
+        <f t="shared" ref="B101" si="26">B100+1</f>
         <v>98</v>
       </c>
       <c r="C101" s="12">
         <v>45717</v>
       </c>
       <c r="D101" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E101" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E101" s="12">
+        <v>45717</v>
+      </c>
       <c r="F101" s="13">
         <f t="shared" si="25"/>
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G101" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H101" s="13" t="s">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="I101" s="14" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J101" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B102" s="11">
-        <f t="shared" ref="B102" si="28">B101+1</f>
+        <f t="shared" ref="B102" si="27">B101+1</f>
         <v>99</v>
       </c>
       <c r="C102" s="12">
@@ -6132,24 +6157,24 @@
       <c r="E102" s="12"/>
       <c r="F102" s="13">
         <f t="shared" si="25"/>
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G102" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H102" s="13" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="I102" s="14" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="J102" s="15" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="103" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B103" s="11">
-        <f t="shared" ref="B103" si="29">B102+1</f>
+        <f t="shared" ref="B103" si="28">B102+1</f>
         <v>100</v>
       </c>
       <c r="C103" s="12">
@@ -6161,24 +6186,24 @@
       <c r="E103" s="12"/>
       <c r="F103" s="13">
         <f t="shared" si="25"/>
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G103" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H103" s="13" t="s">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="I103" s="14" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="J103" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="104" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B104" s="11">
-        <f t="shared" ref="B104" si="30">B103+1</f>
+        <f t="shared" ref="B104" si="29">B103+1</f>
         <v>101</v>
       </c>
       <c r="C104" s="12">
@@ -6190,7 +6215,7 @@
       <c r="E104" s="12"/>
       <c r="F104" s="13">
         <f t="shared" si="25"/>
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G104" s="13" t="s">
         <v>14</v>
@@ -6202,48 +6227,51 @@
         <v>129</v>
       </c>
       <c r="J104" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="105" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B105" s="11">
-        <f t="shared" ref="B105:B123" si="31">B104+1</f>
+        <f t="shared" ref="B105" si="30">B104+1</f>
         <v>102</v>
       </c>
-      <c r="C105" s="12"/>
-      <c r="D105" s="13"/>
+      <c r="C105" s="12">
+        <v>45717</v>
+      </c>
+      <c r="D105" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E105" s="12"/>
-      <c r="F105" s="13"/>
-      <c r="G105" s="13"/>
-      <c r="H105" s="13"/>
-      <c r="I105" s="14"/>
-      <c r="J105" s="15"/>
+      <c r="F105" s="13">
+        <f t="shared" si="25"/>
+        <v>95</v>
+      </c>
+      <c r="G105" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H105" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="I105" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="J105" s="15" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="106" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B106" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="B106:B124" si="31">B105+1</f>
         <v>103</v>
       </c>
-      <c r="C106" s="12">
-        <v>45719</v>
-      </c>
-      <c r="D106" s="13" t="s">
-        <v>11</v>
-      </c>
+      <c r="C106" s="12"/>
+      <c r="D106" s="13"/>
       <c r="E106" s="12"/>
       <c r="F106" s="13"/>
-      <c r="G106" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H106" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I106" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="J106" s="15" t="s">
-        <v>141</v>
-      </c>
+      <c r="G106" s="13"/>
+      <c r="H106" s="13"/>
+      <c r="I106" s="14"/>
+      <c r="J106" s="15"/>
     </row>
     <row r="107" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B107" s="11">
@@ -6254,15 +6282,10 @@
         <v>45719</v>
       </c>
       <c r="D107" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E107" s="12">
-        <v>45719</v>
-      </c>
-      <c r="F107" s="13">
-        <f>$B$106</f>
-        <v>103</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E107" s="12"/>
+      <c r="F107" s="13"/>
       <c r="G107" s="13" t="s">
         <v>14</v>
       </c>
@@ -6273,7 +6296,7 @@
         <v>140</v>
       </c>
       <c r="J107" s="15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="108" spans="2:10" x14ac:dyDescent="0.3">
@@ -6288,11 +6311,11 @@
         <v>12</v>
       </c>
       <c r="E108" s="12">
-        <v>45720</v>
+        <v>45719</v>
       </c>
       <c r="F108" s="13">
-        <f>$B$106</f>
-        <v>103</v>
+        <f>$B$107</f>
+        <v>104</v>
       </c>
       <c r="G108" s="13" t="s">
         <v>14</v>
@@ -6304,7 +6327,7 @@
         <v>140</v>
       </c>
       <c r="J108" s="15" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="109" spans="2:10" x14ac:dyDescent="0.3">
@@ -6316,12 +6339,14 @@
         <v>45719</v>
       </c>
       <c r="D109" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E109" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E109" s="12">
+        <v>45720</v>
+      </c>
       <c r="F109" s="13">
-        <f>$B$106</f>
-        <v>103</v>
+        <f>$B$107</f>
+        <v>104</v>
       </c>
       <c r="G109" s="13" t="s">
         <v>14</v>
@@ -6333,7 +6358,7 @@
         <v>140</v>
       </c>
       <c r="J109" s="15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="110" spans="2:10" x14ac:dyDescent="0.3">
@@ -6345,14 +6370,12 @@
         <v>45719</v>
       </c>
       <c r="D110" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E110" s="12">
-        <v>45719</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E110" s="12"/>
       <c r="F110" s="13">
-        <f>$B$113</f>
-        <v>110</v>
+        <f>$B$107</f>
+        <v>104</v>
       </c>
       <c r="G110" s="13" t="s">
         <v>14</v>
@@ -6364,7 +6387,7 @@
         <v>140</v>
       </c>
       <c r="J110" s="15" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
     </row>
     <row r="111" spans="2:10" x14ac:dyDescent="0.3">
@@ -6373,15 +6396,17 @@
         <v>108</v>
       </c>
       <c r="C111" s="12">
-        <v>45735</v>
+        <v>45719</v>
       </c>
       <c r="D111" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E111" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E111" s="12">
+        <v>45719</v>
+      </c>
       <c r="F111" s="13">
-        <f>$B$113</f>
-        <v>110</v>
+        <f>$B$114</f>
+        <v>111</v>
       </c>
       <c r="G111" s="13" t="s">
         <v>14</v>
@@ -6393,7 +6418,7 @@
         <v>140</v>
       </c>
       <c r="J111" s="15" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
     </row>
     <row r="112" spans="2:10" x14ac:dyDescent="0.3">
@@ -6405,14 +6430,12 @@
         <v>45735</v>
       </c>
       <c r="D112" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E112" s="12">
-        <v>45735</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E112" s="12"/>
       <c r="F112" s="13">
-        <f>$B$109</f>
-        <v>106</v>
+        <f>$B$114</f>
+        <v>111</v>
       </c>
       <c r="G112" s="13" t="s">
         <v>14</v>
@@ -6424,7 +6447,7 @@
         <v>140</v>
       </c>
       <c r="J112" s="15" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
@@ -6436,12 +6459,14 @@
         <v>45735</v>
       </c>
       <c r="D113" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E113" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E113" s="12">
+        <v>45735</v>
+      </c>
       <c r="F113" s="13">
-        <f>$B$109</f>
-        <v>106</v>
+        <f>$B$110</f>
+        <v>107</v>
       </c>
       <c r="G113" s="13" t="s">
         <v>14</v>
@@ -6453,7 +6478,7 @@
         <v>140</v>
       </c>
       <c r="J113" s="15" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
     </row>
     <row r="114" spans="2:10" x14ac:dyDescent="0.3">
@@ -6462,17 +6487,15 @@
         <v>111</v>
       </c>
       <c r="C114" s="12">
-        <v>45737</v>
+        <v>45735</v>
       </c>
       <c r="D114" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E114" s="12">
-        <v>45738</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E114" s="12"/>
       <c r="F114" s="13">
-        <f>$B$106</f>
-        <v>103</v>
+        <f>$B$110</f>
+        <v>107</v>
       </c>
       <c r="G114" s="13" t="s">
         <v>14</v>
@@ -6481,10 +6504,10 @@
         <v>21</v>
       </c>
       <c r="I114" s="15" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="J114" s="15" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="115" spans="2:10" x14ac:dyDescent="0.3">
@@ -6502,8 +6525,8 @@
         <v>45738</v>
       </c>
       <c r="F115" s="13">
-        <f>$B$113</f>
-        <v>110</v>
+        <f>$B$107</f>
+        <v>104</v>
       </c>
       <c r="G115" s="13" t="s">
         <v>14</v>
@@ -6511,11 +6534,11 @@
       <c r="H115" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I115" s="24" t="s">
-        <v>167</v>
+      <c r="I115" s="15" t="s">
+        <v>165</v>
       </c>
       <c r="J115" s="15" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="116" spans="2:10" x14ac:dyDescent="0.3">
@@ -6527,12 +6550,14 @@
         <v>45737</v>
       </c>
       <c r="D116" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E116" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E116" s="12">
+        <v>45738</v>
+      </c>
       <c r="F116" s="13">
-        <f>$B$113</f>
-        <v>110</v>
+        <f>$B$114</f>
+        <v>111</v>
       </c>
       <c r="G116" s="13" t="s">
         <v>14</v>
@@ -6544,7 +6569,7 @@
         <v>167</v>
       </c>
       <c r="J116" s="15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="117" spans="2:10" x14ac:dyDescent="0.3">
@@ -6552,14 +6577,29 @@
         <f t="shared" si="31"/>
         <v>114</v>
       </c>
-      <c r="C117" s="12"/>
-      <c r="D117" s="13"/>
+      <c r="C117" s="12">
+        <v>45737</v>
+      </c>
+      <c r="D117" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E117" s="12"/>
-      <c r="F117" s="13"/>
-      <c r="G117" s="13"/>
-      <c r="H117" s="13"/>
-      <c r="I117" s="24"/>
-      <c r="J117" s="15"/>
+      <c r="F117" s="13">
+        <f>$B$114</f>
+        <v>111</v>
+      </c>
+      <c r="G117" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H117" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I117" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="J117" s="15" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="118" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B118" s="11">
@@ -6600,7 +6640,7 @@
       <c r="F120" s="13"/>
       <c r="G120" s="13"/>
       <c r="H120" s="13"/>
-      <c r="I120" s="14"/>
+      <c r="I120" s="24"/>
       <c r="J120" s="15"/>
     </row>
     <row r="121" spans="2:10" x14ac:dyDescent="0.3">
@@ -6608,40 +6648,40 @@
         <f t="shared" si="31"/>
         <v>118</v>
       </c>
-      <c r="C121" s="12">
-        <v>45734</v>
-      </c>
-      <c r="D121" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C121" s="12"/>
+      <c r="D121" s="13"/>
       <c r="E121" s="12"/>
       <c r="F121" s="13"/>
-      <c r="G121" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="H121" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I121" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="J121" s="15" t="s">
-        <v>161</v>
-      </c>
+      <c r="G121" s="13"/>
+      <c r="H121" s="13"/>
+      <c r="I121" s="14"/>
+      <c r="J121" s="15"/>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B122" s="11">
         <f t="shared" si="31"/>
         <v>119</v>
       </c>
-      <c r="C122" s="12"/>
-      <c r="D122" s="13"/>
+      <c r="C122" s="12">
+        <v>45734</v>
+      </c>
+      <c r="D122" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E122" s="12"/>
       <c r="F122" s="13"/>
-      <c r="G122" s="13"/>
-      <c r="H122" s="13"/>
-      <c r="I122" s="14"/>
-      <c r="J122" s="15"/>
+      <c r="G122" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H122" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I122" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="J122" s="15" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="123" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B123" s="11">
@@ -6657,24 +6697,38 @@
       <c r="I123" s="14"/>
       <c r="J123" s="15"/>
     </row>
-    <row r="124" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B124" s="18">
+    <row r="124" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B124" s="11">
+        <f t="shared" si="31"/>
+        <v>121</v>
+      </c>
+      <c r="C124" s="12"/>
+      <c r="D124" s="13"/>
+      <c r="E124" s="12"/>
+      <c r="F124" s="13"/>
+      <c r="G124" s="13"/>
+      <c r="H124" s="13"/>
+      <c r="I124" s="14"/>
+      <c r="J124" s="15"/>
+    </row>
+    <row r="125" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B125" s="18">
         <f t="shared" si="0"/>
-        <v>121</v>
-      </c>
-      <c r="C124" s="19"/>
-      <c r="D124" s="20"/>
-      <c r="E124" s="19"/>
-      <c r="F124" s="20"/>
-      <c r="G124" s="20"/>
-      <c r="H124" s="20"/>
-      <c r="I124" s="21"/>
-      <c r="J124" s="22"/>
+        <v>122</v>
+      </c>
+      <c r="C125" s="19"/>
+      <c r="D125" s="20"/>
+      <c r="E125" s="19"/>
+      <c r="F125" s="20"/>
+      <c r="G125" s="20"/>
+      <c r="H125" s="20"/>
+      <c r="I125" s="21"/>
+      <c r="J125" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:J124" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
+  <autoFilter ref="B2:J125" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B3:J45 A43:A45 A46:J46 A47:A51 B47:J124">
+  <conditionalFormatting sqref="B3:J45 A43:A45 A46:J46 A47:A51 B47:J125">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>
@@ -6691,25 +6745,25 @@
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H122:H124 H85:H96 H3:H61 H83</xm:sqref>
+          <xm:sqref>H123:H125 H86:H97 H3:H61 H84</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D6F2F62E-6D63-4E2D-8772-1211A4C3A979}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$10</xm:f>
           </x14:formula1>
-          <xm:sqref>H84 H97:H121 H62:H82</xm:sqref>
+          <xm:sqref>H85 H98:H122 H62:H83</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C61EF0EC-B820-4CEA-8AA2-04B5D172AE2C}">
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D124</xm:sqref>
+          <xm:sqref>D3:D125</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G124</xm:sqref>
+          <xm:sqref>G3:G125</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{420970AC-F5C9-4541-B7E4-FDABCBCA6061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3C5195-ABC7-44F2-92E1-2D27AAD031B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
   <sheets>
     <sheet name="作業項目" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="187">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -2570,6 +2570,26 @@
   </si>
   <si>
     <t>-</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>loadメソッド構築 : HtmlOrderDisp01で使用</t>
+    <rPh sb="8" eb="10">
+      <t>コウチク</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>受注情報</t>
+    <rPh sb="0" eb="2">
+      <t>ジュチュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5335,7 +5355,9 @@
       <c r="D71" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="E71" s="12"/>
+      <c r="E71" s="12">
+        <v>45729</v>
+      </c>
       <c r="F71" s="13">
         <f>$B$69</f>
         <v>67</v>
@@ -5493,7 +5515,7 @@
         <v>45740</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E77" s="12"/>
       <c r="F77" s="13">
@@ -5525,7 +5547,10 @@
         <v>10</v>
       </c>
       <c r="E78" s="12"/>
-      <c r="F78" s="13"/>
+      <c r="F78" s="13">
+        <f>$B$74</f>
+        <v>71</v>
+      </c>
       <c r="G78" s="13" t="s">
         <v>14</v>
       </c>
@@ -5544,14 +5569,29 @@
         <f t="shared" si="23"/>
         <v>76</v>
       </c>
-      <c r="C79" s="12"/>
-      <c r="D79" s="13"/>
+      <c r="C79" s="12">
+        <v>45741</v>
+      </c>
+      <c r="D79" s="13" t="s">
+        <v>11</v>
+      </c>
       <c r="E79" s="12"/>
-      <c r="F79" s="13"/>
-      <c r="G79" s="13"/>
-      <c r="H79" s="13"/>
-      <c r="I79" s="14"/>
-      <c r="J79" s="15"/>
+      <c r="F79" s="13">
+        <f>$B$72</f>
+        <v>69</v>
+      </c>
+      <c r="G79" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H79" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I79" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="J79" s="15" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="80" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B80" s="11">
@@ -6606,14 +6646,31 @@
         <f t="shared" si="31"/>
         <v>115</v>
       </c>
-      <c r="C118" s="12"/>
-      <c r="D118" s="13"/>
-      <c r="E118" s="12"/>
-      <c r="F118" s="13"/>
-      <c r="G118" s="13"/>
-      <c r="H118" s="13"/>
-      <c r="I118" s="24"/>
-      <c r="J118" s="15"/>
+      <c r="C118" s="12">
+        <v>45741</v>
+      </c>
+      <c r="D118" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E118" s="12">
+        <v>45741</v>
+      </c>
+      <c r="F118" s="13">
+        <f>$B$107</f>
+        <v>104</v>
+      </c>
+      <c r="G118" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H118" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I118" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="J118" s="15" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B119" s="11">
@@ -6751,7 +6808,7 @@
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$10</xm:f>
           </x14:formula1>
-          <xm:sqref>H85 H98:H122 H62:H83</xm:sqref>
+          <xm:sqref>H85 H62:H83 H98:H122</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C61EF0EC-B820-4CEA-8AA2-04B5D172AE2C}">
           <x14:formula1>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3C5195-ABC7-44F2-92E1-2D27AAD031B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3D2BFC1-41AA-472D-BF40-52BCF50769D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -5515,9 +5515,11 @@
         <v>45740</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E77" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E77" s="12">
+        <v>45741</v>
+      </c>
       <c r="F77" s="13">
         <f>$B$76</f>
         <v>73</v>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3D2BFC1-41AA-472D-BF40-52BCF50769D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{431C5F5F-BA92-4419-BFCE-52D3182B6BCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="188">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -2590,6 +2590,10 @@
     <rPh sb="2" eb="4">
       <t>ジョウホウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">テーブル項目情報テーブル構築 : sys_column </t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5546,7 +5550,7 @@
         <v>45740</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E78" s="12"/>
       <c r="F78" s="13">
@@ -5575,9 +5579,11 @@
         <v>45741</v>
       </c>
       <c r="D79" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E79" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E79" s="12">
+        <v>45741</v>
+      </c>
       <c r="F79" s="13">
         <f>$B$72</f>
         <v>69</v>
@@ -5600,14 +5606,29 @@
         <f t="shared" si="23"/>
         <v>77</v>
       </c>
-      <c r="C80" s="12"/>
-      <c r="D80" s="13"/>
+      <c r="C80" s="12">
+        <v>45741</v>
+      </c>
+      <c r="D80" s="13" t="s">
+        <v>11</v>
+      </c>
       <c r="E80" s="12"/>
-      <c r="F80" s="13"/>
-      <c r="G80" s="13"/>
-      <c r="H80" s="13"/>
-      <c r="I80" s="14"/>
-      <c r="J80" s="15"/>
+      <c r="F80" s="13">
+        <f>$B$78</f>
+        <v>75</v>
+      </c>
+      <c r="G80" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H80" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I80" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="J80" s="15" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="81" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B81" s="11">
@@ -6810,7 +6831,7 @@
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$10</xm:f>
           </x14:formula1>
-          <xm:sqref>H85 H62:H83 H98:H122</xm:sqref>
+          <xm:sqref>H85 H98:H122 H62:H83</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C61EF0EC-B820-4CEA-8AA2-04B5D172AE2C}">
           <x14:formula1>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{431C5F5F-BA92-4419-BFCE-52D3182B6BCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A20B82F-232D-4CF5-98EC-6830765FB438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -5491,9 +5491,11 @@
         <v>45740</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E76" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E76" s="12">
+        <v>45741</v>
+      </c>
       <c r="F76" s="13" t="s">
         <v>184</v>
       </c>
@@ -5550,9 +5552,11 @@
         <v>45740</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E78" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E78" s="12">
+        <v>45742</v>
+      </c>
       <c r="F78" s="13">
         <f>$B$74</f>
         <v>71</v>
@@ -5610,9 +5614,11 @@
         <v>45741</v>
       </c>
       <c r="D80" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E80" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E80" s="12">
+        <v>45742</v>
+      </c>
       <c r="F80" s="13">
         <f>$B$78</f>
         <v>75</v>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A20B82F-232D-4CF5-98EC-6830765FB438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA93539-40D9-4430-A629-F4B403CD850C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="190">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -2594,6 +2594,32 @@
   </si>
   <si>
     <t xml:space="preserve">テーブル項目情報テーブル構築 : sys_column </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テーブル項目情報</t>
+    <rPh sb="4" eb="6">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>受注情報 Lv.01の項目登録</t>
+    <rPh sb="0" eb="2">
+      <t>ジュチュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>トウロク</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -6706,28 +6732,52 @@
         <f t="shared" si="31"/>
         <v>116</v>
       </c>
-      <c r="C119" s="12"/>
-      <c r="D119" s="13"/>
+      <c r="C119" s="12">
+        <v>45742</v>
+      </c>
+      <c r="D119" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E119" s="12"/>
       <c r="F119" s="13"/>
-      <c r="G119" s="13"/>
-      <c r="H119" s="13"/>
-      <c r="I119" s="24"/>
-      <c r="J119" s="15"/>
+      <c r="G119" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H119" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I119" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="J119" s="15" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="120" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B120" s="11">
         <f t="shared" si="31"/>
         <v>117</v>
       </c>
-      <c r="C120" s="12"/>
-      <c r="D120" s="13"/>
+      <c r="C120" s="12">
+        <v>45742</v>
+      </c>
+      <c r="D120" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E120" s="12"/>
       <c r="F120" s="13"/>
-      <c r="G120" s="13"/>
-      <c r="H120" s="13"/>
-      <c r="I120" s="24"/>
-      <c r="J120" s="15"/>
+      <c r="G120" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H120" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I120" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="J120" s="15" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="121" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B121" s="11">
@@ -6837,7 +6887,7 @@
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$10</xm:f>
           </x14:formula1>
-          <xm:sqref>H85 H98:H122 H62:H83</xm:sqref>
+          <xm:sqref>H85 H62:H83 H98:H122</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C61EF0EC-B820-4CEA-8AA2-04B5D172AE2C}">
           <x14:formula1>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA93539-40D9-4430-A629-F4B403CD850C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D45F475-5FB6-4111-AE8C-CAEA7C78C456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作業項目!$B$2:$J$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作業項目!$B$2:$J$129</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="194">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -2619,6 +2619,46 @@
     </rPh>
     <rPh sb="13" eb="15">
       <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>受注照会</t>
+    <rPh sb="0" eb="2">
+      <t>ジュチュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショウカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テーブル情報の読込</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヨミコミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テーブル情報</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>loadメソッドにテーブル詳細リスト構築を追加</t>
+    <rPh sb="13" eb="15">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>コウチク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ツイカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3359,7 +3399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="A1:K125"/>
+  <dimension ref="A1:K129"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -3557,7 +3597,7 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
-        <f t="shared" ref="A8:B125" si="0">B7+1</f>
+        <f t="shared" ref="A8:B129" si="0">B7+1</f>
         <v>6</v>
       </c>
       <c r="C8" s="12">
@@ -6356,7 +6396,7 @@
     </row>
     <row r="106" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B106" s="11">
-        <f t="shared" ref="B106:B124" si="31">B105+1</f>
+        <f t="shared" ref="B106:B128" si="31">B105+1</f>
         <v>103</v>
       </c>
       <c r="C106" s="12"/>
@@ -6736,9 +6776,11 @@
         <v>45742</v>
       </c>
       <c r="D119" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E119" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E119" s="12">
+        <v>45745</v>
+      </c>
       <c r="F119" s="13"/>
       <c r="G119" s="13" t="s">
         <v>14</v>
@@ -6784,14 +6826,29 @@
         <f t="shared" si="31"/>
         <v>118</v>
       </c>
-      <c r="C121" s="12"/>
-      <c r="D121" s="13"/>
+      <c r="C121" s="12">
+        <v>45745</v>
+      </c>
+      <c r="D121" s="13" t="s">
+        <v>11</v>
+      </c>
       <c r="E121" s="12"/>
-      <c r="F121" s="13"/>
-      <c r="G121" s="13"/>
-      <c r="H121" s="13"/>
-      <c r="I121" s="14"/>
-      <c r="J121" s="15"/>
+      <c r="F121" s="13">
+        <f>$B$114</f>
+        <v>111</v>
+      </c>
+      <c r="G121" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H121" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I121" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="J121" s="15" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B122" s="11">
@@ -6799,24 +6856,27 @@
         <v>119</v>
       </c>
       <c r="C122" s="12">
-        <v>45734</v>
+        <v>45745</v>
       </c>
       <c r="D122" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E122" s="12"/>
-      <c r="F122" s="13"/>
+      <c r="F122" s="13">
+        <f>$B$121</f>
+        <v>118</v>
+      </c>
       <c r="G122" s="13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H122" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="I122" s="14" t="s">
-        <v>160</v>
+      <c r="I122" s="24" t="s">
+        <v>192</v>
       </c>
       <c r="J122" s="15" t="s">
-        <v>161</v>
+        <v>193</v>
       </c>
     </row>
     <row r="123" spans="2:10" x14ac:dyDescent="0.3">
@@ -6830,7 +6890,7 @@
       <c r="F123" s="13"/>
       <c r="G123" s="13"/>
       <c r="H123" s="13"/>
-      <c r="I123" s="14"/>
+      <c r="I123" s="24"/>
       <c r="J123" s="15"/>
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.3">
@@ -6844,27 +6904,95 @@
       <c r="F124" s="13"/>
       <c r="G124" s="13"/>
       <c r="H124" s="13"/>
-      <c r="I124" s="14"/>
+      <c r="I124" s="24"/>
       <c r="J124" s="15"/>
     </row>
-    <row r="125" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B125" s="18">
+    <row r="125" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B125" s="11">
+        <f t="shared" si="31"/>
+        <v>122</v>
+      </c>
+      <c r="C125" s="12"/>
+      <c r="D125" s="13"/>
+      <c r="E125" s="12"/>
+      <c r="F125" s="13"/>
+      <c r="G125" s="13"/>
+      <c r="H125" s="13"/>
+      <c r="I125" s="14"/>
+      <c r="J125" s="15"/>
+    </row>
+    <row r="126" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B126" s="11">
+        <f t="shared" si="31"/>
+        <v>123</v>
+      </c>
+      <c r="C126" s="12">
+        <v>45734</v>
+      </c>
+      <c r="D126" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E126" s="12"/>
+      <c r="F126" s="13"/>
+      <c r="G126" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H126" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I126" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="J126" s="15" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="127" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B127" s="11">
+        <f t="shared" si="31"/>
+        <v>124</v>
+      </c>
+      <c r="C127" s="12"/>
+      <c r="D127" s="13"/>
+      <c r="E127" s="12"/>
+      <c r="F127" s="13"/>
+      <c r="G127" s="13"/>
+      <c r="H127" s="13"/>
+      <c r="I127" s="14"/>
+      <c r="J127" s="15"/>
+    </row>
+    <row r="128" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B128" s="11">
+        <f t="shared" si="31"/>
+        <v>125</v>
+      </c>
+      <c r="C128" s="12"/>
+      <c r="D128" s="13"/>
+      <c r="E128" s="12"/>
+      <c r="F128" s="13"/>
+      <c r="G128" s="13"/>
+      <c r="H128" s="13"/>
+      <c r="I128" s="14"/>
+      <c r="J128" s="15"/>
+    </row>
+    <row r="129" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B129" s="18">
         <f t="shared" si="0"/>
-        <v>122</v>
-      </c>
-      <c r="C125" s="19"/>
-      <c r="D125" s="20"/>
-      <c r="E125" s="19"/>
-      <c r="F125" s="20"/>
-      <c r="G125" s="20"/>
-      <c r="H125" s="20"/>
-      <c r="I125" s="21"/>
-      <c r="J125" s="22"/>
+        <v>126</v>
+      </c>
+      <c r="C129" s="19"/>
+      <c r="D129" s="20"/>
+      <c r="E129" s="19"/>
+      <c r="F129" s="20"/>
+      <c r="G129" s="20"/>
+      <c r="H129" s="20"/>
+      <c r="I129" s="21"/>
+      <c r="J129" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:J125" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
+  <autoFilter ref="B2:J129" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B3:J45 A43:A45 A46:J46 A47:A51 B47:J125">
+  <conditionalFormatting sqref="B3:J45 A43:A45 A46:J46 A47:A51 B47:J129">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>
@@ -6881,25 +7009,25 @@
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H123:H125 H86:H97 H3:H61 H84</xm:sqref>
+          <xm:sqref>H127:H129 H86:H97 H3:H61 H84</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D6F2F62E-6D63-4E2D-8772-1211A4C3A979}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$10</xm:f>
           </x14:formula1>
-          <xm:sqref>H85 H62:H83 H98:H122</xm:sqref>
+          <xm:sqref>H85 H62:H83 H98:H126</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C61EF0EC-B820-4CEA-8AA2-04B5D172AE2C}">
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D125</xm:sqref>
+          <xm:sqref>D3:D129</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G125</xm:sqref>
+          <xm:sqref>G3:G129</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D45F475-5FB6-4111-AE8C-CAEA7C78C456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9669ADBF-C0BB-43B1-8FE4-2B9D1BD1D3CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作業項目!$B$2:$J$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作業項目!$B$2:$J$136</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="198">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -2659,6 +2659,49 @@
     </rPh>
     <rPh sb="21" eb="23">
       <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示詳細情報</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テーブル項目情報の追加</t>
+    <rPh sb="4" eb="6">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デーブル生成修正</t>
+    <rPh sb="4" eb="6">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>load()メソッド修正</t>
+    <rPh sb="10" eb="12">
+      <t>シュウセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3399,7 +3442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="A1:K129"/>
+  <dimension ref="A1:K136"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -3597,7 +3640,7 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
-        <f t="shared" ref="A8:B129" si="0">B7+1</f>
+        <f t="shared" ref="A8:B136" si="0">B7+1</f>
         <v>6</v>
       </c>
       <c r="C8" s="12">
@@ -6396,7 +6439,7 @@
     </row>
     <row r="106" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B106" s="11">
-        <f t="shared" ref="B106:B128" si="31">B105+1</f>
+        <f t="shared" ref="B106:B135" si="31">B105+1</f>
         <v>103</v>
       </c>
       <c r="C106" s="12"/>
@@ -6830,9 +6873,11 @@
         <v>45745</v>
       </c>
       <c r="D121" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E121" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E121" s="12">
+        <v>45746</v>
+      </c>
       <c r="F121" s="13">
         <f>$B$114</f>
         <v>111</v>
@@ -6859,9 +6904,11 @@
         <v>45745</v>
       </c>
       <c r="D122" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E122" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E122" s="12">
+        <v>45746</v>
+      </c>
       <c r="F122" s="13">
         <f>$B$121</f>
         <v>118</v>
@@ -6884,68 +6931,101 @@
         <f t="shared" si="31"/>
         <v>120</v>
       </c>
-      <c r="C123" s="12"/>
-      <c r="D123" s="13"/>
+      <c r="C123" s="12">
+        <v>45746</v>
+      </c>
+      <c r="D123" s="13" t="s">
+        <v>11</v>
+      </c>
       <c r="E123" s="12"/>
-      <c r="F123" s="13"/>
-      <c r="G123" s="13"/>
-      <c r="H123" s="13"/>
-      <c r="I123" s="24"/>
-      <c r="J123" s="15"/>
+      <c r="F123" s="13">
+        <f>$B$114</f>
+        <v>111</v>
+      </c>
+      <c r="G123" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H123" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I123" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="J123" s="15" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B124" s="11">
         <f t="shared" si="31"/>
         <v>121</v>
       </c>
-      <c r="C124" s="12"/>
-      <c r="D124" s="13"/>
+      <c r="C124" s="12">
+        <v>45746</v>
+      </c>
+      <c r="D124" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E124" s="12"/>
-      <c r="F124" s="13"/>
-      <c r="G124" s="13"/>
-      <c r="H124" s="13"/>
-      <c r="I124" s="24"/>
-      <c r="J124" s="15"/>
+      <c r="F124" s="13">
+        <f>$B$123</f>
+        <v>120</v>
+      </c>
+      <c r="G124" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H124" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I124" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="J124" s="15" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B125" s="11">
         <f t="shared" si="31"/>
         <v>122</v>
       </c>
-      <c r="C125" s="12"/>
-      <c r="D125" s="13"/>
+      <c r="C125" s="12">
+        <v>45746</v>
+      </c>
+      <c r="D125" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E125" s="12"/>
-      <c r="F125" s="13"/>
-      <c r="G125" s="13"/>
-      <c r="H125" s="13"/>
-      <c r="I125" s="14"/>
-      <c r="J125" s="15"/>
+      <c r="F125" s="13">
+        <f>$B$123</f>
+        <v>120</v>
+      </c>
+      <c r="G125" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H125" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I125" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="J125" s="15" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="126" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B126" s="11">
         <f t="shared" si="31"/>
         <v>123</v>
       </c>
-      <c r="C126" s="12">
-        <v>45734</v>
-      </c>
-      <c r="D126" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C126" s="12"/>
+      <c r="D126" s="13"/>
       <c r="E126" s="12"/>
       <c r="F126" s="13"/>
-      <c r="G126" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="H126" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I126" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="J126" s="15" t="s">
-        <v>161</v>
-      </c>
+      <c r="G126" s="13"/>
+      <c r="H126" s="13"/>
+      <c r="I126" s="24"/>
+      <c r="J126" s="15"/>
     </row>
     <row r="127" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B127" s="11">
@@ -6958,7 +7038,7 @@
       <c r="F127" s="13"/>
       <c r="G127" s="13"/>
       <c r="H127" s="13"/>
-      <c r="I127" s="14"/>
+      <c r="I127" s="24"/>
       <c r="J127" s="15"/>
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.3">
@@ -6972,27 +7052,137 @@
       <c r="F128" s="13"/>
       <c r="G128" s="13"/>
       <c r="H128" s="13"/>
-      <c r="I128" s="14"/>
+      <c r="I128" s="24"/>
       <c r="J128" s="15"/>
     </row>
-    <row r="129" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B129" s="18">
+    <row r="129" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B129" s="11">
+        <f t="shared" si="31"/>
+        <v>126</v>
+      </c>
+      <c r="C129" s="12"/>
+      <c r="D129" s="13"/>
+      <c r="E129" s="12"/>
+      <c r="F129" s="13"/>
+      <c r="G129" s="13"/>
+      <c r="H129" s="13"/>
+      <c r="I129" s="24"/>
+      <c r="J129" s="15"/>
+    </row>
+    <row r="130" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B130" s="11">
+        <f t="shared" si="31"/>
+        <v>127</v>
+      </c>
+      <c r="C130" s="12"/>
+      <c r="D130" s="13"/>
+      <c r="E130" s="12"/>
+      <c r="F130" s="13"/>
+      <c r="G130" s="13"/>
+      <c r="H130" s="13"/>
+      <c r="I130" s="24"/>
+      <c r="J130" s="15"/>
+    </row>
+    <row r="131" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B131" s="11">
+        <f t="shared" si="31"/>
+        <v>128</v>
+      </c>
+      <c r="C131" s="12"/>
+      <c r="D131" s="13"/>
+      <c r="E131" s="12"/>
+      <c r="F131" s="13"/>
+      <c r="G131" s="13"/>
+      <c r="H131" s="13"/>
+      <c r="I131" s="24"/>
+      <c r="J131" s="15"/>
+    </row>
+    <row r="132" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B132" s="11">
+        <f t="shared" si="31"/>
+        <v>129</v>
+      </c>
+      <c r="C132" s="12"/>
+      <c r="D132" s="13"/>
+      <c r="E132" s="12"/>
+      <c r="F132" s="13"/>
+      <c r="G132" s="13"/>
+      <c r="H132" s="13"/>
+      <c r="I132" s="14"/>
+      <c r="J132" s="15"/>
+    </row>
+    <row r="133" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B133" s="11">
+        <f t="shared" si="31"/>
+        <v>130</v>
+      </c>
+      <c r="C133" s="12">
+        <v>45734</v>
+      </c>
+      <c r="D133" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E133" s="12"/>
+      <c r="F133" s="13"/>
+      <c r="G133" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H133" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I133" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="J133" s="15" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="134" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B134" s="11">
+        <f t="shared" si="31"/>
+        <v>131</v>
+      </c>
+      <c r="C134" s="12"/>
+      <c r="D134" s="13"/>
+      <c r="E134" s="12"/>
+      <c r="F134" s="13"/>
+      <c r="G134" s="13"/>
+      <c r="H134" s="13"/>
+      <c r="I134" s="14"/>
+      <c r="J134" s="15"/>
+    </row>
+    <row r="135" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B135" s="11">
+        <f t="shared" si="31"/>
+        <v>132</v>
+      </c>
+      <c r="C135" s="12"/>
+      <c r="D135" s="13"/>
+      <c r="E135" s="12"/>
+      <c r="F135" s="13"/>
+      <c r="G135" s="13"/>
+      <c r="H135" s="13"/>
+      <c r="I135" s="14"/>
+      <c r="J135" s="15"/>
+    </row>
+    <row r="136" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B136" s="18">
         <f t="shared" si="0"/>
-        <v>126</v>
-      </c>
-      <c r="C129" s="19"/>
-      <c r="D129" s="20"/>
-      <c r="E129" s="19"/>
-      <c r="F129" s="20"/>
-      <c r="G129" s="20"/>
-      <c r="H129" s="20"/>
-      <c r="I129" s="21"/>
-      <c r="J129" s="22"/>
+        <v>133</v>
+      </c>
+      <c r="C136" s="19"/>
+      <c r="D136" s="20"/>
+      <c r="E136" s="19"/>
+      <c r="F136" s="20"/>
+      <c r="G136" s="20"/>
+      <c r="H136" s="20"/>
+      <c r="I136" s="21"/>
+      <c r="J136" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:J129" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
+  <autoFilter ref="B2:J136" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B3:J45 A43:A45 A46:J46 A47:A51 B47:J129">
+  <conditionalFormatting sqref="B3:J45 A43:A45 A46:J46 A47:A51 B47:J136">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>
@@ -7009,25 +7199,25 @@
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H127:H129 H86:H97 H3:H61 H84</xm:sqref>
+          <xm:sqref>H134:H136 H86:H97 H3:H61 H84</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D6F2F62E-6D63-4E2D-8772-1211A4C3A979}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$10</xm:f>
           </x14:formula1>
-          <xm:sqref>H85 H62:H83 H98:H126</xm:sqref>
+          <xm:sqref>H85 H62:H83 H98:H133</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C61EF0EC-B820-4CEA-8AA2-04B5D172AE2C}">
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D129</xm:sqref>
+          <xm:sqref>D3:D136</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G129</xm:sqref>
+          <xm:sqref>G3:G136</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9669ADBF-C0BB-43B1-8FE4-2B9D1BD1D3CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F11F0162-9F5A-4B35-A10E-AB0534185820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作業項目!$B$2:$J$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作業項目!$B$2:$J$135</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="200">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -2702,6 +2702,38 @@
     <t>load()メソッド修正</t>
     <rPh sb="10" eb="12">
       <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>受注情報</t>
+    <rPh sb="0" eb="2">
+      <t>ジュチュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テーブル綱目識別CDから受注情報の値を取得する。</t>
+    <rPh sb="4" eb="6">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シキベツ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジュチュウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>シュトク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3442,7 +3474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}">
-  <dimension ref="A1:K136"/>
+  <dimension ref="A1:K135"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.26953125" customWidth="1"/>
@@ -3640,7 +3672,7 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
-        <f t="shared" ref="A8:B136" si="0">B7+1</f>
+        <f t="shared" ref="A8:B135" si="0">B7+1</f>
         <v>6</v>
       </c>
       <c r="C8" s="12">
@@ -6439,7 +6471,7 @@
     </row>
     <row r="106" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B106" s="11">
-        <f t="shared" ref="B106:B135" si="31">B105+1</f>
+        <f t="shared" ref="B106:B134" si="31">B105+1</f>
         <v>103</v>
       </c>
       <c r="C106" s="12"/>
@@ -6844,24 +6876,29 @@
         <v>117</v>
       </c>
       <c r="C120" s="12">
-        <v>45742</v>
+        <v>45745</v>
       </c>
       <c r="D120" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E120" s="12"/>
-      <c r="F120" s="13"/>
+        <v>12</v>
+      </c>
+      <c r="E120" s="12">
+        <v>45746</v>
+      </c>
+      <c r="F120" s="13">
+        <f>$B$114</f>
+        <v>111</v>
+      </c>
       <c r="G120" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H120" s="13" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I120" s="24" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="J120" s="15" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
     </row>
     <row r="121" spans="2:10" x14ac:dyDescent="0.3">
@@ -6879,20 +6916,20 @@
         <v>45746</v>
       </c>
       <c r="F121" s="13">
-        <f>$B$114</f>
-        <v>111</v>
+        <f>$B$120</f>
+        <v>117</v>
       </c>
       <c r="G121" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H121" s="13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I121" s="24" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="J121" s="15" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.3">
@@ -6901,7 +6938,7 @@
         <v>119</v>
       </c>
       <c r="C122" s="12">
-        <v>45745</v>
+        <v>45746</v>
       </c>
       <c r="D122" s="13" t="s">
         <v>12</v>
@@ -6910,8 +6947,8 @@
         <v>45746</v>
       </c>
       <c r="F122" s="13">
-        <f>$B$121</f>
-        <v>118</v>
+        <f>$B$114</f>
+        <v>111</v>
       </c>
       <c r="G122" s="13" t="s">
         <v>14</v>
@@ -6920,10 +6957,10 @@
         <v>19</v>
       </c>
       <c r="I122" s="24" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="J122" s="15" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="123" spans="2:10" x14ac:dyDescent="0.3">
@@ -6935,12 +6972,14 @@
         <v>45746</v>
       </c>
       <c r="D123" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E123" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E123" s="12">
+        <v>45746</v>
+      </c>
       <c r="F123" s="13">
-        <f>$B$114</f>
-        <v>111</v>
+        <f>$B$122</f>
+        <v>119</v>
       </c>
       <c r="G123" s="13" t="s">
         <v>14</v>
@@ -6952,7 +6991,7 @@
         <v>194</v>
       </c>
       <c r="J123" s="15" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.3">
@@ -6964,12 +7003,14 @@
         <v>45746</v>
       </c>
       <c r="D124" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E124" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E124" s="12">
+        <v>45746</v>
+      </c>
       <c r="F124" s="13">
-        <f>$B$123</f>
-        <v>120</v>
+        <f>$B$122</f>
+        <v>119</v>
       </c>
       <c r="G124" s="13" t="s">
         <v>14</v>
@@ -6981,7 +7022,7 @@
         <v>194</v>
       </c>
       <c r="J124" s="15" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.3">
@@ -6993,24 +7034,21 @@
         <v>45746</v>
       </c>
       <c r="D125" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E125" s="12"/>
-      <c r="F125" s="13">
-        <f>$B$123</f>
-        <v>120</v>
-      </c>
+      <c r="F125" s="13"/>
       <c r="G125" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H125" s="13" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I125" s="24" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="J125" s="15" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="126" spans="2:10" x14ac:dyDescent="0.3">
@@ -7094,7 +7132,7 @@
       <c r="F131" s="13"/>
       <c r="G131" s="13"/>
       <c r="H131" s="13"/>
-      <c r="I131" s="24"/>
+      <c r="I131" s="14"/>
       <c r="J131" s="15"/>
     </row>
     <row r="132" spans="2:10" x14ac:dyDescent="0.3">
@@ -7102,40 +7140,40 @@
         <f t="shared" si="31"/>
         <v>129</v>
       </c>
-      <c r="C132" s="12"/>
-      <c r="D132" s="13"/>
+      <c r="C132" s="12">
+        <v>45734</v>
+      </c>
+      <c r="D132" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="E132" s="12"/>
       <c r="F132" s="13"/>
-      <c r="G132" s="13"/>
-      <c r="H132" s="13"/>
-      <c r="I132" s="14"/>
-      <c r="J132" s="15"/>
+      <c r="G132" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H132" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I132" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="J132" s="15" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="133" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B133" s="11">
         <f t="shared" si="31"/>
         <v>130</v>
       </c>
-      <c r="C133" s="12">
-        <v>45734</v>
-      </c>
-      <c r="D133" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C133" s="12"/>
+      <c r="D133" s="13"/>
       <c r="E133" s="12"/>
       <c r="F133" s="13"/>
-      <c r="G133" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="H133" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I133" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="J133" s="15" t="s">
-        <v>161</v>
-      </c>
+      <c r="G133" s="13"/>
+      <c r="H133" s="13"/>
+      <c r="I133" s="14"/>
+      <c r="J133" s="15"/>
     </row>
     <row r="134" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B134" s="11">
@@ -7151,38 +7189,24 @@
       <c r="I134" s="14"/>
       <c r="J134" s="15"/>
     </row>
-    <row r="135" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B135" s="11">
-        <f t="shared" si="31"/>
+    <row r="135" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B135" s="18">
+        <f t="shared" si="0"/>
         <v>132</v>
       </c>
-      <c r="C135" s="12"/>
-      <c r="D135" s="13"/>
-      <c r="E135" s="12"/>
-      <c r="F135" s="13"/>
-      <c r="G135" s="13"/>
-      <c r="H135" s="13"/>
-      <c r="I135" s="14"/>
-      <c r="J135" s="15"/>
-    </row>
-    <row r="136" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B136" s="18">
-        <f t="shared" si="0"/>
-        <v>133</v>
-      </c>
-      <c r="C136" s="19"/>
-      <c r="D136" s="20"/>
-      <c r="E136" s="19"/>
-      <c r="F136" s="20"/>
-      <c r="G136" s="20"/>
-      <c r="H136" s="20"/>
-      <c r="I136" s="21"/>
-      <c r="J136" s="22"/>
+      <c r="C135" s="19"/>
+      <c r="D135" s="20"/>
+      <c r="E135" s="19"/>
+      <c r="F135" s="20"/>
+      <c r="G135" s="20"/>
+      <c r="H135" s="20"/>
+      <c r="I135" s="21"/>
+      <c r="J135" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:J136" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
+  <autoFilter ref="B2:J135" xr:uid="{A16BBA88-B354-4900-8DEA-2F82BFB4D2A4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="B3:J45 A43:A45 A46:J46 A47:A51 B47:J136">
+  <conditionalFormatting sqref="B3:J45 A43:A45 A46:J46 A47:A51 B47:J135">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>$D3="完了"</formula>
     </cfRule>
@@ -7199,25 +7223,25 @@
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H134:H136 H86:H97 H3:H61 H84</xm:sqref>
+          <xm:sqref>H133:H135 H86:H97 H3:H61 H84</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D6F2F62E-6D63-4E2D-8772-1211A4C3A979}">
           <x14:formula1>
             <xm:f>選択情報!$D$3:$D$10</xm:f>
           </x14:formula1>
-          <xm:sqref>H85 H62:H83 H98:H133</xm:sqref>
+          <xm:sqref>H85 H62:H83 H98:H132</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C61EF0EC-B820-4CEA-8AA2-04B5D172AE2C}">
           <x14:formula1>
             <xm:f>選択情報!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D136</xm:sqref>
+          <xm:sqref>D3:D135</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EFCB9F77-76AA-4799-97C8-039262C0582D}">
           <x14:formula1>
             <xm:f>選択情報!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G136</xm:sqref>
+          <xm:sqref>G3:G135</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/document/開発タスク_20241203.xlsx
+++ b/document/開発タスク_20241203.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F11F0162-9F5A-4B35-A10E-AB0534185820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F82EF950-63ED-4FA8-9391-2CA6C1B337D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A645B72-63A1-4741-971E-2F21BDC7C220}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="199">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -2706,34 +2706,12 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>受注情報</t>
-    <rPh sb="0" eb="2">
-      <t>ジュチュウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウホウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>テーブル綱目識別CDから受注情報の値を取得する。</t>
-    <rPh sb="4" eb="6">
-      <t>コウモク</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>シキベツ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ジュチュウ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>アタイ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>シュトク</t>
+    <t>「編集」ボタン追加</t>
+    <rPh sb="1" eb="3">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ツイカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6580,9 +6558,11 @@
         <v>45719</v>
       </c>
       <c r="D110" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E110" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E110" s="12">
+        <v>45758</v>
+      </c>
       <c r="F110" s="13">
         <f>$B$107</f>
         <v>104</v>
@@ -6640,9 +6620,11 @@
         <v>45735</v>
       </c>
       <c r="D112" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E112" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E112" s="12">
+        <v>45758</v>
+      </c>
       <c r="F112" s="13">
         <f>$B$114</f>
         <v>111</v>
@@ -6700,9 +6682,11 @@
         <v>45735</v>
       </c>
       <c r="D114" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E114" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="E114" s="12">
+        <v>45758</v>
+      </c>
       <c r="F114" s="13">
         <f>$B$110</f>
         <v>107</v>
@@ -6808,7 +6792,7 @@
         <v>167</v>
       </c>
       <c r="J117" s="15" t="s">
-        <v>168</v>
+        <v>198</v>
       </c>
     </row>
     <row r="118" spans="2:10" x14ac:dyDescent="0.3">
@@ -6817,17 +6801,15 @@
         <v>115</v>
       </c>
       <c r="C118" s="12">
-        <v>45741</v>
+        <v>45737</v>
       </c>
       <c r="D118" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E118" s="12">
-        <v>45741</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E118" s="12"/>
       <c r="F118" s="13">
-        <f>$B$107</f>
-        <v>104</v>
+        <f>$B$114</f>
+        <v>111</v>
       </c>
       <c r="G118" s="13" t="s">
         <v>14</v>
@@ -6836,10 +6818,10 @@
         <v>21</v>
       </c>
       <c r="I118" s="24" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="J118" s="15" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.3">
@@ -6848,15 +6830,18 @@
         <v>116</v>
       </c>
       <c r="C119" s="12">
-        <v>45742</v>
+        <v>45741</v>
       </c>
       <c r="D119" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E119" s="12">
-        <v>45745</v>
-      </c>
-      <c r="F119" s="13"/>
+        <v>45741</v>
+      </c>
+      <c r="F119" s="13">
+        <f>$B$107</f>
+        <v>104</v>
+      </c>
       <c r="G119" s="13" t="s">
         <v>14</v>
       </c>
@@ -6864,10 +6849,10 @@
         <v>21</v>
       </c>
       <c r="I119" s="24" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="J119" s="15" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="120" spans="2:10" x14ac:dyDescent="0.3">
@@ -6876,18 +6861,15 @@
         <v>117</v>
       </c>
       <c r="C120" s="12">
+        <v>45742</v>
+      </c>
+      <c r="D120" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E120" s="12">
         <v>45745</v>
       </c>
-      <c r="D120" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E120" s="12">
-        <v>45746</v>
-      </c>
-      <c r="F120" s="13">
-        <f>$B$114</f>
-        <v>111</v>
-      </c>
+      <c r="F120" s="13"/>
       <c r="G120" s="13" t="s">
         <v>14</v>
       </c>
@@ -6895,10 +6877,10 @@
         <v>21</v>
       </c>
       <c r="I120" s="24" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="J120" s="15" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="121" spans="2:10" x14ac:dyDescent="0.3">
@@ -6916,20 +6898,20 @@
         <v>45746</v>
       </c>
       <c r="F121" s="13">
-        <f>$B$120</f>
-        <v>117</v>
+        <f>$B$114</f>
+        <v>111</v>
       </c>
       <c r="G121" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H121" s="13" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I121" s="24" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J121" s="15" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.3">
@@ -6938,7 +6920,7 @@
         <v>119</v>
       </c>
       <c r="C122" s="12">
-        <v>45746</v>
+        <v>45745</v>
       </c>
       <c r="D122" s="13" t="s">
         <v>12</v>
@@ -6947,8 +6929,8 @@
         <v>45746</v>
       </c>
       <c r="F122" s="13">
-        <f>$B$114</f>
-        <v>111</v>
+        <f>$B$121</f>
+        <v>118</v>
       </c>
       <c r="G122" s="13" t="s">
         <v>14</v>
@@ -6957,10 +6939,10 @@
         <v>19</v>
       </c>
       <c r="I122" s="24" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J122" s="15" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="123" spans="2:10" x14ac:dyDescent="0.3">
@@ -6978,8 +6960,8 @@
         <v>45746</v>
       </c>
       <c r="F123" s="13">
-        <f>$B$122</f>
-        <v>119</v>
+        <f>$B$114</f>
+        <v>111</v>
       </c>
       <c r="G123" s="13" t="s">
         <v>14</v>
@@ -6991,7 +6973,7 @@
         <v>194</v>
       </c>
       <c r="J123" s="15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.3">
@@ -7009,8 +6991,8 @@
         <v>45746</v>
       </c>
       <c r="F124" s="13">
-        <f>$B$122</f>
-        <v>119</v>
+        <f>$B$123</f>
+        <v>120</v>
       </c>
       <c r="G124" s="13" t="s">
         <v>14</v>
@@ -7022,7 +7004,7 @@
         <v>194</v>
       </c>
       <c r="J124" s="15" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.3">
@@ -7034,21 +7016,26 @@
         <v>45746</v>
       </c>
       <c r="D125" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E125" s="12"/>
-      <c r="F125" s="13"/>
+        <v>12</v>
+      </c>
+      <c r="E125" s="12">
+        <v>45746</v>
+      </c>
+      <c r="F125" s="13">
+        <f>$B$123</f>
+        <v>120</v>
+      </c>
       <c r="G125" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H125" s="13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I125" s="24" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="J125" s="15" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="126" spans="2:10" x14ac:dyDescent="0.3">
